--- a/output/tailored_resumes.xlsx
+++ b/output/tailored_resumes.xlsx
@@ -34,7 +34,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +51,16 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -64,11 +74,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P65"/>
+  <dimension ref="A1:P129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -541,41 +553,49 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>0</v>
+      <c r="B2" s="4" t="n">
+        <v>88</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$135k–$180k</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fortinet</t>
+          <t>Truveta</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Applied AI Engineer - AI Agent</t>
+          <t>Software Engineer - Live Link</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Near-perfect profile match â€” an explicitly new-grad backend role building APIs, distributed services, databases, data pipelines, and cloud infra with privacy/security emphasis, which maps directly onto Nate's Raft/LSM KV store, Java Spring microservices, OIDC/entitlements work, and AWS/Azure/K8s experience; the only friction is Seattle-hybrid vs. his Boston/NYC preference and a May 2027 grad date that may be later than the posting wants.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Truveta is a heavily funded (~$300M+ raised) Seattle health-data startup founded and staffed largely by ex-Microsoft leadership, and it benchmarks against Seattle big-tech pay to compete for the same candidates. Expect new-grad SWE base around $130-150k plus annual bonus and a meaningful private-equity grant (illiquid, so discount it). This is an estimate from company tier and Seattle market, not from a published pay band â€” treat the top of the range as uncertain because private-company equity valuation varies widely. Comfortably above the candidate's ~$130k anchor.</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -583,7 +603,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>Truveta_Software_Engineer_Live_Link.pdf</t>
+        </is>
+      </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -599,41 +623,49 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>0</v>
+      <c r="B3" s="4" t="n">
+        <v>78</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$130k–$175k</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>Alkira</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Software Engineer New Grad</t>
+          <t>Software Engineer - Datapath</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Burlington, MA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Strong infra/systems overlap â€” Python + C/C++/Rust, Linux, AWS/Azure, Kubernetes/Terraform/CI-CD automation, a Computer Networks course, and a production on-call/incident-triage project map cleanly onto this orchestration role; the gaps are hands-on networking depth (TCP/IP, VNFs, firewalls), Ansible, and Go (learning only), plus San Jose hybrid vs. a Boston-based May 2027 grad.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Alkira is a well-funded late-stage networking startup (Viptela founders) now part of Lumen, headquartered in San Jose with Bay Area pay bands. Startup-acquired-by-carrier comp typically lands slightly below big-tech: new-grad SWE base ~$125-150K, plus 10% target bonus and equity/RSU. Band is somewhat wide because private/post-acquisition comp data for Alkira new grads is thin â€” treat as an estimate, not fact. Note: this posting is a standard (not explicitly new-grad/2027-start) req, so the offer level and start timing would need clarification.</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>error:Command '['latexmk', '-pdf', '</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -657,41 +689,53 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>0</v>
+      <c r="B4" s="5" t="n">
+        <v>70</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$165k–$215k</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Fortinet</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Product Software Engineer 1</t>
+          <t>Applied AI Engineer - AI Agent</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Glendale, CA</t>
+          <t>Sunnyvale, CA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>graduating by summer 2026; summer 2026</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Content fit is excellent â€” production LLM/RAG pipelines, an agentic AI SRE triage tool that mirrors their SOC/NOC product, backend microservices with message queues and Postgres, plus a systems-security concentration â€” but the posting restricts eligibility to candidates graduating by Summer 2026, and Nate graduates May 2027, so timing (and Sunnyvale-only location) is the main drag.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>The posting itself states a $179.5Kâ€“$220K base for Sunnyvale, which is unusually high for Fortinet new-grad hiring and likely reflects a broad AI-team band rather than the new-grad landing spot; a new grad would realistically land at or just below the floor, plus a modest equity grant (Fortinet RSUs, ~$10â€“25K/yr) and discretionary bonus. Fortinet historically pays below top-tier (Meta/Google/OpenAI) for entry level, so I widened the low end below the posted floor â€” treat this as an estimate with meaningful uncertainty. Well above the ~$130K anchor either way.</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>error:Command '['latexmk', '-pdf', '</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -715,41 +759,49 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
+      <c r="B5" s="4" t="n">
+        <v>80</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$100k–$130k</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Trustpilot</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Software Engineer 1 - Trust Tech</t>
+          <t>Software Engineer New Grad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Edinburgh, UK</t>
+          <t>Burlington, MA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Symbotic's new-grad SWE work is systems/real-time software for warehouse automation in Burlington, MA â€” a strong match for his systems concentration, C/C++/Java/Rust background, and distributed-systems project work, in his preferred Boston area; the only drag is that comp likely lands at or below his 130k anchor and the domain leans robotics/controls rather than cloud backend.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Estimate, not fact. Symbotic (NASDAQ: SYM) is a mid-tier public automation/robotics company in the Boston suburbs â€” pays competitively for the region but below big-tech. Typical new-grad base ~$90â€“110k, plus modest RSU grant and ~5â€“10% bonus, putting TC roughly $100â€“130k. Band is wide because Symbotic new-grad data points are sparse and level/title banding varies.</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>error:Command '['latexmk', '-pdf', '</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -773,33 +825,41 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>0</v>
+      <c r="B6" s="4" t="n">
+        <v>77</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$110k–$150k</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Trustpilot</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Software Engineer 1 - Trust Tech</t>
+          <t>Product Software Engineer 1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Glendale, CA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Strong new-grad backend/platform fit â€” the role wants Java/Python, data pipelines, SQL, AWS/Terraform/Docker/K8s and AI-assisted dev tooling, all of which he has real experience in; the only gaps are no explicit Spark/Kafka/Flink/Databricks/Snowflake (the posting only asks for "interest in learning") and a fully on-site Glendale, CA requirement against his Boston/NYC preference.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Estimate, not fact. Disney Entertainment &amp; ESPN Product Technology (Ad Platforms) pays solid-but-below-FAANG for entry level. California pay-transparency postings for Disney SWE I in Glendale typically list base around $100Kâ€“$135K; add ~10% target bonus and a small/inconsistent RSU grant at this level. Realistic first-year TC lands ~$110Kâ€“$150K, with the midpoint (~$125â€“135K) most likely â€” right at the candidate's $130K anchor, so comp is acceptable but not a standout, and Glendale cost-of-living eats into it.</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>full</t>
@@ -807,7 +867,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>error:Command '['latexmk', '-pdf', '</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -831,41 +891,53 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>0</v>
+      <c r="B7" s="5" t="n">
+        <v>70</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$118k–$142k</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Alkira</t>
+          <t>Cohesity</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Software Engineer - Datapath</t>
+          <t>Software Engineer New Grad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Santa Clara, CA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>start date and have the legal right to wo</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>The technical content is a bullseye â€” distributed systems, cloud, and enterprise-grade C/C++/Java/Python work maps directly onto his from-scratch Raft/LSM-tree/MVCC KV store and microservice experience â€” but the posting explicitly targets May/June 2026 grads (he's May 2027), demands on-site Santa Clara presence, and posts a $113.4â€“126k base that sits at or below his comp anchor.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posting states base $113,400â€“$126,000. Cohesity is a late-stage private (pre-IPO) enterprise infra company, so add roughly a 5â€“10% target bonus plus a pre-IPO option/RSU grant that is illiquid and hard to value â€” realistic on-paper TC lands ~$118kâ€“$142k, with cash-only comp closer to $120â€“135k. Estimate, not fact; the equity portion is the widest uncertainty.</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -873,7 +945,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Cohesity_Software_Engineer_New_Grad.pdf</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -889,33 +965,41 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>0</v>
+      <c r="B8" s="5" t="n">
+        <v>55</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$145k–$185k</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Failure Analysis Engineer</t>
+          <t>Photoshop Developer - GPU/Imaging</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Acton, MA</t>
+          <t>Seattle, WA, SF, San Jose, CA, NYC</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Strong low-level systems, modern C++/Rust, and performance-tuning signal (LSM-tree storage engine, custom-silicon real-time inference, spectrogram/image ML) plus an explicitly early-career-friendly posting, but the core of the job â€” graphics APIs, shaders/WGSL, and GPU rendering pipelines â€” is absent from the profile, making this a stretch outside his backend/distributed-systems lane.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Estimate, not fact. Adobe is upper-tier-but-not-top-of-market for new grads; entry SWE in SF/San Jose/Seattle/NYC typically lands ~$125â€“145K base, ~10% target bonus, and ~$20â€“40K/yr in RSUs plus a sign-on, putting year-one TC roughly $145â€“185K. Comfortably above the $130K anchor.</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>full</t>
@@ -923,7 +1007,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -931,7 +1015,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Adobe_Photoshop_Developer_GPU_Imaging.pdf</t>
+        </is>
+      </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -947,33 +1035,41 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>0</v>
+      <c r="B9" s="5" t="n">
+        <v>52</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$155k–$195k</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Entry Level Java Developer</t>
+          <t>Software Engineer 2 - Wireless Platform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Silver Creek, NY</t>
+          <t>SF, San Jose, CA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Strong systems fundamentals (C/C++, Rust, Linux, concurrency, from-scratch storage/consensus internals) and the explicit AI-assisted-engineering emphasis fit well, but this is an embedded platform/BSP/board-bring-up role â€” squarely in the candidate's low-fit "embedded" bucket with no driver, RTOS, or UART/SPI/I2C experience on the resume â€” and the Bachelors+2yrs / Masters+0 minimum is a real gate for a May 2027 BS grad.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Cisco posts $125.7Kâ€“$176.6K base for this SWE II req (Bay Area). Cisco new-grad/early-career SWE typically lands in the lower-middle of a posted band: ~$130â€“150K base, ~8â€“12% target bonus, and ~$15â€“35K/yr RSU amortized plus a sign-on. That puts realistic year-one TC around $155â€“195K, with the top of the band reserved for candidates who genuinely clear the "Bachelors + 2 yrs" bar. Cisco is a solid-but-not-top-tier payer for new grads; Bay Area location pushes it above the candidate's $130K anchor comfortably. Estimate, not fact.</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>full</t>
@@ -981,7 +1077,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -989,7 +1085,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Cisco_Software_Engineer_2_Wireless_Platform.pdf</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1005,41 +1105,49 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>0</v>
+      <c r="B10" s="5" t="n">
+        <v>58</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$95k–$125k</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cohesity</t>
+          <t>T-Mobile</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Software Engineer New Grad</t>
+          <t>Associate Engineer - Software</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Santa Clara, CA</t>
+          <t>Frisco, TX</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Solid technical overlap â€” scalable/highly-available microservices, containers/K8s, CI/CD, and cloud all map directly to the posting â€” but it's an entry-level "routine assignments under close supervision" role in Frisco, TX with a base band whose realistic new-grad midpoint lands below Nate's ~130K anchor.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posting states base $66,900â€“$120,600 + 10% corporate bonus target, plus annual stock grant and ESPP. New grads in Frisco typically land in the lower-middle of that band (~$85â€“105K base); adding the 10% target bonus and a modest RSU grant puts realistic TC around $95â€“125K. T-Mobile is a non-tech-tier (telecom) employer, so comp sits well below FAANG/Wayfair-style new-grad packages. Estimate, not fact.</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1047,7 +1155,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>T_Mobile_Associate_Engineer_Software.pdf</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1063,41 +1175,49 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
+      <c r="B11" s="5" t="n">
+        <v>58</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$82k–$105k</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Valeo Foods</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Enterprise Applications Developer - Enterprise Applications</t>
+          <t>Associate Software Engineer - Multiple Teams</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Leeds, UK</t>
+          <t>Irving, TX</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Legitimate new-grad backend/software role that maps to his Java microservices and regulated-healthcare software experience (Wolters Kluwer clinical systems is a direct domain match for Abbott medtech), but Abbott's associate SWE work skews embedded/device and regulated-QMS rather than distributed systems or AI infra, and the comp tier sits well below his ~130k anchor.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Abbott is a large-cap medical device/diagnostics company, not a tech-tier payer; new-grad software base in the Irving/DFW market typically lands ~$78â€“95k with a modest (5â€“10%) bonus and small or no equity, plus occasional relocation/signing. Band is an estimate from general medtech/Fortune-500 non-tech comp levels, not from verified Abbott data â€” treat as approximate. This falls materially under the candidate's ~$130k target and below the ~$120k low-match floor, so comp is the main downside here even though the role itself is on-profile.</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1105,7 +1225,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Abbott_Associate_Software_Engineer_Multiple_Teams.pdf</t>
+        </is>
+      </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1122,32 +1246,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$135k–$180k</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Valeo Foods</t>
+          <t>Mach Industries</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Enterprise Applications Developer - Enterprise Applications</t>
+          <t>Software Engineer New Grad - Software - GNC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norwich, UK</t>
+          <t>Huntington Beach, CA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Strong language overlap (Rust/C++/C/Python), real-time inference and autonomous-vehicle project work, and a student engineering team lead role make the technical profile credible, but the posting hard-requires graduation by end of 2026 or January 2027 (candidate is May 2027) and centers on GNC/embedded/RTOS work rather than backend or distributed-systems infrastructure.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Estimate, not fact. Mach Industries is a well-funded 2023-founded defense-tech startup (~350 employees) in the Anduril/Applied Intuition competitive band for SoCal new-grad software. Typical new-grad base for that tier runs ~$125-155k, and the posting explicitly notes "highly competitive equity grants" as part of total comp, pushing paper TC to roughly $135-180k. Startup equity is illiquid, so realized value is uncertain and the band is intentionally wide.</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>full</t>
@@ -1155,7 +1287,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1163,7 +1295,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Mach_Industries_Software_Engineer_New_Grad_Software_GNC.pdf</t>
+        </is>
+      </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1180,32 +1316,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$80k–$115k</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SOSi</t>
+          <t xml:space="preserve">Seagate Technology </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PeopleSoft Software Developer</t>
+          <t>Firmware Engineer</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Charleston, SC</t>
+          <t>Longmont, CO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Real overlap exists on storage systems and C/C++ (his Rust/C++ LSM-tree + WAL + SSTable KV store is genuine storage-engine work, and the AI/ML "plus" is well covered), but the core ask is embedded firmware on HDD hardware â€” an area he has no experience in and flagged as low-fit â€” and the posted base band ($72.6â€“103.8k) sits below his ~120k floor.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posting states base $72,571â€“$103,784 for Longmont, CO; Seagate NCG offers typically land mid-band (~$85â€“98k base) plus discretionary bonus (~5â€“8%), ESPP discount, and 401k match â€” no meaningful equity grant at NCG level. Band widened slightly at the top for a strong-interview offer at band max plus bonus.</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>full</t>
@@ -1213,7 +1357,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1221,7 +1365,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Seagate_Technology_Firmware_Engineer.pdf</t>
+        </is>
+      </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1238,32 +1386,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$105k–$145k</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Vector Atomic</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Associate Software Engineer 1</t>
+          <t>Associate Firmware Engineer - Firmware</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>North Chicago, IL</t>
+          <t>Pleasanton, CA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Firmware/embedded at a quantum-sensing hardware company is adjacent to his systems + C/C++/Rust + computer-architecture background (and his real-time onboard-inference and hardware-device work), but it is not backend/distributed/AI-infra and sits in his explicitly low-fit "hardware/embedded-only" bucket, with an on-site Pleasanton requirement and no bare-metal RTOS/board-bring-up experience on the resume.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Estimate, low confidence â€” Vector Atomic is a small (~100-person) Bay Area quantum-sensing/defense-funded hardware startup, not a public comp band. Bay Area associate/new-grad firmware roles at hardware startups typically run ~$105-135k base with modest early-stage equity and small/no bonus, so ~$105-145k TC; the posting's stray "29.2" may be an hourly figure (~$60k/yr annualized) for an intern/contract variant, which would put it well under his $120k floor. Range is wide deliberately; treat the midpoint (~$125k) as at-or-slightly-below his $130k anchor.</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>full</t>
@@ -1271,7 +1427,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1279,7 +1435,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Vector_Atomic_Associate_Firmware_Engineer_Firmware.pdf</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1296,32 +1456,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$72k–$95k</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PaperCut</t>
+          <t>Securian Financial Group</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Associate Support Engineer</t>
+          <t>Engineering Analyst</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bracknell, UK</t>
+          <t>St Paul, MN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>A legitimate entry-level backend/cloud engineering role his skills clearly cover (integrations, Azure/AWS, microservices, CI/CD), but the posted $55.7Kâ€“$103.4K base puts realistic new-grad TC well under his ~130K anchor, and the generic insurance-IT scope is far below his distributed-systems/AI-infra profile.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>The posting states its own base band ($55,700â€“$103,400) for the whole "Engineering Analyst" career level; a May-2027 new grad lands near the bottom third, realistically ~$68â€“82K base in the St. Paul market. Securian adds a company-funded pension plus a performance-tied 401(k) contribution targeting 5% (up to 10%), and a small annual incentive, which is worth roughly $5â€“12K on top. That yields ~$72â€“95K first-year TC. Midwest insurance/financial-services carriers pay non-tech-tier rates, so this band is fairly confident on the low side rather than wide â€” treat as an estimate, not fact.</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>full</t>
@@ -1329,7 +1497,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1337,7 +1505,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Securian_Financial_Group_Engineering_Analyst.pdf</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1354,32 +1526,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$78k–$105k</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ERPA</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Franklin County, OH</t>
+          <t>Cedar Rapids, IA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Genuine systems-engineering overlap (C/C++/Rust, systems concentration, real-time onboard inference work), but RTX/Collins avionics in Cedar Rapids is embedded/real-time defense software at a citizenship- and often clearance-gated site, with new-grad comp far below the candidate's ~$130k anchor and outside his Boston/NYC preference.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Estimate, not fact. RTX (Collins Aerospace) is a traditional defense prime, not a tech-tier payer: new-grad SWE1 base typically ~$78-95k, with a small annual bonus and no meaningful equity, landing TC around $80-105k. Cedar Rapids, IA is a low-cost-of-living site and sits at the lower end of RTX's geographic bands, so the realistic center of mass is ~$85-95k TC. Defense roles also commonly gate on US citizenship and clearance eligibility, which can further limit competing-offer leverage. This is roughly 60-70% of the candidate's ~$130k target and below the stated ~$120k low-match floor.</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>full</t>
@@ -1387,7 +1567,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1395,7 +1575,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>RTX_Software_Engineer_1.pdf</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1412,32 +1596,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$70k–$110k</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TOMRA</t>
+          <t>AmNet Services</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Field Service Engineer - London/South East</t>
+          <t>Software Systems Engineer 3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Warren, NJ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>The underlying work (Erlang backend for a distributed IoT/sensor network) genuinely maps to Nate's distributed-systems and backend strengths, but this is a contract staffing req nominally asking for 7-10 years and admitting new grads only at the Master's level, with an immediate start rather than mid-2027 and comp almost certainly below his ~130K anchor.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Low confidence â€” wide band. AmNet Services/America Networks is a small private IoT sensor-and-networking firm, and this is posted as a contract role through a staffing recruiter, so pay is likely hourly W2 with little-to-no equity or bonus. Estimate is an annualized-hourly equivalent for a NJ contract backend role at a non-tech-tier employer; a fresh-grad contractor would realistically land near the bottom of the band ($70-90K equivalent), with the top of the band reflecting the posting's nominal 7-10 year seniority. This sits below the ~120K low-match threshold.</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>full</t>
@@ -1445,7 +1637,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -1453,7 +1645,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>AmNet_Services_Software_Systems_Engineer_3.pdf</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1470,32 +1666,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$55k–$80k</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>Trustpilot</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Entry Level .NET Developer</t>
+          <t>Software Engineer 1 - Trust Tech</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Louisville, CO</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Backend + AWS + applied-AI content is genuinely adjacent to his profile, but the role is London-only (no UK work authorization signaled), is a TypeScript/Node full-stack position rather than distributed-systems/infra, and UK entry-level comp lands far below his ~$130K anchor.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Estimate, not fact. Trustpilot is a profitable FTSE-250 mid-cap, not a top-of-market payer. UK "Software Engineer I" roles at companies of this tier typically run roughly Â£42â€“58K base plus a modest bonus, i.e. ~$55Kâ€“$80K USD at ~1.27 GBP/USD. London weighting is included; Copenhagen/Edinburgh would be similar or lower in USD terms. Band is wide because Trustpilot does not publish levels and no public new-grad data points are reliable.</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>full</t>
@@ -1503,7 +1707,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>error:Command '['latexmk', '-pdf', '</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -1528,32 +1732,44 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$90k–$118k</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>General Motors</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Warren, MI</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>graduating between december 2025</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Hard mismatches stack up: the posting requires graduation between Dec 2025 and Aug 2026 (candidate is May 2027), requires Android/mobile app experience for Kotlin-based in-vehicle HMI work (candidate is backend/distributed-systems), is hybrid 3x/week in Warren MI, and pays well under the ~$120k floor.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>GM is a non-tech-tier automotive employer; entry-level SWE base in Warren, MI typically ~$85â€“105k with a modest performance bonus (~5â€“10%) and no equity for entry level. Estimate band ~$90â€“118k TC, well below the candidate's ~$130â€“165k anchor. Moderate confidence.</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>full</t>
@@ -1561,7 +1777,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -1569,7 +1785,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>General_Motors_Software_Engineer.pdf</t>
+        </is>
+      </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1586,32 +1806,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$65k–$88k</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>D.R. Horton</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Entry Level Software Developer</t>
+          <t>Application Developer 1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Copperhill, TN</t>
+          <t>Arlington, TX</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>It is real backend/web SWE work he could do, but it's an entry-level .NET/C#/MVC internal-apps role at a non-tech homebuilder's corporate IT org in Arlington TX, with a high-school-diploma bar and a pay tier far below his backend/distributed-systems profile and ~130K anchor.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Estimate, not fact. D.R. Horton is a Fortune 500 homebuilder, not a tech company â€” engineering is a corporate IT cost center in DFW, so pay tracks regional non-tech IT bands rather than software-industry bands. An "Application Developer I" (0-1 yrs, .NET) in Arlington TX most likely lands ~$65-80K base with a modest discretionary bonus, 401(k) match, and ESPP, putting TC roughly $65-88K. Band is somewhat wide because D.R. Horton does not publish leveled comp and there is little public new-grad data for this req.</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>full</t>
@@ -1619,7 +1847,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -1627,7 +1855,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>D_R_Horton_Application_Developer_1.pdf</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1644,32 +1876,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$45k–$62k</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>Trustpilot</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Entry Level Java Developer</t>
+          <t>Software Engineer 1 - Trust Tech</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Elk Grove, CA</t>
+          <t>Edinburgh, UK</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>The backend/AWS/applied-AI/high-volume-data work is genuinely on-profile, but this is an Edinburgh-based UK role (needs UK work authorization, immediate start, not a May 2027 US new-grad pipeline) centered on Node.js/TypeScript full-stack rather than distributed systems, and UK SWE I comp lands far below the candidate's ~$130K anchor.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Estimate, not fact. Trustpilot is a FTSE-250 UK tech company paying market-rate but non-FAANG comp; Edinburgh SWE I base is likely ~Â£33-45K plus a small bonus and pension, which converts to roughly $45-62K USD. Even the top of this band is less than half the candidate's $130K target â€” the comp gap here is a currency/market gap, not a leveling gap, and this band would be non-competitive for a US-based new grad.</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>full</t>
@@ -1677,7 +1917,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>error:Command '['latexmk', '-pdf', '</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -1702,11 +1942,11 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$55k–$85k</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1716,18 +1956,26 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Entry Level Java Developer</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Silver Creek, NY</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Hard blockers dominate: the posting requires an interim SECRET clearance plus CompTIA Security+ certification to begin work (the candidate has no clearance and can't start until May 2027), and it's a staffing-firm Java/JavaScript/HTML web-maintenance role in rural Silver Creek, NY at roughly half the candidate's ~$130k comp anchor â€” his Java Spring microservices and SQL/REST background is genuinely relevant, but the role is far below his level and off his profile.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>9to9 Software Solutions is a small Connecticut-based IT staffing/consulting body shop placing entry-level developers on client/government contracts â€” not a product company, so no public new-grad comp data exists and the band is necessarily wide. Comparable entry-level Java contractor/staffing roles in upstate NY (Silver Creek is a rural Chautauqua County location, very low cost-of-labor market) typically pay $55kâ€“$85k base with little to no equity and minimal bonus. Cleared entry-level work can push toward the top of that band, but staffing intermediaries capture most of the contract margin. This is an estimate, not fact, and sits well below the candidate's ~$130k anchor.</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>full</t>
@@ -1735,7 +1983,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -1743,7 +1991,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>9to9_Software_Solutions_Entry_Level_Java_Developer.pdf</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1760,11 +2012,11 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$60k–$85k</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1774,18 +2026,26 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Entry Level Software Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Randolph AFB, TX</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>The Java/Spring/REST/SQL work is squarely in Nate's wheelhouse, but the posting hard-requires an interim SECRET clearance and CompTIA Security+ to even begin the contract (both disqualifying per his constraints), it's an IT-staffing body shop whose entry-level comp sits far below his ~$130K anchor, and it's an immediate-start role that doesn't line up with a May 2027 graduation.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Low confidence â€” 9to9 Software Solutions is a small Connecticut-based IT staffing/consulting firm placing developers on government and enterprise contracts, not a comp-transparent product company. Entry-level Java contract roles at this tier typically run $28-40/hr or $60-80K base with minimal bonus and no meaningful equity; Portland, OR adds little premium at this level. Band is intentionally wide and could skew lower if billed hourly without benefits. Roughly half the candidate's $130K anchor.</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>full</t>
@@ -1793,7 +2053,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -1801,7 +2061,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>9to9_Software_Solutions_Java_Developer.pdf</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1818,40 +2082,48 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$60k–$85k</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall - PhD</t>
+          <t>Entry Level Software Developer</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Randolph AFB, TX</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>The Java/Spring/REST/SQL technical content is a reasonable backend fit, but the posting hard-requires an interim SECRET clearance plus an existing Security+ certification to start work on the contract â€” both explicit disqualifiers for this candidate â€” at a small defense-staffing firm on an Air Force base whose comp sits far below the ~130k anchor.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Estimate only, wide band due to low visibility: 9to9 Software Solutions is a small Connecticut-based IT staffing/consulting firm placing entry-level developers on government contracts (Randolph AFB, TX). Government-contract entry-level dev rates in San Antonio typically land ~$60-80k base with minimal bonus/equity; cleared-contract premium is small at entry level. Well below the candidate's ~130k anchor â€” a low match on comp as well as clearance.</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -1859,7 +2131,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>9to9_Software_Solutions_Entry_Level_Software_Developer.pdf</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1876,32 +2152,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$62k–$78k</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>An onsite San Diego rotational program centered on SSIS packages, stored-procedure/BI reporting, and Salesforce Apex at a posted $30/hr sits well outside Nate's backend/distributed-systems/AI-infra profile and far below his ~130K TC anchor, even though his SQL and Azure Data Factory pipeline work is transferable.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>The posting states the pay range explicitly: $30.00/hr flat, which is ~$62.4K base at 2,080 hrs, plus a 10% discretionary cash bonus target and 10% discretionary RSU target. Fully-paid targets put TC near $75K; discretionary bonuses may pay under target, hence the $62K floor. This is a mid-tier regional bank rotational program, not a tech-comp band â€” roughly half of Nate's $130K anchor and below his ~$120K low-match line.</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>full</t>
@@ -1909,7 +2193,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -1917,7 +2201,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Axos_Bank_Data_Engineer.pdf</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1934,40 +2222,48 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$65k–$88k</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>SOSi</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation - PhD</t>
+          <t>PeopleSoft Software Developer</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Charleston, SC</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Off-profile: this is entry-level PeopleSoft/ERP maintenance work (PeopleCode, HCM/Payroll modules) at a defense integrator requiring an interim Secret clearance, 5 days on-site in Charleston, SC â€” none of which touches the candidate's backend/distributed-systems/AI-infra profile, and the comp tier sits well below his ~130k anchor.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Estimate only â€” SOSi is a mid-size private government/defense services integrator, a tier where entry-level developer pay is cost-plus contract-driven rather than market-competitive. Cleared entry-level ERP/PeopleSoft roles in Charleston, SC typically land ~$65-85k base with a small (0-5%) bonus and no equity; band widened because SOSi does not publish new-grad ranges. Even the top of this band is ~35% below the candidate's ~$130k target.</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -1975,7 +2271,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>SOSi_PeopleSoft_Software_Developer.pdf</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1992,32 +2292,40 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$55k–$85k</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation - PhD</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Hard-requires an interim SECRET clearance plus CompTIA Security+ to begin work â€” both of which this candidate explicitly cannot satisfy â€” and it is a contract legacy-Java/JSP web role at a small IT staffing firm with comp far below the ~130k anchor.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Low confidence, wide band: 9to9 Software Solutions is a small private Connecticut-based IT staffing/services firm with no public comp data, so this is inferred from tier rather than known. Contract entry-level Java developer roles at IT services shops on government subcontracts typically pay $30-45/hr (~$60-90k annualized) with thin or no equity/bonus. Cleared work carries a premium, but it is unreachable here without the required clearance. No realistic path to the $130k target.</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>full</t>
@@ -2025,7 +2333,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2033,7 +2341,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>9to9_Software_Solutions_Software_Developer.pdf</t>
+        </is>
+      </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2050,32 +2362,40 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$85k–$112k</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer Graduate - Recommendation &amp; LLM</t>
+          <t>Failure Analysis Engineer</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Acton, MA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>This is a hands-on hardware/photonics failure-analysis role (coherent optical transceivers, oscilloscopes, RF/optical spectrum analyzers, onsite in Maynard, MA) that maps to the candidate's explicit "hardware/embedded-only, EE-centric" low-fit bucket, and the posted $79.2Kâ€“$100.4K base sits below his ~$120K floor.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>The posting states a base range of $79,200â€“$100,400 for U.S. new hires. Cisco supply-chain/manufacturing-ops entry roles typically add a modest bonus target (~5%) and a small RSU grant (~$5â€“10K/yr vested over 4 years), so realistic year-one TC lands roughly $85Kâ€“$112K. This is well below Cisco's software-engineering new-grad bands (~$120â€“150K) because the job family and location band are different.</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>full</t>
@@ -2083,7 +2403,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>error:Command '['latexmk', '-pdf', '</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -2108,32 +2428,40 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$55k–$80k</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation</t>
+          <t>Entry Level Software Developer</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Copperhill, TN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Hard-blocked despite nominal Java/backend overlap: the posting is a staffing-firm contract in rural Copperhill, TN that requires an interim SECRET clearance and an existing CompTIA Security+ certification just to begin work â€” both of which this candidate lacks and cannot obtain as a 2027 new grad â€” and the work (JSP/WebLogic/Subversion-era Java web apps) is well below his distributed-systems/AI-infra profile and TC anchor.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Low confidence, wide band. 9to9 Software Solutions is a small Connecticut-based IT staffing/consulting firm, not a product company with published levels â€” this is a W2/contract billing arrangement on a government subcontract, so comp is hourly-rate-driven with little or no equity and thin benefits. Entry-level cleared Java contract developers in a low-cost rural TN market typically bill out such that the developer sees roughly $28â€“$40/hr, i.e. ~$55â€“80K annualized. Even the top of this band is far below the candidate's ~$130â€“165K anchor, and contract status adds bench/term risk.</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>full</t>
@@ -2141,7 +2469,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -2149,7 +2477,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>9to9_Software_Solutions_Entry_Level_Software_Developer.pdf</t>
+        </is>
+      </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2166,32 +2498,40 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$60k–$90k</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer Graduate - Recommendation &amp; LLM</t>
+          <t>Entry Level Java Developer</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Elk Grove, CA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Hard-blocked by requirements the candidate cannot meet â€” an interim SECRET clearance to begin work and an active CompTIA Security+ certification â€” and it is a legacy JSP/Hibernate/WebLogic contract role at a small IT staffing firm in Elk Grove, CA, well below his backend/distributed-systems level and ~$120k TC floor.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Low-confidence, deliberately wide band. 9to9 Software Solutions is a small Connecticut-based IT services/staffing firm with no public compensation data, and this is an explicitly contract engagement. Entry-level contract Java roles at firms of this tier typically bill W2 hourly around $28-42/hr (roughly $58-87k annualized) with little or no bonus/equity. Even the top of the band sits ~30% below the candidate's ~$120k low-match threshold, so this is a low-comp match regardless of band precision.</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>full</t>
@@ -2199,7 +2539,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -2207,7 +2547,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>9to9_Software_Solutions_Entry_Level_Java_Developer.pdf</t>
+        </is>
+      </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2224,40 +2568,48 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$85k–$110k</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Photoshop Developer - GPU/Imaging</t>
+          <t>Reliability Engineer 2</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Seattle, WA, SF, San Jose, CA, NYC</t>
+          <t>Chandler, AZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>This is an EE-centric semiconductor reliability role (transistor-level device physics, HTOL/burn-in, lab test equipment, JMP/MATLAB, automotive qual) that explicitly targets BS/MS EE with 0â€“3 yrs â€” squarely in the candidate's role_fit_low bucket, with no distributed-systems/backend/AI-infra surface, plus a start-date mismatch (available May 2027) and TC well under the $120k floor.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Microchip is a lower-paying semiconductor employer relative to big tech; Chandler, AZ market. New-grad/Engineer II reliability roles there typically run ~$80â€“100k base plus modest bonus/ESPP, so ~$85â€“110k TC. Wide band because Microchip does not publish and levels vary; well below the candidate's ~$130k anchor, so this is a low comp match.</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -2265,7 +2617,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Microchip_Technology_Reliability_Engineer_2.pdf</t>
+        </is>
+      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2282,40 +2638,48 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$35k–$50k</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Valeo Foods</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Reliability Engineer 2</t>
+          <t>Enterprise Applications Developer - Enterprise Applications</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chandler, AZ</t>
+          <t>Norwich, UK</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Norwich, UK-based junior ERP/Microsoft-stack applications role (SSRS, Power Apps, IFS, C#) that neither matches the candidate's backend/distributed-systems/AI-infra profile nor his US work authorization and mid-2027 new-grad timeline.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Estimate, not fact: Valeo Foods is a private-equity-backed UK food manufacturer, not a tech-tier payer. Junior/graduate enterprise applications developer roles in Norwich (low cost-of-living UK region) typically pay ~Â£27â€“38k base plus pension/benefits, which converts to roughly $35â€“50k USD. Wide band given no posted salary. This is far below the candidate's ~$130k anchor.</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -2323,7 +2687,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Valeo_Foods_Enterprise_Applications_Developer_Enterprise_App.pdf</t>
+        </is>
+      </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2340,32 +2708,40 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$45k–$75k</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mach Industries</t>
+          <t>ERPA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Software Engineer New Grad - Software - GNC</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Huntington Beach, CA</t>
+          <t>Franklin County, OH</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>This is a contract "Big Data Training and Placement" bench-consulting program at an Oracle/PeopleSoft implementation partner explicitly targeting graduates with "basic technical skills" who need training â€” a near-total mismatch for a distributed-systems/AI-infra candidate anchored at $130k+ TC, and the contract structure plus Ohio-only location make it a poor use of an application.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ERP Analysts (ERPA) is an Oracle Platinum Partner / staffing-and-consulting shop, and this specific posting is a *contract* "Big Data Training and Placement" program for "fresh graduates with basic technical skills," not a competitive new-grad SWE req. These training-and-placement/bench-consulting arrangements typically pay a low hourly rate or stipend during training and modest salaries once placed at a client â€” commonly in the $45kâ€“$75k range, sometimes with training-cost/contract clauses. No public leveling or comp data exists for this posting, so the band is intentionally wide and low-confidence; it sits well below the candidate's $130k anchor.</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>full</t>
@@ -2373,7 +2749,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2381,7 +2757,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>ERPA_Software_Developer.pdf</t>
+        </is>
+      </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2398,32 +2778,40 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$35k–$50k</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Valeo Foods</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Enterprise Applications Developer - Enterprise Applications</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>Leeds, UK</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Off-profile on three axes at once: the role is UK-based (Leeds) with no US option and the candidate has no UK work authorization, the stack is ERP/Power Apps/SSRS/Crystal Reports/C# enterprise-apps work rather than backend distributed systems or AI infra, and the posting reads as an immediate junior hire rather than a mid-2027 new-grad start â€” the only real overlap is Azure, SQL, Git, and API/integration experience.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Valeo Foods is a UK/Ireland food manufacturer (private-equity backed, non-tech sector); this is an internal IT/enterprise-apps role in Leeds, not a product-engineering role. UK junior/graduate enterprise developer salaries outside London typically run Â£28-40k base with modest benefits (matched pension, 25 days holiday), i.e. roughly $35-50k USD at ~1.27 GBP/USD. No equity or tech-style bonus. Estimate only â€” Valeo does not publish salary bands and this figure is inferred from UK regional market rates, not from company data. This is far below the candidate's ~$130-165k anchor.</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>full</t>
@@ -2431,7 +2819,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -2439,7 +2827,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Valeo_Foods_Enterprise_Applications_Developer_Enterprise_App.pdf</t>
+        </is>
+      </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2456,32 +2848,40 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$34k–$42k</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Truveta</t>
+          <t>PaperCut</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Software Engineer - Live Link</t>
+          <t>Associate Support Engineer</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Bracknell, UK</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Off-profile on three axes at once: it's a frontline customer-support role (not backend/distributed-systems SWE), based in Bracknell UK requiring UK work authorization, and capped at Â£30k (~$38k USD) â€” roughly a quarter of the candidate's ~$130k anchor.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>The posting states compensation directly: "up to GBP 30,000 - yearly." At ~1.27 USD/GBP that's ~$38k base; adding a small bonus/benefits allowance gives ~$34â€“42k USD total comp. PaperCut is a mid-size private print-management software vendor (Australian HQ), not a top-tier payer, so there is little upside beyond the stated cap. Note this is a UK-market salary and not comparable to US new-grad SWE bands.</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>full</t>
@@ -2489,7 +2889,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -2497,7 +2897,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>PaperCut_Associate_Support_Engineer.pdf</t>
+        </is>
+      </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2514,32 +2918,44 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$30k–$50k</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>Hawk-Eye Innovations</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Research Engineer Graduate - Seed Infra - PhD</t>
+          <t>Football Tracking Systems Operator - Remote Operations Centre</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Basingstoke, UK, Southampton, UK, Reading, UK</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>start date: july</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>This is a UK-based, in-office casual hourly contract as a live-broadcast systems *operator* in Basingstoke starting July/August 2026 â€” wrong country, wrong start date (candidate graduates May 2027), wrong role type (operations shift work, not backend/distributed-systems SWE), and wrong comp tier (~Â£13â€“18/hr), so it is genuinely off-profile despite the "technical grounding" overlap.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Comp is stated in the posting: Â£13.00â€“Â£18.20/hour on a casual contract with 10â€“12 hour shifts. Annualized at roughly full-season availability that is ~Â£27kâ€“Â£38k, or about $34kâ€“$48k USD at recent rates; I widened the band slightly since hours are not guaranteed (casual, football-calendar dependent) and there is no equity or new-grad-style bonus. Hawk-Eye (a Sony company) pays engineering roles far better than this operator role â€” this band applies only to the ROC operator posting, and it sits ~2.5â€“4x below the candidate's ~$130k anchor.</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>full</t>
@@ -2547,7 +2963,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -2555,7 +2971,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Hawk_Eye_Innovations_Football_Tracking_Systems_Operator_Remo.pdf</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2572,40 +2992,48 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$33k–$45k</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>Radius Limited</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Graduate Mobile Developer - Vehicle Telematics</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Crewe, UK</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Off-profile on nearly every axis: it's a UK-only (Crewe) mobile/Flutter-Kotlin-Swift graduate role with explicit no-visa-sponsorship, starting now rather than mid-2027, against a US-authorized backend/distributed-systems candidate with no native mobile experience and a ~$130K TC anchor.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Radius is a UK private fleet/fuel-card/telematics company (not a tech-tier payer). UK graduate developer salaries outside London â€” Crewe, Cheshire â€” typically run Â£26Kâ€“Â£34K base with pension and small benefits, i.e. roughly $33Kâ€“$45K USD equivalent. Estimate only; no published band for this posting, and UK comp does not translate cleanly to US TC expectations.</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -2613,7 +3041,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Radius_Limited_Graduate_Mobile_Developer_Vehicle_Telematics.pdf</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2630,32 +3062,40 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$8k–$25k</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>Lilt</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Video/Image AI/ML Software Engineer Graduate - Multimedia</t>
+          <t>AI Training Contributor - French</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Remote in Canada, Québec City, QC, Canada</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Hard mismatch on every axis: it is a part-time 1099 data-annotation gig (explicitly "not ideal as a full time job") requiring native French fluency and Canadian residency, with no engineering scope and comp roughly an order of magnitude below the candidate's ~$130K new-grad anchor.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Lilt AI Training Contributor roles are 1099 part-time annotation/linguistic-QA contracts, not salaried SWE. Market rates for language-pair AI evaluation work run roughly $15â€“35 USD/hr; the posting itself states most tasks require only ~10 hrs/week and warns it is "not ideal as a full time job or primary income source." Annualizing 10â€“15 hrs/week at that rate gives roughly $8Kâ€“$25K with no benefits, equity, or guaranteed hours. This is an estimate; actual rates vary by language pair and project demand.</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>full</t>
@@ -2663,7 +3103,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>error:[WinError 2] The system cannot</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -2671,7 +3111,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Lilt_AI_Training_Contributor_French.pdf</t>
+        </is>
+      </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2697,26 +3141,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>Fortinet</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AI/LLM Network Software Development Engineer Graduate - High Speed Network - PhD</t>
+          <t>Applied AI Engineer - AI Agent</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>Sunnyvale, CA</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2729,7 +3169,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2755,26 +3194,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>D.R. Horton</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Application Developer 1</t>
+          <t>Software Engineer New Grad</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arlington, TX</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>Burlington, MA</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2787,7 +3222,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2813,26 +3247,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AmNet Services</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Software Systems Engineer 3</t>
+          <t>Product Software Engineer 1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Warren, NJ</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>Glendale, CA</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2845,7 +3275,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2871,23 +3300,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Radius Limited</t>
+          <t>Trustpilot</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Graduate Mobile Developer - Vehicle Telematics</t>
+          <t>Software Engineer 1 - Trust Tech</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Crewe, UK</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>Edinburgh, UK</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>full</t>
@@ -2903,7 +3328,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2929,23 +3353,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Barrios</t>
+          <t>Trustpilot</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer 1 - Trust Tech</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>London, UK</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>full</t>
@@ -2961,7 +3381,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2987,12 +3406,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Alkira</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Data Knowledge System Research Scientist Graduate - Data Platform-Global Live</t>
+          <t>Software Engineer - Datapath</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3000,10 +3419,6 @@
           <t>San Jose, CA</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>metadata-only</t>
@@ -3019,7 +3434,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3045,23 +3459,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Research Scientist - Seed AI Foundation Model Infrastructure</t>
+          <t>Failure Analysis Engineer</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>Acton, MA</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>full</t>
@@ -3077,7 +3487,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3103,26 +3512,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Multiple Teams</t>
+          <t>Entry Level Java Developer</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Irving, TX</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>Silver Creek, NY</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3135,7 +3540,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3161,26 +3565,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Lilt</t>
+          <t>Cohesity</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AI Training Contributor - French</t>
+          <t>Software Engineer New Grad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Remote in Canada, Québec City, QC, Canada</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>Santa Clara, CA</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3193,7 +3593,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
       <c r="O47" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3219,26 +3618,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Valeo Foods</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Multiple Teams</t>
+          <t>Enterprise Applications Developer - Enterprise Applications</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Irving, TX</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>Leeds, UK</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3251,7 +3646,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
       <c r="O48" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3277,23 +3671,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Valeo Foods</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Wireless Platform</t>
+          <t>Enterprise Applications Developer - Enterprise Applications</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SF, San Jose, CA</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>Norwich, UK</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>full</t>
@@ -3309,7 +3699,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3335,23 +3724,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>SOSi</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Software Engineer Graduate - Recommendation</t>
+          <t>PeopleSoft Software Developer</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>Charleston, SC</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>full</t>
@@ -3367,7 +3752,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3393,23 +3777,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Big Data Engineer Graduate - TikTok Recommendation Architecture</t>
+          <t>Associate Software Engineer 1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>North Chicago, IL</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>full</t>
@@ -3425,7 +3805,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
       <c r="O51" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3451,23 +3830,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>PaperCut</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - TikTok Vertical Recommendation</t>
+          <t>Associate Support Engineer</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>Bracknell, UK</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>full</t>
@@ -3483,7 +3858,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
       <c r="O52" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3509,23 +3883,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>ERPA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Backend Engineer Graduate - TikTok Vertical Recommendation Architecture - 2027 Start</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>Franklin County, OH</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>full</t>
@@ -3541,7 +3911,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3567,23 +3936,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>TOMRA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall</t>
+          <t>Field Service Engineer - London/South East</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>London, UK</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>full</t>
@@ -3599,7 +3964,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
       <c r="O54" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3625,23 +3989,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall</t>
+          <t>Entry Level .NET Developer</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>Louisville, CO</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>full</t>
@@ -3657,7 +4017,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
       <c r="O55" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3683,26 +4042,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>Pittsburgh, PA</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3715,7 +4070,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
       <c r="O56" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3741,26 +4095,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Entry Level Software Developer</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>Copperhill, TN</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3773,7 +4123,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
       <c r="O57" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3799,26 +4148,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Entry Level Java Developer</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Anaheim, CA</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>Elk Grove, CA</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3831,7 +4176,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
       <c r="O58" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3857,26 +4201,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Vector Atomic</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Associate Firmware Engineer - Firmware</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pleasanton, CA</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>Portland, OR</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3889,7 +4229,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3915,26 +4254,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>General Motors</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Entry Level Software Developer</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Warren, MI</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>Randolph AFB, TX</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3947,7 +4282,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
       <c r="O60" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3973,23 +4307,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Securian Financial Group</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Engineering Analyst</t>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall - PhD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>St Paul, MN</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>metadata-only</t>
@@ -4005,7 +4335,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="O61" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -4031,23 +4360,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seagate Technology </t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Firmware Engineer</t>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Longmont, CO</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>full</t>
@@ -4063,7 +4388,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
       <c r="O62" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -4089,30 +4413,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Hawk-Eye Innovations</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Football Tracking Systems Operator - Remote Operations Centre</t>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation - PhD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Basingstoke, UK, Southampton, UK, Reading, UK</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>start date: july</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4125,7 +4441,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
       <c r="O63" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -4151,26 +4466,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>T-Mobile</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Associate Engineer - Software</t>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation - PhD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Frisco, TX</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4183,7 +4494,6 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
       <c r="O64" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -4209,45 +4519,3572 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AI Infrastructure Engineer Graduate - Recommendation &amp; LLM</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AI Infrastructure Engineer Graduate - Recommendation &amp; LLM</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Photoshop Developer - GPU/Imaging</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Seattle, WA, SF, San Jose, CA, NYC</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>metadata-only</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Microchip Technology</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Reliability Engineer 2</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Chandler, AZ</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>metadata-only</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Mach Industries</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Software Engineer New Grad - Software - GNC</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Huntington Beach, CA</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Handshake</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Truveta</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Software Engineer - Live Link</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Research Engineer Graduate - Seed Infra - PhD</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Axos Bank</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>San Diego, CA</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>metadata-only</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Video/Image AI/ML Software Engineer Graduate - Multimedia</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>San Diego, CA</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AI/LLM Network Software Development Engineer Graduate - High Speed Network - PhD</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>D.R. Horton</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Application Developer 1</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Arlington, TX</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AmNet Services</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Software Systems Engineer 3</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Warren, NJ</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Radius Limited</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Graduate Mobile Developer - Vehicle Telematics</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Crewe, UK</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Barrios</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O80" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Data Knowledge System Research Scientist Graduate - Data Platform-Global Live</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>metadata-only</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O81" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Research Scientist - Seed AI Foundation Model Infrastructure</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O82" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer - Multiple Teams</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Irving, TX</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>metadata-only</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O83" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Lilt</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AI Training Contributor - French</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Remote in Canada, Québec City, QC, Canada</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O84" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer - Multiple Teams</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Irving, TX</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>metadata-only</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O85" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 - Wireless Platform</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>SF, San Jose, CA</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O86" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Software Engineer Graduate - Recommendation</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O87" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Big Data Engineer Graduate - TikTok Recommendation Architecture</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O88" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Graduate - TikTok Vertical Recommendation</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O89" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Backend Engineer Graduate - TikTok Vertical Recommendation Architecture - 2027 Start</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O90" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O91" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O92" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Software Engineer 1</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Cedar Rapids, IA</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>metadata-only</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O93" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Software Engineer 1</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Fort Wayne, IN</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>metadata-only</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O94" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Software Engineer 1</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Anaheim, CA</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>metadata-only</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O95" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Vector Atomic</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Associate Firmware Engineer - Firmware</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>metadata-only</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O96" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>General Motors</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Warren, MI</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>metadata-only</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O97" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Securian Financial Group</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Engineering Analyst</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>St Paul, MN</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>metadata-only</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O98" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seagate Technology </t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Firmware Engineer</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Longmont, CO</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O99" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Hawk-Eye Innovations</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Football Tracking Systems Operator - Remote Operations Centre</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Basingstoke, UK, Southampton, UK, Reading, UK</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>start date: july</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O100" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>T-Mobile</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Associate Engineer - Software</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Frisco, TX</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>metadata-only</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>error:[WinError 2] The system cannot</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O101" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
           <t>Integration Innovation (i3)</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>Associate Software Developer - COMPASS</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>Huntsville, AL</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t>error:[WinError 2] The system cannot</t>
         </is>
       </c>
-      <c r="M65" s="3" t="inlineStr">
-        <is>
-          <t>Apply ↗</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" s="3" t="inlineStr">
-        <is>
-          <t>levels.fyi ↗</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="O102" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer 1</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>North Chicago, IL</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>TOMRA</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Field Service Engineer - London/South East</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>9to9 Software Solutions</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Entry Level .NET Developer</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Louisville, CO</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall - PhD</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation - PhD</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation - PhD</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AI Infrastructure Engineer Graduate - Recommendation &amp; LLM</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AI Infrastructure Engineer Graduate - Recommendation &amp; LLM</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Handshake</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Research Engineer Graduate - Seed Infra - PhD</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Video/Image AI/ML Software Engineer Graduate - Multimedia</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>San Diego, CA</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AI/LLM Network Software Development Engineer Graduate - High Speed Network - PhD</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Barrios</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Data Knowledge System Research Scientist Graduate - Data Platform-Global Live</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Research Scientist - Seed AI Foundation Model Infrastructure</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer - Multiple Teams</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Irving, TX</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Software Engineer Graduate - Recommendation</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Big Data Engineer Graduate - TikTok Recommendation Architecture</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Graduate - TikTok Vertical Recommendation</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Backend Engineer Graduate - TikTok Vertical Recommendation Architecture - 2027 Start</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Software Engineer 1</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Fort Wayne, IN</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Software Engineer 1</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Anaheim, CA</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Integration Innovation (i3)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Associate Software Developer - COMPASS</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Huntsville, AL</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>error:'charmap' codec can't encode c</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
@@ -4256,133 +8093,291 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O98" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M108" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M109" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M110" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M113" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M114" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M115" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M116" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M117" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M118" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M119" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M123" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M124" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M125" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M126" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M127" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M128" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M129" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="rId286"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/tailored_resumes.xlsx
+++ b/output/tailored_resumes.xlsx
@@ -464,7 +464,7 @@
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,7 +545,7 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Date Added</t>
+          <t>Date Scored</t>
         </is>
       </c>
     </row>
@@ -554,38 +554,38 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$135k–$180k</t>
+          <t>$200k–$260k</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Truveta</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Software Engineer - Live Link</t>
+          <t>Software Engineer Graduate - Recommendation</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Near-ideal match: an explicitly new-grad backend req centered on APIs, distributed services, databases, data pipelines, and cloud infra with a privacy/security/entitlements emphasis â€” which maps directly onto his Raft/LSM/MVCC KV store, Java Spring microservices, Azure data pipelines, and OIDC/IdP authorization work at a clinical-software company, with the only real friction being Seattle-hybrid vs. his Boston/NYC preference (he is open to relocation).</t>
+          <t>Near-ideal profile overlap — distributed systems, RAG/multi-agent, LLM serving infra, and large-scale data pipelines match the candidate's Rust Raft/LSM KV store, pgvector/Bedrock RAG, and cloud-infra strengths, with a 2027 start that fits a May 2027 grad; minor gaps are search/IR and recsys domain exposure and a San Jose relocation.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Truveta is a well-funded Seattle health-data startup (~$320M+ raised, founded/led by ex-Microsoft leadership, pays close to Seattle big-tech bands to compete with MSFT/AMZN for the same talent). This is an explicitly new-grad backend req in a HCOL market. Estimate assumes base ~$125-150k plus target bonus and a startup equity grant with uncertain valuation, so the band is wide on the upper end; treat as an estimate, not fact.</t>
+          <t>Posting lists a $128k-$316.8k San Jose base range; new grads typically land at the lower-mid end (~$145-175k base) plus RSUs (~$30-60k/yr) and annual bonus. ByteDance/TikTok pays at or above top-tier big-tech for new-grad SWE, so total package comfortably exceeds the candidate's ~$130k anchor. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>Truveta_Software_Engineer_Live_Link.pdf</t>
+          <t>TikTok_Software_Engineer_Graduate_Recommendation_216add.pdf</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
@@ -623,43 +623,39 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>74</v>
+      <c r="B3" s="2" t="n">
+        <v>92</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$190k–$240k</t>
+          <t>$180k–$240k</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fortinet</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Applied AI Engineer - AI Agent</t>
+          <t>Backend Engineer Graduate - TikTok Vertical Recommendation Architecture - 2027 Start</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>graduating by summer 2026; summer 2026</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Content fit is excellent â€” the role is literally backend services + LLM/RAG/agentic systems in a cybersecurity/SOC context, matching his Sentinel AI SRE agent, SculptAI RAG stack, Java/Flask/FastAPI microservices, and systems-security concentration â€” but the posting explicitly requires graduating by Summer 2026 (or already graduated), and he graduates May 2027, which is the main deduction.</t>
+          <t>Backend/distributed-systems new-grad role centered on high-availability online services, P99/throughput optimization, and large-scale storage/caching/messaging — a direct match for the candidate's Raft/LSM-tree KV store, Java microservices, and ML-infra experience; only concern is the "onboard by end of the year" phrasing vs. a May 2027 graduation, and no remote (San Jose onsite).</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>The posting states a base range of $179,500â€“$220,000 plus equity (Fortinet RSU program) and discretionary bonus; a new grad would land near the bottom of the base band (~$180â€“195K) with maybe $10â€“30K/yr in RSUs and bonus. Band reflects that plus Bay Area/Sunnyvale cost adjustment. Fortinet is a large public security vendor (NASDAQ: FTNT) that historically pays mid-tier, so the high end is unlikely for a new grad â€” estimate, not fact.</t>
+          <t>Posting lists a wide multi-level base range of $128,000-$316,800 for San Jose. TikTok new-grad backend SWE in the Bay Area typically lands ~$145k-$165k base, plus RSUs of roughly $25k-$50k/yr and a discretionary annual bonus, putting first-year TC in the $180k-$240k range. Estimate based on general knowledge of TikTok/ByteDance's tier-1 comp positioning, not a verified offer figure.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -669,7 +665,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -679,7 +675,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>Fortinet_Applied_AI_Engineer_AI_Agent.pdf</t>
+          <t>TikTok_Backend_Engineer_Graduate_TikTok_Vertical_R_1bc2ed.pdf</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -698,48 +694,48 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$110k–$140k</t>
+          <t>$240k–$380k</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>ByteDance</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Software Engineer New Grad</t>
+          <t>Research Scientist - Seed AI Foundation Model Infrastructure</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Burlington, MA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Strong profile match â€” Symbotic's warehouse-automation software is heavily backend/distributed-systems and real-time in Java/C++/Python, all core to this candidate, and it's Boston-local; the only drags are the robotics/embedded-adjacent domain flavor and a TC band that likely sits at the bottom of his anchor.</t>
+          <t>Direct overlap with the candidate's distributed-systems and AI/ML-infra strengths (large-scale training, inference, systems/algorithm co-design) on a Bachelor's-eligible 2027-start req, discounted only because a ByteDance Seed "Research Scientist" bar skews heavily toward PhD/publication-track applicants.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Symbotic is a publicly traded (SYM) warehouse-automation/robotics company headquartered in Wilmington/Burlington MA. It is a solid non-FAANG tech-hardware employer: new-grad SWE base typically ~$95-120K, with a modest RSU grant and small bonus. Only the title and company were available in the posting, so this is a wide inference from company tier and Boston-market robotics/automation pay rather than posting data. Note this likely lands at or slightly below the candidate's ~$130-165K anchor.</t>
+          <t>Posting discloses base $207,480-$368,220 for Seattle; a BS new grad would sit near the low end of base (~$210-240k), with RSUs and discretionary bonus layered on. ByteDance Seed is a top-tier AI-lab payer, so even the floor is far above the candidate's ~$130k anchor. Band is wide because new-grad placement within a research-scientist ladder varies a lot by interview outcome.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -747,11 +743,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>Symbotic_Software_Engineer_New_Grad.pdf</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -768,38 +760,38 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$110k–$150k</t>
+          <t>$180k–$240k</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Product Software Engineer 1</t>
+          <t>AI Infrastructure Engineer Graduate - Recommendation &amp; LLM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Glendale, CA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Strong backend/cloud/data-pipeline overlap for a 0â€“2 YOE req (Java, Python, AWS, Terraform, K8s, microservices, storage internals, plus the AI-assisted-tooling angle they explicitly call out), docked for the data-engineering/big-data slant he hasn't formally used (Spark/Kafka/Flink/Snowflake), fully on-site Glendale vs. his Boston/NYC preference, and a posting that closes Aug 2026 for an immediate hire rather than a May 2027 new-grad start.</t>
+          <t>Explicitly a 2027-start new-grad AI infrastructure role centered on distributed training/serving systems, which maps directly onto the candidate's distributed-systems, LLM/AI-infra, and cloud strengths; the only meaningful gap is hands-on GPU/CUDA and PyTorch-internals experience (FSDP/ZeRO, FlashAttention, KV cache).</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Disney Entertainment/ESPN Product Technology (Ad Platforms) pays upper-mid-tier tech, below FAANG but above traditional media. California pay-transparency postings for SWE I in Glendale typically list base ranges roughly $98Kâ€“$135K; add ~10% target bonus and a small RSU grant for entry level. Estimate, not fact â€” Disney rarely gives meaningful new-grad equity, so realized TC often lands near the base + bonus figure (~$115â€“135K), and the $150K top end assumes a high base offer plus full bonus/RSU.</t>
+          <t>Posting lists a $128k-$316.8k base band spanning multiple levels; TikTok/ByteDance new-grad SWE base typically lands ~$145k-$170k, with RSUs and discretionary bonus pushing total comp to roughly $180k-$240k. AI-infra/LLM roles trend toward the upper half of that. Estimate based on general knowledge of ByteDance's top-of-market pay tier, not verified offer data.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -809,7 +801,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -819,7 +811,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>The_Walt_Disney_Company_Product_Software_Engineer_1.pdf</t>
+          <t>TikTok_AI_Infrastructure_Engineer_Graduate_Recomme_1514d6.pdf</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -837,22 +829,22 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>73</v>
+      <c r="B6" s="2" t="n">
+        <v>87</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>$125k–$170k</t>
+          <t>$170k–$230k</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Alkira</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Software Engineer - Datapath</t>
+          <t>Big Data Engineer Graduate - TikTok Recommendation Architecture</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -864,12 +856,12 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Strong systems/infra alignment â€” Python/C/C++/Rust, Linux, AWS/Azure, Terraform/CI-CD, K8s, production on-call reliability, Computer Networks coursework, and explicit Claude Code use (a listed bonus) â€” held back by no Ansible or production Go experience, limited depth in TCP/IP networking, and a San Jose hybrid requirement against a May 2027 availability date for what reads as an immediate-start role.</t>
+          <t>Core work is large-scale distributed storage/compute and high-availability infrastructure in Java/C++, which aligns closely with the candidate's Rust Raft/LSM-tree/MVCC KV store, backend microservices, and systems concentration; 2027 start matches the May 2027 grad date, with the only real gap being no hands-on Hadoop/Spark/Flink/Kafka big-data tooling.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Estimate, not fact. Alkira is a well-funded Bay Area networking startup (Viptela founders) now under Lumen, hiring in San Jose â€” a high-cost market with strong comp pressure from neighboring infra companies. Typical new-grad/early-career SWE there: ~$120â€“145K base plus ~10% bonus and equity (post-acquisition equity is likely RSU/cash-like rather than high-upside startup options), landing around $125â€“170K first-year TC. Band is wide because private/recently-acquired company data is thin; this clears the candidate's ~$130K anchor at the midpoint, though Bay Area cost of living erodes the real value versus a Boston offer.</t>
+          <t>Posting discloses a $128,000-$316,800 base range for San Jose, but that band spans multiple levels; ByteDance/TikTok new-grad SWE offers in the Bay Area typically sit around $140-165k base plus RSUs and a discretionary bonus, yielding roughly $170-230k first-year total comp. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -879,7 +871,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -889,7 +881,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>Alkira_Software_Engineer_Datapath.pdf</t>
+          <t>TikTok_Big_Data_Engineer_Graduate_TikTok_Recommend_a302cc.pdf</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -907,43 +899,39 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>70</v>
+      <c r="B7" s="2" t="n">
+        <v>88</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>$118k–$142k</t>
+          <t>$145k–$185k</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cohesity</t>
+          <t>Truveta</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Software Engineer New Grad</t>
+          <t>Software Engineer - Live Link</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Santa Clara, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>start date and have the legal right to wo</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>The technical domain (distributed systems, cloud, storage, C/C++/Python/Java) is an near-perfect match for his Raft/LSM-tree/MVCC work, but the posting explicitly targets May/June 2026 grads (he's May 2027) and requires on-site Bay Area presence, and the stated base band tops out below his ~130k anchor.</t>
+          <t>Explicitly a new-grad backend role owning APIs, distributed services, data pipelines, and cloud infra with a security/privacy emphasis — nearly a direct match to the candidate's distributed-systems, microservices, and cloud/infra strengths; only friction is Seattle hybrid (relocation required) and a likely 2026 start vs. May 2027 graduation.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>The posting states a base range of $113.4k-$126k and mentions bonus eligibility plus equity grants. Cohesity is a large late-stage private company (post-Veritas-data-protection acquisition), so equity is illiquid pre-IPO RSUs/options rather than liquid stock â€” treat the equity portion as speculative. Assuming base near the middle-to-top of the stated range, a ~5-8% target bonus, and a modest new-grad equity grant annualized, realistic first-year cash-weighted TC lands roughly $118k-$142k. Note this is an estimate; the only hard datapoint is the disclosed base range, and the low end of that range would put the role below the candidate's stated ~120k floor.</t>
+          <t>Truveta is a well-funded Seattle health-data startup founded/staffed heavily by ex-Microsoft leadership and benchmarks against Seattle big-tech pay; new-grad SWE offers typically land around $135–155k base plus equity/bonus, putting TC roughly $145–185k. Estimate only — private-company equity value is uncertain, so treat the upper half of the band as loosely held.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -953,7 +941,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -961,11 +949,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>Cohesity_Software_Engineer_New_Grad.pdf</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -981,39 +965,39 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>48</v>
+      <c r="B8" s="4" t="n">
+        <v>74</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>$150k–$190k</t>
+          <t>$180k–$240k</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Photoshop Developer - GPU/Imaging</t>
+          <t>Machine Learning Engineer Graduate - TikTok Vertical Recommendation</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Seattle, WA, SF, San Jose, CA, NYC</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>A legitimately systems-flavored, close-to-the-hardware C++ role that the posting explicitly opens to early-career candidates, but it demands graphics/GPU fundamentals (shaders, WebGPU/Metal/Vulkan, rendering pipelines) that this candidate has zero demonstrated experience with â€” his low-level credibility is Rust storage engines and accelerator inference, not rasterization or compositing.</t>
+          <t>Team sits at the ML/large-scale-distributed-systems intersection and explicitly targets 2027 bachelor's grads, which matches the candidate's timing and systems depth, but the day-to-day is retrieval/ranking model development where he lacks recsys, PyTorch/TensorFlow, and Spark/Flink experience.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Adobe is an upper-tier (near-FAANG) payer for university hires. Typical Adobe new-grad SWE (E2/level 2) in high-cost metros: ~$125â€“145K base, ~10â€“15% target bonus, and roughly $60â€“100K RSUs vesting over 4 years, landing around $150â€“190K first-year TC. All four listed offices (SF, San Jose, Seattle, NYC) sit in Adobe's top geo tier, so the band skews to the upper half. Specialized GPU/graphics work can pull slightly above generic SWE bands. Comfortably above the ~$130K anchor. Estimate only â€” not a quoted figure.</t>
+          <t>Posted base range is $128k-$316.8k; TikTok/ByteDance is a top-tier payer for new grads, with typical MLE-grad offers around $145k-$170k base plus RSUs and discretionary bonus, putting first-year TC in the $180k-$240k range. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1023,7 +1007,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1033,7 +1017,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>Adobe_Photoshop_Developer_GPU_Imaging.pdf</t>
+          <t>TikTok_Machine_Learning_Engineer_Graduate_TikTok_V_7d7baa.pdf</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1051,39 +1035,39 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>47</v>
+      <c r="B9" s="2" t="n">
+        <v>76</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>$150k–$195k</t>
+          <t>$140k–$180k</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Alkira</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Wireless Platform</t>
+          <t>Software Engineer - Datapath</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SF, San Jose, CA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cisco is a strong-tier employer and Nate has the C/C++, Linux, concurrency, and systems fundamentals to be credible, but this is an embedded BSP/board-bring-up/device-driver role (his stated low-fit bucket) posted as an SE2 requiring BS+2yrs with an Aug 2026 application close â€” badly misaligned with a May 2027 backend/distributed-systems new grad.</t>
+          <t>Strong infrastructure/platform-SWE match — Go/Python/C, Linux, AWS/Azure, cloud provisioning at scale, and a debugging-heavy systems role that lines up with Nate's cloud/infra and systems concentration; the main gaps are networking depth (TCP/IP, VNFs, routing) and Ansible, both of which the posting explicitly treats as learnable, and it's orchestration/automation rather than the distributed-systems or AI-infra core he's strongest in.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>The posting itself states a base range of $125,700â€“$176,600 for Bay Area locations. Cisco typically adds ~8â€“12% target bonus plus RSUs worth roughly $15â€“30k/yr at this level, so realistic entry-point TC for an SE2 in SF/San Jose lands around $150kâ€“$195k, with a new grad clustering nearer the low end (~$150â€“165k). Estimate only â€” actual offer depends on level calibration and whether he'd be slotted at SE1 instead.</t>
+          <t>Estimate, not fact. Alkira is a well-funded Bay Area networking startup (Viptela founders) now under Lumen, hiring in San Jose — Bay Area cost-of-labor plus startup equity puts new-grad TC roughly $135–155k base with $10–30k/yr equity and a modest bonus. Wide band because private-company new-grad comp data for Alkira is thin and the post-Lumen comp structure may pull equity toward RSU/cash. Comfortably above the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1093,7 +1077,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1101,11 +1085,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>Cisco_Software_Engineer_2_Wireless_Platform.pdf</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1122,38 +1102,42 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>$78k–$108k</t>
+          <t>$190k–$235k</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>T-Mobile</t>
+          <t>Fortinet</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Associate Engineer - Software</t>
+          <t>Applied AI Engineer - AI Agent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Frisco, TX</t>
+          <t>Sunnyvale, CA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>graduating by summer 2026; summer 2026</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>The work itself (microservices, scalable/highly-available systems, containerization, big-data platforms) maps cleanly onto Nate's backend and infra background, but the posted band tops out at $120.6K base with new-grad offers landing far lower, it's Frisco-TX-onsite with travel, and the Aug 17 2026 close date signals an immediate start rather than a May 2027 new-grad class.</t>
+          <t>Near-ideal skill overlap (backend services, LLM/RAG/agentic systems, event-driven data flows, security domain) but the req is explicitly restricted to candidates graduating by Summer 2026, a year ahead of his May 2027 graduation.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Estimate, not fact. The posting states a $66.9Kâ€“$120.6K base range plus a 10% corporate bonus target; associate/new-grad hires realistically land in the lower-middle of that band (~$72â€“92K base) since the top is reserved for experienced hires in high-cost locations, and Frisco TX is a low-cost hub. Adding the 10% target bonus and T-Mobile's annual stock grant (modest for associate level, roughly $3â€“8K/yr) puts realistic first-year TC around $78Kâ€“$108K. T-Mobile is a non-tech-tier telecom payer, so this sits well below the candidate's $130K anchor.</t>
+          <t>Posting states a base range of $179,500-$220,000 plus equity program participation and discretionary bonus; new grads typically land near the bottom of the base band, so ~$190k is the realistic planning figure. The posted band looks broad enough to span multiple levels rather than being new-grad-specific, so treat the high end as optimistic.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1163,7 +1147,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1171,11 +1155,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>T_Mobile_Associate_Engineer_Software.pdf</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1191,49 +1171,49 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>46</v>
+      <c r="B11" s="2" t="n">
+        <v>78</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>$135k–$180k</t>
+          <t>$100k–$135k</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mach Industries</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Software Engineer New Grad - Software - GNC</t>
+          <t>Software Engineer New Grad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Huntington Beach, CA</t>
+          <t>Burlington, MA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Nate's Rust/C++/C systems depth, concurrency work, and the NOAA AUV real-time onboard-inference project map well onto this autonomy role, but the posting hard-gates on graduating by Jan 2027 (he's May 2027) and centers on embedded/GNC/RTOS work rather than his backend and distributed-systems core.</t>
+          <t>Burlington, MA new-grad SWE at a warehouse-automation company whose core work is large-scale distributed control/backend systems in Java/C++/Python — strong overlap with the candidate's backend and systems strengths and ideal location, docked slightly for robotics/embedded-adjacent leanings and a TC band that sits at the low end of the ~130k anchor.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Estimate, not verified. Mach Industries is a heavily VC-funded (Sequoia/Bridgewater-backed) defense-tech startup in the Anduril/Applied Intuition competitive band, hiring in Huntington Beach, CA. New-grad SWE base at this tier typically runs ~$120-150K, with the posting explicitly noting "highly competitive equity grants" in most offers; annualized equity value pushes realistic TC to roughly $135-180K. Equity is illiquid private stock, so the upper end is paper value, and defense-startup bands vary widely by team and offer negotiation.</t>
+          <t>Symbotic is a public (NASDAQ: SYM) automation/robotics firm, not a top-tier tech payer; Boston-area new-grad SWE base typically ~95-115k plus modest bonus and RSU grant. Band is an estimate with moderate confidence — level and team (control systems vs. cloud platform) could shift it either way.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1241,11 +1221,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>Mach_Industries_Software_Engineer_New_Grad_Software_GNC.pdf</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1262,48 +1238,48 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>$80k–$105k</t>
+          <t>$115k–$150k</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Multiple Teams</t>
+          <t>Product Software Engineer 1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Irving, TX</t>
+          <t>Glendale, CA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Role type is on-profile (new-grad general SWE with backend work, and his Wolters Kluwer clinical-software experience maps directly to Abbott's healthcare domain), but Abbott's device-software orgs skew embedded/regulated rather than distributed systems or AI infra, and the expected comp band falls well below his ~$130K anchor.</t>
+          <t>Solid backend/data-platform new-grad role (Java/Python, pipelines, AWS, Kubernetes/Terraform) that maps well to his cloud-infra and backend strengths, docked slightly for being data-engineering-leaning rather than distributed-systems/AI-infra, fully on-site in Glendale, and a 2026 req that likely starts before his May 2027 graduation.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Abbott is a large-cap medical device/healthcare company, not a tech-tier payer. New-grad "Associate Software Engineer" roles in Irving, TX typically run ~$75-95K base with a small (~5%) annual bonus and modest RSU/none, putting TC around $80-105K. Irving/DFW cost-of-living also depresses the band vs. Boston/NYC. This is a general-knowledge estimate, not verified data, and the posting gives no level or comp signal â€” treat the band as approximate. Notably this sits well below the candidate's ~$130-165K anchor.</t>
+          <t>Disney Entertainment/ESPN Product Technology pays upper-mid-tier (below FAANG, above typical enterprise); CA-posted SWE I base ranges typically land ~$100–135k, plus modest bonus and small/no equity at level 1 — so ~$115–150k TC, at or slightly below his ~$130k anchor.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1311,11 +1287,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>Abbott_Associate_Software_Engineer_Multiple_Teams.pdf</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1331,39 +1303,39 @@
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>47</v>
+      <c r="B13" s="4" t="n">
+        <v>58</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>$80k–$105k</t>
+          <t>$185k–$255k</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>The scraped description is empty (cookie-banner boilerplate only), but RTX/Collins Aerospace's Cedar Rapids SWE 1 roles are overwhelmingly safety-critical avionics/embedded C/C++ work that typically requires US citizenship and clearance eligibility â€” the candidate's C/C++/systems background is genuinely relevant, but the domain, Iowa location, and defense-tier new-grad comp all sit well below his backend/distributed-systems and ~$130K anchor.</t>
+          <t>Excellent timing (explicit 2027 start) and compensation tier, but the role is a research-oriented ML position requiring foundation-model pre/post-training, PyTorch depth, and ideally top-conference publications — whereas the candidate's AI experience is applied/infra-side (RAG, agents, LLM plumbing) on a backend/distributed-systems base.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>No comp data in the posting (description failed to scrape), so this is general-knowledge estimation: RTX/Collins Aerospace is a defense/aerospace prime paying below tech-industry scale, and Cedar Rapids is a low-cost-of-living market. Typical new-grad SWE 1 base runs ~$75-95K with a ~4-8% annual incentive plan and relocation; total first-year comp lands roughly $80-105K. That is materially under the candidate's $130K target and below the stated $120K low-match floor. Treat as an estimate, not fact.</t>
+          <t>Posted base range is $128,000-$316,800; TikTok/ByteDance pays at top-tier (FAANG+) levels for new-grad ML roles, with typical new-grad MLE base ~$145-180k plus signing bonus, annual discretionary bonus, and RSUs. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1383,7 +1355,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>RTX_Software_Engineer_1.pdf</t>
+          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_de90c7.pdf</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -1401,39 +1373,39 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="n">
-        <v>42</v>
+      <c r="B14" s="4" t="n">
+        <v>57</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>$105k–$140k</t>
+          <t>$180k–$245k</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Vector Atomic</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Associate Firmware Engineer - Firmware</t>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pleasanton, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Embedded firmware for atomic/quantum sensing hardware is squarely in the candidate's low-fit bucket (hardware-centric, no distributed-systems or AI-infra surface), though his C/C++, computer-architecture coursework, systems concentration, and real-time onboard-inference project make him a plausible-if-stretched associate-level applicant.</t>
+          <t>Timing (2027 start), US location, and Python/AI-infra exposure line up well, but this is a research-leaning ML role centered on LLM/foundation-model pre-training, multimodal tokenization, and generative recommendation — with publications preferred — which sits outside the candidate's backend/distributed-systems/applied-AI (RAG, agents) core and would make him a stretch against PhD/research-track applicants.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Vector Atomic is a venture/DoD-funded quantum-sensing hardware startup (~100 people, Pleasanton CA) â€” pays competitive Bay Area hardware-startup rates but below big-tech software scales, with meaningful early-stage equity. Posting itself gave no comp data (the "29.2" token is Workable form noise, not a salary), so this is a wide inference band: base roughly $100â€“130k plus small bonus/options. Treat as an estimate, not fact.</t>
+          <t>Posting states base $121.6k–$243.2k for Seattle; TikTok/ByteDance new-grad ML offers typically land around $150–180k base plus RSUs and bonus, putting realistic first-year TC in the ~$180–245k range. ByteDance pays at or above top-tier US big-tech for ML/recsys new grads, so this comfortably clears the ~$130–165k anchor. Estimate only.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1443,7 +1415,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1453,7 +1425,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>Vector_Atomic_Associate_Firmware_Engineer_Firmware.pdf</t>
+          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_b2d143.pdf</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -1471,39 +1443,43 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>45</v>
+      <c r="B15" s="4" t="n">
+        <v>68</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$80k–$115k</t>
+          <t>$125k–$150k</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seagate Technology </t>
+          <t>Cohesity</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Firmware Engineer</t>
+          <t>Software Engineer New Grad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Longmont, CO</t>
+          <t>Santa Clara, CA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>start date and have the legal right to wo</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Embedded firmware in C/C++ sits in this candidate's low-fit bucket and the posted base band tops out well under the ~130K anchor, but his from-scratch LSM-tree/SSTable storage engine, C/C++ coursework, systems-security concentration, and AI/ML project work map unusually well to a storage-firmware NCG role that explicitly wants AI/ML applied to firmware workflows.</t>
+          <t>Near-ideal technical match — distributed systems, storage, and cloud infrastructure work in C/C++/Go/Java/Python, directly aligned with the Raft/LSM-tree/MVCC KV store and backend background — but the posting explicitly targets May/June 2026 graduates (candidate is May 2027) and requires on-site Santa Clara presence, so it's a wrong-cycle req rather than a wrong-profile role.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Posting states base $72,571-$103,784. Seagate is a mature hardware/storage company, not a top-tier comp payer: NCG offers typically land mid-band (~$85-95K base) with a discretionary bonus (~5-10%), ESPP, and little to no RSU grant at new-grad level. Band widened to $80-115K to cover a strong offer at the top of the posted base plus bonus. Estimate, not fact â€” Longmont CO cost-of-labor adjustment likely keeps this below the Boston/NYC-equivalent anchor.</t>
+          <t>Posted base range is $113.4k–$126k (stated in the JD). Cohesity is a large late-stage private infrastructure company, so add bonus plus a private-company RSU grant of roughly $15–30k/yr notional, landing total comp around $125–150k. Note the equity is illiquid/pre-IPO, so realized value is uncertain; cash portion alone sits just under the candidate's ~$130k anchor, and Santa Clara cost-of-living erodes it further.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1513,7 +1489,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1521,11 +1497,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>Seagate_Technology_Firmware_Engineer.pdf</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1541,39 +1513,39 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>36</v>
+      <c r="B16" s="4" t="n">
+        <v>52</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>$85k–$125k</t>
+          <t>$180k–$255k</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AmNet Services</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Software Systems Engineer 3</t>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Warren, NJ</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>The backend/distributed-systems substance is genuinely adjacent (Erlang/BEAM concurrency and fault tolerance map well onto his Raft/Tokio and JMS message-broker work), but the posting is a contract role asking for 7â€“10 years or a *fresh Master's* at a small IoT/telecom firm in Warren, NJ â€” so the level, employment type, and likely sub-$120k comp all miss a May-2027 BS new grad targeting $130â€“165k.</t>
+          <t>Timing (2027 start) and comp tier fit well, but this is a deep ML research role in generative recommendation/LLM/RL where the candidate's backend, distributed-systems, and AI-infra strengths only partially transfer — no recsys, modeling research, or publications.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>AmNet Services / America Networks is a small private IoT sensor + LPWA networking integrator, and this is posted explicitly as a **Contract** role through a staffing-style recruiter (individual recruiter name/cell in the posting). No public comp data exists for this company, so the band is wide and inferred from NJ contract backend rates (~$40â€“60/hr W2 equivalent) at a small non-tier-1 hardware/networking firm. Expect little or no equity, and contract roles typically carry reduced or no benefits/bonus. This is an estimate, not fact â€” and it sits below the candidate's ~$130â€“165k anchor.</t>
+          <t>Posted Seattle base band is $121.6k-$243.2k. TikTok new-grad ML/SWE typically lands base ~$145k-$180k plus ~10-15% bonus and ~$30k-$60k/yr RSU, putting total package around $180k-$255k. Given the candidate lacks the ML research/publication signal that drives the top of the band, realistic landing zone is ~$185k-$210k. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1583,7 +1555,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1593,7 +1565,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>AmNet_Services_Software_Systems_Engineer_3.pdf</t>
+          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_59f20c.pdf</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -1612,38 +1584,38 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>$70k–$95k</t>
+          <t>$190k–$280k</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Securian Financial Group</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Engineering Analyst</t>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>St Paul, MN</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>The work itself is legitimately on-profile (enterprise backend/cloud/application-integration SWE, and Nate's Java Spring + Azure + regulated-industry Wolters Kluwer experience maps cleanly), but the posted band tops out at $103.4k base with new grads landing far below that, plus a hybrid St. Paul, MN requirement and an immediate-start posting that doesn't match a May 2027 graduation â€” comp and timing are the disqualifiers, not skills.</t>
+          <t>2027 start date and Python/LLM-agent exposure align, but the role is a research-oriented ML/recsys position (generative retrieval, RL, LLM post-training, top-tier publications preferred) rather than the backend, distributed-systems, or AI-infrastructure work the candidate is strong in — no deep-learning modeling, PyTorch, or recommender-system background.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Securian Financial is a mid-size mutual insurance/financial-services firm in St. Paul, MN â€” solid but well below tech-industry pay bands. The posting itself gives a base range of $55,700â€“$103,400 for this entry-level "Engineering Analyst" band; new grads realistically land in the lower-middle of that (~$70â€“85k base). Securian adds an unusually strong retirement package (company-funded pension plus a 401(k) contribution targeting ~5% and up to 10% of eligible earnings), so effective total comp runs modestly above base. No equity. Estimate, not fact.</t>
+          <t>Posting states base $128,000-$316,800 for San Jose plus RSUs and discretionary bonus. ByteDance/TikTok is a top-of-market payer for new-grad ML engineers; realistic new-grad base lands ~$150-190k with equity and bonus pushing total comp to roughly $190-280k. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1653,7 +1625,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -1663,7 +1635,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Securian_Financial_Group_Engineering_Analyst.pdf</t>
+          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_40ebe3.pdf</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -1681,39 +1653,39 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="n">
-        <v>28</v>
+      <c r="B18" s="4" t="n">
+        <v>58</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>$70k–$92k</t>
+          <t>$140k–$185k</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>D.R. Horton</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Application Developer 1</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arlington, TX</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>It's a legitimate SWE role and the candidate is well past the 0-1 year bar, but it's an entry-level .NET/C# internal web-app position at a homebuilder in Arlington TX â€” a stack, tier, and comp band (~$70-90k) far below the candidate's backend/distributed-systems/AI-infra target, and it's an immediate-start req rather than a May 2027 new-grad pipeline.</t>
+          <t>Legitimate new-grad SWE role (0-2 yrs) at a hot, well-paying SF company, but it's internal operations tooling — communication-heavy, embedded/consulting work that barely touches the candidate's distributed-systems, infra, or AI-platform strengths.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Estimate, not fact. D.R. Horton is a Fortune 500 homebuilder, not a tech company â€” corporate IT pay in the DFW market for an "Application Developer I" (HS diploma minimum, 0-1 yrs) typically runs ~$65-85k base plus a modest bonus, 401(k) match, and ESPP. Band widened slightly for degree-holder premium. This sits well below the candidate's ~$130-165k anchor and would be a low match on comp alone.</t>
+          <t>Well-funded SF unicorn (~$1B run rate, Handshake AI) that competes for Bay Area new-grad talent; "Associate" title suggests the lower rung of their SWE ladder. Estimated base ~$125-150K plus meaningful equity and 401(k) match. Band is moderately wide since Handshake does not publish new-grad levels and SF startup equity valuation is uncertain.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1723,7 +1695,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -1731,11 +1703,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>D_R_Horton_Application_Developer_1.pdf</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1752,38 +1720,38 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$52k–$75k</t>
+          <t>$230k–$400k</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Trustpilot</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Software Engineer 1 - Trust Tech</t>
+          <t>AI Infrastructure Engineer Graduate - Recommendation &amp; LLM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Backend/AWS/applied-AI content aligns decently, but the role is UK/EU-only (London, Edinburgh, Copenhagen) for a US-authorized candidate with no UK work rights, is an immediate-start Node/TypeScript full-stack SE I rather than a May 2027 new-grad req, and pays far below the ~$130k anchor.</t>
+          <t>The technical domain is a near-perfect match (distributed systems, LLM/AI infrastructure, C++/Python, large-scale training and serving), but the posting is explicitly a PhD-only 2027 graduate req with an onboarding deadline by end of year, which hard-filters a BS/MS May 2027 candidate regardless of skill overlap.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Trustpilot is a FTSE-250 mid-cap (not a top-tier payer). London Software Engineer I bands typically run roughly GBP 40-55k base plus a small bonus, which converts to about USD 52-75k total comp. Estimate only, with wide uncertainty across London junior bands; note this sits well below the candidate's ~130-165k USD anchor, so comp is a low match independent of the location constraint.</t>
+          <t>Posting states base $162k–$387.6k for San Jose plus discretionary bonus and RSUs; TikTok/ByteDance pays top-of-market for PhD AI-infra roles, so realistic PhD new-grad TC lands roughly $230k–$400k. Note this band reflects the PhD level of this req — an equivalent BS/MS new-grad AI-infra role at TikTok would be closer to $160k–$230k TC, still well above the candidate's $130k anchor.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1793,7 +1761,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -1803,7 +1771,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Trustpilot_Software_Engineer_1_Trust_Tech.pdf</t>
+          <t>TikTok_AI_Infrastructure_Engineer_Graduate_Recomme_6aeb33.pdf</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -1821,43 +1789,39 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="n">
-        <v>22</v>
+      <c r="B20" s="4" t="n">
+        <v>55</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>$90k–$115k</t>
+          <t>$100k–$128k</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>General Motors</t>
+          <t>T-Mobile</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Engineer - Software</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Warren, MI</t>
+          <t>Frisco, TX</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>graduating between december 2025</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Hard-blocked by the stated graduation window (Dec 2025â€“Aug 2026 vs. his May 2027 date), and the role is Android/Kotlin HMI infotainment app development in Warren, MI â€” off-profile for a backend/distributed-systems candidate with no Android experience, though his Java, CI/CD, Git, and mobile/POS work at Wayfair are partial overlap.</t>
+          <t>Technical scope (microservices, SDN/NFV, big data, scalable HA systems) overlaps his backend/infra profile, but it's a closely-supervised associate role at a mid-tier payer in a non-preferred location with a near-term start signal, landing below his ~130k TC anchor.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>GM is a traditional automaker (non-tech-tier) hiring entry-level SWEs in Warren, MI â€” a low cost-of-living market. Public new-grad data for GM Warren SWE roles clusters around $85â€“100K base with a ~5â€“10% performance bonus and modest relocation/sign-on. Band widened slightly for level/geo variance. Estimate, not fact.</t>
+          <t>Posting states base $66,900-$120,600 with 10% corporate bonus target; CS new grad likely ~$90-110k base, plus ~10% bonus, annual stock grant and ESPP. T-Mobile is a solid but non-top-tier engineering payer; Frisco cost-of-labor puts a new grad mid-range rather than top. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1867,7 +1831,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -1875,11 +1839,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>General_Motors_Software_Engineer.pdf</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1896,38 +1856,38 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>$43k–$70k</t>
+          <t>$150k–$195k</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Trustpilot</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Software Engineer 1 - Trust Tech</t>
+          <t>Photoshop Developer - GPU/Imaging</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Edinburgh, UK</t>
+          <t>Seattle, WA, SF, San Jose, CA, NYC</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>The backend/AWS/applied-AI content genuinely overlaps Nate's profile, but this is a UK/Copenhagen-based Node+TypeScript full-stack req requiring local work authorization, with Edinburgh-level comp roughly a third of his ~$130k target â€” so the mismatch is location and pay, not skills.</t>
+          <t>Performance/low-level systems orientation is a partial match, but the role centers on GPU graphics programming (shaders, WGSL, Metal/Vulkan/WebGPU, color and compositing pipelines) that is entirely absent from this candidate's backend/distributed-systems/AI-infra background.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Trustpilot is a UK/DK FTSE-250 mid-cap product company, not a US big-tech payer, and this req is based in Edinburgh/London/Copenhagen. Edinburgh SWE I base is typically ~Â£33-45k with a small bonus (London ~Â£45-55k), i.e. roughly $43-60k USD at Edinburgh rates. Even at the London end this lands far below the candidate's ~$130-165k anchor, and there is no US-based version of this req. Estimate only â€” no verified Trustpilot new-grad data points.</t>
+          <t>Adobe is upper-middle big-tech for entry-level SWE in SF/San Jose/Seattle/NYC: roughly $130-150k base + 10-15% target bonus + ~$25-40k/yr RSUs. Band is wide because the posting spans early-career through senior; a new grad would land near the low end. Estimate based on general knowledge of Adobe's comp tier, not verified data.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1937,7 +1897,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -1945,11 +1905,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>Trustpilot_Software_Engineer_1_Trust_Tech.pdf</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1966,38 +1922,38 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>$65k–$90k</t>
+          <t>$140k–$175k</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Software Engineer 2 - Wireless Platform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>SF, San Jose, CA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>The Java/Spring/REST/SQL technical content is a reasonable match for his Wolters Kluwer backend work, but the posting hard-requires an interim SECRET clearance and Security+ certification to begin work â€” an explicit disqualifier on his constraint list â€” and it is a Portland, OR staffing/consultancy contract role whose comp tier sits far below his ~130K anchor.</t>
+          <t>Embedded platform/BSP work (board bring-up, device drivers, boot-time init, UART/SPI/I2C) is squarely in the candidate's low-fit hardware/embedded bucket and the BS+2yrs / MS+0 minimum disfavors a May-2027 bachelor's new grad, though C/C++ plus a systems-security concentration and embedded-Linux debugging overlap give it partial credit.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Estimate only â€” 9to9 Software Solutions is a small Connecticut-based IT staffing/consulting firm with no public comp data, so this is a wide band inferred from the tier. Entry-level Java contract/consulting roles on government-adjacent contracts typically pay $65-90K base with little to no equity and a modest bonus; cleared-work premiums might push the top slightly higher, but body-shop consultancies rarely reach six figures for new grads. This is roughly half the candidate's $130K anchor.</t>
+          <t>Posting states $125,700-$176,600 base for US/Canada new hires at this level, excluding bonus, equity, and benefits. Cisco is a solid mid-to-upper-tier payer (below FAANG/HFT, above most enterprise IT). Assuming an entry-of-band base for a near-new-grad in SF/San Jose (~$130-150k), plus ~10% target bonus and a modest RSU grant, TC lands around $140-175k. Note this is a SWE II req rather than a dedicated new-grad req, so an actual new-grad-equivalent offer could come in nearer the low end or slightly below.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2007,7 +1963,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2015,11 +1971,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>9to9_Software_Solutions_Java_Developer.pdf</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2036,38 +1988,38 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>$62k–$76k</t>
+          <t>$250k–$420k</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Knowledge System Research Scientist Graduate - Data Platform-Global Live</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Off-profile on both stack and comp: it's an onsite San Diego SQL Server/SSIS/Salesforce-Apex rotational data-engineering program paying a flat $30/hr (~$75K TC), far below the candidate's $130K anchor and unrelated to his backend/distributed-systems/AI-infra strengths.</t>
+          <t>Technical content is an excellent match (RAG, agentic systems, vector DBs, knowledge/data platform, distributed systems, Python/Java), but the minimum qualification is a completed or near-complete PhD, which hard-gates a May 2027 bachelor's-level new grad.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>The posting states the pay range explicitly: $30.00/hr flat, which at 2,080 hrs is ~$62.4K base. It adds a discretionary 10% cash bonus target and a 10% RSU target, so full attainment is ~$62.4K + $6.2K + $6.2K â‰ˆ $75K. Low end assumes zero discretionary bonus payout. This is a regional bank's rotational program, not a top-tier tech comp band â€” high confidence in the band since it is quoted directly in the job description.</t>
+          <t>Posting states base $218,400-$480,000 for San Jose, which reflects PhD research-scientist banding rather than a BS/MS new-grad band; adding typical TikTok bonus/RSU on a mid-range base yields roughly $250k-$420k TC. This is an estimate, and it is not the band this candidate would be hired into — TikTok's comparable BS/MS new-grad SWE roles are closer to $145k-$200k TC.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2077,7 +2029,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -2087,7 +2039,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>Axos_Bank_Data_Engineer.pdf</t>
+          <t>TikTok_Data_Knowledge_System_Research_Scientist_Gr_e0c0d2.pdf</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -2106,38 +2058,38 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>$85k–$115k</t>
+          <t>$230k–$350k</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>ByteDance</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Reliability Engineer 2</t>
+          <t>AI/LLM Network Software Development Engineer Graduate - High Speed Network - PhD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chandler, AZ</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>This is an EE-centric semiconductor reliability/qualification role (device physics, transistor-level ICs, HTOL burn-in ovens, lab test equipment, JMP/MATLAB stats) that explicitly targets Electrical/Computer Engineering degrees â€” almost none of the candidate's backend/distributed-systems/AI-infra profile transfers, and the Chandler, AZ semiconductor pay band sits below his ~130K anchor.</t>
+          <t>Timing (2027 start) and the systems/infra domain fit, but the role hard-requires a completed PhD plus specialized high-speed networking research depth (RDMA, congestion control, NCCL/MPI) that a BS-level backend/distributed-systems candidate does not have.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Estimate, not fact. Microchip is a mid-tier semiconductor employer (not a top-paying chip company like NVIDIA/Apple/Qualcomm) in a low-cost Phoenix-metro market. "Engineer II" with 0â€“3 YOE typically lands ~$80â€“100K base, plus a modest bonus and small RSU/ESPP component, putting first-year TC roughly $85â€“115K. Band is somewhat wide because Microchip does not publish new-grad levels and reliability engineering often pays slightly under design/software roles at the same company.</t>
+          <t>Posted base range $153.9k-$300.96k; ByteDance is a top-tier payer and PhD new-grad infra offers typically add substantial RSUs plus bonus on top of a ~$180-220k base. Estimate, not fact — and it reflects the PhD hiring level, not what this candidate would be offered.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2147,7 +2099,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2155,11 +2107,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>Microchip_Technology_Reliability_Engineer_2.pdf</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2176,38 +2124,38 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>$85k–$115k</t>
+          <t>$135k–$180k</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Mach Industries</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Failure Analysis Engineer</t>
+          <t>Software Engineer New Grad - Software - GNC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Acton, MA</t>
+          <t>Huntington Beach, CA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>This is an EE/photonics hands-on hardware role (coherent optical transceiver debug with oscilloscopes, pattern generators, and optical spectrum analyzers) that sits squarely in the candidate's role_fit_low bucket, and the posted $79.2Kâ€“$100.4K base is well below the ~120K floor.</t>
+          <t>Hard eligibility mismatch — the posting requires graduation by end of 2026 or January 2027 and Nate graduates May 2027 — and the role centers on GNC/embedded/real-time firmware rather than his backend/distributed-systems/AI-infra profile, though his Rust, C/C++, Linux, concurrency, and CI/CD background would otherwise be a reasonable partial match.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>The posting states the base range directly: $79,200â€“$100,400. Cisco adds a modest annual bonus and small RSU grant at this level (Supply Chain/Manufacturing Ops bands run below Cisco's SWE bands), so realistic first-year TC lands roughly $85Kâ€“$115K. Acton/Maynard MA would be near the middle-to-upper end of the base band. This is below the candidate's 130K target and below Cisco's own new-grad SWE comp (~$120â€“150K TC).</t>
+          <t>Mach Industries is a well-funded (Sequoia/Bridgewater-backed) defense-tech startup in the Anduril/Applied Intuition orbit; those firms typically pay new-grad SWEs ~$120-150k base in high-COL SoCal plus meaningful early-stage equity, which the posting explicitly says is part of TC. Band is wide because private-startup equity value is speculative and Mach does not publish new-grad levels — this is an estimate, not fact.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2217,7 +2165,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -2225,11 +2173,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>Cisco_Failure_Analysis_Engineer.pdf</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2246,48 +2190,48 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>$58k–$90k</t>
+          <t>$85k–$110k</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Entry Level Java Developer</t>
+          <t>Associate Software Engineer - Multiple Teams</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Elk Grove, CA</t>
+          <t>Irving, TX</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Hard-blocked on the candidate's stated constraints â€” it mandates an interim SECRET clearance to even begin work plus an existing CompTIA Security+ certification, and it's a contract role at a staffing firm in Elk Grove, CA with comp far under the ~$120k floor, despite the Java/Spring/REST/SQL stack itself being a genuine match.</t>
+          <t>Entry-level SWE title is right, but Abbott's software work is medtech/embedded and regulated rather than backend distributed systems or AI infra, and the comp tier falls short of the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Small Connecticut-based IT staffing/consulting body shop placing entry-level developers on government/commercial contracts â€” not a product company, so this is a compensation tier well below Wayfair/big-tech new grad. Posting is explicitly a *Contract* role (likely W2 hourly, possibly limited or no benefits/bonus/equity). Entry-level Java contract rates at firms like this typically run ~$28â€“$45/hr, which annualizes to roughly $58kâ€“$90k; Elk Grove, CA (Sacramento metro) cost-of-living pushes toward the upper end but not much. No public comp data exists for this company, so the band is wide and low-confidence. This is an estimate, not fact â€” and it sits far below the candidate's ~$130k anchor and below the ~$120k "low match" floor.</t>
+          <t>Abbott is a large non-tech medical-device employer; new-grad associate engineer base in Irving, TX typically ~$75-95k plus a small bonus and negligible equity. Posting gave no level or comp detail, so the band is widened; estimate only.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -2295,11 +2239,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>9to9_Software_Solutions_Entry_Level_Java_Developer.pdf</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2316,38 +2256,38 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>$65k–$90k</t>
+          <t>$280k–$450k</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Entry Level Software Developer</t>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall - PhD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Randolph AFB, TX</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Hard-blocked by requirements the candidate cannot meet â€” an interim SECRET clearance plus CompTIA Security+ before start â€” and the work itself is on-site legacy Java/JSP/Oracle web maintenance at an Air Force base in Texas at staffing-firm pay, far off his backend/distributed-systems and comp targets.</t>
+          <t>Role hard-requires a completing/completed PhD with ML research depth in generative recommenders, LLM/RL post-training, and top-tier publications — off-profile for a May 2027 BS-level backend/distributed-systems new grad, despite some adjacent AI/agentic and infra exposure.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Low confidence / wide band: 9to9 Software Solutions is a small Connecticut-based IT staffing and services firm placing entry-level developers on government contracts, not a company with published new-grad bands. Federal-contract entry-level Java developer roles at small primes/subs in the San Antonio, TX market typically pay ~$65k-$85k base with minimal bonus/equity (occasionally a small clearance or certification premium), so effective TC lands well under the candidate's ~$130k anchor. Treat as an estimate, not fact.</t>
+          <t>Posting states base $153,900-$300,960 for Seattle; TikTok/ByteDance PhD MLE offers typically add sizable RSU grants plus discretionary bonus, putting total package well above base. Band is wide because PhD research-track comp varies heavily with publication record and competing offers. Estimate reflects the posted PhD role, not a level this candidate would be hired into.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2357,7 +2297,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2367,7 +2307,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>9to9_Software_Solutions_Entry_Level_Software_Developer.pdf</t>
+          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_1700a5.pdf</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -2386,38 +2326,38 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>$55k–$85k</t>
+          <t>$300k–$550k</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>ByteDance</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Research Engineer Graduate - Seed Infra - PhD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Entry-level Java web contract role at a staffing/consulting firm that hard-requires an interim SECRET clearance plus CompTIA Security+ at start â€” both of which the candidate lacks â€” and the comp tier and generic web-app work sit well below his 130k+ backend/distributed-systems target.</t>
+          <t>The AI-training-infrastructure domain (distributed systems, fault-tolerant infra, GPU cluster scaling) maps well to Nate's Raft/KV-store and ML-infra interests, but the posting is a hard PhD-only requirement with a 2026 onboarding deadline and expects deep LLM/RL training-systems research experience — disqualifying for a May 2027 bachelor's/master's new grad.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions is a small IT staffing/consulting shop (CT-based) placing contract developers on government-adjacent contracts; no public comp data, so this is a wide, low-confidence band. Contract entry-level Java roles in Pittsburgh typically run ~$28-40/hr ($58-83k annualized), often with limited or no equity/bonus and thin benefits on a W2 contract. Cleared work can add a modest premium, but not enough to approach the candidate's 130k anchor.</t>
+          <t>Posted base range is $254.4k–$480k for this San Jose Seed Infra PhD role; adding RSUs and bonus puts realistic first-year TC around $300k–$550k. Note this is PhD-research-engineer compensation at ByteDance's top AI-lab band, not a standard new-grad SWE band (ByteDance new-grad SWE is more like $200–250k TC) — the figures above are not attainable at Nate's level.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2427,7 +2367,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -2435,11 +2375,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>9to9_Software_Solutions_Software_Developer.pdf</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2456,38 +2392,38 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>$55k–$85k</t>
+          <t>$250k–$400k</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Entry Level Software Developer</t>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation - PhD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Copperhill, TN</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Hard-blocked: the posting requires an interim SECRET clearance and CompTIA Security+ to begin work on a contract in rural Copperhill, TN, and it's a legacy Java/JSP staffing-firm contract role â€” off-profile on clearance, comp tier, and timing (candidate graduates May 2027).</t>
+          <t>Hard PhD requirement plus deep ML-research expectations (LLM pre/post-training, generative recommendation, top-tier publications) that a BS-level backend/distributed-systems new grad cannot meet, despite some adjacent applied-AI/RAG experience.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Estimate, not fact. 9to9 Software Solutions is a small CT-based IT staffing/consulting firm; this is a W2/contract government-adjacent Java role in a very low-cost-of-living TN location. Small IT services shops on federal subcontracts typically pay entry-level devs $55k-$85k with minimal bonus/equity. Wide band because no public comp data exists for this firm. This is far below the candidate's ~$130-165k anchor.</t>
+          <t>Posting states base $162k–$387.6k for this PhD ML role; TikTok pays top-of-market for PhD ML/recsys, with RSUs and bonus on top of base — typical PhD new-grad offers land ~$250k–$400k TC (higher for exceptional research profiles). Not applicable to this candidate's BS-level band (~$130–165k).</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2497,7 +2433,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -2507,7 +2443,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>9to9_Software_Solutions_Entry_Level_Software_Developer.pdf</t>
+          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_bfd35d.pdf</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -2526,38 +2462,38 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>$65k–$88k</t>
+          <t>$250k–$350k</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SOSi</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PeopleSoft Software Developer</t>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation - PhD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Charleston, SC</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PeopleSoft/ERP (HCM, Payroll, PeopleTools) development in a 5-day-onsite, Secret-cleared defense facility in Charleston is far off this candidate's backend/distributed-systems/AI-infra profile, and the entry-level defense-contractor comp tier sits well below his ~130K anchor.</t>
+          <t>Hard PhD requirement plus a research profile (LLM pre/post-training, generative recommendation, NeurIPS/ICML-tier publications) that a BS-level backend/distributed-systems candidate cannot satisfy — the AI/RAG experience is applied infra, not foundation-model research.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SOSi is a mid-size private defense/government services integrator; entry-level cleared developer roles in Charleston, SC typically pay base-heavy comp with little/no equity and a small bonus. Estimate based on general government-contractor new-grad tiering plus lower Charleston cost-of-labor rates â€” treat as a wide, low-confidence estimate (I have no specific SOSi salary data).</t>
+          <t>Posting states base $153,900–$300,960 for Seattle; TikTok PhD MLE new-grad offers typically land in the low-to-mid $200k base range plus RSUs (~$40–100k/yr) and bonus, putting realistic total comp for a fresh PhD around $250k–$350k. Band is wide because TikTok's ML research bands are unusually broad and heavily calibrated to publication record.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2567,7 +2503,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -2577,7 +2513,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>SOSi_PeopleSoft_Software_Developer.pdf</t>
+          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_499a7c.pdf</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -2596,38 +2532,38 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>$55k–$80k</t>
+          <t>$200k–$300k</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>ByteDance</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Entry Level Java Developer</t>
+          <t>Video/Image AI/ML Software Engineer Graduate - Multimedia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Silver Creek, NY</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Hard-blocked: the posting requires an existing/interim SECRET clearance and CompTIA Security+ certification (candidate has neither and is a 2027 new grad), and the work is body-shop Java/JSP web development at a staffing firm in rural Silver Creek, NY â€” far below the candidate's distributed-systems/AI-infra profile and ~130k TC anchor.</t>
+          <t>Hard PhD requirement (candidate is a 2027 bachelor's-level new grad) combined with a deeply specialized video codec / image-quality-algorithm domain (VMAF, PSNR, SSIM, AVC/HEVC/AV1, FPGA/ASIC C-models, RTOS/embedded) that has almost no overlap with his distributed-systems, backend, and AI-infra background.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Estimate only â€” 9to9 Software Solutions is a small CT-based IT staffing/consulting firm with no public comp data, so this is a wide, low-confidence band. Cleared entry-level Java contract roles at small integrators in low-cost upstate NY typically pay $55kâ€“$80k base with minimal bonus/equity; a clearance premium might push the top end slightly. This sits roughly $50â€“75k below the candidate's ~$130k anchor.</t>
+          <t>ByteDance is a top-of-market payer; the posting itself lists $122.6k–$301k base for this PhD-level San Diego role, plus RSUs and bonus. PhD new-grad hires typically land in the upper-middle of that band, so ~$200–300k TC is realistic here. Note this is a PhD-track number — a bachelor's new-grad SWE at ByteDance would be closer to $180–230k TC, and this specific req would not be open to him.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2637,7 +2573,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -2645,11 +2581,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>9to9_Software_Solutions_Entry_Level_Java_Developer.pdf</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2666,38 +2598,38 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>$45k–$75k</t>
+          <t>$80k–$105k</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ERPA</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Franklin County, OH</t>
+          <t>Cedar Rapids, IA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>This is a contract "Big Data Training and Placement" staffing/bench-consulting posting from an Oracle ERP body shop targeting candidates with "basic technical skills" who need training â€” it is far below the candidate's level (Wayfair/Wolters Kluwer backend + distributed systems), is a contract rather than a full-time new-grad SWE role, and almost certainly pays well under the ~120k floor.</t>
+          <t>Generic entry-level SWE title is nominally on-profile, but RTX/Collins avionics work in Cedar Rapids skews embedded/safety-critical C rather than distributed systems or AI infra, almost certainly requires clearance eligibility (candidate has none), and the TC ceiling sits well under the ~130k anchor.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Low confidence / wide band. ERP Analysts Inc. is a mid-size Oracle Platinum Partner IT consultancy, and this specific posting is a contract "training and placement" program â€” a staffing model where candidates are trained then billed out to clients. These roles typically pay hourly W2/C2C in the ~$22-35/hr range (~$45-70k annualized) with limited or no bonus/equity, sometimes with training agreements or repayment clauses. Even direct-hire developer roles at Oracle-partner consultancies in Columbus, OH generally land ~$70-90k for new grads, so the upper end here is optimistic. No public leveling or comp data specific to this program.</t>
+          <t>Description body failed to scrape (cookie banner only), so this is based on general knowledge: RTX/Collins Aerospace in Cedar Rapids, IA is defense-primes tier — new-grad SWE 1 base typically ~$75-95k with a small bonus, and low-COL Iowa pulls it further down. Defense primes also commonly gate these roles on US citizenship plus clearance eligibility. Band is wide given the missing posting text.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2707,7 +2639,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -2715,11 +2647,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t>ERPA_Software_Developer.pdf</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2736,38 +2664,38 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>$36k–$55k</t>
+          <t>$95k–$130k</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Valeo Foods</t>
+          <t>Vector Atomic</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Enterprise Applications Developer - Enterprise Applications</t>
+          <t>Associate Firmware Engineer - Firmware</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norwich, UK</t>
+          <t>Pleasanton, CA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>This is a UK-based (Norwich) junior ERP/enterprise-applications role centered on C#, SQL Server, SSRS/Power BI, Power Apps and IFS ERP â€” off-profile for a US-authorized backend/distributed-systems new grad targeting $130K+, both on work-authorization/location and on technical direction.</t>
+          <t>This is an embedded/firmware role at a quantum-hardware company — squarely in the candidate's stated low-fit bucket (hardware/embedded-only, EE-centric), with no backend, distributed-systems, cloud, or AI-infra surface; only the C/C++/Rust overlap and systems concentration keep it from scoring lower, and the on-site Pleasanton requirement plus likely sub-$120k associate-tier comp further weaken the match.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Estimate, not fact. Valeo Foods is a UK/Ireland food manufacturer (PE-backed), not a tech firm; junior/graduate enterprise-app developer roles outside London typically pay roughly Â£28-42K base plus pension/benefits, which converts to about $36-55K USD. Well below the candidate's ~$130-165K anchor, and the posting is UK-only with no visa signal.</t>
+          <t>Vector Atomic is a small deep-tech quantum-sensing startup (atomic clocks/inertial sensors, DoD-adjacent funding), not a big-tech or high-comp software firm. New-grad "Associate" firmware roles there typically land around $95-125k base with modest early-stage equity and limited bonus; the scraped "29.2" in the posting may even hint at an hourly/associate-tier rate, which would push the low end down. Band is wide because private startup comp data for this company is sparse — this is an estimate, not fact.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2777,7 +2705,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2785,11 +2713,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>Valeo_Foods_Enterprise_Applications_Developer_Enterprise_App.pdf</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2806,38 +2730,38 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>$33k–$52k</t>
+          <t>$78k–$108k</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Valeo Foods</t>
+          <t xml:space="preserve">Seagate Technology </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Enterprise Applications Developer - Enterprise Applications</t>
+          <t>Firmware Engineer</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leeds, UK</t>
+          <t>Longmont, CO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>This is a UK-based (Leeds) junior ERP/Microsoft-stack enterprise applications role â€” SQL/C#/Power Apps/SSRS/IFS â€” which is geographically inaccessible to a US-authorized candidate with no stated UK work rights and technically off-profile for a backend/distributed-systems/AI-infra new grad, with comp far below the ~130k anchor.</t>
+          <t>Embedded C/C++ firmware for HDDs is squarely in the candidate's low-fit bucket (hardware-adjacent, EE-centric) despite tangential overlap with his storage-engine/LSM-tree work and C/C++ fluency, and the posted base of $72.6-103.8k sits well below his ~130k anchor.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Estimate only â€” Valeo Foods is a private-equity-backed UK food manufacturer, not a tech-tier employer, and this is an in-house IT/enterprise-apps role in Leeds. Typical UK junior/graduate enterprise developer salaries outside London run roughly Â£26kâ€“Â£40k base with minimal bonus/equity (matched pension only per the posting), converting to roughly $33kâ€“$52k USD. Band is wide because no salary was disclosed and the posting spans "recent graduate" through "junior developer looking for the next challenge." This is well below the candidate's ~130â€“165k target.</t>
+          <t>Posting states base $72,571-$103,784 for Longmont, CO; adding Seagate's discretionary bonus (~5-8%) and ESPP but no meaningful RSU grant at NCG level puts realistic TC in the high-70s to ~108k — hardware-tier compensation, roughly 20-40% under the candidate's target.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2847,7 +2771,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -2855,11 +2779,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t>Valeo_Foods_Enterprise_Applications_Developer_Enterprise_App.pdf</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2876,38 +2796,38 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>$37k–$42k</t>
+          <t>$75k–$95k</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PaperCut</t>
+          <t>Securian Financial Group</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Associate Support Engineer</t>
+          <t>Engineering Analyst</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bracknell, UK</t>
+          <t>St Paul, MN</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Off-profile on nearly every axis: it's a UK-based (Bracknell) frontline customer-support role at ~Â£30k rather than a US backend/distributed-systems SWE position, and the comp is roughly a third of the candidate's ~$130k anchor.</t>
+          <t>Generic entry-level enterprise application/IT engineering role at an insurance carrier — technically adjacent but with no distributed-systems, infra, or AI depth, hybrid-onsite in a non-target metro, and a posted base band whose midpoint sits far below the candidate's ~130k TC anchor.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Posting states "up to GBP 30,000 - yearly" (~$38K USD); band widened for benefits and FX. PaperCut is a mid-size private software vendor, not a top-tier payer, and this is an associate frontline support role â€” well below the ~$120K low-match floor.</t>
+          <t>Posting states base range $55,700–$103,400; a new grad would land in the lower-middle (~$72–85k). Add performance-tied 401k contribution (target 5%, up to 10%) and a company-funded pension; no equity. Midwest insurance-carrier tier — well below FAANG/Wayfair-level new-grad comp.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2917,7 +2837,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -2925,11 +2845,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>PaperCut_Associate_Support_Engineer.pdf</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2946,38 +2862,38 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>$32k–$45k</t>
+          <t>$72k–$95k</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Radius Limited</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Graduate Mobile Developer - Vehicle Telematics</t>
+          <t>Associate Software Engineer 1</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Crewe, UK</t>
+          <t>North Chicago, IL</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Hard disqualifiers stack up: the role is UK-based in Crewe with explicitly no visa sponsorship (candidate is US-authorized only), it's a mobile-first Flutter/Kotlin/Swift position rather than backend/distributed-systems, and the ~$32â€“45k UK graduate comp is far below the ~$130k anchor â€” the only real overlap is REST APIs, Java, and general new-grad status.</t>
+          <t>Generic pharma-IT associate SWE role centered on GxP documentation, vendor estimates, and supervised routine tasks rather than backend/distributed-systems or AI-infra engineering, and the posted comp band sits well below Nate's ~120k floor — the one bright spot is the "agentic workflows and LLMs" preferred qualification, which he over-satisfies.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Radius Limited is a UK private fleet-services/telematics company (~3,000 staff, Crewe HQ). UK graduate developer salaries outside London/at a mid-market firm typically run Â£25kâ€“Â£33k base plus pension/perks (no equity, no meaningful bonus). Converted at ~1.27 USD/GBP that is roughly $32kâ€“$45k USD total comp. This is an estimate from general UK graduate-market knowledge, not posted data.</t>
+          <t>Posting discloses base 58,656–103,500 (Workday grade 12); a zero-experience new grad in North Chicago realistically lands in the lower-middle of that band (~70–88k base), plus a modest short-term incentive (~5–8%) and 401k match. AbbVie is a large-pharma non-tech employer, so software comp tracks internal IT grades rather than tech-industry scales — no equity component typical at this level.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2987,7 +2903,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -2995,11 +2911,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t>Radius_Limited_Graduate_Mobile_Developer_Vehicle_Telematics.pdf</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3016,42 +2928,38 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>$22k–$45k</t>
+          <t>$78k–$105k</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Hawk-Eye Innovations</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Football Tracking Systems Operator - Remote Operations Centre</t>
+          <t>Associate Software Engineer - Multiple Teams</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Basingstoke, UK, Southampton, UK, Reading, UK</t>
+          <t>Irving, TX</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>start date: july</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>This is a UK-based (Basingstoke, in-office, must live locally), casual hourly Â£13â€“18.20 match-day operations technician contract starting July/August 2026 â€” it is not a software engineering role, pays roughly a quarter of the candidate's ~$130k anchor, is geographically and work-authorization incompatible, and conflicts with his May 2027 graduation and current Wayfair co-op.</t>
+          <t>Regulated medical-device C++ work across embedded/desktop/IoT connectivity in a mandatory on-site Irving TX role is well off Nate's backend/distributed-systems/AI-infra profile, and the posted base range tops out below his ~130k TC anchor.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Rate is stated in the posting: Â£13.00â€“Â£18.20/hour on a casual contract with 10â€“12 hour match-day shifts. Annualizing depends entirely on hours actually offered â€” the football calendar makes this seasonal and irregular. At ~25â€“40 paid hours/week that is roughly Â£17kâ€“Â£38k/yr, or about $22kâ€“$48k USD at ~1.27 USD/GBP; I used a wide band because casual hours are unguaranteed. No equity, no new-grad salary structure â€” Hawk-Eye (Sony-owned) does hire salaried engineers, but this specific req is an hourly operator role, not that ladder.</t>
+          <t>Posting states base $50.7k–$101.3k; a new grad realistically lands in the low-to-mid part of that band (~$75–95k base) plus a modest ~5% bonus and strong retirement match typical of Abbott's non-tech-tier medtech comp — TX cost of living keeps offers lower than coastal tech.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3061,7 +2969,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -3069,11 +2977,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>Hawk_Eye_Innovations_Football_Tracking_Systems_Operator_Remo.pdf</t>
-        </is>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3090,38 +2994,38 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>$10k–$35k</t>
+          <t>$70k–$115k</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Lilt</t>
+          <t>AmNet Services</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AI Training Contributor - French</t>
+          <t>Software Systems Engineer 3</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Remote in Canada, Québec City, QC, Canada</t>
+          <t>Warren, NJ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>This is a part-time 1099 gig contract for French-native human annotators in Canada with no benefits, no guaranteed hours, and no engineering scope â€” it is off-profile on role type, comp, geography, and the hard requirement of native French fluency, which the candidate's materials do not evidence.</t>
+          <t>Contract role at a small IoT/sensor networking firm requiring 7-10 years of experience (new grads only via fresh CS Master's), on an Erlang backend with no distributed-systems, cloud, or AI-infra overlap — off-profile on seniority, employment type, and stack despite being nominally "backend."</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Lilt "AI Training Contributor" roles are 1099 piecework/gig engagements, not salaried positions. Typical language-annotation/evaluation rates run roughly $15-40/hr with no guaranteed hours, and the posting itself states it is "not ideal as a full time job or primary income source" with no benefits. Band below is a very rough annualized-equivalent estimate at part-time volume (~10-20 hrs/week) and is highly uncertain; there is no new-grad salary/TC package attached to this role at all.</t>
+          <t>AmNet Services (America Networks) is a small private sensor/networking and staffing-style firm with no public comp tier, so this is a wide, low-confidence band. Posting is explicitly a Contract engagement, which typically means hourly pay (~$40-55/hr for a junior contractor in NJ), no equity, and limited or no benefits. Annualized that lands roughly $85-115k gross at the top end and well below at the bottom — under the candidate's ~$130k anchor and below the ~$120k low-match threshold.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3131,7 +3035,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -3139,11 +3043,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>Lilt_AI_Training_Contributor_French.pdf</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -3160,32 +3060,40 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$72k–$95k</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Barrios</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Associate Software Engineer 1</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>North Chicago, IL</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Off-profile: C#/.NET web-app maintenance at a NASA support contractor in Houston, with clearance-eligibility requirements and gov-contractor pay well under the candidate's ~130k anchor — little overlap with his Rust/Java distributed-systems and AI-infra strengths beyond incidental Docker/K8s/CI-CD exposure.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Estimate only. Barrios Technology is a mid-size NASA/JSC engineering services contractor; government cost-plus contract labor rates put entry-level SWE base around 70-88k in Houston, with minimal bonus/equity (typically none), so TC ≈ base. Band is wide because the posting spans 0-5 YOE and comp data for this employer is sparse.</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>full</t>
@@ -3193,7 +3101,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -3218,32 +3126,40 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$70k–$90k</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>TOMRA</t>
+          <t>D.R. Horton</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Field Service Engineer - London/South East</t>
+          <t>Application Developer 1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Arlington, TX</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Internal .NET/C#/React business-application and legacy-app maintenance work at a homebuilder's corporate IT group, which has essentially no overlap with the candidate's backend/distributed-systems, cloud-infra, or AI-platform focus and sits at a much lower comp and technical tier.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Non-tech Fortune 500 homebuilder; corporate IT cost-center role in the Dallas-Fort Worth market, posting accepts a HS diploma with 0-1 years experience. Estimate assumes ~$70-85k base plus modest bonus/ESPP; band is approximate since D.R. Horton IT comp is not widely reported on levels.fyi.</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>full</t>
@@ -3251,7 +3167,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -3276,32 +3192,40 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$85k–$115k</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Entry Level .NET Developer</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Louisville, CO</t>
+          <t>Anaheim, CA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Hard-blocked: the req demands an active TS/SCI with polygraph on day 1 and is earmarked for an RTX intern converting to full-time, and the C++/Qt/Angular defense-systems work plus sub-$120k band misses both the candidate's clearance-free constraint and TC anchor.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Posting states salary range 62,900–119,700 USD; RTX new-grad SWE offers typically land near the lower-middle of that band (~$85–100k base) plus modest 401k match and small/no annual incentive at level 1. Defense-primes pay well below the candidate's ~$130–165k anchor; cleared work in Anaheim may add a slight premium, hence the top of the band.</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>full</t>
@@ -3309,7 +3233,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -3334,32 +3258,44 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$85k–$115k</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>General Motors</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall - PhD</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Warren, MI</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>graduating between december 2025</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Hard-disqualifying graduation window (Dec 2025–Aug 2026 vs. candidate's May 2027) combined with an Android/Kotlin infotainment HMI focus that sits far from his backend/distributed-systems/AI-infra profile, in a hybrid Warren, MI role paying below his TC floor.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>GM is a non-tech-tier automotive employer; entry-level SWE base in Warren, MI typically ~$80–100k plus modest performance bonus (~5-10%) and relocation, putting TC roughly $85–115k — well below the candidate's ~$130k anchor. Estimate from general knowledge of GM/Big Three new-grad pay in low-cost Midwest markets, not from the posting (no range disclosed).</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>full</t>
@@ -3367,7 +3303,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -3392,32 +3328,40 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$72k–$92k</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Integration Innovation (i3)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation</t>
+          <t>Associate Software Developer - COMPASS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Huntsville, AL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Requires an active/obtainable DoD Secret clearance and on-site residency near Redstone Arsenal with a C#/HTML/CSS stack, all of which conflict with the candidate's stated constraints and backend/distributed-systems strengths, despite some Azure/AWS microservices and event-queue overlap.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Mid-size employee-owned defense/government services contractor (i3) in Huntsville, AL — low cost-of-living market with cost-plus contract rate structures. Typical 0-3 yr associate developer base ~$70-85k plus 401(k) match and ESOP; no equity grant or notable signing bonus. Band is a general-knowledge estimate for the defense-services tier, not verified company data, and falls well below the candidate's ~$130k anchor.</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>full</t>
@@ -3425,7 +3369,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -3450,32 +3394,40 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$45k–$62k</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Trustpilot</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation - PhD</t>
+          <t>Software Engineer 1 - Trust Tech</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Edinburgh, UK</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Backend-adjacent work the candidate could handle, but it is a UK/EU-located role (Edinburgh/London/Copenhagen) he lacks work authorization for, and the Node/TypeScript/React full-stack stack is off his Rust/Java distributed-systems and AI-infra profile.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Trustpilot is a profitable FTSE-250 tech company, not a top-tier payer. Edinburgh/UK graduate-to-SWE I base bands typically run ~£35-48k with a modest bonus, converting to roughly $45-62k USD — well below the candidate's ~$130k anchor. Wide-ish band; UK pay data for this specific level is inferred from general UK market rates rather than verified comp reports.</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>full</t>
@@ -3483,7 +3435,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -3508,32 +3460,40 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$48k–$65k</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Trustpilot</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation - PhD</t>
+          <t>Software Engineer 1 - Trust Tech</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>UK/Denmark-only role (no US location or stated sponsorship) with a Node.js/TypeScript full-stack + React internal-tooling focus, which misses the candidate's Java/Rust/Go backend and distributed-systems profile despite some AWS/Postgres and applied-AI overlap.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Estimate, not fact: Trustpilot is a profitable FTSE-250 mid-tier tech company; London/Edinburgh graduate SWE I base typically ~£38-50k plus a modest bonus, converting to roughly $48-65k USD. UK/EU pay scales sit far below the candidate's ~$130-165k US anchor, so the shortfall is structural rather than negotiable.</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>full</t>
@@ -3541,7 +3501,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -3566,32 +3526,40 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$65k–$90k</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer Graduate - Recommendation &amp; LLM</t>
+          <t>Entry Level .NET Developer</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Louisville, CO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Hard-blocked by the SECRET clearance and Security+ certification requirements, and the work is legacy Java/.NET web-app consulting with no backend-distributed-systems, infra, or AI-platform overlap.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Small IT staffing/consulting firm (Connecticut-based body shop) with no public comp data; estimate based on typical entry-level government-contract staffing pay in a mid-cost Colorado market. Wide band due to unknown company; likely far below the candidate's ~130k anchor.</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>full</t>
@@ -3599,7 +3567,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -3624,32 +3592,40 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$65k–$90k</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Hard disqualifier: the posting requires an interim SECRET clearance to begin work plus existing CompTIA Security+ certification, which the candidate explicitly lacks — and the role itself is legacy full-stack JSP/Hibernate/WebLogic consulting work with graphic-designer/site-design duties, far from backend distributed systems or AI infra, at a comp tier well under the 120k floor.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>9to9 Software Solutions is a small Connecticut-based IT services/staffing consultancy, not a product company — entry-level Java/consulting roles at this tier typically pay near-flat base with minimal bonus or equity. Wide band due to low visibility into this specific firm's pay; Portland, OR cost-of-living offers slight upward pressure but government-contract billing rates cap entry-level comp. Well below the candidate's ~130-165k anchor.</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>full</t>
@@ -3657,7 +3633,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -3682,32 +3658,40 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$60k–$85k</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer Graduate - Recommendation &amp; LLM</t>
+          <t>Entry Level Java Developer</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Silver Creek, NY</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>IT staffing/consulting shop posting a legacy Java web-app contract role that hard-requires an interim SECRET clearance plus Security+ certification — an explicit disqualifier for this candidate — and the work (JSP/WebLogic/Subversion, "site-design instincts") is far below his distributed-systems/AI-infra profile and TC anchor.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>9to9 Software Solutions is a small Connecticut-based IT services/staffing firm with no public compensation data, so this is a wide, low-confidence band inferred from typical entry-level government-contract Java staffing rates (largely base salary, minimal equity or bonus). Well below the candidate's ~130-165k anchor.</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>full</t>
@@ -3715,7 +3699,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -3740,32 +3724,40 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$60k–$85k</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Entry Level Java Developer</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>Elk Grove, CA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Contract staffing role that hard-requires an interim/full SECRET clearance and Security+ certification (both explicit candidate disqualifiers), on legacy JSP/Hibernate/WebLogic web-app work with design responsibilities — off-profile for a backend/distributed-systems new grad and almost certainly below the ~120k TC floor.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>No public comp data for 9to9 Software Solutions — a small CT-based IT staffing/consulting firm. Band inferred from typical entry-level contract Java roles at government-contract body shops (roughly $30–40/hr, little to no bonus or equity). Wide band reflects low confidence and the contract (non-FTE) structure.</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>full</t>
@@ -3773,7 +3765,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -3798,32 +3790,40 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$85k–$110k</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Research Engineer Graduate - Seed Infra - PhD</t>
+          <t>Failure Analysis Engineer</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Acton, MA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>EE/photonics lab failure-analysis role (coherent optical transceivers, oscilloscopes, RF/optical spectrum analyzers) with zero software content, requiring prior hands-on FA experience — squarely in the candidate's hardware/embedded-only low-fit bucket, and the immediate onsite start conflicts with a mid-2027 new-grad timeline.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Posting explicitly states a new-hire base range of $79,200-$100,400; adding a ~5-8% Cisco bonus and a small RSU grant yields roughly $85-110k TC. Cisco's Supply Chain and Manufacturing Ops org pays materially below its SWE ladder, and a new grad would land in the lower half of the posted band, so the realistic center is ~$90k — below the candidate's ~120k low-match floor.</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>full</t>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -3856,32 +3856,40 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$90k–$110k</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Video/Image AI/ML Software Engineer Graduate - Multimedia</t>
+          <t>Reliability Engineer 2</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Chandler, AZ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>This is an EE-centric hardware reliability role (device physics, transistor-level ICs, HTOL burn-in, lab bench equipment, JMP/LabVIEW) with essentially no backend, distributed-systems, or AI-infra content — squarely in the candidate's stated low-fit bucket, and it's an immediate-start req rather than a May 2027 new-grad pipeline.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Microchip is a mid-tier semiconductor employer in a low-cost metro (Chandler, AZ); new-grad/Engineer II reliability roles there typically pay ~$80-95k base plus modest bonus/ESPP/small RSU, landing around $90-110k TC. Estimate based on general semiconductor-industry knowledge, not a verified data point.</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>full</t>
@@ -3889,7 +3897,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -3914,32 +3922,40 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$75k–$95k</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AI/LLM Network Software Development Engineer Graduate - High Speed Network - PhD</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Fort Wayne, IN</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Hard-blocked: the req demands an active DoD Secret clearance from day 1 and is explicitly reserved for an RTX intern converting to full-time, and the Ada/Java C2 work in onsite Fort Wayne at 57–109k misses the candidate's distributed-systems/AI-infra profile and ~130k TC anchor.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Posted range 57.2k–108.8k; RTX defense new-grad SWE typically lands ~75–90k base with small (0–5%) bonus and no equity, and Fort Wayne IN is a low cost-of-living site so offers skew to the lower-middle of the band. Well below the candidate's ~130k anchor.</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>full</t>
@@ -3947,7 +3963,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -3972,32 +3988,40 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$68k–$80k</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Barrios</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SQL Server/SSIS/Salesforce-Apex BI rotational program at ~$75k TC — off-profile for a backend/distributed-systems candidate and far below the ~$130k anchor.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Posting states an explicit flat rate of $30.00/hr (~$62.4k base at 2,080 hrs) plus a 10% discretionary cash bonus target and a 10% discretionary RSU target; band spans low-to-full attainment of both. Consistent with Axos as a mid-size digital bank running a below-market entry-level rotational pipeline rather than a comp-competitive tech employer.</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>full</t>
@@ -4005,7 +4029,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -4030,32 +4054,40 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$60k–$85k</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Data Knowledge System Research Scientist Graduate - Data Platform-Global Live</t>
+          <t>Entry Level Software Developer</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Randolph AFB, TX</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Requires an interim SECRET clearance to start plus Security+ certification (candidate has no clearance — an explicit disqualifier), and the work is legacy Java/JSP/WebLogic/Subversion web development at an IT staffing firm on an Air Force base, with no overlap with the candidate's distributed-systems, cloud-infra, or AI-platform strengths.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>9to9 Software Solutions is a small Connecticut-based IT services/staffing firm placing contractors on government contracts. This tier typically pays far below product-company new-grad bands, and clearance-gated entry-level contract roles rarely carry equity or meaningful bonus. No public comp data for this company, so the band is wide and low-confidence; it falls well under the candidate's ~$120k floor.</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>full</t>
@@ -4063,7 +4095,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -4088,32 +4120,40 @@
         <v>54</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$60k–$90k</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Research Scientist - Seed AI Foundation Model Infrastructure</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Hard-blocked by an explicit interim SECRET clearance + Security+ certification requirement (both listed as minimum quals) that the candidate cannot meet, and the work itself is legacy contract JSP/Hibernate/WebLogic web development at a staffing firm — no overlap with distributed systems, infra, or AI platform work, at contractor-tier pay far below the $130k anchor.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>9to9 Software Solutions is a small IT staffing/consulting body shop, and this is an explicitly Contract (not FTE) government-adjacent role — no equity, likely hourly with little or no bonus. Comparable entry-level contract Java dev rates through such firms run roughly $30-45/hr, i.e. ~$60-90k annualized. Low confidence, wide band; well below the candidate's ~$130k anchor.</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>full</t>
@@ -4121,7 +4161,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -4146,32 +4186,40 @@
         <v>55</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$60k–$85k</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Multiple Teams</t>
+          <t>Entry Level Software Developer</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Irving, TX</t>
+          <t>Copperhill, TN</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Requires an existing interim SECRET clearance and Security+ certification to start (candidate has neither and lists clearance roles as a hard mismatch), and it is a contract legacy Java/JSP/WebLogic web-dev role at a staffing consultancy in rural Copperhill, TN with no distributed-systems, infra, or AI-platform content.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Company is not well known publicly — wide, low-confidence band. 9to9 Software Solutions is a small Connecticut-based IT staffing/services consultancy rather than a product company, and this is explicitly a Contract position, implying an hourly rate with minimal-to-no equity or bonus. Cleared entry-level government-contract Java work in a low-cost rural TN market typically pays in the $60-85k equivalent range, well below the candidate's ~$130-165k anchor and under the ~$120k low-match floor.</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>full</t>
@@ -4179,7 +4227,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -4204,32 +4252,40 @@
         <v>56</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$65k–$85k</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>SOSi</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Software Engineer Graduate - Recommendation</t>
+          <t>PeopleSoft Software Developer</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Charleston, SC</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Hard-blocked by the Secret clearance requirement (an explicit candidate constraint) and the work is PeopleSoft/PeopleCode ERP maintenance — no overlap with backend distributed systems, Rust/systems, or AI infra — plus onsite 5 days in Charleston at roughly half the target TC.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Defense/government services integrator (SOSi) entry-level ERP developer in Charleston, SC — cleared-work government contracting pay bands are well below product-tech; base likely $65-80k with minimal bonus/equity. Wide band due to no public comp data for SOSi.</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>full</t>
@@ -4237,7 +4293,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -4262,32 +4318,40 @@
         <v>57</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$45k–$70k</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>ERPA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Big Data Engineer Graduate - TikTok Recommendation Architecture</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Franklin County, OH</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Contract "training and placement" body-shop posting at an Oracle/PeopleSoft consulting partner targeting candidates with "basic technical skills" — no backend, distributed-systems, or AI-infra content, and the contract/staffing model is far off-profile for this candidate.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>ERP Analysts is a small Oracle Platinum Partner consulting/staffing firm; "training and placement" contract roles are typically hourly W2/C2C with no equity and minimal bonus. Band is wide because comp is unpublished and contract terms vary — estimate based on general IT-staffing/consulting entry-level market rates, not company data. Well below the candidate's ~$130k anchor.</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>full</t>
@@ -4295,7 +4359,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -4320,32 +4384,40 @@
         <v>58</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$35k–$50k</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Valeo Foods</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - TikTok Vertical Recommendation</t>
+          <t>Enterprise Applications Developer - Enterprise Applications</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Leeds, UK</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>UK-based (Leeds) ERP/Power Apps/SSRS enterprise-applications role in a Microsoft low-code stack at a food manufacturer — no backend/distributed-systems or AI-infra content, wrong geography for a US-authorized candidate, immediate start rather than mid-2027, and comp far below the ~$130k anchor.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>UK non-tech-sector (food manufacturing) enterprise applications developer in a regional, non-London market; junior/grad-level Microsoft ERP dev bands in Leeds run roughly £28-38k base, converting to ~$35-50k USD. Benefits listed are largely non-cash (25 days + bank holidays, matched pension, cycle-to-work, staff discount), so total cash comp is close to base. Wide-ish band because no salary was posted and the company is not a known tech-comp benchmark; this is an estimate, not fact.</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>full</t>
@@ -4353,7 +4425,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -4378,32 +4450,40 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$34k–$48k</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Valeo Foods</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Backend Engineer Graduate - TikTok Vertical Recommendation Architecture - 2027 Start</t>
+          <t>Enterprise Applications Developer - Enterprise Applications</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Norwich, UK</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>UK-only (Norwich) internal-IT ERP/low-code role built on C#, SSRS/Power BI, Logic Apps and Power Apps — no overlap with the candidate's backend/distributed-systems/AI-infra profile, and the location is impractical for a US-authorized new grad.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Valeo Foods is a UK food manufacturer, not a tech company; this is an internal enterprise-applications/IT position in Norwich, a low-cost regional UK market. No salary posted, so the band is inferred from typical UK junior enterprise/ERP developer pay outside London (~£27-38k) converted to USD. Wide band, low confidence; well below the candidate's ~$130k anchor.</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>full</t>
@@ -4411,7 +4491,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -4436,32 +4516,40 @@
         <v>60</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$33k–$45k</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Radius Limited</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall</t>
+          <t>Graduate Mobile Developer - Vehicle Telematics</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Crewe, UK</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>UK-only role in Crewe with explicit no-visa-sponsorship and UK right-to-work requirement, focused on cross-platform mobile app development (Flutter/React Native/Kotlin/Swift) — off-profile on both geography/authorization and technical domain for a US-based backend/distributed-systems candidate.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Estimate, not fact. Radius Limited is a mid-market UK fleet services/telematics company (fuel cards, leasing, telecoms), not a tech-tier compensator. Regional graduate developer salaries in Cheshire/North West England typically run roughly £26–35k GBP base with a benefits package (pension, life assurance, fuel card, EV scheme) and little to no equity; converted at ~1.27 USD/GBP that is ~$33–45k USD. Band is wide because the posting states only "competitive salary" with no figure. Note this is GBP-denominated UK comp and not directly comparable to US new-grad TC benchmarks — it sits far below the candidate's ~$130k anchor.</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>full</t>
@@ -4469,7 +4557,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -4494,32 +4582,40 @@
         <v>61</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$44k–$56k</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>TOMRA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall</t>
+          <t>Field Service Engineer - London/South East</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Hands-on electro-mechanical field service role repairing reverse vending machines across London/South East, requiring a full UK driving licence and on-site/rota shift work — zero software engineering overlap with the candidate's backend/distributed-systems/AI-infra profile, and wrong country.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Posting explicitly lists GBP 35,000-41,000/year base; adding 10% non-contributory pension, company bonus, and paid overtime and converting at ~1.27 USD/GBP gives roughly $44k-$56k USD equivalent. UK field-service comp bands are not comparable to US new-grad SWE, and this sits far below the candidate's ~$130k target.</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>full</t>
@@ -4527,7 +4623,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -4552,32 +4648,40 @@
         <v>62</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$36k–$40k</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>PaperCut</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Associate Support Engineer</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN</t>
+          <t>Bracknell, UK</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Frontline customer-support role in Bracknell, UK — not a backend/distributed-systems SWE position, outside the candidate's US work authorization, and capped at ~$38k TC versus a ~$130k anchor.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Posting states "up to GBP 30,000 - yearly"; converted at ~1.27 USD/GBP. PaperCut is a mid-size private print-management vendor, and associate support roles in the UK typically have no meaningful equity component, so base is effectively total comp. Estimate, not fact.</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>full</t>
@@ -4585,7 +4689,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -4610,32 +4714,44 @@
         <v>63</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$20k–$45k</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Hawk-Eye Innovations</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Football Tracking Systems Operator - Remote Operations Centre</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Anaheim, CA</t>
+          <t>Basingstoke, UK, Southampton, UK, Reading, UK</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>start date: july</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>A UK-based, in-office casual hourly shift role operating live Goal Line Technology broadcast systems — not a software engineering position, wrong country, wrong start date (July/August 2026 vs. May 2027 graduation), and pay far below the candidate's floor.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Posting states £13.00–£18.20/hr on a casual contract with 10–12 hour match-day shifts. At ~$1.27/£, full-time-equivalent hours (~2,080) would be roughly $34k–48k; because hours are casual and clustered around the football calendar, realized annual earnings are likely lower, hence the wide $20k–45k band. This is not a salaried new-grad SWE offer and Hawk-Eye (Sony-owned sports tech) does not run this as a graduate engineering pipeline, so no standard new-grad TC benchmark applies. Estimate only, low confidence on total realized comp.</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>full</t>
@@ -4643,7 +4759,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -4668,32 +4784,40 @@
         <v>64</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>$15k–$45k</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Integration Innovation (i3)</t>
+          <t>Lilt</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Associate Software Developer - COMPASS</t>
+          <t>AI Training Contributor - French</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Huntsville, AL</t>
+          <t>Remote in Canada, Québec City, QC, Canada</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>This is a part-time 1099 data-annotation/linguist gig in Canada requiring native French fluency — no software engineering content, no US full-time new-grad path, and nothing touching the candidate's backend/distributed-systems/AI-infra profile.</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Not a salaried role — Lilt pays AI-training contractors hourly/per-task (typically ~$15-30/hr USD equivalent) with no benefits and no guaranteed hours; the posting explicitly says it is unsuitable as primary income. Band shown is a rough annualized figure assuming the stated 10+ hrs/week minimum up to near-full-time utilization, and is highly uncertain. Far below the ~$130k anchor.</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>full</t>
@@ -4701,7 +4825,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>error:'charmap' codec can't encode c</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
@@ -4730,164 +4854,141 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId142"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/tailored_resumes.xlsx
+++ b/output/tailored_resumes.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1155,7 +1155,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Fortinet_Applied_AI_Engineer_AI_Agent_bf9f59.pdf</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1213,7 +1217,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1221,7 +1225,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Symbotic_Software_Engineer_New_Grad_81ed4e.pdf</t>
+        </is>
+      </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -4869,126 +4877,128 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId144"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/tailored_resumes.xlsx
+++ b/output/tailored_resumes.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P65"/>
+  <dimension ref="A1:P68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1175,44 +1175,44 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>78</v>
+      <c r="B11" s="4" t="n">
+        <v>74</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>$100k–$135k</t>
+          <t>$140k–$175k</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Software Engineer New Grad</t>
+          <t>Software Engineer - Information Systems and Technology - Early Career</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Burlington, MA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Burlington, MA new-grad SWE at a warehouse-automation company whose core work is large-scale distributed control/backend systems in Java/C++/Python — strong overlap with the candidate's backend and systems strengths and ideal location, docked slightly for robotics/embedded-adjacent leanings and a TC band that sits at the low end of the ~130k anchor.</t>
+          <t>Strong on-profile match — the posting explicitly lists Backend SWE and SRE tracks with Java/Python plus AWS/GCP preferred, which maps directly onto the candidate's microservices and cloud/infra strengths — but it's a generic IS&amp;T requisition weighted toward enterprise/internal systems (SAP, BI, retail tooling) rather than the low-level distributed-systems or AI-infra work the candidate is strongest in, and team assignment is out of his control; timing works since the Aug 2026 posting targets 2027 early-career starts.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Symbotic is a public (NASDAQ: SYM) automation/robotics firm, not a top-tier tech payer; Boston-area new-grad SWE base typically ~95-115k plus modest bonus and RSU grant. Band is an estimate with moderate confidence — level and team (control systems vs. cloud platform) could shift it either way.</t>
+          <t>Apple ICT2 new-grad software engineering, adjusted down for Austin vs Bay Area and for IS&amp;T (typically at or slightly below the core-OS/silicon bands): base roughly $115–140k, first-year RSU value roughly $15–25k (4-yr vest on a ~$60–100k grant), plus ~10% target bonus and a signing bonus. Apple's leveling is fairly consistent, so the band is moderately tight; IS&amp;T-specific data is thinner than for core engineering orgs, so treat the low end as more likely for enterprise/BI/SAP teams and the high end for Infrastructure Services / SRE-type placements.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>Symbotic_Software_Engineer_New_Grad_81ed4e.pdf</t>
+          <t>Apple_Software_Engineer_Information_Systems_and_Te_8039e5.pdf</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1245,49 +1245,49 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>73</v>
+      <c r="B12" s="2" t="n">
+        <v>78</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>$115k–$150k</t>
+          <t>$100k–$135k</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Product Software Engineer 1</t>
+          <t>Software Engineer New Grad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Glendale, CA</t>
+          <t>Burlington, MA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Solid backend/data-platform new-grad role (Java/Python, pipelines, AWS, Kubernetes/Terraform) that maps well to his cloud-infra and backend strengths, docked slightly for being data-engineering-leaning rather than distributed-systems/AI-infra, fully on-site in Glendale, and a 2026 req that likely starts before his May 2027 graduation.</t>
+          <t>Burlington, MA new-grad SWE at a warehouse-automation company whose core work is large-scale distributed control/backend systems in Java/C++/Python — strong overlap with the candidate's backend and systems strengths and ideal location, docked slightly for robotics/embedded-adjacent leanings and a TC band that sits at the low end of the ~130k anchor.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Disney Entertainment/ESPN Product Technology pays upper-mid-tier (below FAANG, above typical enterprise); CA-posted SWE I base ranges typically land ~$100–135k, plus modest bonus and small/no equity at level 1 — so ~$115–150k TC, at or slightly below his ~$130k anchor.</t>
+          <t>Symbotic is a public (NASDAQ: SYM) automation/robotics firm, not a top-tier tech payer; Boston-area new-grad SWE base typically ~95-115k plus modest bonus and RSU grant. Band is an estimate with moderate confidence — level and team (control systems vs. cloud platform) could shift it either way.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1295,7 +1295,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Symbotic_Software_Engineer_New_Grad_81ed4e.pdf</t>
+        </is>
+      </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1312,38 +1316,38 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>$185k–$255k</t>
+          <t>$115k–$150k</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation</t>
+          <t>Product Software Engineer 1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Glendale, CA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Excellent timing (explicit 2027 start) and compensation tier, but the role is a research-oriented ML position requiring foundation-model pre/post-training, PyTorch depth, and ideally top-conference publications — whereas the candidate's AI experience is applied/infra-side (RAG, agents, LLM plumbing) on a backend/distributed-systems base.</t>
+          <t>Solid backend/data-platform new-grad role (Java/Python, pipelines, AWS, Kubernetes/Terraform) that maps well to his cloud-infra and backend strengths, docked slightly for being data-engineering-leaning rather than distributed-systems/AI-infra, fully on-site in Glendale, and a 2026 req that likely starts before his May 2027 graduation.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Posted base range is $128,000-$316,800; TikTok/ByteDance pays at top-tier (FAANG+) levels for new-grad ML roles, with typical new-grad MLE base ~$145-180k plus signing bonus, annual discretionary bonus, and RSUs. Estimate, not fact.</t>
+          <t>Disney Entertainment/ESPN Product Technology pays upper-mid-tier (below FAANG, above typical enterprise); CA-posted SWE I base ranges typically land ~$100–135k, plus modest bonus and small/no equity at level 1 — so ~$115–150k TC, at or slightly below his ~$130k anchor.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1353,7 +1357,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>tailored</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1361,11 +1365,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_de90c7.pdf</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1382,11 +1382,11 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>$180k–$245k</t>
+          <t>$185k–$255k</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1401,19 +1401,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Timing (2027 start), US location, and Python/AI-infra exposure line up well, but this is a research-leaning ML role centered on LLM/foundation-model pre-training, multimodal tokenization, and generative recommendation — with publications preferred — which sits outside the candidate's backend/distributed-systems/applied-AI (RAG, agents) core and would make him a stretch against PhD/research-track applicants.</t>
+          <t>Excellent timing (explicit 2027 start) and compensation tier, but the role is a research-oriented ML position requiring foundation-model pre/post-training, PyTorch depth, and ideally top-conference publications — whereas the candidate's AI experience is applied/infra-side (RAG, agents, LLM plumbing) on a backend/distributed-systems base.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Posting states base $121.6k–$243.2k for Seattle; TikTok/ByteDance new-grad ML offers typically land around $150–180k base plus RSUs and bonus, putting realistic first-year TC in the ~$180–245k range. ByteDance pays at or above top-tier US big-tech for ML/recsys new grads, so this comfortably clears the ~$130–165k anchor. Estimate only.</t>
+          <t>Posted base range is $128,000-$316,800; TikTok/ByteDance pays at top-tier (FAANG+) levels for new-grad ML roles, with typical new-grad MLE base ~$145-180k plus signing bonus, annual discretionary bonus, and RSUs. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_b2d143.pdf</t>
+          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_de90c7.pdf</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -1452,42 +1452,38 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$125k–$150k</t>
+          <t>$180k–$245k</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cohesity</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Software Engineer New Grad</t>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Santa Clara, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>start date and have the legal right to wo</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Near-ideal technical match — distributed systems, storage, and cloud infrastructure work in C/C++/Go/Java/Python, directly aligned with the Raft/LSM-tree/MVCC KV store and backend background — but the posting explicitly targets May/June 2026 graduates (candidate is May 2027) and requires on-site Santa Clara presence, so it's a wrong-cycle req rather than a wrong-profile role.</t>
+          <t>Timing (2027 start), US location, and Python/AI-infra exposure line up well, but this is a research-leaning ML role centered on LLM/foundation-model pre-training, multimodal tokenization, and generative recommendation — with publications preferred — which sits outside the candidate's backend/distributed-systems/applied-AI (RAG, agents) core and would make him a stretch against PhD/research-track applicants.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Posted base range is $113.4k–$126k (stated in the JD). Cohesity is a large late-stage private infrastructure company, so add bonus plus a private-company RSU grant of roughly $15–30k/yr notional, landing total comp around $125–150k. Note the equity is illiquid/pre-IPO, so realized value is uncertain; cash portion alone sits just under the candidate's ~$130k anchor, and Santa Clara cost-of-living erodes it further.</t>
+          <t>Posting states base $121.6k–$243.2k for Seattle; TikTok/ByteDance new-grad ML offers typically land around $150–180k base plus RSUs and bonus, putting realistic first-year TC in the ~$180–245k range. ByteDance pays at or above top-tier US big-tech for ML/recsys new grads, so this comfortably clears the ~$130–165k anchor. Estimate only.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1497,7 +1493,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1505,7 +1501,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_b2d143.pdf</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1522,38 +1522,42 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>$180k–$255k</t>
+          <t>$125k–$150k</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Cohesity</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall</t>
+          <t>Software Engineer New Grad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Santa Clara, CA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>start date and have the legal right to wo</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Timing (2027 start) and comp tier fit well, but this is a deep ML research role in generative recommendation/LLM/RL where the candidate's backend, distributed-systems, and AI-infra strengths only partially transfer — no recsys, modeling research, or publications.</t>
+          <t>Near-ideal technical match — distributed systems, storage, and cloud infrastructure work in C/C++/Go/Java/Python, directly aligned with the Raft/LSM-tree/MVCC KV store and backend background — but the posting explicitly targets May/June 2026 graduates (candidate is May 2027) and requires on-site Santa Clara presence, so it's a wrong-cycle req rather than a wrong-profile role.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Posted Seattle base band is $121.6k-$243.2k. TikTok new-grad ML/SWE typically lands base ~$145k-$180k plus ~10-15% bonus and ~$30k-$60k/yr RSU, putting total package around $180k-$255k. Given the candidate lacks the ML research/publication signal that drives the top of the band, realistic landing zone is ~$185k-$210k. Estimate, not fact.</t>
+          <t>Posted base range is $113.4k–$126k (stated in the JD). Cohesity is a large late-stage private infrastructure company, so add bonus plus a private-company RSU grant of roughly $15–30k/yr notional, landing total comp around $125–150k. Note the equity is illiquid/pre-IPO, so realized value is uncertain; cash portion alone sits just under the candidate's ~$130k anchor, and Santa Clara cost-of-living erodes it further.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1563,7 +1567,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>tailored</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1571,11 +1575,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_59f20c.pdf</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1591,12 +1591,12 @@
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>45</v>
+      <c r="B17" s="4" t="n">
+        <v>52</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>$190k–$280k</t>
+          <t>$180k–$255k</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1611,19 +1611,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2027 start date and Python/LLM-agent exposure align, but the role is a research-oriented ML/recsys position (generative retrieval, RL, LLM post-training, top-tier publications preferred) rather than the backend, distributed-systems, or AI-infrastructure work the candidate is strong in — no deep-learning modeling, PyTorch, or recommender-system background.</t>
+          <t>Timing (2027 start) and comp tier fit well, but this is a deep ML research role in generative recommendation/LLM/RL where the candidate's backend, distributed-systems, and AI-infra strengths only partially transfer — no recsys, modeling research, or publications.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Posting states base $128,000-$316,800 for San Jose plus RSUs and discretionary bonus. ByteDance/TikTok is a top-of-market payer for new-grad ML engineers; realistic new-grad base lands ~$150-190k with equity and bonus pushing total comp to roughly $190-280k. Estimate, not fact.</t>
+          <t>Posted Seattle base band is $121.6k-$243.2k. TikTok new-grad ML/SWE typically lands base ~$145k-$180k plus ~10-15% bonus and ~$30k-$60k/yr RSU, putting total package around $180k-$255k. Given the candidate lacks the ML research/publication signal that drives the top of the band, realistic landing zone is ~$185k-$210k. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_40ebe3.pdf</t>
+          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_59f20c.pdf</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -1661,39 +1661,39 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="n">
-        <v>58</v>
+      <c r="B18" s="5" t="n">
+        <v>45</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>$140k–$185k</t>
+          <t>$190k–$280k</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Legitimate new-grad SWE role (0-2 yrs) at a hot, well-paying SF company, but it's internal operations tooling — communication-heavy, embedded/consulting work that barely touches the candidate's distributed-systems, infra, or AI-platform strengths.</t>
+          <t>2027 start date and Python/LLM-agent exposure align, but the role is a research-oriented ML/recsys position (generative retrieval, RL, LLM post-training, top-tier publications preferred) rather than the backend, distributed-systems, or AI-infrastructure work the candidate is strong in — no deep-learning modeling, PyTorch, or recommender-system background.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Well-funded SF unicorn (~$1B run rate, Handshake AI) that competes for Bay Area new-grad talent; "Associate" title suggests the lower rung of their SWE ladder. Estimated base ~$125-150K plus meaningful equity and 401(k) match. Band is moderately wide since Handshake does not publish new-grad levels and SF startup equity valuation is uncertain.</t>
+          <t>Posting states base $128,000-$316,800 for San Jose plus RSUs and discretionary bonus. ByteDance/TikTok is a top-of-market payer for new-grad ML engineers; realistic new-grad base lands ~$150-190k with equity and bonus pushing total comp to roughly $190-280k. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -1711,7 +1711,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_40ebe3.pdf</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1727,39 +1731,39 @@
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="n">
-        <v>32</v>
+      <c r="B19" s="4" t="n">
+        <v>58</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$230k–$400k</t>
+          <t>$140k–$185k</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer Graduate - Recommendation &amp; LLM</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>The technical domain is a near-perfect match (distributed systems, LLM/AI infrastructure, C++/Python, large-scale training and serving), but the posting is explicitly a PhD-only 2027 graduate req with an onboarding deadline by end of year, which hard-filters a BS/MS May 2027 candidate regardless of skill overlap.</t>
+          <t>Legitimate new-grad SWE role (0-2 yrs) at a hot, well-paying SF company, but it's internal operations tooling — communication-heavy, embedded/consulting work that barely touches the candidate's distributed-systems, infra, or AI-platform strengths.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Posting states base $162k–$387.6k for San Jose plus discretionary bonus and RSUs; TikTok/ByteDance pays top-of-market for PhD AI-infra roles, so realistic PhD new-grad TC lands roughly $230k–$400k. Note this band reflects the PhD level of this req — an equivalent BS/MS new-grad AI-infra role at TikTok would be closer to $160k–$230k TC, still well above the candidate's $130k anchor.</t>
+          <t>Well-funded SF unicorn (~$1B run rate, Handshake AI) that competes for Bay Area new-grad talent; "Associate" title suggests the lower rung of their SWE ladder. Estimated base ~$125-150K plus meaningful equity and 401(k) match. Band is moderately wide since Handshake does not publish new-grad levels and SF startup equity valuation is uncertain.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1769,7 +1773,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>tailored</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -1777,11 +1781,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>TikTok_AI_Infrastructure_Engineer_Graduate_Recomme_6aeb33.pdf</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1797,39 +1797,39 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="n">
-        <v>55</v>
+      <c r="B20" s="5" t="n">
+        <v>32</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>$100k–$128k</t>
+          <t>$230k–$400k</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>T-Mobile</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Associate Engineer - Software</t>
+          <t>AI Infrastructure Engineer Graduate - Recommendation &amp; LLM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Frisco, TX</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Technical scope (microservices, SDN/NFV, big data, scalable HA systems) overlaps his backend/infra profile, but it's a closely-supervised associate role at a mid-tier payer in a non-preferred location with a near-term start signal, landing below his ~130k TC anchor.</t>
+          <t>The technical domain is a near-perfect match (distributed systems, LLM/AI infrastructure, C++/Python, large-scale training and serving), but the posting is explicitly a PhD-only 2027 graduate req with an onboarding deadline by end of year, which hard-filters a BS/MS May 2027 candidate regardless of skill overlap.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Posting states base $66,900-$120,600 with 10% corporate bonus target; CS new grad likely ~$90-110k base, plus ~10% bonus, annual stock grant and ESPP. T-Mobile is a solid but non-top-tier engineering payer; Frisco cost-of-labor puts a new grad mid-range rather than top. Estimate, not fact.</t>
+          <t>Posting states base $162k–$387.6k for San Jose plus discretionary bonus and RSUs; TikTok/ByteDance pays top-of-market for PhD AI-infra roles, so realistic PhD new-grad TC lands roughly $230k–$400k. Note this band reflects the PhD level of this req — an equivalent BS/MS new-grad AI-infra role at TikTok would be closer to $160k–$230k TC, still well above the candidate's $130k anchor.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -1847,7 +1847,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>TikTok_AI_Infrastructure_Engineer_Graduate_Recomme_6aeb33.pdf</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -1863,39 +1867,39 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="n">
-        <v>45</v>
+      <c r="B21" s="4" t="n">
+        <v>55</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>$150k–$195k</t>
+          <t>$100k–$128k</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>T-Mobile</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Photoshop Developer - GPU/Imaging</t>
+          <t>Associate Engineer - Software</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Seattle, WA, SF, San Jose, CA, NYC</t>
+          <t>Frisco, TX</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Performance/low-level systems orientation is a partial match, but the role centers on GPU graphics programming (shaders, WGSL, Metal/Vulkan/WebGPU, color and compositing pipelines) that is entirely absent from this candidate's backend/distributed-systems/AI-infra background.</t>
+          <t>Technical scope (microservices, SDN/NFV, big data, scalable HA systems) overlaps his backend/infra profile, but it's a closely-supervised associate role at a mid-tier payer in a non-preferred location with a near-term start signal, landing below his ~130k TC anchor.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Adobe is upper-middle big-tech for entry-level SWE in SF/San Jose/Seattle/NYC: roughly $130-150k base + 10-15% target bonus + ~$25-40k/yr RSUs. Band is wide because the posting spans early-career through senior; a new grad would land near the low end. Estimate based on general knowledge of Adobe's comp tier, not verified data.</t>
+          <t>Posting states base $66,900-$120,600 with 10% corporate bonus target; CS new grad likely ~$90-110k base, plus ~10% bonus, annual stock grant and ESPP. T-Mobile is a solid but non-top-tier engineering payer; Frisco cost-of-labor puts a new grad mid-range rather than top. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1934,34 +1938,34 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>$140k–$175k</t>
+          <t>$150k–$195k</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Wireless Platform</t>
+          <t>Photoshop Developer - GPU/Imaging</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SF, San Jose, CA</t>
+          <t>Seattle, WA, SF, San Jose, CA, NYC</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Embedded platform/BSP work (board bring-up, device drivers, boot-time init, UART/SPI/I2C) is squarely in the candidate's low-fit hardware/embedded bucket and the BS+2yrs / MS+0 minimum disfavors a May-2027 bachelor's new grad, though C/C++ plus a systems-security concentration and embedded-Linux debugging overlap give it partial credit.</t>
+          <t>Performance/low-level systems orientation is a partial match, but the role centers on GPU graphics programming (shaders, WGSL, Metal/Vulkan/WebGPU, color and compositing pipelines) that is entirely absent from this candidate's backend/distributed-systems/AI-infra background.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Posting states $125,700-$176,600 base for US/Canada new hires at this level, excluding bonus, equity, and benefits. Cisco is a solid mid-to-upper-tier payer (below FAANG/HFT, above most enterprise IT). Assuming an entry-of-band base for a near-new-grad in SF/San Jose (~$130-150k), plus ~10% target bonus and a modest RSU grant, TC lands around $140-175k. Note this is a SWE II req rather than a dedicated new-grad req, so an actual new-grad-equivalent offer could come in nearer the low end or slightly below.</t>
+          <t>Adobe is upper-middle big-tech for entry-level SWE in SF/San Jose/Seattle/NYC: roughly $130-150k base + 10-15% target bonus + ~$25-40k/yr RSUs. Band is wide because the posting spans early-career through senior; a new grad would land near the low end. Estimate based on general knowledge of Adobe's comp tier, not verified data.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1996,38 +2000,38 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>$250k–$420k</t>
+          <t>$140k–$175k</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Knowledge System Research Scientist Graduate - Data Platform-Global Live</t>
+          <t>Software Engineer 2 - Wireless Platform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>SF, San Jose, CA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Technical content is an excellent match (RAG, agentic systems, vector DBs, knowledge/data platform, distributed systems, Python/Java), but the minimum qualification is a completed or near-complete PhD, which hard-gates a May 2027 bachelor's-level new grad.</t>
+          <t>Embedded platform/BSP work (board bring-up, device drivers, boot-time init, UART/SPI/I2C) is squarely in the candidate's low-fit hardware/embedded bucket and the BS+2yrs / MS+0 minimum disfavors a May-2027 bachelor's new grad, though C/C++ plus a systems-security concentration and embedded-Linux debugging overlap give it partial credit.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Posting states base $218,400-$480,000 for San Jose, which reflects PhD research-scientist banding rather than a BS/MS new-grad band; adding typical TikTok bonus/RSU on a mid-range base yields roughly $250k-$420k TC. This is an estimate, and it is not the band this candidate would be hired into — TikTok's comparable BS/MS new-grad SWE roles are closer to $145k-$200k TC.</t>
+          <t>Posting states $125,700-$176,600 base for US/Canada new hires at this level, excluding bonus, equity, and benefits. Cisco is a solid mid-to-upper-tier payer (below FAANG/HFT, above most enterprise IT). Assuming an entry-of-band base for a near-new-grad in SF/San Jose (~$130-150k), plus ~10% target bonus and a modest RSU grant, TC lands around $140-175k. Note this is a SWE II req rather than a dedicated new-grad req, so an actual new-grad-equivalent offer could come in nearer the low end or slightly below.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2037,7 +2041,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>tailored</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -2045,11 +2049,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>TikTok_Data_Knowledge_System_Research_Scientist_Gr_e0c0d2.pdf</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2066,38 +2066,38 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>$230k–$350k</t>
+          <t>$250k–$420k</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI/LLM Network Software Development Engineer Graduate - High Speed Network - PhD</t>
+          <t>Data Knowledge System Research Scientist Graduate - Data Platform-Global Live</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Timing (2027 start) and the systems/infra domain fit, but the role hard-requires a completed PhD plus specialized high-speed networking research depth (RDMA, congestion control, NCCL/MPI) that a BS-level backend/distributed-systems candidate does not have.</t>
+          <t>Technical content is an excellent match (RAG, agentic systems, vector DBs, knowledge/data platform, distributed systems, Python/Java), but the minimum qualification is a completed or near-complete PhD, which hard-gates a May 2027 bachelor's-level new grad.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Posted base range $153.9k-$300.96k; ByteDance is a top-tier payer and PhD new-grad infra offers typically add substantial RSUs plus bonus on top of a ~$180-220k base. Estimate, not fact — and it reflects the PhD hiring level, not what this candidate would be offered.</t>
+          <t>Posting states base $218,400-$480,000 for San Jose, which reflects PhD research-scientist banding rather than a BS/MS new-grad band; adding typical TikTok bonus/RSU on a mid-range base yields roughly $250k-$420k TC. This is an estimate, and it is not the band this candidate would be hired into — TikTok's comparable BS/MS new-grad SWE roles are closer to $145k-$200k TC.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2115,7 +2115,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>TikTok_Data_Knowledge_System_Research_Scientist_Gr_e0c0d2.pdf</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2132,38 +2136,38 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>$135k–$180k</t>
+          <t>$160k–$230k</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mach Industries</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Software Engineer New Grad - Software - GNC</t>
+          <t>Software Engineer - Early Career</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Huntington Beach, CA</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Hard eligibility mismatch — the posting requires graduation by end of 2026 or January 2027 and Nate graduates May 2027 — and the role centers on GNC/embedded/real-time firmware rather than his backend/distributed-systems/AI-infra profile, though his Rust, C/C++, Linux, concurrency, and CI/CD background would otherwise be a reasonable partial match.</t>
+          <t>Comp, tier, and NYC location are excellent fits, but the posting hard-gates on a degree completed between December 2024 and September 2026 while the candidate graduates May 2027, making him ineligible for this cohort; the role is also full-stack/web-leaning rather than backend/distributed-systems focused.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Mach Industries is a well-funded (Sequoia/Bridgewater-backed) defense-tech startup in the Anduril/Applied Intuition orbit; those firms typically pay new-grad SWEs ~$120-150k base in high-COL SoCal plus meaningful early-stage equity, which the posting explicitly says is part of TC. Band is wide because private-startup equity value is speculative and Mach does not publish new-grad levels — this is an estimate, not fact.</t>
+          <t>Posted NYC base range is $138,400-$198,000; a new grad would land near the low end (~$138-155k base). Uniswap Labs is a well-funded crypto/DeFi employer paying at or above top-tier tech, and the posting explicitly lists token compensation plus benefits on top of base. The band is intentionally wide on the upper end because token grant sizing and valuation are undisclosed and volatile. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2173,7 +2177,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -2181,7 +2185,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Uniswap_Software_Engineer_Early_Career_5a340c.pdf</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2198,43 +2206,43 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>$85k–$110k</t>
+          <t>$230k–$350k</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>ByteDance</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Multiple Teams</t>
+          <t>AI/LLM Network Software Development Engineer Graduate - High Speed Network - PhD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Irving, TX</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Entry-level SWE title is right, but Abbott's software work is medtech/embedded and regulated rather than backend distributed systems or AI infra, and the comp tier falls short of the candidate's ~130k anchor.</t>
+          <t>Timing (2027 start) and the systems/infra domain fit, but the role hard-requires a completed PhD plus specialized high-speed networking research depth (RDMA, congestion control, NCCL/MPI) that a BS-level backend/distributed-systems candidate does not have.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Abbott is a large non-tech medical-device employer; new-grad associate engineer base in Irving, TX typically ~$75-95k plus a small bonus and negligible equity. Posting gave no level or comp detail, so the band is widened; estimate only.</t>
+          <t>Posted base range $153.9k-$300.96k; ByteDance is a top-tier payer and PhD new-grad infra offers typically add substantial RSUs plus bonus on top of a ~$180-220k base. Estimate, not fact — and it reflects the PhD hiring level, not what this candidate would be offered.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2264,38 +2272,38 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>$280k–$450k</t>
+          <t>$135k–$180k</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Mach Industries</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall - PhD</t>
+          <t>Software Engineer New Grad - Software - GNC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Huntington Beach, CA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Role hard-requires a completing/completed PhD with ML research depth in generative recommenders, LLM/RL post-training, and top-tier publications — off-profile for a May 2027 BS-level backend/distributed-systems new grad, despite some adjacent AI/agentic and infra exposure.</t>
+          <t>Hard eligibility mismatch — the posting requires graduation by end of 2026 or January 2027 and Nate graduates May 2027 — and the role centers on GNC/embedded/real-time firmware rather than his backend/distributed-systems/AI-infra profile, though his Rust, C/C++, Linux, concurrency, and CI/CD background would otherwise be a reasonable partial match.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Posting states base $153,900-$300,960 for Seattle; TikTok/ByteDance PhD MLE offers typically add sizable RSU grants plus discretionary bonus, putting total package well above base. Band is wide because PhD research-track comp varies heavily with publication record and competing offers. Estimate reflects the posted PhD role, not a level this candidate would be hired into.</t>
+          <t>Mach Industries is a well-funded (Sequoia/Bridgewater-backed) defense-tech startup in the Anduril/Applied Intuition orbit; those firms typically pay new-grad SWEs ~$120-150k base in high-COL SoCal plus meaningful early-stage equity, which the posting explicitly says is part of TC. Band is wide because private-startup equity value is speculative and Mach does not publish new-grad levels — this is an estimate, not fact.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2305,7 +2313,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>tailored</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2313,11 +2321,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_1700a5.pdf</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2334,43 +2338,43 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>$300k–$550k</t>
+          <t>$85k–$110k</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Research Engineer Graduate - Seed Infra - PhD</t>
+          <t>Associate Software Engineer - Multiple Teams</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Irving, TX</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>The AI-training-infrastructure domain (distributed systems, fault-tolerant infra, GPU cluster scaling) maps well to Nate's Raft/KV-store and ML-infra interests, but the posting is a hard PhD-only requirement with a 2026 onboarding deadline and expects deep LLM/RL training-systems research experience — disqualifying for a May 2027 bachelor's/master's new grad.</t>
+          <t>Entry-level SWE title is right, but Abbott's software work is medtech/embedded and regulated rather than backend distributed systems or AI infra, and the comp tier falls short of the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Posted base range is $254.4k–$480k for this San Jose Seed Infra PhD role; adding RSUs and bonus puts realistic first-year TC around $300k–$550k. Note this is PhD-research-engineer compensation at ByteDance's top AI-lab band, not a standard new-grad SWE band (ByteDance new-grad SWE is more like $200–250k TC) — the figures above are not attainable at Nate's level.</t>
+          <t>Abbott is a large non-tech medical-device employer; new-grad associate engineer base in Irving, TX typically ~$75-95k plus a small bonus and negligible equity. Posting gave no level or comp detail, so the band is widened; estimate only.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2400,11 +2404,11 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>$250k–$400k</t>
+          <t>$280k–$450k</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2414,24 +2418,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation - PhD</t>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Mall - PhD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Hard PhD requirement plus deep ML-research expectations (LLM pre/post-training, generative recommendation, top-tier publications) that a BS-level backend/distributed-systems new grad cannot meet, despite some adjacent applied-AI/RAG experience.</t>
+          <t>Role hard-requires a completing/completed PhD with ML research depth in generative recommenders, LLM/RL post-training, and top-tier publications — off-profile for a May 2027 BS-level backend/distributed-systems new grad, despite some adjacent AI/agentic and infra exposure.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Posting states base $162k–$387.6k for this PhD ML role; TikTok pays top-of-market for PhD ML/recsys, with RSUs and bonus on top of base — typical PhD new-grad offers land ~$250k–$400k TC (higher for exceptional research profiles). Not applicable to this candidate's BS-level band (~$130–165k).</t>
+          <t>Posting states base $153,900-$300,960 for Seattle; TikTok/ByteDance PhD MLE offers typically add sizable RSU grants plus discretionary bonus, putting total package well above base. Band is wide because PhD research-track comp varies heavily with publication record and competing offers. Estimate reflects the posted PhD role, not a level this candidate would be hired into.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2451,7 +2455,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_bfd35d.pdf</t>
+          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_1700a5.pdf</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -2470,38 +2474,38 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>$250k–$350k</t>
+          <t>$300k–$550k</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>ByteDance</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation - PhD</t>
+          <t>Research Engineer Graduate - Seed Infra - PhD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Hard PhD requirement plus a research profile (LLM pre/post-training, generative recommendation, NeurIPS/ICML-tier publications) that a BS-level backend/distributed-systems candidate cannot satisfy — the AI/RAG experience is applied infra, not foundation-model research.</t>
+          <t>The AI-training-infrastructure domain (distributed systems, fault-tolerant infra, GPU cluster scaling) maps well to Nate's Raft/KV-store and ML-infra interests, but the posting is a hard PhD-only requirement with a 2026 onboarding deadline and expects deep LLM/RL training-systems research experience — disqualifying for a May 2027 bachelor's/master's new grad.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Posting states base $153,900–$300,960 for Seattle; TikTok PhD MLE new-grad offers typically land in the low-to-mid $200k base range plus RSUs (~$40–100k/yr) and bonus, putting realistic total comp for a fresh PhD around $250k–$350k. Band is wide because TikTok's ML research bands are unusually broad and heavily calibrated to publication record.</t>
+          <t>Posted base range is $254.4k–$480k for this San Jose Seed Infra PhD role; adding RSUs and bonus puts realistic first-year TC around $300k–$550k. Note this is PhD-research-engineer compensation at ByteDance's top AI-lab band, not a standard new-grad SWE band (ByteDance new-grad SWE is more like $200–250k TC) — the figures above are not attainable at Nate's level.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2511,7 +2515,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>tailored</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -2519,11 +2523,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_499a7c.pdf</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2540,38 +2540,38 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>$200k–$300k</t>
+          <t>$250k–$400k</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Video/Image AI/ML Software Engineer Graduate - Multimedia</t>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation - PhD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Hard PhD requirement (candidate is a 2027 bachelor's-level new grad) combined with a deeply specialized video codec / image-quality-algorithm domain (VMAF, PSNR, SSIM, AVC/HEVC/AV1, FPGA/ASIC C-models, RTOS/embedded) that has almost no overlap with his distributed-systems, backend, and AI-infra background.</t>
+          <t>Hard PhD requirement plus deep ML-research expectations (LLM pre/post-training, generative recommendation, top-tier publications) that a BS-level backend/distributed-systems new grad cannot meet, despite some adjacent applied-AI/RAG experience.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>ByteDance is a top-of-market payer; the posting itself lists $122.6k–$301k base for this PhD-level San Diego role, plus RSUs and bonus. PhD new-grad hires typically land in the upper-middle of that band, so ~$200–300k TC is realistic here. Note this is a PhD-track number — a bachelor's new-grad SWE at ByteDance would be closer to $180–230k TC, and this specific req would not be open to him.</t>
+          <t>Posting states base $162k–$387.6k for this PhD ML role; TikTok pays top-of-market for PhD ML/recsys, with RSUs and bonus on top of base — typical PhD new-grad offers land ~$250k–$400k TC (higher for exceptional research profiles). Not applicable to this candidate's BS-level band (~$130–165k).</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -2589,7 +2589,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_bfd35d.pdf</t>
+        </is>
+      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2606,38 +2610,34 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>$80k–$105k</t>
+          <t>$130k–$190k</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Mach Industries</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Cedar Rapids, IA</t>
-        </is>
-      </c>
+          <t>Software Engineer New Grad - Software - GNC</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Generic entry-level SWE title is nominally on-profile, but RTX/Collins avionics work in Cedar Rapids skews embedded/safety-critical C rather than distributed systems or AI infra, almost certainly requires clearance eligibility (candidate has none), and the TC ceiling sits well under the ~130k anchor.</t>
+          <t>Hard timing blocker — the posting requires graduation by end of 2026 or January 2027 and Nate graduates May 2027 — and the role centers on GNC/embedded/real-time firmware rather than his backend and distributed-systems core, though his Rust/C++ depth and the "Linux, concurrency, distributed systems" preferred bullet keep it from scoring lower.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Description body failed to scrape (cookie banner only), so this is based on general knowledge: RTX/Collins Aerospace in Cedar Rapids, IA is defense-primes tier — new-grad SWE 1 base typically ~$75-95k with a small bonus, and low-COL Iowa pulls it further down. Defense primes also commonly gate these roles on US citizenship plus clearance eligibility. Band is wide given the missing posting text.</t>
+          <t>Mach Industries is a well-funded defense-tech startup (Sequoia/Bedrock-backed, ~350 employees) competing with Anduril/SpaceX for talent; new-grad SWE base likely ~$120-160k with meaningful equity on top. Estimate is uncertain — no public leveling data for Mach specifically, so band is wide.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -2655,7 +2655,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Mach_Industries_Software_Engineer_New_Grad_Softwar_82c258.pdf</t>
+        </is>
+      </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2672,38 +2676,38 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>$95k–$130k</t>
+          <t>$250k–$350k</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Vector Atomic</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Associate Firmware Engineer - Firmware</t>
+          <t>Machine Learning Engineer Graduate - E-Commerce Recommendation Foundation - PhD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pleasanton, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>This is an embedded/firmware role at a quantum-hardware company — squarely in the candidate's stated low-fit bucket (hardware/embedded-only, EE-centric), with no backend, distributed-systems, cloud, or AI-infra surface; only the C/C++/Rust overlap and systems concentration keep it from scoring lower, and the on-site Pleasanton requirement plus likely sub-$120k associate-tier comp further weaken the match.</t>
+          <t>Hard PhD requirement plus a research profile (LLM pre/post-training, generative recommendation, NeurIPS/ICML-tier publications) that a BS-level backend/distributed-systems candidate cannot satisfy — the AI/RAG experience is applied infra, not foundation-model research.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Vector Atomic is a small deep-tech quantum-sensing startup (atomic clocks/inertial sensors, DoD-adjacent funding), not a big-tech or high-comp software firm. New-grad "Associate" firmware roles there typically land around $95-125k base with modest early-stage equity and limited bonus; the scraped "29.2" in the posting may even hint at an hourly/associate-tier rate, which would push the low end down. Band is wide because private startup comp data for this company is sparse — this is an estimate, not fact.</t>
+          <t>Posting states base $153,900–$300,960 for Seattle; TikTok PhD MLE new-grad offers typically land in the low-to-mid $200k base range plus RSUs (~$40–100k/yr) and bonus, putting realistic total comp for a fresh PhD around $250k–$350k. Band is wide because TikTok's ML research bands are unusually broad and heavily calibrated to publication record.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2713,7 +2717,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2721,7 +2725,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>TikTok_Machine_Learning_Engineer_Graduate_E_Commer_499a7c.pdf</t>
+        </is>
+      </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -2738,38 +2746,38 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>$78k–$108k</t>
+          <t>$200k–$300k</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seagate Technology </t>
+          <t>ByteDance</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Firmware Engineer</t>
+          <t>Video/Image AI/ML Software Engineer Graduate - Multimedia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Longmont, CO</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Embedded C/C++ firmware for HDDs is squarely in the candidate's low-fit bucket (hardware-adjacent, EE-centric) despite tangential overlap with his storage-engine/LSM-tree work and C/C++ fluency, and the posted base of $72.6-103.8k sits well below his ~130k anchor.</t>
+          <t>Hard PhD requirement (candidate is a 2027 bachelor's-level new grad) combined with a deeply specialized video codec / image-quality-algorithm domain (VMAF, PSNR, SSIM, AVC/HEVC/AV1, FPGA/ASIC C-models, RTOS/embedded) that has almost no overlap with his distributed-systems, backend, and AI-infra background.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Posting states base $72,571-$103,784 for Longmont, CO; adding Seagate's discretionary bonus (~5-8%) and ESPP but no meaningful RSU grant at NCG level puts realistic TC in the high-70s to ~108k — hardware-tier compensation, roughly 20-40% under the candidate's target.</t>
+          <t>ByteDance is a top-of-market payer; the posting itself lists $122.6k–$301k base for this PhD-level San Diego role, plus RSUs and bonus. PhD new-grad hires typically land in the upper-middle of that band, so ~$200–300k TC is realistic here. Note this is a PhD-track number — a bachelor's new-grad SWE at ByteDance would be closer to $180–230k TC, and this specific req would not be open to him.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2804,38 +2812,38 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>$75k–$95k</t>
+          <t>$80k–$105k</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Securian Financial Group</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Engineering Analyst</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St Paul, MN</t>
+          <t>Cedar Rapids, IA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Generic entry-level enterprise application/IT engineering role at an insurance carrier — technically adjacent but with no distributed-systems, infra, or AI depth, hybrid-onsite in a non-target metro, and a posted base band whose midpoint sits far below the candidate's ~130k TC anchor.</t>
+          <t>Generic entry-level SWE title is nominally on-profile, but RTX/Collins avionics work in Cedar Rapids skews embedded/safety-critical C rather than distributed systems or AI infra, almost certainly requires clearance eligibility (candidate has none), and the TC ceiling sits well under the ~130k anchor.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Posting states base range $55,700–$103,400; a new grad would land in the lower-middle (~$72–85k). Add performance-tied 401k contribution (target 5%, up to 10%) and a company-funded pension; no equity. Midwest insurance-carrier tier — well below FAANG/Wayfair-level new-grad comp.</t>
+          <t>Description body failed to scrape (cookie banner only), so this is based on general knowledge: RTX/Collins Aerospace in Cedar Rapids, IA is defense-primes tier — new-grad SWE 1 base typically ~$75-95k with a small bonus, and low-COL Iowa pulls it further down. Defense primes also commonly gate these roles on US citizenship plus clearance eligibility. Band is wide given the missing posting text.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2874,34 +2882,34 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>$72k–$95k</t>
+          <t>$95k–$130k</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Vector Atomic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Associate Software Engineer 1</t>
+          <t>Associate Firmware Engineer - Firmware</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>North Chicago, IL</t>
+          <t>Pleasanton, CA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Generic pharma-IT associate SWE role centered on GxP documentation, vendor estimates, and supervised routine tasks rather than backend/distributed-systems or AI-infra engineering, and the posted comp band sits well below Nate's ~120k floor — the one bright spot is the "agentic workflows and LLMs" preferred qualification, which he over-satisfies.</t>
+          <t>This is an embedded/firmware role at a quantum-hardware company — squarely in the candidate's stated low-fit bucket (hardware/embedded-only, EE-centric), with no backend, distributed-systems, cloud, or AI-infra surface; only the C/C++/Rust overlap and systems concentration keep it from scoring lower, and the on-site Pleasanton requirement plus likely sub-$120k associate-tier comp further weaken the match.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Posting discloses base 58,656–103,500 (Workday grade 12); a zero-experience new grad in North Chicago realistically lands in the lower-middle of that band (~70–88k base), plus a modest short-term incentive (~5–8%) and 401k match. AbbVie is a large-pharma non-tech employer, so software comp tracks internal IT grades rather than tech-industry scales — no equity component typical at this level.</t>
+          <t>Vector Atomic is a small deep-tech quantum-sensing startup (atomic clocks/inertial sensors, DoD-adjacent funding), not a big-tech or high-comp software firm. New-grad "Associate" firmware roles there typically land around $95-125k base with modest early-stage equity and limited bonus; the scraped "29.2" in the posting may even hint at an hourly/associate-tier rate, which would push the low end down. Band is wide because private startup comp data for this company is sparse — this is an estimate, not fact.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2936,38 +2944,38 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>$78k–$105k</t>
+          <t>$78k–$108k</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t xml:space="preserve">Seagate Technology </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Multiple Teams</t>
+          <t>Firmware Engineer</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Irving, TX</t>
+          <t>Longmont, CO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Regulated medical-device C++ work across embedded/desktop/IoT connectivity in a mandatory on-site Irving TX role is well off Nate's backend/distributed-systems/AI-infra profile, and the posted base range tops out below his ~130k TC anchor.</t>
+          <t>Embedded C/C++ firmware for HDDs is squarely in the candidate's low-fit bucket (hardware-adjacent, EE-centric) despite tangential overlap with his storage-engine/LSM-tree work and C/C++ fluency, and the posted base of $72.6-103.8k sits well below his ~130k anchor.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Posting states base $50.7k–$101.3k; a new grad realistically lands in the low-to-mid part of that band (~$75–95k base) plus a modest ~5% bonus and strong retirement match typical of Abbott's non-tech-tier medtech comp — TX cost of living keeps offers lower than coastal tech.</t>
+          <t>Posting states base $72,571-$103,784 for Longmont, CO; adding Seagate's discretionary bonus (~5-8%) and ESPP but no meaningful RSU grant at NCG level puts realistic TC in the high-70s to ~108k — hardware-tier compensation, roughly 20-40% under the candidate's target.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3002,38 +3010,38 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>$70k–$115k</t>
+          <t>$75k–$95k</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AmNet Services</t>
+          <t>Securian Financial Group</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Software Systems Engineer 3</t>
+          <t>Engineering Analyst</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Warren, NJ</t>
+          <t>St Paul, MN</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Contract role at a small IoT/sensor networking firm requiring 7-10 years of experience (new grads only via fresh CS Master's), on an Erlang backend with no distributed-systems, cloud, or AI-infra overlap — off-profile on seniority, employment type, and stack despite being nominally "backend."</t>
+          <t>Generic entry-level enterprise application/IT engineering role at an insurance carrier — technically adjacent but with no distributed-systems, infra, or AI depth, hybrid-onsite in a non-target metro, and a posted base band whose midpoint sits far below the candidate's ~130k TC anchor.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>AmNet Services (America Networks) is a small private sensor/networking and staffing-style firm with no public comp tier, so this is a wide, low-confidence band. Posting is explicitly a Contract engagement, which typically means hourly pay (~$40-55/hr for a junior contractor in NJ), no equity, and limited or no benefits. Annualized that lands roughly $85-115k gross at the top end and well below at the bottom — under the candidate's ~$130k anchor and below the ~$120k low-match threshold.</t>
+          <t>Posting states base range $55,700–$103,400; a new grad would land in the lower-middle (~$72–85k). Add performance-tied 401k contribution (target 5%, up to 10%) and a company-funded pension; no equity. Midwest insurance-carrier tier — well below FAANG/Wayfair-level new-grad comp.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3068,7 +3076,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -3077,29 +3085,29 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Barrios</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Associate Software Engineer 1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>North Chicago, IL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Off-profile: C#/.NET web-app maintenance at a NASA support contractor in Houston, with clearance-eligibility requirements and gov-contractor pay well under the candidate's ~130k anchor — little overlap with his Rust/Java distributed-systems and AI-infra strengths beyond incidental Docker/K8s/CI-CD exposure.</t>
+          <t>Generic pharma-IT associate SWE role centered on GxP documentation, vendor estimates, and supervised routine tasks rather than backend/distributed-systems or AI-infra engineering, and the posted comp band sits well below Nate's ~120k floor — the one bright spot is the "agentic workflows and LLMs" preferred qualification, which he over-satisfies.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Estimate only. Barrios Technology is a mid-size NASA/JSC engineering services contractor; government cost-plus contract labor rates put entry-level SWE base around 70-88k in Houston, with minimal bonus/equity (typically none), so TC ≈ base. Band is wide because the posting spans 0-5 YOE and comp data for this employer is sparse.</t>
+          <t>Posting discloses base 58,656–103,500 (Workday grade 12); a zero-experience new grad in North Chicago realistically lands in the lower-middle of that band (~70–88k base), plus a modest short-term incentive (~5–8%) and 401k match. AbbVie is a large-pharma non-tech employer, so software comp tracks internal IT grades rather than tech-industry scales — no equity component typical at this level.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3134,38 +3142,38 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>$70k–$90k</t>
+          <t>$78k–$105k</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>D.R. Horton</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Application Developer 1</t>
+          <t>Associate Software Engineer - Multiple Teams</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arlington, TX</t>
+          <t>Irving, TX</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Internal .NET/C#/React business-application and legacy-app maintenance work at a homebuilder's corporate IT group, which has essentially no overlap with the candidate's backend/distributed-systems, cloud-infra, or AI-platform focus and sits at a much lower comp and technical tier.</t>
+          <t>Regulated medical-device C++ work across embedded/desktop/IoT connectivity in a mandatory on-site Irving TX role is well off Nate's backend/distributed-systems/AI-infra profile, and the posted base range tops out below his ~130k TC anchor.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Non-tech Fortune 500 homebuilder; corporate IT cost-center role in the Dallas-Fort Worth market, posting accepts a HS diploma with 0-1 years experience. Estimate assumes ~$70-85k base plus modest bonus/ESPP; band is approximate since D.R. Horton IT comp is not widely reported on levels.fyi.</t>
+          <t>Posting states base $50.7k–$101.3k; a new grad realistically lands in the low-to-mid part of that band (~$75–95k base) plus a modest ~5% bonus and strong retirement match typical of Abbott's non-tech-tier medtech comp — TX cost of living keeps offers lower than coastal tech.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3200,38 +3208,38 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>$85k–$115k</t>
+          <t>$70k–$115k</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>AmNet Services</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Software Systems Engineer 3</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anaheim, CA</t>
+          <t>Warren, NJ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Hard-blocked: the req demands an active TS/SCI with polygraph on day 1 and is earmarked for an RTX intern converting to full-time, and the C++/Qt/Angular defense-systems work plus sub-$120k band misses both the candidate's clearance-free constraint and TC anchor.</t>
+          <t>Contract role at a small IoT/sensor networking firm requiring 7-10 years of experience (new grads only via fresh CS Master's), on an Erlang backend with no distributed-systems, cloud, or AI-infra overlap — off-profile on seniority, employment type, and stack despite being nominally "backend."</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Posting states salary range 62,900–119,700 USD; RTX new-grad SWE offers typically land near the lower-middle of that band (~$85–100k base) plus modest 401k match and small/no annual incentive at level 1. Defense-primes pay well below the candidate's ~$130–165k anchor; cleared work in Anaheim may add a slight premium, hence the top of the band.</t>
+          <t>AmNet Services (America Networks) is a small private sensor/networking and staffing-style firm with no public comp tier, so this is a wide, low-confidence band. Posting is explicitly a Contract engagement, which typically means hourly pay (~$40-55/hr for a junior contractor in NJ), no equity, and limited or no benefits. Annualized that lands roughly $85-115k gross at the top end and well below at the bottom — under the candidate's ~$130k anchor and below the ~$120k low-match threshold.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3266,42 +3274,38 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>$85k–$115k</t>
+          <t>$72k–$95k</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>General Motors</t>
+          <t>Barrios</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Warren, MI</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>graduating between december 2025</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Hard-disqualifying graduation window (Dec 2025–Aug 2026 vs. candidate's May 2027) combined with an Android/Kotlin infotainment HMI focus that sits far from his backend/distributed-systems/AI-infra profile, in a hybrid Warren, MI role paying below his TC floor.</t>
+          <t>Off-profile: C#/.NET web-app maintenance at a NASA support contractor in Houston, with clearance-eligibility requirements and gov-contractor pay well under the candidate's ~130k anchor — little overlap with his Rust/Java distributed-systems and AI-infra strengths beyond incidental Docker/K8s/CI-CD exposure.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>GM is a non-tech-tier automotive employer; entry-level SWE base in Warren, MI typically ~$80–100k plus modest performance bonus (~5-10%) and relocation, putting TC roughly $85–115k — well below the candidate's ~$130k anchor. Estimate from general knowledge of GM/Big Three new-grad pay in low-cost Midwest markets, not from the posting (no range disclosed).</t>
+          <t>Estimate only. Barrios Technology is a mid-size NASA/JSC engineering services contractor; government cost-plus contract labor rates put entry-level SWE base around 70-88k in Houston, with minimal bonus/equity (typically none), so TC ≈ base. Band is wide because the posting spans 0-5 YOE and comp data for this employer is sparse.</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3336,38 +3340,38 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>$72k–$92k</t>
+          <t>$70k–$90k</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Integration Innovation (i3)</t>
+          <t>D.R. Horton</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Associate Software Developer - COMPASS</t>
+          <t>Application Developer 1</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Huntsville, AL</t>
+          <t>Arlington, TX</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Requires an active/obtainable DoD Secret clearance and on-site residency near Redstone Arsenal with a C#/HTML/CSS stack, all of which conflict with the candidate's stated constraints and backend/distributed-systems strengths, despite some Azure/AWS microservices and event-queue overlap.</t>
+          <t>Internal .NET/C#/React business-application and legacy-app maintenance work at a homebuilder's corporate IT group, which has essentially no overlap with the candidate's backend/distributed-systems, cloud-infra, or AI-platform focus and sits at a much lower comp and technical tier.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Mid-size employee-owned defense/government services contractor (i3) in Huntsville, AL — low cost-of-living market with cost-plus contract rate structures. Typical 0-3 yr associate developer base ~$70-85k plus 401(k) match and ESOP; no equity grant or notable signing bonus. Band is a general-knowledge estimate for the defense-services tier, not verified company data, and falls well below the candidate's ~$130k anchor.</t>
+          <t>Non-tech Fortune 500 homebuilder; corporate IT cost-center role in the Dallas-Fort Worth market, posting accepts a HS diploma with 0-1 years experience. Estimate assumes ~$70-85k base plus modest bonus/ESPP; band is approximate since D.R. Horton IT comp is not widely reported on levels.fyi.</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3402,38 +3406,38 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>$45k–$62k</t>
+          <t>$85k–$115k</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Trustpilot</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Software Engineer 1 - Trust Tech</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Edinburgh, UK</t>
+          <t>Anaheim, CA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Backend-adjacent work the candidate could handle, but it is a UK/EU-located role (Edinburgh/London/Copenhagen) he lacks work authorization for, and the Node/TypeScript/React full-stack stack is off his Rust/Java distributed-systems and AI-infra profile.</t>
+          <t>Hard-blocked: the req demands an active TS/SCI with polygraph on day 1 and is earmarked for an RTX intern converting to full-time, and the C++/Qt/Angular defense-systems work plus sub-$120k band misses both the candidate's clearance-free constraint and TC anchor.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Trustpilot is a profitable FTSE-250 tech company, not a top-tier payer. Edinburgh/UK graduate-to-SWE I base bands typically run ~£35-48k with a modest bonus, converting to roughly $45-62k USD — well below the candidate's ~$130k anchor. Wide-ish band; UK pay data for this specific level is inferred from general UK market rates rather than verified comp reports.</t>
+          <t>Posting states salary range 62,900–119,700 USD; RTX new-grad SWE offers typically land near the lower-middle of that band (~$85–100k base) plus modest 401k match and small/no annual incentive at level 1. Defense-primes pay well below the candidate's ~$130–165k anchor; cleared work in Anaheim may add a slight premium, hence the top of the band.</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3468,38 +3472,42 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>$48k–$65k</t>
+          <t>$85k–$115k</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Trustpilot</t>
+          <t>General Motors</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Software Engineer 1 - Trust Tech</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Warren, MI</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>graduating between december 2025</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>UK/Denmark-only role (no US location or stated sponsorship) with a Node.js/TypeScript full-stack + React internal-tooling focus, which misses the candidate's Java/Rust/Go backend and distributed-systems profile despite some AWS/Postgres and applied-AI overlap.</t>
+          <t>Hard-disqualifying graduation window (Dec 2025–Aug 2026 vs. candidate's May 2027) combined with an Android/Kotlin infotainment HMI focus that sits far from his backend/distributed-systems/AI-infra profile, in a hybrid Warren, MI role paying below his TC floor.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Estimate, not fact: Trustpilot is a profitable FTSE-250 mid-tier tech company; London/Edinburgh graduate SWE I base typically ~£38-50k plus a modest bonus, converting to roughly $48-65k USD. UK/EU pay scales sit far below the candidate's ~$130-165k US anchor, so the shortfall is structural rather than negotiable.</t>
+          <t>GM is a non-tech-tier automotive employer; entry-level SWE base in Warren, MI typically ~$80–100k plus modest performance bonus (~5-10%) and relocation, putting TC roughly $85–115k — well below the candidate's ~$130k anchor. Estimate from general knowledge of GM/Big Three new-grad pay in low-cost Midwest markets, not from the posting (no range disclosed).</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3534,38 +3542,38 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>$65k–$90k</t>
+          <t>$72k–$92k</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>Integration Innovation (i3)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Entry Level .NET Developer</t>
+          <t>Associate Software Developer - COMPASS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Louisville, CO</t>
+          <t>Huntsville, AL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Hard-blocked by the SECRET clearance and Security+ certification requirements, and the work is legacy Java/.NET web-app consulting with no backend-distributed-systems, infra, or AI-platform overlap.</t>
+          <t>Requires an active/obtainable DoD Secret clearance and on-site residency near Redstone Arsenal with a C#/HTML/CSS stack, all of which conflict with the candidate's stated constraints and backend/distributed-systems strengths, despite some Azure/AWS microservices and event-queue overlap.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Small IT staffing/consulting firm (Connecticut-based body shop) with no public comp data; estimate based on typical entry-level government-contract staffing pay in a mid-cost Colorado market. Wide band due to unknown company; likely far below the candidate's ~130k anchor.</t>
+          <t>Mid-size employee-owned defense/government services contractor (i3) in Huntsville, AL — low cost-of-living market with cost-plus contract rate structures. Typical 0-3 yr associate developer base ~$70-85k plus 401(k) match and ESOP; no equity grant or notable signing bonus. Band is a general-knowledge estimate for the defense-services tier, not verified company data, and falls well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3600,38 +3608,38 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>$65k–$90k</t>
+          <t>$45k–$62k</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>Trustpilot</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Software Engineer 1 - Trust Tech</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Edinburgh, UK</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Hard disqualifier: the posting requires an interim SECRET clearance to begin work plus existing CompTIA Security+ certification, which the candidate explicitly lacks — and the role itself is legacy full-stack JSP/Hibernate/WebLogic consulting work with graphic-designer/site-design duties, far from backend distributed systems or AI infra, at a comp tier well under the 120k floor.</t>
+          <t>Backend-adjacent work the candidate could handle, but it is a UK/EU-located role (Edinburgh/London/Copenhagen) he lacks work authorization for, and the Node/TypeScript/React full-stack stack is off his Rust/Java distributed-systems and AI-infra profile.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions is a small Connecticut-based IT services/staffing consultancy, not a product company — entry-level Java/consulting roles at this tier typically pay near-flat base with minimal bonus or equity. Wide band due to low visibility into this specific firm's pay; Portland, OR cost-of-living offers slight upward pressure but government-contract billing rates cap entry-level comp. Well below the candidate's ~130-165k anchor.</t>
+          <t>Trustpilot is a profitable FTSE-250 tech company, not a top-tier payer. Edinburgh/UK graduate-to-SWE I base bands typically run ~£35-48k with a modest bonus, converting to roughly $45-62k USD — well below the candidate's ~$130k anchor. Wide-ish band; UK pay data for this specific level is inferred from general UK market rates rather than verified comp reports.</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3666,38 +3674,38 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>$60k–$85k</t>
+          <t>$48k–$65k</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>Trustpilot</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Entry Level Java Developer</t>
+          <t>Software Engineer 1 - Trust Tech</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Silver Creek, NY</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>IT staffing/consulting shop posting a legacy Java web-app contract role that hard-requires an interim SECRET clearance plus Security+ certification — an explicit disqualifier for this candidate — and the work (JSP/WebLogic/Subversion, "site-design instincts") is far below his distributed-systems/AI-infra profile and TC anchor.</t>
+          <t>UK/Denmark-only role (no US location or stated sponsorship) with a Node.js/TypeScript full-stack + React internal-tooling focus, which misses the candidate's Java/Rust/Go backend and distributed-systems profile despite some AWS/Postgres and applied-AI overlap.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions is a small Connecticut-based IT services/staffing firm with no public compensation data, so this is a wide, low-confidence band inferred from typical entry-level government-contract Java staffing rates (largely base salary, minimal equity or bonus). Well below the candidate's ~130-165k anchor.</t>
+          <t>Estimate, not fact: Trustpilot is a profitable FTSE-250 mid-tier tech company; London/Edinburgh graduate SWE I base typically ~£38-50k plus a modest bonus, converting to roughly $48-65k USD. UK/EU pay scales sit far below the candidate's ~$130-165k US anchor, so the shortfall is structural rather than negotiable.</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3736,7 +3744,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>$60k–$85k</t>
+          <t>$65k–$90k</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3746,24 +3754,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Entry Level Java Developer</t>
+          <t>Entry Level .NET Developer</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Elk Grove, CA</t>
+          <t>Louisville, CO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Contract staffing role that hard-requires an interim/full SECRET clearance and Security+ certification (both explicit candidate disqualifiers), on legacy JSP/Hibernate/WebLogic web-app work with design responsibilities — off-profile for a backend/distributed-systems new grad and almost certainly below the ~120k TC floor.</t>
+          <t>Hard-blocked by the SECRET clearance and Security+ certification requirements, and the work is legacy Java/.NET web-app consulting with no backend-distributed-systems, infra, or AI-platform overlap.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>No public comp data for 9to9 Software Solutions — a small CT-based IT staffing/consulting firm. Band inferred from typical entry-level contract Java roles at government-contract body shops (roughly $30–40/hr, little to no bonus or equity). Wide band reflects low confidence and the contract (non-FTE) structure.</t>
+          <t>Small IT staffing/consulting firm (Connecticut-based body shop) with no public comp data; estimate based on typical entry-level government-contract staffing pay in a mid-cost Colorado market. Wide band due to unknown company; likely far below the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3798,38 +3806,38 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$85k–$110k</t>
+          <t>$65k–$90k</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Failure Analysis Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Acton, MA</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>EE/photonics lab failure-analysis role (coherent optical transceivers, oscilloscopes, RF/optical spectrum analyzers) with zero software content, requiring prior hands-on FA experience — squarely in the candidate's hardware/embedded-only low-fit bucket, and the immediate onsite start conflicts with a mid-2027 new-grad timeline.</t>
+          <t>Hard disqualifier: the posting requires an interim SECRET clearance to begin work plus existing CompTIA Security+ certification, which the candidate explicitly lacks — and the role itself is legacy full-stack JSP/Hibernate/WebLogic consulting work with graphic-designer/site-design duties, far from backend distributed systems or AI infra, at a comp tier well under the 120k floor.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Posting explicitly states a new-hire base range of $79,200-$100,400; adding a ~5-8% Cisco bonus and a small RSU grant yields roughly $85-110k TC. Cisco's Supply Chain and Manufacturing Ops org pays materially below its SWE ladder, and a new grad would land in the lower half of the posted band, so the realistic center is ~$90k — below the candidate's ~120k low-match floor.</t>
+          <t>9to9 Software Solutions is a small Connecticut-based IT services/staffing consultancy, not a product company — entry-level Java/consulting roles at this tier typically pay near-flat base with minimal bonus or equity. Wide band due to low visibility into this specific firm's pay; Portland, OR cost-of-living offers slight upward pressure but government-contract billing rates cap entry-level comp. Well below the candidate's ~130-165k anchor.</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3864,38 +3872,38 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$90k–$110k</t>
+          <t>$60k–$85k</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Reliability Engineer 2</t>
+          <t>Entry Level Java Developer</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chandler, AZ</t>
+          <t>Silver Creek, NY</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>This is an EE-centric hardware reliability role (device physics, transistor-level ICs, HTOL burn-in, lab bench equipment, JMP/LabVIEW) with essentially no backend, distributed-systems, or AI-infra content — squarely in the candidate's stated low-fit bucket, and it's an immediate-start req rather than a May 2027 new-grad pipeline.</t>
+          <t>IT staffing/consulting shop posting a legacy Java web-app contract role that hard-requires an interim SECRET clearance plus Security+ certification — an explicit disqualifier for this candidate — and the work (JSP/WebLogic/Subversion, "site-design instincts") is far below his distributed-systems/AI-infra profile and TC anchor.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Microchip is a mid-tier semiconductor employer in a low-cost metro (Chandler, AZ); new-grad/Engineer II reliability roles there typically pay ~$80-95k base plus modest bonus/ESPP/small RSU, landing around $90-110k TC. Estimate based on general semiconductor-industry knowledge, not a verified data point.</t>
+          <t>9to9 Software Solutions is a small Connecticut-based IT services/staffing firm with no public compensation data, so this is a wide, low-confidence band inferred from typical entry-level government-contract Java staffing rates (largely base salary, minimal equity or bonus). Well below the candidate's ~130-165k anchor.</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3930,38 +3938,38 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$75k–$95k</t>
+          <t>$60k–$85k</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Entry Level Java Developer</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN</t>
+          <t>Elk Grove, CA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Hard-blocked: the req demands an active DoD Secret clearance from day 1 and is explicitly reserved for an RTX intern converting to full-time, and the Ada/Java C2 work in onsite Fort Wayne at 57–109k misses the candidate's distributed-systems/AI-infra profile and ~130k TC anchor.</t>
+          <t>Contract staffing role that hard-requires an interim/full SECRET clearance and Security+ certification (both explicit candidate disqualifiers), on legacy JSP/Hibernate/WebLogic web-app work with design responsibilities — off-profile for a backend/distributed-systems new grad and almost certainly below the ~120k TC floor.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Posted range 57.2k–108.8k; RTX defense new-grad SWE typically lands ~75–90k base with small (0–5%) bonus and no equity, and Fort Wayne IN is a low cost-of-living site so offers skew to the lower-middle of the band. Well below the candidate's ~130k anchor.</t>
+          <t>No public comp data for 9to9 Software Solutions — a small CT-based IT staffing/consulting firm. Band inferred from typical entry-level contract Java roles at government-contract body shops (roughly $30–40/hr, little to no bonus or equity). Wide band reflects low confidence and the contract (non-FTE) structure.</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3996,38 +4004,38 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>$68k–$80k</t>
+          <t>$85k–$110k</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Failure Analysis Engineer</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Acton, MA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SQL Server/SSIS/Salesforce-Apex BI rotational program at ~$75k TC — off-profile for a backend/distributed-systems candidate and far below the ~$130k anchor.</t>
+          <t>EE/photonics lab failure-analysis role (coherent optical transceivers, oscilloscopes, RF/optical spectrum analyzers) with zero software content, requiring prior hands-on FA experience — squarely in the candidate's hardware/embedded-only low-fit bucket, and the immediate onsite start conflicts with a mid-2027 new-grad timeline.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Posting states an explicit flat rate of $30.00/hr (~$62.4k base at 2,080 hrs) plus a 10% discretionary cash bonus target and a 10% discretionary RSU target; band spans low-to-full attainment of both. Consistent with Axos as a mid-size digital bank running a below-market entry-level rotational pipeline rather than a comp-competitive tech employer.</t>
+          <t>Posting explicitly states a new-hire base range of $79,200-$100,400; adding a ~5-8% Cisco bonus and a small RSU grant yields roughly $85-110k TC. Cisco's Supply Chain and Manufacturing Ops org pays materially below its SWE ladder, and a new grad would land in the lower half of the posted band, so the realistic center is ~$90k — below the candidate's ~120k low-match floor.</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4062,38 +4070,38 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>$60k–$85k</t>
+          <t>$90k–$110k</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Entry Level Software Developer</t>
+          <t>Reliability Engineer 2</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Randolph AFB, TX</t>
+          <t>Chandler, AZ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Requires an interim SECRET clearance to start plus Security+ certification (candidate has no clearance — an explicit disqualifier), and the work is legacy Java/JSP/WebLogic/Subversion web development at an IT staffing firm on an Air Force base, with no overlap with the candidate's distributed-systems, cloud-infra, or AI-platform strengths.</t>
+          <t>This is an EE-centric hardware reliability role (device physics, transistor-level ICs, HTOL burn-in, lab bench equipment, JMP/LabVIEW) with essentially no backend, distributed-systems, or AI-infra content — squarely in the candidate's stated low-fit bucket, and it's an immediate-start req rather than a May 2027 new-grad pipeline.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions is a small Connecticut-based IT services/staffing firm placing contractors on government contracts. This tier typically pays far below product-company new-grad bands, and clearance-gated entry-level contract roles rarely carry equity or meaningful bonus. No public comp data for this company, so the band is wide and low-confidence; it falls well under the candidate's ~$120k floor.</t>
+          <t>Microchip is a mid-tier semiconductor employer in a low-cost metro (Chandler, AZ); new-grad/Engineer II reliability roles there typically pay ~$80-95k base plus modest bonus/ESPP/small RSU, landing around $90-110k TC. Estimate based on general semiconductor-industry knowledge, not a verified data point.</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4128,38 +4136,38 @@
         <v>54</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>$60k–$90k</t>
+          <t>$75k–$95k</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Fort Wayne, IN</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Hard-blocked by an explicit interim SECRET clearance + Security+ certification requirement (both listed as minimum quals) that the candidate cannot meet, and the work itself is legacy contract JSP/Hibernate/WebLogic web development at a staffing firm — no overlap with distributed systems, infra, or AI platform work, at contractor-tier pay far below the $130k anchor.</t>
+          <t>Hard-blocked: the req demands an active DoD Secret clearance from day 1 and is explicitly reserved for an RTX intern converting to full-time, and the Ada/Java C2 work in onsite Fort Wayne at 57–109k misses the candidate's distributed-systems/AI-infra profile and ~130k TC anchor.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions is a small IT staffing/consulting body shop, and this is an explicitly Contract (not FTE) government-adjacent role — no equity, likely hourly with little or no bonus. Comparable entry-level contract Java dev rates through such firms run roughly $30-45/hr, i.e. ~$60-90k annualized. Low confidence, wide band; well below the candidate's ~$130k anchor.</t>
+          <t>Posted range 57.2k–108.8k; RTX defense new-grad SWE typically lands ~75–90k base with small (0–5%) bonus and no equity, and Fort Wayne IN is a low cost-of-living site so offers skew to the lower-middle of the band. Well below the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4194,38 +4202,38 @@
         <v>55</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>$60k–$85k</t>
+          <t>$68k–$80k</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Entry Level Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Copperhill, TN</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Requires an existing interim SECRET clearance and Security+ certification to start (candidate has neither and lists clearance roles as a hard mismatch), and it is a contract legacy Java/JSP/WebLogic web-dev role at a staffing consultancy in rural Copperhill, TN with no distributed-systems, infra, or AI-platform content.</t>
+          <t>SQL Server/SSIS/Salesforce-Apex BI rotational program at ~$75k TC — off-profile for a backend/distributed-systems candidate and far below the ~$130k anchor.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Company is not well known publicly — wide, low-confidence band. 9to9 Software Solutions is a small Connecticut-based IT staffing/services consultancy rather than a product company, and this is explicitly a Contract position, implying an hourly rate with minimal-to-no equity or bonus. Cleared entry-level government-contract Java work in a low-cost rural TN market typically pays in the $60-85k equivalent range, well below the candidate's ~$130-165k anchor and under the ~$120k low-match floor.</t>
+          <t>Posting states an explicit flat rate of $30.00/hr (~$62.4k base at 2,080 hrs) plus a 10% discretionary cash bonus target and a 10% discretionary RSU target; band spans low-to-full attainment of both. Consistent with Axos as a mid-size digital bank running a below-market entry-level rotational pipeline rather than a comp-competitive tech employer.</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4260,38 +4268,38 @@
         <v>56</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>$65k–$85k</t>
+          <t>$60k–$85k</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SOSi</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>PeopleSoft Software Developer</t>
+          <t>Entry Level Software Developer</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Charleston, SC</t>
+          <t>Randolph AFB, TX</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Hard-blocked by the Secret clearance requirement (an explicit candidate constraint) and the work is PeopleSoft/PeopleCode ERP maintenance — no overlap with backend distributed systems, Rust/systems, or AI infra — plus onsite 5 days in Charleston at roughly half the target TC.</t>
+          <t>Requires an interim SECRET clearance to start plus Security+ certification (candidate has no clearance — an explicit disqualifier), and the work is legacy Java/JSP/WebLogic/Subversion web development at an IT staffing firm on an Air Force base, with no overlap with the candidate's distributed-systems, cloud-infra, or AI-platform strengths.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Defense/government services integrator (SOSi) entry-level ERP developer in Charleston, SC — cleared-work government contracting pay bands are well below product-tech; base likely $65-80k with minimal bonus/equity. Wide band due to no public comp data for SOSi.</t>
+          <t>9to9 Software Solutions is a small Connecticut-based IT services/staffing firm placing contractors on government contracts. This tier typically pays far below product-company new-grad bands, and clearance-gated entry-level contract roles rarely carry equity or meaningful bonus. No public comp data for this company, so the band is wide and low-confidence; it falls well under the candidate's ~$120k floor.</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4330,12 +4338,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>$45k–$70k</t>
+          <t>$60k–$90k</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ERPA</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4345,19 +4353,19 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Franklin County, OH</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Contract "training and placement" body-shop posting at an Oracle/PeopleSoft consulting partner targeting candidates with "basic technical skills" — no backend, distributed-systems, or AI-infra content, and the contract/staffing model is far off-profile for this candidate.</t>
+          <t>Hard-blocked by an explicit interim SECRET clearance + Security+ certification requirement (both listed as minimum quals) that the candidate cannot meet, and the work itself is legacy contract JSP/Hibernate/WebLogic web development at a staffing firm — no overlap with distributed systems, infra, or AI platform work, at contractor-tier pay far below the $130k anchor.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>ERP Analysts is a small Oracle Platinum Partner consulting/staffing firm; "training and placement" contract roles are typically hourly W2/C2C with no equity and minimal bonus. Band is wide because comp is unpublished and contract terms vary — estimate based on general IT-staffing/consulting entry-level market rates, not company data. Well below the candidate's ~$130k anchor.</t>
+          <t>9to9 Software Solutions is a small IT staffing/consulting body shop, and this is an explicitly Contract (not FTE) government-adjacent role — no equity, likely hourly with little or no bonus. Comparable entry-level contract Java dev rates through such firms run roughly $30-45/hr, i.e. ~$60-90k annualized. Low confidence, wide band; well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4396,34 +4404,34 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>$35k–$50k</t>
+          <t>$60k–$85k</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Valeo Foods</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Enterprise Applications Developer - Enterprise Applications</t>
+          <t>Entry Level Software Developer</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Leeds, UK</t>
+          <t>Copperhill, TN</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>UK-based (Leeds) ERP/Power Apps/SSRS enterprise-applications role in a Microsoft low-code stack at a food manufacturer — no backend/distributed-systems or AI-infra content, wrong geography for a US-authorized candidate, immediate start rather than mid-2027, and comp far below the ~$130k anchor.</t>
+          <t>Requires an existing interim SECRET clearance and Security+ certification to start (candidate has neither and lists clearance roles as a hard mismatch), and it is a contract legacy Java/JSP/WebLogic web-dev role at a staffing consultancy in rural Copperhill, TN with no distributed-systems, infra, or AI-platform content.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>UK non-tech-sector (food manufacturing) enterprise applications developer in a regional, non-London market; junior/grad-level Microsoft ERP dev bands in Leeds run roughly £28-38k base, converting to ~$35-50k USD. Benefits listed are largely non-cash (25 days + bank holidays, matched pension, cycle-to-work, staff discount), so total cash comp is close to base. Wide-ish band because no salary was posted and the company is not a known tech-comp benchmark; this is an estimate, not fact.</t>
+          <t>Company is not well known publicly — wide, low-confidence band. 9to9 Software Solutions is a small Connecticut-based IT staffing/services consultancy rather than a product company, and this is explicitly a Contract position, implying an hourly rate with minimal-to-no equity or bonus. Cleared entry-level government-contract Java work in a low-cost rural TN market typically pays in the $60-85k equivalent range, well below the candidate's ~$130-165k anchor and under the ~$120k low-match floor.</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4458,38 +4466,38 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>$34k–$48k</t>
+          <t>$65k–$85k</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Valeo Foods</t>
+          <t>SOSi</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Enterprise Applications Developer - Enterprise Applications</t>
+          <t>PeopleSoft Software Developer</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Norwich, UK</t>
+          <t>Charleston, SC</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>UK-only (Norwich) internal-IT ERP/low-code role built on C#, SSRS/Power BI, Logic Apps and Power Apps — no overlap with the candidate's backend/distributed-systems/AI-infra profile, and the location is impractical for a US-authorized new grad.</t>
+          <t>Hard-blocked by the Secret clearance requirement (an explicit candidate constraint) and the work is PeopleSoft/PeopleCode ERP maintenance — no overlap with backend distributed systems, Rust/systems, or AI infra — plus onsite 5 days in Charleston at roughly half the target TC.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Valeo Foods is a UK food manufacturer, not a tech company; this is an internal enterprise-applications/IT position in Norwich, a low-cost regional UK market. No salary posted, so the band is inferred from typical UK junior enterprise/ERP developer pay outside London (~£27-38k) converted to USD. Wide band, low confidence; well below the candidate's ~$130k anchor.</t>
+          <t>Defense/government services integrator (SOSi) entry-level ERP developer in Charleston, SC — cleared-work government contracting pay bands are well below product-tech; base likely $65-80k with minimal bonus/equity. Wide band due to no public comp data for SOSi.</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4528,34 +4536,34 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>$33k–$45k</t>
+          <t>$45k–$70k</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Radius Limited</t>
+          <t>ERPA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Graduate Mobile Developer - Vehicle Telematics</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Crewe, UK</t>
+          <t>Franklin County, OH</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>UK-only role in Crewe with explicit no-visa-sponsorship and UK right-to-work requirement, focused on cross-platform mobile app development (Flutter/React Native/Kotlin/Swift) — off-profile on both geography/authorization and technical domain for a US-based backend/distributed-systems candidate.</t>
+          <t>Contract "training and placement" body-shop posting at an Oracle/PeopleSoft consulting partner targeting candidates with "basic technical skills" — no backend, distributed-systems, or AI-infra content, and the contract/staffing model is far off-profile for this candidate.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Estimate, not fact. Radius Limited is a mid-market UK fleet services/telematics company (fuel cards, leasing, telecoms), not a tech-tier compensator. Regional graduate developer salaries in Cheshire/North West England typically run roughly £26–35k GBP base with a benefits package (pension, life assurance, fuel card, EV scheme) and little to no equity; converted at ~1.27 USD/GBP that is ~$33–45k USD. Band is wide because the posting states only "competitive salary" with no figure. Note this is GBP-denominated UK comp and not directly comparable to US new-grad TC benchmarks — it sits far below the candidate's ~$130k anchor.</t>
+          <t>ERP Analysts is a small Oracle Platinum Partner consulting/staffing firm; "training and placement" contract roles are typically hourly W2/C2C with no equity and minimal bonus. Band is wide because comp is unpublished and contract terms vary — estimate based on general IT-staffing/consulting entry-level market rates, not company data. Well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4590,38 +4598,38 @@
         <v>61</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>$44k–$56k</t>
+          <t>$35k–$50k</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TOMRA</t>
+          <t>Valeo Foods</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Field Service Engineer - London/South East</t>
+          <t>Enterprise Applications Developer - Enterprise Applications</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Leeds, UK</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Hands-on electro-mechanical field service role repairing reverse vending machines across London/South East, requiring a full UK driving licence and on-site/rota shift work — zero software engineering overlap with the candidate's backend/distributed-systems/AI-infra profile, and wrong country.</t>
+          <t>UK-based (Leeds) ERP/Power Apps/SSRS enterprise-applications role in a Microsoft low-code stack at a food manufacturer — no backend/distributed-systems or AI-infra content, wrong geography for a US-authorized candidate, immediate start rather than mid-2027, and comp far below the ~$130k anchor.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Posting explicitly lists GBP 35,000-41,000/year base; adding 10% non-contributory pension, company bonus, and paid overtime and converting at ~1.27 USD/GBP gives roughly $44k-$56k USD equivalent. UK field-service comp bands are not comparable to US new-grad SWE, and this sits far below the candidate's ~$130k target.</t>
+          <t>UK non-tech-sector (food manufacturing) enterprise applications developer in a regional, non-London market; junior/grad-level Microsoft ERP dev bands in Leeds run roughly £28-38k base, converting to ~$35-50k USD. Benefits listed are largely non-cash (25 days + bank holidays, matched pension, cycle-to-work, staff discount), so total cash comp is close to base. Wide-ish band because no salary was posted and the company is not a known tech-comp benchmark; this is an estimate, not fact.</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4656,38 +4664,38 @@
         <v>62</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>$36k–$40k</t>
+          <t>$34k–$48k</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PaperCut</t>
+          <t>Valeo Foods</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Associate Support Engineer</t>
+          <t>Enterprise Applications Developer - Enterprise Applications</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bracknell, UK</t>
+          <t>Norwich, UK</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Frontline customer-support role in Bracknell, UK — not a backend/distributed-systems SWE position, outside the candidate's US work authorization, and capped at ~$38k TC versus a ~$130k anchor.</t>
+          <t>UK-only (Norwich) internal-IT ERP/low-code role built on C#, SSRS/Power BI, Logic Apps and Power Apps — no overlap with the candidate's backend/distributed-systems/AI-infra profile, and the location is impractical for a US-authorized new grad.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Posting states "up to GBP 30,000 - yearly"; converted at ~1.27 USD/GBP. PaperCut is a mid-size private print-management vendor, and associate support roles in the UK typically have no meaningful equity component, so base is effectively total comp. Estimate, not fact.</t>
+          <t>Valeo Foods is a UK food manufacturer, not a tech company; this is an internal enterprise-applications/IT position in Norwich, a low-cost regional UK market. No salary posted, so the band is inferred from typical UK junior enterprise/ERP developer pay outside London (~£27-38k) converted to USD. Wide band, low confidence; well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4722,42 +4730,38 @@
         <v>63</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>$20k–$45k</t>
+          <t>$33k–$45k</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Hawk-Eye Innovations</t>
+          <t>Radius Limited</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Football Tracking Systems Operator - Remote Operations Centre</t>
+          <t>Graduate Mobile Developer - Vehicle Telematics</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Basingstoke, UK, Southampton, UK, Reading, UK</t>
+          <t>Crewe, UK</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>start date: july</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>A UK-based, in-office casual hourly shift role operating live Goal Line Technology broadcast systems — not a software engineering position, wrong country, wrong start date (July/August 2026 vs. May 2027 graduation), and pay far below the candidate's floor.</t>
+          <t>UK-only role in Crewe with explicit no-visa-sponsorship and UK right-to-work requirement, focused on cross-platform mobile app development (Flutter/React Native/Kotlin/Swift) — off-profile on both geography/authorization and technical domain for a US-based backend/distributed-systems candidate.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Posting states £13.00–£18.20/hr on a casual contract with 10–12 hour match-day shifts. At ~$1.27/£, full-time-equivalent hours (~2,080) would be roughly $34k–48k; because hours are casual and clustered around the football calendar, realized annual earnings are likely lower, hence the wide $20k–45k band. This is not a salaried new-grad SWE offer and Hawk-Eye (Sony-owned sports tech) does not run this as a graduate engineering pipeline, so no standard new-grad TC benchmark applies. Estimate only, low confidence on total realized comp.</t>
+          <t>Estimate, not fact. Radius Limited is a mid-market UK fleet services/telematics company (fuel cards, leasing, telecoms), not a tech-tier compensator. Regional graduate developer salaries in Cheshire/North West England typically run roughly £26–35k GBP base with a benefits package (pension, life assurance, fuel card, EV scheme) and little to no equity; converted at ~1.27 USD/GBP that is ~$33–45k USD. Band is wide because the posting states only "competitive salary" with no figure. Note this is GBP-denominated UK comp and not directly comparable to US new-grad TC benchmarks — it sits far below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4796,34 +4800,34 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>$15k–$45k</t>
+          <t>$44k–$56k</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Lilt</t>
+          <t>TOMRA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AI Training Contributor - French</t>
+          <t>Field Service Engineer - London/South East</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Remote in Canada, Québec City, QC, Canada</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>This is a part-time 1099 data-annotation/linguist gig in Canada requiring native French fluency — no software engineering content, no US full-time new-grad path, and nothing touching the candidate's backend/distributed-systems/AI-infra profile.</t>
+          <t>Hands-on electro-mechanical field service role repairing reverse vending machines across London/South East, requiring a full UK driving licence and on-site/rota shift work — zero software engineering overlap with the candidate's backend/distributed-systems/AI-infra profile, and wrong country.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Not a salaried role — Lilt pays AI-training contractors hourly/per-task (typically ~$15-30/hr USD equivalent) with no benefits and no guaranteed hours; the posting explicitly says it is unsuitable as primary income. Band shown is a rough annualized figure assuming the stated 10+ hrs/week minimum up to near-full-time utilization, and is highly uncertain. Far below the ~$130k anchor.</t>
+          <t>Posting explicitly lists GBP 35,000-41,000/year base; adding 10% non-contributory pension, company bonus, and paid overtime and converting at ~1.27 USD/GBP gives roughly $44k-$56k USD equivalent. UK field-service comp bands are not comparable to US new-grad SWE, and this sits far below the candidate's ~$130k target.</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4848,6 +4852,208 @@
         </is>
       </c>
       <c r="P65" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>$36k–$40k</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>PaperCut</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Associate Support Engineer</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Bracknell, UK</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Frontline customer-support role in Bracknell, UK — not a backend/distributed-systems SWE position, outside the candidate's US work authorization, and capped at ~$38k TC versus a ~$130k anchor.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Posting states "up to GBP 30,000 - yearly"; converted at ~1.27 USD/GBP. PaperCut is a mid-size private print-management vendor, and associate support roles in the UK typically have no meaningful equity component, so base is effectively total comp. Estimate, not fact.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>scored</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>$20k–$45k</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Hawk-Eye Innovations</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Football Tracking Systems Operator - Remote Operations Centre</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Basingstoke, UK, Southampton, UK, Reading, UK</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>start date: july</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>A UK-based, in-office casual hourly shift role operating live Goal Line Technology broadcast systems — not a software engineering position, wrong country, wrong start date (July/August 2026 vs. May 2027 graduation), and pay far below the candidate's floor.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Posting states £13.00–£18.20/hr on a casual contract with 10–12 hour match-day shifts. At ~$1.27/£, full-time-equivalent hours (~2,080) would be roughly $34k–48k; because hours are casual and clustered around the football calendar, realized annual earnings are likely lower, hence the wide $20k–45k band. This is not a salaried new-grad SWE offer and Hawk-Eye (Sony-owned sports tech) does not run this as a graduate engineering pipeline, so no standard new-grad TC benchmark applies. Estimate only, low confidence on total realized comp.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>scored</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>$15k–$45k</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Lilt</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AI Training Contributor - French</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Remote in Canada, Québec City, QC, Canada</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>This is a part-time 1099 data-annotation/linguist gig in Canada requiring native French fluency — no software engineering content, no US full-time new-grad path, and nothing touching the candidate's backend/distributed-systems/AI-infra profile.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Not a salaried role — Lilt pays AI-training contractors hourly/per-task (typically ~$15-30/hr USD equivalent) with no benefits and no guaranteed hours; the posting explicitly says it is unsuitable as primary income. Band shown is a rough annualized figure assuming the stated 10+ hrs/week minimum up to near-full-time utilization, and is highly uncertain. Far below the ~$130k anchor.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>scored</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
@@ -4883,122 +5089,131 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId153"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/tailored_resumes.xlsx
+++ b/output/tailored_resumes.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P335"/>
+  <dimension ref="A1:P336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11276,38 +11276,38 @@
         <v>160</v>
       </c>
       <c r="B161" s="5" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>$80k–$100k</t>
+          <t>$150k–$185k</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Software Engineering Intern (Winter)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Annapolis, MD</t>
+          <t>Boston, MA; New York, NY</t>
         </is>
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
-          <t>The networking/high-availability systems work is adjacent to his backend/distributed-systems strengths, but this req is explicitly reserved for an RTX intern converting to full-time, is onsite-only in Annapolis, requires U.S. citizenship, and posts a 57.2k–108.8k band whose midpoint sits far below his ~130k anchor.</t>
+          <t>The technical content is a near-perfect match (large-scale distributed systems, Kubernetes, cloud-native infra, AI products), but this is a Winter 2027 internship explicitly requiring a 2028 full-time start date and full-time in-office availability Jan 4 – Apr 23, 2027 — a period when Nate is finishing his final semester before a May 2027 graduation, making him ineligible on both counts.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Posted range is 57,200–108,800 USD; new grads in a defense/aerospace SWE I role typically land in the lower-middle of that band (~78–95k base) plus a modest annual incentive and 401(k) match, so realistic TC is roughly 80–100k — well under the 130k target and below Wayfair-new-grad level.</t>
+          <t>Estimate is for Datadog's full-time new-grad SWE role (the relevant comparison, since this posting is an internship): Datadog is a strong-paying public infra company, typically ~$135–150k base plus RSUs and bonus in NYC/Boston, landing around $150–185k first-year TC. This is an estimate from general market knowledge, not verified data. The posting itself quotes $100–110k annualized for the intern role (~$8.3–9.2k/month), which is competitive for an internship but is not a new-grad TC figure. Note: Nate should instead watch for Datadog's 2027 full-time new-grad reqs, which fit his profile and TC anchor well.</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M161" s="3" t="inlineStr">
@@ -11325,7 +11325,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr"/>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
+          <t>Datadog_Software_Engineering_Intern_Winter_f5c5d2.pdf</t>
+        </is>
+      </c>
       <c r="O161" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -11333,7 +11337,7 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -11342,38 +11346,38 @@
         <v>161</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>$105k–$135k</t>
+          <t>$80k–$100k</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Applications Development Engineer - Broadband Plasma Division</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Milpitas, CA</t>
+          <t>Annapolis, MD</t>
         </is>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
-          <t>This is a customer-facing semiconductor applications/field engineering role (product characterization, alpha/beta testing, on-site demos and training, 70% travel) targeted at physics/materials/EE backgrounds — it involves essentially no backend, distributed-systems, or AI-infra software work, putting it squarely in the candidate's role_fit_low bucket.</t>
+          <t>The networking/high-availability systems work is adjacent to his backend/distributed-systems strengths, but this req is explicitly reserved for an RTX intern converting to full-time, is onsite-only in Annapolis, requires U.S. citizenship, and posts a 57.2k–108.8k band whose midpoint sits far below his ~130k anchor.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Posted base range is $97.8k–$166.3k, but new grads (BS/MS, 0 yrs) land near the bottom third — realistically ~$95–115k base in Milpitas. KLA adds a performance bonus (~5–10%) and modest RSUs/ESPP, giving roughly $105–135k first-year TC. Semiconductor-equipment tier pays below big-tech SWE; applications-engineering tracks typically sit at the lower end of the posted band.</t>
+          <t>Posted range is 57,200–108,800 USD; new grads in a defense/aerospace SWE I role typically land in the lower-middle of that band (~78–95k base) plus a modest annual incentive and 401(k) match, so realistic TC is roughly 80–100k — well under the 130k target and below Wayfair-new-grad level.</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -11399,7 +11403,7 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11408,42 +11412,38 @@
         <v>162</v>
       </c>
       <c r="B163" s="5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>$85k–$110k</t>
+          <t>$105k–$135k</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Johns Hopkins Applied Physics Laboratory</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Systems Engineer Graduate - Systems Engineer - Analyst</t>
+          <t>Applications Development Engineer - Broadband Plasma Division</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Laurel, MD</t>
+          <t>Milpitas, CA</t>
         </is>
       </c>
       <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>start date and can ultimately obtain a se</t>
-        </is>
-      </c>
+      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
-          <t>The 2027-grad timing and C++/Java/Python baseline match, but this is defense systems-of-systems engineering (requirements, trade studies, CONOPS, MS A analyses) rather than backend/distributed-systems or AI-infra software, it requires obtaining a Secret clearance, and APL's UARC pay sits well below the candidate's ~130k anchor.</t>
+          <t>This is a customer-facing semiconductor applications/field engineering role (product characterization, alpha/beta testing, on-site demos and training, 70% travel) targeted at physics/materials/EE backgrounds — it involves essentially no backend, distributed-systems, or AI-infra software work, putting it squarely in the candidate's role_fit_low bucket.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>JHU/APL is a non-profit university-affiliated research center: salary-only comp with no equity and at most a modest sign-on, offset by unusually strong retirement (~10%+ employer contribution) and tuition benefits. Band reflects typical new-grad systems-engineer offers in the Laurel/Baltimore-DC market; estimate, not fact.</t>
+          <t>Posted base range is $97.8k–$166.3k, but new grads (BS/MS, 0 yrs) land near the bottom third — realistically ~$95–115k base in Milpitas. KLA adds a performance bonus (~5–10%) and modest RSUs/ESPP, giving roughly $105–135k first-year TC. Semiconductor-equipment tier pays below big-tech SWE; applications-engineering tracks typically sit at the lower end of the posted band.</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11478,38 +11478,42 @@
         <v>163</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>$135k–$180k</t>
+          <t>$85k–$110k</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>Johns Hopkins Applied Physics Laboratory</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>New Grad Engineer - Silicon Engineering</t>
+          <t>Systems Engineer Graduate - Systems Engineer - Analyst</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, Irvine, CA, Redmond, WA</t>
+          <t>Laurel, MD</t>
         </is>
       </c>
       <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>start date and can ultimately obtain a se</t>
+        </is>
+      </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>EE-centric silicon role (ASIC/RTL/RFIC/DSP/physical design) requiring ASIC/SOC/FPGA/RFIC experience the candidate lacks — matches only incidental Python/C++ bullets and falls in his hardware/embedded-only low-fit category, despite the 2027 grad timing being eligible.</t>
+          <t>The 2027-grad timing and C++/Java/Python baseline match, but this is defense systems-of-systems engineering (requirements, trade studies, CONOPS, MS A analyses) rather than backend/distributed-systems or AI-infra software, it requires obtaining a Secret clearance, and APL's UARC pay sits well below the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Posting lists base pay directly: Level 1 $125k-$160k, Level 2 $145k-$195k. A new grad lands L1, so base ~$125-145k, plus SpaceX's modest illiquid stock-option grant (tender-offer dependent) and bonus. Estimate, not fact.</t>
+          <t>JHU/APL is a non-profit university-affiliated research center: salary-only comp with no equity and at most a modest sign-on, offset by unusually strong retirement (~10%+ employer contribution) and tuition benefits. Band reflects typical new-grad systems-engineer offers in the Laurel/Baltimore-DC market; estimate, not fact.</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -11535,7 +11539,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -11544,38 +11548,38 @@
         <v>164</v>
       </c>
       <c r="B165" s="5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>$78k–$105k</t>
+          <t>$135k–$180k</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Northrop Grumman</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Associate Software Engineer/Software Engineer - Associate Engineer Software (T01) - Engineer Software (T02)</t>
+          <t>New Grad Engineer - Silicon Engineering</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Melbourne, FL</t>
+          <t>Palo Alto, CA, Irvine, CA, Redmond, WA</t>
         </is>
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Timing (Aug 2027 grad, STEM degree) and generic software work fit, but this hits two of the candidate's explicit low-fit filters — an active Secret clearance plus Program Special Access required at start, which he doesn't have — and the posted pay ($65.8K–$118.9K base, likely T01) sits well under the ~$130K anchor, with defense-aeronautics embedded/systems work only loosely touching his distributed-systems and AI-infra strengths.</t>
+          <t>EE-centric silicon role (ASIC/RTL/RFIC/DSP/physical design) requiring ASIC/SOC/FPGA/RFIC experience the candidate lacks — matches only incidental Python/C++ bullets and falls in his hardware/embedded-only low-fit category, despite the 2027 grad timing being eligible.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Posting states base ranges directly: Associate SWE (T01) $65.8K–$98.8K, SWE (T02) $79.3K–$118.9K. A May-2027 BS grad lands at T01, realistically mid-range base (~$78–92K) plus a small discretionary bonus (~3-5%) and standard 401k match; defense-primes rarely give equity. Band reflects T01 typical offer with a little room upward if placed at T02 or given a clearance/location premium.</t>
+          <t>Posting lists base pay directly: Level 1 $125k-$160k, Level 2 $145k-$195k. A new grad lands L1, so base ~$125-145k, plus SpaceX's modest illiquid stock-option grant (tender-offer dependent) and bonus. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -11601,7 +11605,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -11614,42 +11618,34 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>$75k–$105k</t>
+          <t>$78k–$105k</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>GlobalFoundries</t>
+          <t>Northrop Grumman</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Tapeout and Mask Operations Engineer New Grad</t>
+          <t>Associate Software Engineer/Software Engineer - Associate Engineer Software (T01) - Engineer Software (T02)</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Essex Junction, VT</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>graduating in 2027</t>
-        </is>
-      </c>
+          <t>Melbourne, FL</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Semiconductor tapeout/mask manufacturing-operations role focused on EDA workflows, dashboards, and fab KPIs rather than backend/distributed systems or AI infra; grad-year timing fits but the domain, tech stack (QuickSight/Power Platform/Angular), and sub-$101k posted range are all off-profile.</t>
+          <t>Timing (Aug 2027 grad, STEM degree) and generic software work fit, but this hits two of the candidate's explicit low-fit filters — an active Secret clearance plus Program Special Access required at start, which he doesn't have — and the posted pay ($65.8K–$118.9K base, likely T01) sits well under the ~$130K anchor, with defense-aeronautics embedded/systems work only loosely touching his distributed-systems and AI-infra strengths.</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Posting explicitly lists $58,400-$100,800 base; a high-GPA new grad in Essex Junction, VT likely lands ~$75-95k base plus ~5-10% bonus and minimal equity/sign-on, typical of semiconductor-foundry (non-software-tier) new-grad comp.</t>
+          <t>Posting states base ranges directly: Associate SWE (T01) $65.8K–$98.8K, SWE (T02) $79.3K–$118.9K. A May-2027 BS grad lands at T01, realistically mid-range base (~$78–92K) plus a small discretionary bonus (~3-5%) and standard 401k match; defense-primes rarely give equity. Band reflects T01 typical offer with a little room upward if placed at T02 or given a clearance/location premium.</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -11675,7 +11671,7 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11684,38 +11680,46 @@
         <v>166</v>
       </c>
       <c r="B167" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>$95k–$125k</t>
+          <t>$75k–$105k</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Rocket Lab USA</t>
+          <t>GlobalFoundries</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Flight Software Engineer 1</t>
+          <t>Tapeout and Mask Operations Engineer New Grad</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Littleton, CO</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
+          <t>Essex Junction, VT</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>graduating in 2027</t>
+        </is>
+      </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>This is a hardware-adjacent embedded role (RTOS, IMU/star-tracker drivers, CAN-FD, hardware-in-the-loop) that maps to the candidate's explicit role_fit_low bucket and leans on C/C++ embedded experience he doesn't have, while none of his distributed-systems, cloud, or AI-infra strengths transfer; it also requires U.S. citizenship, prefers an active clearance, and is a fill-now req rather than a May-2027 new-grad pipeline.</t>
+          <t>Semiconductor tapeout/mask manufacturing-operations role focused on EDA workflows, dashboards, and fab KPIs rather than backend/distributed systems or AI infra; grad-year timing fits but the domain, tech stack (QuickSight/Power Platform/Angular), and sub-$101k posted range are all off-profile.</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Rocket Lab is an aerospace/defense employer, a tier that pays well below big tech for new grads: Level I flight software base typically ~$85-110k in the Denver/Littleton market, plus modest RSUs (RKLB) and a small bonus. Band widened slightly on the top end because Rocket Lab has been competing harder for flight software talent, but even the high end sits below the candidate's ~130k anchor.</t>
+          <t>Posting explicitly lists $58,400-$100,800 base; a high-GPA new grad in Essex Junction, VT likely lands ~$75-95k base plus ~5-10% bonus and minimal equity/sign-on, typical of semiconductor-foundry (non-software-tier) new-grad comp.</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -11741,7 +11745,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -11750,38 +11754,38 @@
         <v>167</v>
       </c>
       <c r="B168" s="5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>$88k–$100k</t>
+          <t>$95k–$125k</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Rocket Lab USA</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Software Development and Engineering Associate - Wealth and Advice Solutions Technology</t>
+          <t>Flight Software Engineer 1</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Littleton, CO</t>
         </is>
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Java/cloud enterprise backend work is loosely on-profile, but the posted $40.87-$42.31/hr (~$85-88k base) is well under the candidate's ~120k floor, the role skews toward QA, requirements validation, and production support rather than distributed systems or AI infra, and the 8/17/2026 application deadline indicates an immediate start that conflicts with a May 2027 graduation.</t>
+          <t>This is a hardware-adjacent embedded role (RTOS, IMU/star-tracker drivers, CAN-FD, hardware-in-the-loop) that maps to the candidate's explicit role_fit_low bucket and leans on C/C++ embedded experience he doesn't have, while none of his distributed-systems, cloud, or AI-infra strengths transfer; it also requires U.S. citizenship, prefers an active clearance, and is a fill-now req rather than a May-2027 new-grad pipeline.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Posting states the pay range explicitly: USD $40.87-$42.31/hour, which annualizes to roughly $85-88k base. Schwab is a mid-tier financial-services employer that typically adds a ~5-10% target bonus plus 401(k) match and ESPP at the associate level, with no meaningful equity grant for new grads; Austin onsite. Band reflects base plus bonus.</t>
+          <t>Rocket Lab is an aerospace/defense employer, a tier that pays well below big tech for new grads: Level I flight software base typically ~$85-110k in the Denver/Littleton market, plus modest RSUs (RKLB) and a small bonus. Band widened slightly on the top end because Rocket Lab has been competing harder for flight software talent, but even the high end sits below the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -11807,7 +11811,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11820,34 +11824,34 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>$78k–$100k</t>
+          <t>$88k–$100k</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>L3Harris Technologies</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Software Development and Engineering Associate - Wealth and Advice Solutions Technology</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sunrise, FL</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
-          <t>This is embedded/RTOS firmware for tactical radios (VxWorks, QNX, hardware-software interfaces) — squarely in the candidate's low-fit "embedded-only" bucket rather than backend/distributed/AI-infra, and defense-prime comp lands far under the ~$120k floor; his C/C++ and systems-security background is the only real overlap.</t>
+          <t>Java/cloud enterprise backend work is loosely on-profile, but the posted $40.87-$42.31/hr (~$85-88k base) is well under the candidate's ~120k floor, the role skews toward QA, requirements validation, and production support rather than distributed systems or AI infra, and the 8/17/2026 application deadline indicates an immediate start that conflicts with a May 2027 graduation.</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>L3Harris is a defense prime with below-market new-grad pay: associate SWE base typically ~$75-95k in a low-COL market like Sunrise, FL, with a small (often 0-5%) bonus and no meaningful equity. Estimate is from general knowledge of defense-contractor new-grad bands, not a verified offer — well below the candidate's ~$130k anchor.</t>
+          <t>Posting states the pay range explicitly: USD $40.87-$42.31/hour, which annualizes to roughly $85-88k base. Schwab is a mid-tier financial-services employer that typically adds a ~5-10% target bonus plus 401(k) match and ESPP at the associate level, with no meaningful equity grant for new grads; Austin onsite. Band reflects base plus bonus.</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -11886,34 +11890,34 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>$80k–$100k</t>
+          <t>$78k–$100k</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>L3Harris Technologies</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Systems Analyst - Leap Program</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Westlake, TX, Durham, NC, Merrimack, NH</t>
+          <t>Sunrise, FL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
-          <t>This is a business/systems analyst role centered on requirements gathering, documentation, and test execution rather than engineering, so it uses none of the candidate's distributed-systems, backend, or AI-infra strengths — and the April 2027 cohort start also predates a May 2027 graduation (the sibling July 2027 req would be the correct one).</t>
+          <t>This is embedded/RTOS firmware for tactical radios (VxWorks, QNX, hardware-software interfaces) — squarely in the candidate's low-fit "embedded-only" bucket rather than backend/distributed/AI-infra, and defense-prime comp lands far under the ~$120k floor; his C/C++ and systems-security background is the only real overlap.</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Fidelity is a non-tech financial-services employer paying below tech-company scale for new grads; rotational analyst-track roles typically run ~$75-90k base plus a ~5-10% bonus with no meaningful equity. Fidelity's new-grad software engineer roles run higher (~$95-115k), but this analyst track sits at the lower end. Estimate, not fact; falls below the candidate's ~$120k floor.</t>
+          <t>L3Harris is a defense prime with below-market new-grad pay: associate SWE base typically ~$75-95k in a low-COL market like Sunrise, FL, with a small (often 0-5%) bonus and no meaningful equity. Estimate is from general knowledge of defense-contractor new-grad bands, not a verified offer — well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -11952,34 +11956,34 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>$72k–$95k</t>
+          <t>$80k–$100k</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Panasonic Holdings</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Software Engineer 1 - Embedded Systems</t>
+          <t>Systems Analyst - Leap Program</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Irvine, CA</t>
+          <t>Westlake, TX, Durham, NC, Merrimack, NH</t>
         </is>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Embedded/real-time role centered on VxWorks BSP, kernel config, and device drivers falls in the candidate's explicitly low-fit hardware/embedded category, and the posted hourly range implies TC far below his ~130k anchor.</t>
+          <t>This is a business/systems analyst role centered on requirements gathering, documentation, and test execution rather than engineering, so it uses none of the candidate's distributed-systems, backend, or AI-infra strengths — and the April 2027 cohort start also predates a May 2027 graduation (the sibling July 2027 req would be the correct one).</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Posting discloses $33.17-$55.29/hr; a 0-YOE new grad realistically lands near the low end (~$69-80k base at 2080 hrs) plus a small discretionary bonus. Panasonic Avionics is a non-tech-tier avionics/hardware employer, so comp trails software-industry new-grad benchmarks even in Irvine, CA.</t>
+          <t>Fidelity is a non-tech financial-services employer paying below tech-company scale for new grads; rotational analyst-track roles typically run ~$75-90k base plus a ~5-10% bonus with no meaningful equity. Fidelity's new-grad software engineer roles run higher (~$95-115k), but this analyst track sits at the lower end. Estimate, not fact; falls below the candidate's ~$120k floor.</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -12005,7 +12009,7 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -12018,34 +12022,34 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>$70k–$95k</t>
+          <t>$72k–$95k</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Dunn Solutions Group</t>
+          <t>Panasonic Holdings</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Software Engineer 1 - Embedded Systems</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Minneapolis, MN</t>
+          <t>Irvine, CA</t>
         </is>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Backend Java is nominally in-profile, but this is an immediate-start IT consulting role wanting 2-5 years of experience on a dated stack (Java Applets, web UI design, multimedia authoring, BI/portal work) with no distributed-systems, cloud, or AI-infra depth, no new-grad pipeline for a May 2027 start, and comp well under the ~120k floor.</t>
+          <t>Embedded/real-time role centered on VxWorks BSP, kernel config, and device drivers falls in the candidate's explicitly low-fit hardware/embedded category, and the posted hourly range implies TC far below his ~130k anchor.</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Dunn Solutions is a small private SAP/Liferay-partner IT consultancy (Chicago/Minneapolis/Bangalore), not a public-comp company — band is inferred from typical Midwest mid-size consulting-shop junior Java developer salaries (~$70-90k base plus a modest bonus, little to no equity). Wide and low-confidence; no published new-grad data exists for this employer.</t>
+          <t>Posting discloses $33.17-$55.29/hr; a 0-YOE new grad realistically lands near the low end (~$69-80k base at 2080 hrs) plus a small discretionary bonus. Panasonic Avionics is a non-tech-tier avionics/hardware employer, so comp trails software-industry new-grad benchmarks even in Irvine, CA.</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -12084,34 +12088,34 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>$75k–$95k</t>
+          <t>$70k–$95k</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Urban Science</t>
+          <t>Dunn Solutions Group</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Serviceview</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Minneapolis, MN</t>
         </is>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
-          <t>A .NET/C#/ASP.NET + jQuery web-application role at a Detroit automotive analytics consultancy with no distributed-systems, infra, or AI/ML surface, an apparent immediate (not 2027) start, and estimated TC far below the candidate's ~130k anchor.</t>
+          <t>Backend Java is nominally in-profile, but this is an immediate-start IT consulting role wanting 2-5 years of experience on a dated stack (Java Applets, web UI design, multimedia authoring, BI/portal work) with no distributed-systems, cloud, or AI-infra depth, no new-grad pipeline for a May 2027 start, and comp well under the ~120k floor.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Urban Science is a mid-market private automotive analytics/consulting firm in Detroit, not a tech-tier employer. Associate SWE comp tracks Midwest non-tech-industry rates: base roughly $70-88k plus a small bonus, minimal/no equity. No public leveling data, so the band is wide and low-confidence.</t>
+          <t>Dunn Solutions is a small private SAP/Liferay-partner IT consultancy (Chicago/Minneapolis/Bangalore), not a public-comp company — band is inferred from typical Midwest mid-size consulting-shop junior Java developer salaries (~$70-90k base plus a modest bonus, little to no equity). Wide and low-confidence; no published new-grad data exists for this employer.</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -12137,7 +12141,7 @@
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12146,38 +12150,38 @@
         <v>173</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>$70k–$115k</t>
+          <t>$75k–$95k</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>AmNet Services</t>
+          <t>Urban Science</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Software Systems Engineer 3</t>
+          <t>Associate Software Engineer - Serviceview</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Warren, NJ</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Contract role at a small IoT/sensor networking firm requiring 7-10 years of experience (new grads only via fresh CS Master's), on an Erlang backend with no distributed-systems, cloud, or AI-infra overlap — off-profile on seniority, employment type, and stack despite being nominally "backend."</t>
+          <t>A .NET/C#/ASP.NET + jQuery web-application role at a Detroit automotive analytics consultancy with no distributed-systems, infra, or AI/ML surface, an apparent immediate (not 2027) start, and estimated TC far below the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>AmNet Services (America Networks) is a small private sensor/networking and staffing-style firm with no public comp tier, so this is a wide, low-confidence band. Posting is explicitly a Contract engagement, which typically means hourly pay (~$40-55/hr for a junior contractor in NJ), no equity, and limited or no benefits. Annualized that lands roughly $85-115k gross at the top end and well below at the bottom — under the candidate's ~$130k anchor and below the ~$120k low-match threshold.</t>
+          <t>Urban Science is a mid-market private automotive analytics/consulting firm in Detroit, not a tech-tier employer. Associate SWE comp tracks Midwest non-tech-industry rates: base roughly $70-88k plus a small bonus, minimal/no equity. No public leveling data, so the band is wide and low-confidence.</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -12203,7 +12207,7 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -12216,34 +12220,34 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>$95k–$115k</t>
+          <t>$70k–$115k</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Pennsylvania State University</t>
+          <t>AmNet Services</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Software Research and Development Engineer - Applied Research Laboratory</t>
+          <t>Software Systems Engineer 3</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>State College, PA</t>
+          <t>Warren, NJ</t>
         </is>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Technically adjacent work (Rust/Python/C++, data pipelines, Docker/K8s/CI-CD) but requires current TS/SCI clearance eligibility — an explicit disqualifier for this candidate — plus fully on-site State College, PA and no new-grad/2027-start structure.</t>
+          <t>Contract role at a small IoT/sensor networking firm requiring 7-10 years of experience (new grads only via fresh CS Master's), on an Erlang backend with no distributed-systems, cloud, or AI-infra overlap — off-profile on seniority, employment type, and stack despite being nominally "backend."</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Employer-published range of $92,100-$174,708 spans all grades; a zero-experience "Professional" hire at a university-affiliated DoD research lab lands near the floor. No equity and little/no bonus, offset by strong benefits (75% tuition discount, university retirement). Falls below the candidate's ~120k floor.</t>
+          <t>AmNet Services (America Networks) is a small private sensor/networking and staffing-style firm with no public comp tier, so this is a wide, low-confidence band. Posting is explicitly a Contract engagement, which typically means hourly pay (~$40-55/hr for a junior contractor in NJ), no equity, and limited or no benefits. Annualized that lands roughly $85-115k gross at the top end and well below at the bottom — under the candidate's ~$130k anchor and below the ~$120k low-match threshold.</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -12269,7 +12273,7 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -12278,42 +12282,38 @@
         <v>175</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>$80k–$100k</t>
+          <t>$95k–$115k</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Pennsylvania State University</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Software Research and Development Engineer - Applied Research Laboratory</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tucson, AZ</t>
+          <t>State College, PA</t>
         </is>
       </c>
       <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>start date experience using common ide pr</t>
-        </is>
-      </c>
+      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Defense-sector enterprise app work (UI screens, custom reports/dashboards, Oracle PL/SQL for the EAGLE MMIS product line) rather than backend/distributed-systems/AI-infra, plus it's an intern-to-FT conversion req, hybrid in Tucson with 4-6 weeks/yr travel, and requires ability to obtain a security clearance.</t>
+          <t>Technically adjacent work (Rust/Python/C++, data pipelines, Docker/K8s/CI-CD) but requires current TS/SCI clearance eligibility — an explicit disqualifier for this candidate — plus fully on-site State College, PA and no new-grad/2027-start structure.</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Posted range is $57.2k-$108.8k across all experience levels; new grad likely lands ~$75-92k base plus a small annual incentive. RTX/Raytheon pays at the defense-primes tier, well below the ~$130-165k anchor, and Tucson is a low-cost locality — below the ~$120k floor even at the optimistic end.</t>
+          <t>Employer-published range of $92,100-$174,708 spans all grades; a zero-experience "Professional" hire at a university-affiliated DoD research lab lands near the floor. No equity and little/no bonus, offset by strong benefits (75% tuition discount, university retirement). Falls below the candidate's ~120k floor.</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -12348,42 +12348,42 @@
         <v>176</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>$85k–$110k</t>
+          <t>$80k–$100k</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Johns Hopkins Applied Physics Laboratory</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Synthetic Aperture Radar Machine Learning Engineer - Imaging Systems</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Laurel, MD</t>
+          <t>Tucson, AZ</t>
         </is>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>start date and can ultimately obtain a ts</t>
+          <t>start date experience using common ide pr</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>SAR/RF signal-processing and edge-GPU embedded ML is an EE-centric role far from the candidate's backend/distributed-systems/AI-infra profile, plus it's a 2026-grad req requiring Interim Secret and eventual TS/SCI clearance — both listed low-fit constraints for a May 2027 grad with no clearance.</t>
+          <t>Defense-sector enterprise app work (UI screens, custom reports/dashboards, Oracle PL/SQL for the EAGLE MMIS product line) rather than backend/distributed-systems/AI-infra, plus it's an intern-to-FT conversion req, hybrid in Tucson with 4-6 weeks/yr travel, and requires ability to obtain a security clearance.</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>JHU APL is a university-affiliated FFRDC/defense lab: competitive-for-defense base salary with no equity, strong retirement (~10%+ employer contribution) and education benefits, but cash TC well below big-tech/Wayfair-tier new-grad levels. Estimate anchored on typical entry-level engineer/scientist offers in the Baltimore-DC defense-lab market; moderate confidence, band widened for degree level and clearance premium.</t>
+          <t>Posted range is $57.2k-$108.8k across all experience levels; new grad likely lands ~$75-92k base plus a small annual incentive. RTX/Raytheon pays at the defense-primes tier, well below the ~$130-165k anchor, and Tucson is a low-cost locality — below the ~$120k floor even at the optimistic end.</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Computer Engineer New Grad - Shipboard Systems Team</t>
+          <t>Synthetic Aperture Radar Machine Learning Engineer - Imaging Systems</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -12443,17 +12443,17 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>start date and can ultimately obtain a se</t>
+          <t>start date and can ultimately obtain a ts</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Off-profile: 2026-grad req vs. May 2027 graduation, requires US citizenship and Interim Secret clearance the candidate cannot offer, and the work is legacy C++/MATLAB plus sensor/hardware data-acquisition rather than backend, distributed systems, or AI infra.</t>
+          <t>SAR/RF signal-processing and edge-GPU embedded ML is an EE-centric role far from the candidate's backend/distributed-systems/AI-infra profile, plus it's a 2026-grad req requiring Interim Secret and eventual TS/SCI clearance — both listed low-fit constraints for a May 2027 grad with no clearance.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>JHU APL is a non-profit university-affiliated defense lab; new-grad engineer offers in the Baltimore/DC market are typically base-only (~$85-105k) with strong retirement contributions and tuition benefits but no equity and minimal bonus, putting TC below the candidate's ~$120k floor.</t>
+          <t>JHU APL is a university-affiliated FFRDC/defense lab: competitive-for-defense base salary with no equity, strong retirement (~10%+ employer contribution) and education benefits, but cash TC well below big-tech/Wayfair-tier new-grad levels. Estimate anchored on typical entry-level engineer/scientist offers in the Baltimore-DC defense-lab market; moderate confidence, band widened for degree level and clearance premium.</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Engineer Graduate - Multi-Mission Planning Development</t>
+          <t>Computer Engineer New Grad - Shipboard Systems Team</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -12513,17 +12513,17 @@
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
-          <t>start date and can ultimately obtain secr</t>
+          <t>start date and can ultimately obtain a se</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Clearance-gated (Interim Secret by start date), targeted at 2026 grads rather than May 2027, on-site-only in Laurel MD, and the work is defense mission-planning / modeling-and-simulation systems engineering rather than backend, distributed systems, or AI-infra SWE.</t>
+          <t>Off-profile: 2026-grad req vs. May 2027 graduation, requires US citizenship and Interim Secret clearance the candidate cannot offer, and the work is legacy C++/MATLAB plus sensor/hardware data-acquisition rather than backend, distributed systems, or AI infra.</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>JHU APL is a non-profit UARC, not a comp-competitive tech employer: new-grad engineering base typically ~$80-100k with no equity and little/no signing bonus, partially offset by strong retirement contributions and education benefits. Band is moderately wide since APL does not publish new-grad ranges; this falls below the candidate's ~$120k floor.</t>
+          <t>JHU APL is a non-profit university-affiliated defense lab; new-grad engineer offers in the Baltimore/DC market are typically base-only (~$85-105k) with strong retirement contributions and tuition benefits but no equity and minimal bonus, putting TC below the candidate's ~$120k floor.</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -12558,38 +12558,42 @@
         <v>179</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>$72k–$95k</t>
+          <t>$85k–$110k</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Barrios</t>
+          <t>Johns Hopkins Applied Physics Laboratory</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Engineer Graduate - Multi-Mission Planning Development</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>Laurel, MD</t>
         </is>
       </c>
       <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>start date and can ultimately obtain secr</t>
+        </is>
+      </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Off-profile: C#/.NET web-app maintenance at a NASA support contractor in Houston, with clearance-eligibility requirements and gov-contractor pay well under the candidate's ~130k anchor — little overlap with his Rust/Java distributed-systems and AI-infra strengths beyond incidental Docker/K8s/CI-CD exposure.</t>
+          <t>Clearance-gated (Interim Secret by start date), targeted at 2026 grads rather than May 2027, on-site-only in Laurel MD, and the work is defense mission-planning / modeling-and-simulation systems engineering rather than backend, distributed systems, or AI-infra SWE.</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Estimate only. Barrios Technology is a mid-size NASA/JSC engineering services contractor; government cost-plus contract labor rates put entry-level SWE base around 70-88k in Houston, with minimal bonus/equity (typically none), so TC ≈ base. Band is wide because the posting spans 0-5 YOE and comp data for this employer is sparse.</t>
+          <t>JHU APL is a non-profit UARC, not a comp-competitive tech employer: new-grad engineering base typically ~$80-100k with no equity and little/no signing bonus, partially offset by strong retirement contributions and education benefits. Band is moderately wide since APL does not publish new-grad ranges; this falls below the candidate's ~$120k floor.</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -12615,7 +12619,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -12624,38 +12628,38 @@
         <v>180</v>
       </c>
       <c r="B181" s="5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>$88k–$120k</t>
+          <t>$72k–$95k</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Northrop Grumman</t>
+          <t>Barrios</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Associate Software Engineer/Software Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Redondo Beach, CA, Palmdale, CA, Oklahoma City, OK, San Diego, CA, El Segundo, CA</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Requires an approved Top Secret clearance plus Program Special Access at start (candidate has none) and the Associate pay band tops out below the ~120k floor, making this defense-embedded role off-profile despite the matching 2027 grad timing.</t>
+          <t>Off-profile: C#/.NET web-app maintenance at a NASA support contractor in Houston, with clearance-eligibility requirements and gov-contractor pay well under the candidate's ~130k anchor — little overlap with his Rust/Java distributed-systems and AI-infra strengths beyond incidental Docker/K8s/CI-CD exposure.</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Posted Associate Engineer Software range $62.3k-$114.4k; SoCal new-grad offers at defense primes typically land ~$85-100k base plus a small discretionary bonus and no equity, so total comp clusters well under big-tech tiers. Estimate, not fact.</t>
+          <t>Estimate only. Barrios Technology is a mid-size NASA/JSC engineering services contractor; government cost-plus contract labor rates put entry-level SWE base around 70-88k in Houston, with minimal bonus/equity (typically none), so TC ≈ base. Band is wide because the posting spans 0-5 YOE and comp data for this employer is sparse.</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -12681,7 +12685,7 @@
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -12690,38 +12694,38 @@
         <v>181</v>
       </c>
       <c r="B182" s="5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>$75k–$85k</t>
+          <t>$88k–$120k</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VTG</t>
+          <t>Northrop Grumman</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Associate Software Engineer/Software Engineer</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Manassas, VA</t>
+          <t>Redondo Beach, CA, Palmdale, CA, Oklahoma City, OK, San Diego, CA, El Segundo, CA</t>
         </is>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Technical stack (Python backend, gRPC/REST, Kubernetes, scaling and GPU work) overlaps the candidate's backend/infra profile, but the disclosed $75-80k base is far below the ~120k floor, the role requires ability to obtain a Secret clearance, and it is an immediate-fill position rather than a 2027 new-grad opening.</t>
+          <t>Requires an approved Top Secret clearance plus Program Special Access at start (candidate has none) and the Associate pay band tops out below the ~120k floor, making this defense-embedded role off-profile despite the matching 2027 grad timing.</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>The posting itself discloses a $75,000-$80,000 starting pay range, so confidence is high. Defense services integrators like VTG typically offer negligible equity and small or no signing bonus at entry level, so total comp lands at or just slightly above the stated base band.</t>
+          <t>Posted Associate Engineer Software range $62.3k-$114.4k; SoCal new-grad offers at defense primes typically land ~$85-100k base plus a small discretionary bonus and no equity, so total comp clusters well under big-tech tiers. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -12747,7 +12751,7 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12756,43 +12760,43 @@
         <v>182</v>
       </c>
       <c r="B183" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>$80k–$105k</t>
+          <t>$75k–$85k</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Broadcom Limited</t>
+          <t>VTG</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Support Engineer - Mainframe</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Lisle, IL</t>
+          <t>Manassas, VA</t>
         </is>
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Customer-facing mainframe (z/OS/JCL/COBOL) support and ticket-triage role rather than backend/distributed-systems development, so none of the candidate's Rust/Raft, microservices, or AI-infra strengths apply, and it's a separate career track from SWE.</t>
+          <t>Technical stack (Python backend, gRPC/REST, Kubernetes, scaling and GPU work) overlaps the candidate's backend/infra profile, but the disclosed $75-80k base is far below the ~120k floor, the role requires ability to obtain a Secret clearance, and it is an immediate-fill position rather than a 2027 new-grad opening.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Broadcom is a strong-paying infra company for its core engineering ladders, but support engineering sits on a materially lower band than SWE, and Lisle IL (Chicago suburb) carries non-tier-1 geo pay. Posting scraped as title-only, so this band is inferred from company tier + role family + location rather than stated comp; treat as a wide estimate. Falls well below the candidate's ~130-165k anchor.</t>
+          <t>The posting itself discloses a $75,000-$80,000 starting pay range, so confidence is high. Defense services integrators like VTG typically offer negligible equity and small or no signing bonus at entry level, so total comp lands at or just slightly above the stated base band.</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -12831,29 +12835,29 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>The Boeing Company</t>
+          <t>Broadcom Limited</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Embedded Software Engineer - Government Training</t>
+          <t>Support Engineer - Mainframe</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Berkeley, MO, Hazelwood, MO</t>
+          <t>Lisle, IL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Embedded/firmware defense work in suburban St. Louis that almost certainly requires clearance eligibility — hits two explicit low-fit categories and offers none of the candidate's backend/distributed-systems/AI-infra strengths.</t>
+          <t>Customer-facing mainframe (z/OS/JCL/COBOL) support and ticket-triage role rather than backend/distributed-systems development, so none of the candidate's Rust/Raft, microservices, or AI-infra strengths apply, and it's a separate career track from SWE.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Boeing is a traditional aerospace/defense employer paying well below tech scales: new-grad SWE base typically ~$78-95k plus a ~5-10% incentive target and no meaningful equity; cleared embedded roles trend to the top of that band. Falls below the candidate's ~$120k floor.</t>
+          <t>Broadcom is a strong-paying infra company for its core engineering ladders, but support engineering sits on a materially lower band than SWE, and Lisle IL (Chicago suburb) carries non-tier-1 geo pay. Posting scraped as title-only, so this band is inferred from company tier + role family + location rather than stated comp; treat as a wide estimate. Falls well below the candidate's ~130-165k anchor.</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -12888,43 +12892,43 @@
         <v>184</v>
       </c>
       <c r="B185" s="5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>$52k–$82k</t>
+          <t>$80k–$105k</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>The Boeing Company</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Officer</t>
+          <t>Embedded Software Engineer - Government Training</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Berkeley, MO, Hazelwood, MO</t>
         </is>
       </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Backend Java/Spring Boot/Kafka/Kubernetes elements are on-profile, but the role is Toronto-based (candidate is US-authorized with no Canadian work authorization), targets immediate 0-2 yr hires rather than a mid-2027 new-grad start, leans heavily full-stack/React, and its posted CAD 67k-110k range converts to roughly USD 48-79k — far under the ~120k floor.</t>
+          <t>Embedded/firmware defense work in suburban St. Louis that almost certainly requires clearance eligibility — hits two explicit low-fit categories and offers none of the candidate's backend/distributed-systems/AI-infra strengths.</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Posting states CAD 67,000-109,750 base; a new-grad Officer would sit low-to-mid (~CAD 70-95k) plus a modest 5-10% bank bonus, which at ~0.72 USD/CAD is roughly USD 52-82k. State Street is a lower-paying custody-bank tier and Toronto comp trails the US market for equivalent roles.</t>
+          <t>Boeing is a traditional aerospace/defense employer paying well below tech scales: new-grad SWE base typically ~$78-95k plus a ~5-10% incentive target and no meaningful equity; cleared embedded roles trend to the top of that band. Falls below the candidate's ~$120k floor.</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -12945,7 +12949,7 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -12954,38 +12958,38 @@
         <v>185</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>$120k–$150k</t>
+          <t>$52k–$82k</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Johns Hopkins Applied Physics Laboratory</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AI/ML Data Scientist/Engineer New Grad - Analytic Capabilities</t>
+          <t>Full Stack Software Engineer - Officer</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Laurel, MD</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Hard-blocked on two of the candidate's stated constraints — the posting requires a PhD (he's a May 2027 BS/MS grad) and an Interim Secret clearance by start date leading to Top Secret, which he doesn't have and listed as a low-fit criterion; the 2026 start date also misses his timeline, despite genuinely relevant LLM/RAG/agentic and Python/Java overlap.</t>
+          <t>Backend Java/Spring Boot/Kafka/Kubernetes elements are on-profile, but the role is Toronto-based (candidate is US-authorized with no Canadian work authorization), targets immediate 0-2 yr hires rather than a mid-2027 new-grad start, leans heavily full-stack/React, and its posted CAD 67k-110k range converts to roughly USD 48-79k — far under the ~120k floor.</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>JHU/APL is a non-profit university-affiliated research center (UARC) — solid but below big-tech pay, with strong retirement/benefits offsetting base. Posted range ($105k–$245k) spans all levels and is not indicative. PhD new-grad hires at APL typically land ~$120–150k base with limited bonus/equity (none); a BS/MS new grad would be closer to $90–110k. Estimate given for the PhD-level posting as written; moderate confidence.</t>
+          <t>Posting states CAD 67,000-109,750 base; a new-grad Officer would sit low-to-mid (~CAD 70-95k) plus a modest 5-10% bank bonus, which at ~0.72 USD/CAD is roughly USD 52-82k. State Street is a lower-paying custody-bank tier and Toronto comp trails the US market for equivalent roles.</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -13011,7 +13015,7 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13020,38 +13024,38 @@
         <v>186</v>
       </c>
       <c r="B187" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>$88k–$115k</t>
+          <t>$120k–$150k</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Johns Hopkins Applied Physics Laboratory</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Software Engineer - iOS</t>
+          <t>AI/ML Data Scientist/Engineer New Grad - Analytic Capabilities</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tempe, AZ, Dunwoody, GA, Richardson, TX, Bloomington, IL</t>
+          <t>Laurel, MD</t>
         </is>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Swift/SwiftUI/UIKit iOS mobile client role is squarely in the candidate's low-fit category (frontend/UI-heavy) with no backend, distributed-systems, or AI-infra overlap, and it's hybrid-only in Tempe/Dunwoody/Richardson/Bloomington with a below-anchor pay band.</t>
+          <t>Hard-blocked on two of the candidate's stated constraints — the posting requires a PhD (he's a May 2027 BS/MS grad) and an Interim Secret clearance by start date leading to Top Secret, which he doesn't have and listed as a low-fit criterion; the 2026 start date also misses his timeline, despite genuinely relevant LLM/RAG/agentic and Python/Java overlap.</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Posting discloses $81k-$123k base with the high end explicitly limited to candidates with significant relevant experience, plus up to 15% incentive pay. A new grad would land in the bottom third of base (~$82-95k), giving roughly $90-108k TC as the likely center; band widened to $88-115k for offer variance. State Farm is a non-tech Fortune 50 insurer paying well below big-tech new-grad levels, so this falls under the candidate's ~$120k floor.</t>
+          <t>JHU/APL is a non-profit university-affiliated research center (UARC) — solid but below big-tech pay, with strong retirement/benefits offsetting base. Posted range ($105k–$245k) spans all levels and is not indicative. PhD new-grad hires at APL typically land ~$120–150k base with limited bonus/equity (none); a BS/MS new grad would be closer to $90–110k. Estimate given for the PhD-level posting as written; moderate confidence.</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -13077,7 +13081,7 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -13086,38 +13090,38 @@
         <v>187</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>$80k–$100k</t>
+          <t>$88k–$115k</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Software Engineer - iOS</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA</t>
+          <t>Tempe, AZ, Dunwoody, GA, Richardson, TX, Bloomington, IL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Safety-critical real-time embedded avionics work in C and MATLAB/Simulink under DO-178B/C, onsite in Cedar Rapids IA, is squarely in the candidate's low-fit "embedded-only" category with no distributed-systems, cloud, or AI-infra overlap, and reads as an immediate-start req rather than a May 2027 new-grad pipeline.</t>
+          <t>Swift/SwiftUI/UIKit iOS mobile client role is squarely in the candidate's low-fit category (frontend/UI-heavy) with no backend, distributed-systems, or AI-infra overlap, and it's hybrid-only in Tempe/Dunwoody/Richardson/Bloomington with a below-anchor pay band.</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>RTX/Collins Aerospace is a defense prime paying traditional-industry scale, not tech-company scale: entry-level Software Engineer 1 base is roughly $75-92k in a low-cost-of-living market like Cedar Rapids, IA, plus a modest ~3-5% annual bonus and effectively no equity for new grads. This falls well below the candidate's ~$130k anchor and beneath the ~$120k low-match floor. Estimate only.</t>
+          <t>Posting discloses $81k-$123k base with the high end explicitly limited to candidates with significant relevant experience, plus up to 15% incentive pay. A new grad would land in the bottom third of base (~$82-95k), giving roughly $90-108k TC as the likely center; band widened to $88-115k for offer variance. State Farm is a non-tech Fortune 50 insurer paying well below big-tech new-grad levels, so this falls under the candidate's ~$120k floor.</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -13143,7 +13147,7 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -13156,7 +13160,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>$78k–$98k</t>
+          <t>$80k–$100k</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -13171,19 +13175,19 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Annapolis, MD</t>
+          <t>Cedar Rapids, IA</t>
         </is>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Defense avionics C++/full-stack work rather than distributed systems or AI infra, the req is reserved for an RTX intern converting to FT (closing in ~1 day), and the entire posted range tops out below the candidate's ~$130k anchor.</t>
+          <t>Safety-critical real-time embedded avionics work in C and MATLAB/Simulink under DO-178B/C, onsite in Cedar Rapids IA, is squarely in the candidate's low-fit "embedded-only" category with no distributed-systems, cloud, or AI-infra overlap, and reads as an immediate-start req rather than a May 2027 new-grad pipeline.</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Posting states $62,900–$119,700 across all experience levels; a SWE 1 new grad sits near the low-middle. RTX is a traditional aerospace/defense primer with no equity for entry-level and a small (~2-5%) bonus, so realistic new-grad TC is roughly $80-95k base plus modest bonus. Estimate, not fact.</t>
+          <t>RTX/Collins Aerospace is a defense prime paying traditional-industry scale, not tech-company scale: entry-level Software Engineer 1 base is roughly $75-92k in a low-cost-of-living market like Cedar Rapids, IA, plus a modest ~3-5% annual bonus and effectively no equity for new grads. This falls well below the candidate's ~$130k anchor and beneath the ~$120k low-match floor. Estimate only.</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -13237,19 +13241,19 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC</t>
+          <t>Annapolis, MD</t>
         </is>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Embedded/DO-178 avionics work onsite in Winston-Salem NC, explicitly earmarked for an RTX intern converting to full-time — off-profile for a backend/distributed-systems/AI-infra candidate and far below his TC anchor.</t>
+          <t>Defense avionics C++/full-stack work rather than distributed systems or AI infra, the req is reserved for an RTX intern converting to FT (closing in ~1 day), and the entire posted range tops out below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Posting lists 57.2K-108.8K across all experience levels; defense-prime (RTX/Raytheon) new-grad SWE base typically ~75-90K in a low-COL NC location plus a modest 3-5% incentive target and 401k match. Estimate, not fact.</t>
+          <t>Posting states $62,900–$119,700 across all experience levels; a SWE 1 new grad sits near the low-middle. RTX is a traditional aerospace/defense primer with no equity for entry-level and a small (~2-5%) bonus, so realistic new-grad TC is roughly $80-95k base plus modest bonus. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -13275,7 +13279,7 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13284,38 +13288,38 @@
         <v>190</v>
       </c>
       <c r="B191" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>$92k–$110k</t>
+          <t>$78k–$98k</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Technology Development Program New Grad - Data &amp; Analytics Engineering Track</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, St. Louis, MO, Bloomfield, CT</t>
+          <t>Winston-Salem, NC</t>
         </is>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Hard-gated to candidates who already completed a Cigna internship, and the track is data/analytics engineering (ETL, warehousing, SQL/Spark) rather than the candidate's backend/distributed-systems/AI-infra profile, at hybrid NJ/MO/CT sites with no relocation and comp far below the ~130k anchor.</t>
+          <t>Embedded/DO-178 avionics work onsite in Winston-Salem NC, explicitly earmarked for an RTX intern converting to full-time — off-profile for a backend/distributed-systems/AI-infra candidate and far below his TC anchor.</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Posting states base directly: $88,000 for bachelor's and $100,000 for master's graduates, plus eligibility for an annual bonus (typically low single-digit % at this level for a large health insurer); no equity typical for Cigna new-grad rotational programs. Band reflects bachelor's-with-bonus at the low end through master's-with-bonus at the high end.</t>
+          <t>Posting lists 57.2K-108.8K across all experience levels; defense-prime (RTX/Raytheon) new-grad SWE base typically ~75-90K in a low-COL NC location plus a modest 3-5% incentive target and 401k match. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -13341,7 +13345,7 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -13354,39 +13358,39 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>$85k–$110k</t>
+          <t>$92k–$110k</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Technology Development Program New Grad - Data &amp; Analytics Engineering Track</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Windsor Locks, CT</t>
+          <t>Morris Plains, NJ, St. Louis, MO, Bloomfield, CT</t>
         </is>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Defense-prime (Collins Aerospace) role that is likely embedded/avionics with citizenship/clearance expectations and is pitched at an experienced "SWE 2" level, not a 2027 new-grad backend/distributed-systems opening.</t>
+          <t>Hard-gated to candidates who already completed a Cigna internship, and the track is data/analytics engineering (ETL, warehousing, SQL/Spark) rather than the candidate's backend/distributed-systems/AI-infra profile, at hybrid NJ/MO/CT sites with no relocation and comp far below the ~130k anchor.</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>RTX/Collins pays traditional defense-contractor scale: entry-level SWE base roughly $80-100k in Connecticut plus a modest bonus and negligible equity. This sits well below the candidate's ~$120k floor and far under the $130-165k anchor. Estimate from general knowledge of defense-prime comp tiers, not from the posting.</t>
+          <t>Posting states base directly: $88,000 for bachelor's and $100,000 for master's graduates, plus eligibility for an annual bonus (typically low single-digit % at this level for a large health insurer); no equity typical for Cigna new-grad rotational programs. Band reflects bachelor's-with-bonus at the low end through master's-with-bonus at the high end.</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -13407,7 +13411,7 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13416,43 +13420,43 @@
         <v>192</v>
       </c>
       <c r="B193" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>$70k–$95k</t>
+          <t>$85k–$110k</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Dunn Solutions Group</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Raleigh, NC</t>
+          <t>Windsor Locks, CT</t>
         </is>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Java is a candidate strength, but this is a client-facing consulting role emphasizing UI/web development and "Java Applets"-era skills with zero distributed-systems, cloud, or AI-infra content, it wants 2-5 years of experience for an immediate start rather than a May 2027 new grad, and the expected comp sits roughly $40-60k below the candidate's floor.</t>
+          <t>Defense-prime (Collins Aerospace) role that is likely embedded/avionics with citizenship/clearance expectations and is pitched at an experienced "SWE 2" level, not a 2027 new-grad backend/distributed-systems opening.</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Small private IT consulting firm (SAP/Liferay/Informatica partner) in Raleigh, NC — a low-tier compensation market segment well below product-company scale. Consulting-shop Java dev roles at the 1-5 yr level in Raleigh typically pay ~$70-90k base with a modest bonus; no equity. Band is wide because the company is small and non-public with no reliable comp data, but essentially all plausible outcomes fall far below the candidate's ~$130k anchor.</t>
+          <t>RTX/Collins pays traditional defense-contractor scale: entry-level SWE base roughly $80-100k in Connecticut plus a modest bonus and negligible equity. This sits well below the candidate's ~$120k floor and far under the $130-165k anchor. Estimate from general knowledge of defense-prime comp tiers, not from the posting.</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -13473,7 +13477,7 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -13486,34 +13490,34 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>$75k–$95k</t>
+          <t>$70k–$95k</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Dunn Solutions Group</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Systems Analyst - Leap Program</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Westlake, TX, Durham, NC, Merrimack, NH</t>
+          <t>Raleigh, NC</t>
         </is>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Timing (July 2027 new-grad start) and the CS-degree requirement line up, but the role is systems/business analysis — requirements gathering, user stories, Visio diagrams, test-case execution — with no coding, distributed-systems, or infra work, which wastes the candidate's Rust/Raft/backend/AI-infra strengths and sits well below his ~$130k TC anchor; the non-preferred onsite locations (Westlake/Durham/Merrimack) and no-sponsorship-but-that's-fine note are secondary concerns.</t>
+          <t>Java is a candidate strength, but this is a client-facing consulting role emphasizing UI/web development and "Java Applets"-era skills with zero distributed-systems, cloud, or AI-infra content, it wants 2-5 years of experience for an immediate start rather than a May 2027 new grad, and the expected comp sits roughly $40-60k below the candidate's floor.</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Fidelity is a stable non-tech-tier financial firm; new-grad SWE there typically lands ~$85-105k TC, and analyst-track roles (Leap Systems Analyst) usually pay a notch below engineering, roughly $75-90k base plus a small bonus. Estimate, not fact — no published band in the posting.</t>
+          <t>Small private IT consulting firm (SAP/Liferay/Informatica partner) in Raleigh, NC — a low-tier compensation market segment well below product-company scale. Consulting-shop Java dev roles at the 1-5 yr level in Raleigh typically pay ~$70-90k base with a modest bonus; no equity. Band is wide because the company is small and non-public with no reliable comp data, but essentially all plausible outcomes fall far below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -13539,7 +13543,7 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13548,38 +13552,38 @@
         <v>194</v>
       </c>
       <c r="B195" s="5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>$52k–$72k</t>
+          <t>$75k–$95k</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>FactSet</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Software Engineer 1 - Infrastructure</t>
+          <t>Systems Analyst - Leap Program</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Westlake, TX, Durham, NC, Merrimack, NH</t>
         </is>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>The infrastructure work (Tier 0 hybrid-cloud, Kubernetes, Terraform, AWS, Linux, microservice routing, internal developer platform) is a near-ideal technical match for this candidate's platform/infra strengths, but the role is London, UK with a mandatory 3-day/week hybrid onsite requirement — the candidate is US-authorized with no UK work authorization — and FactSet's comp tier sits far below the ~130k TC anchor.</t>
+          <t>Timing (July 2027 new-grad start) and the CS-degree requirement line up, but the role is systems/business analysis — requirements gathering, user stories, Visio diagrams, test-case execution — with no coding, distributed-systems, or infra work, which wastes the candidate's Rust/Raft/backend/AI-infra strengths and sits well below his ~$130k TC anchor; the non-preferred onsite locations (Westlake/Durham/Merrimack) and no-sponsorship-but-that's-fine note are secondary concerns.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>FactSet is a mid-tier financial-data/software firm (S&amp;P 500 but not a top-paying fintech or HFT); US new-grad SWE offers typically land ~$85-105k TC, while London new-grad SWE bands run materially lower at roughly £40-55k base plus small bonus, converting to roughly $52-72k USD. Band is kept wide because FactSet-specific UK new-grad data points are sparse and GBP/USD conversion adds noise.</t>
+          <t>Fidelity is a stable non-tech-tier financial firm; new-grad SWE there typically lands ~$85-105k TC, and analyst-track roles (Leap Systems Analyst) usually pay a notch below engineering, roughly $75-90k base plus a small bonus. Estimate, not fact — no published band in the posting.</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -13614,38 +13618,38 @@
         <v>195</v>
       </c>
       <c r="B196" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>$68k–$92k</t>
+          <t>$52k–$72k</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>DecisionPoint Corporation</t>
+          <t>FactSet</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Entry-level Software Developer</t>
+          <t>Software Engineer 1 - Infrastructure</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Remote in USA</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>DoD contractor sustainment role with clearance requirement and heavy Angular/front-end emphasis, hiring an experienced-now candidate rather than a mid-2027 new grad, and pay tier far below the candidate's ~130k anchor.</t>
+          <t>The infrastructure work (Tier 0 hybrid-cloud, Kubernetes, Terraform, AWS, Linux, microservice routing, internal developer platform) is a near-ideal technical match for this candidate's platform/infra strengths, but the role is London, UK with a mandatory 3-day/week hybrid onsite requirement — the candidate is US-authorized with no UK work authorization — and FactSet's comp tier sits far below the ~130k TC anchor.</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Small/mid-size federal IT services contractor on cost-plus DoD contracts; entry-level dev salaries typically high-$60s to low-$90s with negligible bonus/equity. Wide band because the company publishes no leveling data and the role is remote-nationwide; an in-hand Secret clearance would push toward the top. Estimate, not fact.</t>
+          <t>FactSet is a mid-tier financial-data/software firm (S&amp;P 500 but not a top-paying fintech or HFT); US new-grad SWE offers typically land ~$85-105k TC, while London new-grad SWE bands run materially lower at roughly £40-55k base plus small bonus, converting to roughly $52-72k USD. Band is kept wide because FactSet-specific UK new-grad data points are sparse and GBP/USD conversion adds noise.</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -13671,7 +13675,7 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -13684,34 +13688,34 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>$70k–$90k</t>
+          <t>$68k–$92k</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>D.R. Horton</t>
+          <t>DecisionPoint Corporation</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Application Developer 1</t>
+          <t>Entry-level Software Developer</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Arlington, TX</t>
+          <t>Remote in USA</t>
         </is>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Internal .NET/C#/React business-application and legacy-app maintenance work at a homebuilder's corporate IT group, which has essentially no overlap with the candidate's backend/distributed-systems, cloud-infra, or AI-platform focus and sits at a much lower comp and technical tier.</t>
+          <t>DoD contractor sustainment role with clearance requirement and heavy Angular/front-end emphasis, hiring an experienced-now candidate rather than a mid-2027 new grad, and pay tier far below the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Non-tech Fortune 500 homebuilder; corporate IT cost-center role in the Dallas-Fort Worth market, posting accepts a HS diploma with 0-1 years experience. Estimate assumes ~$70-85k base plus modest bonus/ESPP; band is approximate since D.R. Horton IT comp is not widely reported on levels.fyi.</t>
+          <t>Small/mid-size federal IT services contractor on cost-plus DoD contracts; entry-level dev salaries typically high-$60s to low-$90s with negligible bonus/equity. Wide band because the company publishes no leveling data and the role is remote-nationwide; an in-hand Secret clearance would push toward the top. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -13737,7 +13741,7 @@
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -13746,38 +13750,38 @@
         <v>197</v>
       </c>
       <c r="B198" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>$78k–$100k</t>
+          <t>$70k–$90k</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>PNC Financial Services</t>
+          <t>D.R. Horton</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Software Engineer Associate Mainframe Testing/Selenium</t>
+          <t>Application Developer 1</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Dallas, TX, Pittsburgh, PA, Strongsville, OH</t>
+          <t>Arlington, TX</t>
         </is>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Mainframe/Selenium test-automation QA work at an in-office bank is far off the candidate's backend, distributed-systems, and AI-infra profile, and the req appears to be an immediate-start associate role rather than a May 2027 new-grad position.</t>
+          <t>Internal .NET/C#/React business-application and legacy-app maintenance work at a homebuilder's corporate IT group, which has essentially no overlap with the candidate's backend/distributed-systems, cloud-infra, or AI-platform focus and sits at a much lower comp and technical tier.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Non-tech financial-services tier; posted base band $63.75k-$127.5k is wide across geo/level, so entry-level associate realistically lands ~$70-88k base plus ~5-10% bonus and 401k match/pension. Well below the ~$130k target anchor.</t>
+          <t>Non-tech Fortune 500 homebuilder; corporate IT cost-center role in the Dallas-Fort Worth market, posting accepts a HS diploma with 0-1 years experience. Estimate assumes ~$70-85k base plus modest bonus/ESPP; band is approximate since D.R. Horton IT comp is not widely reported on levels.fyi.</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -13803,7 +13807,7 @@
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -13816,34 +13820,34 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>$80k–$100k</t>
+          <t>$78k–$100k</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>MSA Safety</t>
+          <t>PNC Financial Services</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Embedded Software Engineer 1/2 - Fire Service</t>
+          <t>Software Engineer Associate Mainframe Testing/Selenium</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Cranberry Township, PA</t>
+          <t>Dallas, TX, Pittsburgh, PA, Strongsville, OH</t>
         </is>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Embedded firmware for fire-service safety hardware is explicitly in the candidate's low-fit category (embedded-only, no distributed systems/backend/AI-infra surface), and the scraped posting returned a 404 so the req appears closed.</t>
+          <t>Mainframe/Selenium test-automation QA work at an in-office bank is far off the candidate's backend, distributed-systems, and AI-infra profile, and the req appears to be an immediate-start associate role rather than a May 2027 new-grad position.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>MSA Safety is a non-tech industrial safety equipment manufacturer headquartered in the Pittsburgh area; entry-level (Engineer 1/2) embedded software base pay there is typically ~$75-92k with a modest annual bonus and no equity, consistent with Midwest/Rust Belt manufacturing pay bands rather than tech-company scales. Estimate, not fact — the posting itself was a 404 with no comp data.</t>
+          <t>Non-tech financial-services tier; posted base band $63.75k-$127.5k is wide across geo/level, so entry-level associate realistically lands ~$70-88k base plus ~5-10% bonus and 401k match/pension. Well below the ~$130k target anchor.</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -13869,7 +13873,7 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13878,38 +13882,38 @@
         <v>199</v>
       </c>
       <c r="B200" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>$80k–$112k</t>
+          <t>$80k–$100k</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>The Boeing Company</t>
+          <t>MSA Safety</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Embedded Software Engineer</t>
+          <t>Embedded Software Engineer 1/2 - Fire Service</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Berkeley, MO, Hazelwood, MO</t>
+          <t>Cranberry Township, PA</t>
         </is>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Embedded C++/hardware-integration defense role requiring a US Secret clearance and 100% onsite work in Hazelwood/Berkeley MO — it matches the candidate's explicit low-fit categories (hardware/embedded-only, clearance-required) and leverages none of his distributed-systems, backend, or AI-infra strengths.</t>
+          <t>Embedded firmware for fire-service safety hardware is explicitly in the candidate's low-fit category (embedded-only, no distributed systems/backend/AI-infra surface), and the scraped posting returned a 404 so the req appears closed.</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Posting explicitly lists Entry-level (Level 1) base pay range of $78,200-$105,800. Boeing is a traditional defense/aerospace payer: modest annual incentive (~3-6%), no equity for entry level, occasional signing bonus for eligible external candidates. Band reflects base plus small variable comp. Estimate, not fact — top of range is unlikely for a new grad without prior relevant experience, and the whole band sits below the candidate's ~$130k anchor.</t>
+          <t>MSA Safety is a non-tech industrial safety equipment manufacturer headquartered in the Pittsburgh area; entry-level (Engineer 1/2) embedded software base pay there is typically ~$75-92k with a modest annual bonus and no equity, consistent with Midwest/Rust Belt manufacturing pay bands rather than tech-company scales. Estimate, not fact — the posting itself was a 404 with no comp data.</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -13944,38 +13948,38 @@
         <v>200</v>
       </c>
       <c r="B201" s="5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>$75k–$98k</t>
+          <t>$80k–$112k</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>L3Harris Technologies</t>
+          <t>The Boeing Company</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Embedded Software Engineer</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Greenville, TX</t>
+          <t>Berkeley, MO, Hazelwood, MO</t>
         </is>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Embedded real-time firmware for tactical radios (VxWorks/QNX, hardware-software interfaces) is squarely in the candidate's role_fit_low bucket, the defense-prime TC band sits far below the ~$120k floor, and a Greenville TX radio program almost certainly gates on a clearance the candidate doesn't hold — the only real positives are the new-grad level and C/C++ overlap.</t>
+          <t>Embedded C++/hardware-integration defense role requiring a US Secret clearance and 100% onsite work in Hazelwood/Berkeley MO — it matches the candidate's explicit low-fit categories (hardware/embedded-only, clearance-required) and leverages none of his distributed-systems, backend, or AI-infra strengths.</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>L3Harris is a defense prime with public-sector pay bands well below tech-industry rates; associate/new-grad SWE base in a low-cost Texas market typically lands ~$72-90k, with a small bonus and no meaningful equity. Band is moderately wide to cover degree/level variation, but the ceiling is confidently far under the candidate's ~$130k anchor.</t>
+          <t>Posting explicitly lists Entry-level (Level 1) base pay range of $78,200-$105,800. Boeing is a traditional defense/aerospace payer: modest annual incentive (~3-6%), no equity for entry level, occasional signing bonus for eligible external candidates. Band reflects base plus small variable comp. Estimate, not fact — top of range is unlikely for a new grad without prior relevant experience, and the whole band sits below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -14001,7 +14005,7 @@
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -14010,38 +14014,38 @@
         <v>201</v>
       </c>
       <c r="B202" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>$92k–$110k</t>
+          <t>$75k–$98k</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>L3Harris Technologies</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Technology Development Program - Software Engineering Track</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Bloomington, MN, Austin, TX, Morris Plains, NJ, St. Louis, MO, Bloomfield, CT</t>
+          <t>Greenville, TX</t>
         </is>
       </c>
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Hard-gated to candidates who already completed a Cigna internship (which he has not), and the stated $88K bachelor's base lands well below his ~120K floor — the AI/coding content is otherwise a reasonable but shallow match for a distributed-systems-focused profile.</t>
+          <t>Embedded real-time firmware for tactical radios (VxWorks/QNX, hardware-software interfaces) is squarely in the candidate's role_fit_low bucket, the defense-prime TC band sits far below the ~$120k floor, and a Greenville TX radio program almost certainly gates on a clearance the candidate doesn't hold — the only real positives are the new-grad level and C/C++ overlap.</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Posting states explicit base of $88,000 (bachelor's) / $100,000 (master's) for TECDP, plus benefits and an anticipated annual bonus (typically ~5-10% at Cigna for early-career). Low end assumes bachelor's base with minimal bonus; high end assumes master's base plus bonus. No equity component for this program; healthcare/insurance sector pays well below tech-company new-grad bands.</t>
+          <t>L3Harris is a defense prime with public-sector pay bands well below tech-industry rates; associate/new-grad SWE base in a low-cost Texas market typically lands ~$72-90k, with a small bonus and no meaningful equity. Band is moderately wide to cover degree/level variation, but the ceiling is confidently far under the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -14080,38 +14084,34 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>$85k–$110k</t>
+          <t>$92k–$110k</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Johns Hopkins Applied Physics Laboratory</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Intelligent Systems Development Engineer - Intelligent Combat Platforms Group</t>
+          <t>Technology Development Program - Software Engineering Track</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Laurel, MD</t>
+          <t>Bloomington, MN, Austin, TX, Morris Plains, NJ, St. Louis, MO, Bloomfield, CT</t>
         </is>
       </c>
       <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>start date and can ultimately obtain top</t>
-        </is>
-      </c>
+      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Requires obtaining an Interim Secret/Top Secret clearance by start date (an explicit candidate exclusion) and the role is .NET/C#/Blazor full-stack with React/HTML/CSS UI design work rather than backend, distributed systems, or AI-infra engineering; on-site-only Laurel, MD with no telework adds a further mismatch.</t>
+          <t>Hard-gated to candidates who already completed a Cigna internship (which he has not), and the stated $88K bachelor's base lands well below his ~120K floor — the AI/coding content is otherwise a reasonable but shallow match for a distributed-systems-focused profile.</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>JHU APL is a non-profit university-affiliated FFRDC: new-grad base typically high-$80s to low-$100s, no equity and minimal bonus, offset by unusually strong retirement contributions and education benefits. Cash TC therefore falls below the candidate's ~$120k low-match floor even at the top of the band. Estimate based on general knowledge of defense/FFRDC compensation tiers, not a posted range.</t>
+          <t>Posting states explicit base of $88,000 (bachelor's) / $100,000 (master's) for TECDP, plus benefits and an anticipated annual bonus (typically ~5-10% at Cigna for early-career). Low end assumes bachelor's base with minimal bonus; high end assumes master's base plus bonus. No equity component for this program; healthcare/insurance sector pays well below tech-company new-grad bands.</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14160,7 +14160,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Navigation Systems Analyst/Engineer</t>
+          <t>Intelligent Systems Development Engineer - Intelligent Combat Platforms Group</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -14171,17 +14171,17 @@
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
-          <t>start date and can ultimately obtain a to</t>
+          <t>start date and can ultimately obtain top</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Navigation/geophysics systems analysis (Kalman filters, MATLAB, sensor modeling, trade studies) for Navy submarine platforms is far from the candidate's backend/distributed-systems/AI-infra profile, and the req targets 2026 grads with a Secret clearance required by start date, on-site in Laurel MD with no telework.</t>
+          <t>Requires obtaining an Interim Secret/Top Secret clearance by start date (an explicit candidate exclusion) and the role is .NET/C#/Blazor full-stack with React/HTML/CSS UI design work rather than backend, distributed systems, or AI-infra engineering; on-site-only Laurel, MD with no telework adds a further mismatch.</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>JHU/APL is a non-profit university-affiliated research center (UARC/FFRDC): salary-only comp with no equity, strong benefits and retirement, but pay well below big-tech/product-company scales. BS new grads typically ~$85-95k, MS ~$95-110k. Estimate based on general knowledge of defense-lab/FFRDC pay bands, not a verified band for this req; falls below the candidate's ~$130k anchor.</t>
+          <t>JHU APL is a non-profit university-affiliated FFRDC: new-grad base typically high-$80s to low-$100s, no equity and minimal bonus, offset by unusually strong retirement contributions and education benefits. Cash TC therefore falls below the candidate's ~$120k low-match floor even at the top of the band. Estimate based on general knowledge of defense/FFRDC compensation tiers, not a posted range.</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -14216,38 +14216,42 @@
         <v>204</v>
       </c>
       <c r="B205" s="5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>$75k–$95k</t>
+          <t>$85k–$110k</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Johns Hopkins Applied Physics Laboratory</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Navigation Systems Analyst/Engineer</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA</t>
+          <t>Laurel, MD</t>
         </is>
       </c>
       <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>start date and can ultimately obtain a to</t>
+        </is>
+      </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Embedded/real-time C/C++ avionics work in onsite Cedar Rapids, IA is squarely in the candidate's low-fit bucket with no distributed-systems, backend, cloud, or AI overlap — and the req is explicitly reserved for an RTX intern converting to full-time.</t>
+          <t>Navigation/geophysics systems analysis (Kalman filters, MATLAB, sensor modeling, trade studies) for Navy submarine platforms is far from the candidate's backend/distributed-systems/AI-infra profile, and the req targets 2026 grads with a Secret clearance required by start date, on-site in Laurel MD with no telework.</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Posting lists $57.2k-$108.8k across all experience levels; defense-prime new-grad SWE I in a low-COL metro typically lands ~$72-88k base plus a small non-guaranteed annual incentive and 401k match, with no meaningful equity. Well below the candidate's ~$130k anchor.</t>
+          <t>JHU/APL is a non-profit university-affiliated research center (UARC/FFRDC): salary-only comp with no equity, strong benefits and retirement, but pay well below big-tech/product-company scales. BS new grads typically ~$85-95k, MS ~$95-110k. Estimate based on general knowledge of defense-lab/FFRDC pay bands, not a verified band for this req; falls below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -14273,7 +14277,7 @@
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -14282,42 +14286,38 @@
         <v>205</v>
       </c>
       <c r="B206" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>$130k–$165k</t>
+          <t>$75k–$95k</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Johns Hopkins Applied Physics Laboratory</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Software Engineering/ML/Data Scientist Graduate - Intelligence Systems</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Laurel, MD</t>
+          <t>Cedar Rapids, IA</t>
         </is>
       </c>
       <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>start date and can ultimately obtain a to</t>
-        </is>
-      </c>
+      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Requires a completed PhD, U.S. security clearance (Interim Secret → Top Secret), and a 2026 start — all three are disqualifiers for a clearance-free May 2027 BS/MS new grad, despite topical overlap with his AI/ML and software engineering background.</t>
+          <t>Embedded/real-time C/C++ avionics work in onsite Cedar Rapids, IA is squarely in the candidate's low-fit bucket with no distributed-systems, backend, cloud, or AI overlap — and the req is explicitly reserved for an RTX intern converting to full-time.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Posted range $105k–$245k spans all levels; APL is a non-profit FFRDC/UARC paying below big-tech but solidly for cleared PhD technical staff, so PhD entry typically lands ~$130–160k salary with strong retirement contributions and no equity. APL's BS/MS new-grad band is lower, roughly $95k–$120k, which would fall below the candidate's ~$130k anchor.</t>
+          <t>Posting lists $57.2k-$108.8k across all experience levels; defense-prime new-grad SWE I in a low-COL metro typically lands ~$72-88k base plus a small non-guaranteed annual incentive and 401k match, with no meaningful equity. Well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14352,38 +14352,42 @@
         <v>206</v>
       </c>
       <c r="B207" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>$72k–$95k</t>
+          <t>$130k–$165k</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Johns Hopkins Applied Physics Laboratory</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Software Engineering/ML/Data Scientist Graduate - Intelligence Systems</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Melbourne, FL</t>
+          <t>Laurel, MD</t>
         </is>
       </c>
       <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>start date and can ultimately obtain a to</t>
+        </is>
+      </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>C#/.NET + Vue/SQL Server internal-tools/ERP work at a defense prime has essentially no overlap with the candidate's backend/distributed-systems/AI-infra profile, and the req is explicitly reserved for an RTX intern converting to full-time.</t>
+          <t>Requires a completed PhD, U.S. security clearance (Interim Secret → Top Secret), and a 2026 start — all three are disqualifiers for a clearance-free May 2027 BS/MS new grad, despite topical overlap with his AI/ML and software engineering background.</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Posting states a $57.2k-$108.8k salary range spanning all experience levels; a new grad realistically lands low-to-mid in that band. Defense primes (RTX/Raytheon) pay well below big-tech/Wayfair tier, Melbourne FL has no metro premium, and total comp adds only a small annual bonus plus 401(k) match on top of base — no meaningful equity. Falls under the candidate's ~$120k floor.</t>
+          <t>Posted range $105k–$245k spans all levels; APL is a non-profit FFRDC/UARC paying below big-tech but solidly for cleared PhD technical staff, so PhD entry typically lands ~$130–160k salary with strong retirement contributions and no equity. APL's BS/MS new-grad band is lower, roughly $95k–$120k, which would fall below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -14409,7 +14413,7 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -14418,43 +14422,43 @@
         <v>207</v>
       </c>
       <c r="B208" s="5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$115k–$150k</t>
+          <t>$72k–$95k</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>SoC Design Verification Engineer</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Santa Clara, CA</t>
+          <t>Melbourne, FL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
-          <t>SoC design verification is hardware/EE-centric (SystemVerilog, UVM, RTL) and matches the candidate's explicit role_fit_low category; his distributed-systems, backend microservices, and AI-infra experience in Rust/Java/Python has essentially no overlap with silicon DV work.</t>
+          <t>C#/.NET + Vue/SQL Server internal-tools/ERP work at a defense prime has essentially no overlap with the candidate's backend/distributed-systems/AI-infra profile, and the req is explicitly reserved for an RTX intern converting to full-time.</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Intel new-grad silicon/DV roles in Santa Clara typically pay ~$105-125k base plus modest bonus and a small RSU grant. Intel is a large-cap but below-market payer relative to FAANG/HFT/quant, and recent cost-cutting has compressed new-grad packages. Band is moderately wide to account for BS vs MS (MS-level DV offers land toward the top).</t>
+          <t>Posting states a $57.2k-$108.8k salary range spanning all experience levels; a new grad realistically lands low-to-mid in that band. Defense primes (RTX/Raytheon) pay well below big-tech/Wayfair tier, Melbourne FL has no metro premium, and total comp adds only a small annual bonus plus 401(k) match on top of base — no meaningful equity. Falls under the candidate's ~$120k floor.</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -14475,7 +14479,7 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -14484,43 +14488,43 @@
         <v>208</v>
       </c>
       <c r="B209" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$70k–$90k</t>
+          <t>$115k–$150k</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>M.C. Dean</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Engineer 1 New Grad - Cis</t>
+          <t>SoC Design Verification Engineer</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Richmond, VA</t>
+          <t>Santa Clara, CA</t>
         </is>
       </c>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
-          <t>M.C. Dean is an electrical/systems-integration contractor for mission-critical and cleared federal facilities, so this Engineer 1 role is field/controls engineering rather than backend, distributed-systems, or AI-infra software — and it targets the 2026 grad class in Richmond VA, missing the candidate's May 2027 timeline, location preference, and no-clearance constraint.</t>
+          <t>SoC design verification is hardware/EE-centric (SystemVerilog, UVM, RTL) and matches the candidate's explicit role_fit_low category; his distributed-systems, backend microservices, and AI-infra experience in Rust/Java/Python has essentially no overlap with silicon DV work.</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Defense/infrastructure-integration contractor tier (comparable to Parsons, Burns &amp;amp; McDonnell entry engineering): base-heavy with little to no equity, and a lower-cost Richmond VA market. Scraped description contained only site navigation and footer text with no requirements or comp data, so this band rests on company-tier priors and is a rough estimate; it falls well below the candidate's ~120k floor.</t>
+          <t>Intel new-grad silicon/DV roles in Santa Clara typically pay ~$105-125k base plus modest bonus and a small RSU grant. Intel is a large-cap but below-market payer relative to FAANG/HFT/quant, and recent cost-cutting has compressed new-grad packages. Band is moderately wide to account for BS vs MS (MS-level DV offers land toward the top).</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -14550,38 +14554,38 @@
         <v>209</v>
       </c>
       <c r="B210" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>$80k–$100k</t>
+          <t>$70k–$90k</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Smith+Nephew</t>
+          <t>M.C. Dean</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Quality Engineer - Data Science</t>
+          <t>Engineer 1 New Grad - Cis</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Richmond, VA</t>
         </is>
       </c>
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Quality/statistics analyst role (SPC, FMEA, Six Sigma, CAPA, Power BI dashboards) at a medical device manufacturer — essentially no overlap with the candidate's backend, distributed-systems, or AI-infra strengths beyond basic Python/SQL, and it's an immediate-start hybrid position rather than a 2027 new-grad req.</t>
+          <t>M.C. Dean is an electrical/systems-integration contractor for mission-critical and cleared federal facilities, so this Engineer 1 role is field/controls engineering rather than backend, distributed-systems, or AI-infra software — and it targets the 2026 grad class in Richmond VA, missing the candidate's May 2027 timeline, location preference, and no-clearance constraint.</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Smith+Nephew is a non-tech medtech manufacturer; entry-level quality engineering in the Pittsburgh market typically pays ~$75-90k base plus a modest bonus and negligible equity. Band is a general-knowledge estimate, not verified data, and sits well below the candidate's ~$130k anchor.</t>
+          <t>Defense/infrastructure-integration contractor tier (comparable to Parsons, Burns &amp;amp; McDonnell entry engineering): base-heavy with little to no equity, and a lower-cost Richmond VA market. Scraped description contained only site navigation and footer text with no requirements or comp data, so this band rests on company-tier priors and is a rough estimate; it falls well below the candidate's ~120k floor.</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -14607,7 +14611,7 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -14620,34 +14624,34 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>$80k–$98k</t>
+          <t>$80k–$100k</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Smith+Nephew</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Quality Engineer - Data Science</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Fullerton, CA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Off-profile on nearly every axis: the work is DO-178B requirements-based verification, test support, and documentation rather than backend/distributed-systems/AI-infra engineering; it is onsite-only in Fullerton CA, and the posting explicitly states the req exists to convert a current RTX intern to full-time — so it is effectively not an open external new-grad pipeline.</t>
+          <t>Quality/statistics analyst role (SPC, FMEA, Six Sigma, CAPA, Power BI dashboards) at a medical device manufacturer — essentially no overlap with the candidate's backend, distributed-systems, or AI-infra strengths beyond basic Python/SQL, and it's an immediate-start hybrid position rather than a 2027 new-grad req.</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Posted range is $62.9k–$119.7k spanning all levels; defense primes pay new grads near the bottom third, and Software Engineer I in Fullerton CA typically lands ~$78–95k base with a small (~3-5%) bonus and no equity. Little upside above six figures for a Level 1 hire.</t>
+          <t>Smith+Nephew is a non-tech medtech manufacturer; entry-level quality engineering in the Pittsburgh market typically pays ~$75-90k base plus a modest bonus and negligible equity. Band is a general-knowledge estimate, not verified data, and sits well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -14682,42 +14686,38 @@
         <v>211</v>
       </c>
       <c r="B212" s="5" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>$130k–$165k</t>
+          <t>$80k–$98k</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Johns Hopkins Applied Physics Laboratory</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Research Scientist - Artificial Intelligence and Machine Learning</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Laurel, MD</t>
+          <t>Fullerton, CA</t>
         </is>
       </c>
       <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>start date and can ultimately acquire a f</t>
-        </is>
-      </c>
+      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Requires a completed PhD with strong publication record, an Interim Secret clearance by start date, and a 2026 start — all disqualifying for a May 2027 BS/MS new grad with no clearance — and the fundamental AI research focus (alignment, neural rendering, robotic control) is off-profile versus backend/distributed-systems/AI-infra engineering.</t>
+          <t>Off-profile on nearly every axis: the work is DO-178B requirements-based verification, test support, and documentation rather than backend/distributed-systems/AI-infra engineering; it is onsite-only in Fullerton CA, and the posting explicitly states the req exists to convert a current RTX intern to full-time — so it is effectively not an open external new-grad pipeline.</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>JHU/APL is a non-profit UARC that pays below big tech but offers strong retirement (~10%+) and education benefits; PhD-entry research scientist comp in the Baltimore-DC area typically runs ~$125-155k base plus modest bonus. Posted pay range was not captured in the scrape, so the band is moderately wide. This reflects the PhD-level entry band the posting actually hires for, not a BS new-grad offer, which would be materially lower.</t>
+          <t>Posted range is $62.9k–$119.7k spanning all levels; defense primes pay new grads near the bottom third, and Software Engineer I in Fullerton CA typically lands ~$78–95k base with a small (~3-5%) bonus and no equity. Little upside above six figures for a Level 1 hire.</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -14752,38 +14752,42 @@
         <v>212</v>
       </c>
       <c r="B213" s="5" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>$70k–$95k</t>
+          <t>$130k–$165k</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Consumer Direct Care Network</t>
+          <t>Johns Hopkins Applied Physics Laboratory</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Artificial Intelligence Research Scientist - Artificial Intelligence and Machine Learning</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Missoula, MT</t>
+          <t>Laurel, MD</t>
         </is>
       </c>
       <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr"/>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>start date and can ultimately acquire a f</t>
+        </is>
+      </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Supervised junior full-stack .NET/Angular/MSSQL work at a home-care services company in Missoula uses almost none of the candidate's distributed-systems, Rust/Java backend, or AI-infra depth, and the pay tier sits well under the ~120k floor — the only overlap is generic Azure cloud exposure.</t>
+          <t>Requires a completed PhD with strong publication record, an Interim Secret clearance by start date, and a 2026 start — all disqualifying for a May 2027 BS/MS new grad with no clearance — and the fundamental AI research focus (alignment, neural rendering, robotic control) is off-profile versus backend/distributed-systems/AI-infra engineering.</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Non-tech home-care services company in Missoula, MT (low cost-of-living, no tech-market comp pressure), Level "Individual Contributor II" entry role with 0-2 yrs experience. No comp disclosed, so this is a wide estimate from general knowledge of healthcare-services IT pay in Montana; base likely $70-88k with a small 401k match/profit-sharing, no equity.</t>
+          <t>JHU/APL is a non-profit UARC that pays below big tech but offers strong retirement (~10%+) and education benefits; PhD-entry research scientist comp in the Baltimore-DC area typically runs ~$125-155k base plus modest bonus. Posted pay range was not captured in the scrape, so the band is moderately wide. This reflects the PhD-level entry band the posting actually hires for, not a BS new-grad offer, which would be materially lower.</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -14809,7 +14813,7 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -14827,29 +14831,29 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Sigla</t>
+          <t>Consumer Direct Care Network</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>St. Louis, MO</t>
+          <t>Missoula, MT</t>
         </is>
       </c>
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Full-stack JavaScript/Angular/Node role with PHP CMS and native Android/iOS work at a small St. Louis startup studio — essentially no overlap with the candidate's backend/distributed-systems/AI-infra strengths, and the posting is stale (targets 2016/2017 grads, not a May 2027 grad).</t>
+          <t>Supervised junior full-stack .NET/Angular/MSSQL work at a home-care services company in Missoula uses almost none of the candidate's distributed-systems, Rust/Java backend, or AI-infra depth, and the pay tier sits well under the ~120k floor — the only overlap is generic Azure cloud exposure.</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Company is unknown/non-tier (small St. Louis startup studio, no public comp data), so this is a wide inferred band based on typical midwest SMB/startup new-grad software salaries; equity is illiquid studio equity and benefits are strong but don't lift cash TC toward the ~130k anchor.</t>
+          <t>Non-tech home-care services company in Missoula, MT (low cost-of-living, no tech-market comp pressure), Level "Individual Contributor II" entry role with 0-2 yrs experience. No comp disclosed, so this is a wide estimate from general knowledge of healthcare-services IT pay in Montana; base likely $70-88k with a small 401k match/profit-sharing, no equity.</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -14893,29 +14897,29 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>M.C. Dean</t>
+          <t>Sigla</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Engineer 1 - New College Graduate</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Tysons, VA</t>
+          <t>St. Louis, MO</t>
         </is>
       </c>
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
-          <t>M.C. Dean is an electrical/systems-integration contractor for secure federal facilities, so this generic "Engineer 1" new-grad role is almost certainly EE/field or building-systems engineering rather than backend/distributed-systems software, and the Tysons/cleared-environment context conflicts with the candidate's no-clearance constraint.</t>
+          <t>Full-stack JavaScript/Angular/Node role with PHP CMS and native Android/iOS work at a small St. Louis startup studio — essentially no overlap with the candidate's backend/distributed-systems/AI-infra strengths, and the posting is stale (targets 2016/2017 grads, not a May 2027 grad).</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Defense/construction-engineering contractor tier (not a tech-comp payer): mostly base salary plus a modest bonus, typical of DC-area federal integrators. Scraped description was site navigation boilerplate with no real job content, so this band is inferred from company tier rather than the posting; treat as a wide estimate.</t>
+          <t>Company is unknown/non-tier (small St. Louis startup studio, no public comp data), so this is a wide inferred band based on typical midwest SMB/startup new-grad software salaries; equity is illiquid studio equity and benefits are strong but don't lift cash TC toward the ~130k anchor.</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -14941,7 +14945,7 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14950,38 +14954,38 @@
         <v>215</v>
       </c>
       <c r="B216" s="5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>$85k–$115k</t>
+          <t>$70k–$95k</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>M.C. Dean</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Engineer 1 - New College Graduate</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Anaheim, CA</t>
+          <t>Tysons, VA</t>
         </is>
       </c>
       <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Hard-blocked: the req demands an active TS/SCI with polygraph on day 1 and is earmarked for an RTX intern converting to full-time, and the C++/Qt/Angular defense-systems work plus sub-$120k band misses both the candidate's clearance-free constraint and TC anchor.</t>
+          <t>M.C. Dean is an electrical/systems-integration contractor for secure federal facilities, so this generic "Engineer 1" new-grad role is almost certainly EE/field or building-systems engineering rather than backend/distributed-systems software, and the Tysons/cleared-environment context conflicts with the candidate's no-clearance constraint.</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Posting states salary range 62,900–119,700 USD; RTX new-grad SWE offers typically land near the lower-middle of that band (~$85–100k base) plus modest 401k match and small/no annual incentive at level 1. Defense-primes pay well below the candidate's ~$130–165k anchor; cleared work in Anaheim may add a slight premium, hence the top of the band.</t>
+          <t>Defense/construction-engineering contractor tier (not a tech-comp payer): mostly base salary plus a modest bonus, typical of DC-area federal integrators. Scraped description was site navigation boilerplate with no real job content, so this band is inferred from company tier rather than the posting; treat as a wide estimate.</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -15007,7 +15011,7 @@
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -15025,33 +15029,29 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>General Motors</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Warren, MI</t>
+          <t>Anaheim, CA</t>
         </is>
       </c>
       <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>graduating between december 2025</t>
-        </is>
-      </c>
+      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Hard-disqualifying graduation window (Dec 2025–Aug 2026 vs. candidate's May 2027) combined with an Android/Kotlin infotainment HMI focus that sits far from his backend/distributed-systems/AI-infra profile, in a hybrid Warren, MI role paying below his TC floor.</t>
+          <t>Hard-blocked: the req demands an active TS/SCI with polygraph on day 1 and is earmarked for an RTX intern converting to full-time, and the C++/Qt/Angular defense-systems work plus sub-$120k band misses both the candidate's clearance-free constraint and TC anchor.</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>GM is a non-tech-tier automotive employer; entry-level SWE base in Warren, MI typically ~$80–100k plus modest performance bonus (~5-10%) and relocation, putting TC roughly $85–115k — well below the candidate's ~$130k anchor. Estimate from general knowledge of GM/Big Three new-grad pay in low-cost Midwest markets, not from the posting (no range disclosed).</t>
+          <t>Posting states salary range 62,900–119,700 USD; RTX new-grad SWE offers typically land near the lower-middle of that band (~$85–100k base) plus modest 401k match and small/no annual incentive at level 1. Defense-primes pay well below the candidate's ~$130–165k anchor; cleared work in Anaheim may add a slight premium, hence the top of the band.</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -15086,38 +15086,42 @@
         <v>217</v>
       </c>
       <c r="B218" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>$125k–$150k</t>
+          <t>$85k–$115k</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Rambus</t>
+          <t>General Motors</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Lead MTS Application Engineer - Memory Interface</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Warren, MI</t>
         </is>
       </c>
       <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr"/>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>graduating between december 2025</t>
+        </is>
+      </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Hardware/EE post-silicon ASIC bench validation role (I2C/I3C, DDR5 PMIC/SPD, lab automation) at Lead level requiring 5+ years and an EE/CE degree — hits both the "hardware/embedded-only" and "5+ yrs experience" exclusions, with Python scripting as the only overlap with the candidate's backend/distributed-systems/AI-infra profile.</t>
+          <t>Hard-disqualifying graduation window (Dec 2025–Aug 2026 vs. candidate's May 2027) combined with an Android/Kotlin infotainment HMI focus that sits far from his backend/distributed-systems/AI-infra profile, in a hybrid Warren, MI role paying below his TC floor.</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Posting states a $117.3k-$167.5k base range for this San Jose Lead MTS req; a new grad would land at or below the floor (~$115-130k base), plus Rambus's stated bonus, equity, and ESPP adding roughly 10-18%. Rambus is a mid-cap semiconductor IP firm — competitive for the semi sector but below big-tech software new-grad bands. Estimate, not fact; actual new-grad offers would likely be posted under a lower-level req than this one.</t>
+          <t>GM is a non-tech-tier automotive employer; entry-level SWE base in Warren, MI typically ~$80–100k plus modest performance bonus (~5-10%) and relocation, putting TC roughly $85–115k — well below the candidate's ~$130k anchor. Estimate from general knowledge of GM/Big Three new-grad pay in low-cost Midwest markets, not from the posting (no range disclosed).</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -15143,7 +15147,7 @@
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -15152,21 +15156,21 @@
         <v>218</v>
       </c>
       <c r="B219" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>$105k–$135k</t>
+          <t>$125k–$150k</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Rambus</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Lead MTS Application Engineer - Memory Interface</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -15178,12 +15182,12 @@
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Requires an active TS/SCI with Polygraph on day 1 and a Master's by start date, and the req is reserved for a converting RTX intern — all disqualifying for this candidate despite a reasonable C++/Linux/Kubernetes technical overlap.</t>
+          <t>Hardware/EE post-silicon ASIC bench validation role (I2C/I3C, DDR5 PMIC/SPD, lab automation) at Lead level requiring 5+ years and an EE/CE degree — hits both the "hardware/embedded-only" and "5+ yrs experience" exclusions, with Python scripting as the only overlap with the candidate's backend/distributed-systems/AI-infra profile.</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Posting lists $75.8k-$144.2k across all experience levels. RTX is defense-tier (below big tech, minimal equity), but San Jose geo plus a cleared TS/SCI-poly role lifts entry-level offers into the upper half: roughly $100-128k base, ~5% bonus, 401k match. Estimate, not fact.</t>
+          <t>Posting states a $117.3k-$167.5k base range for this San Jose Lead MTS req; a new grad would land at or below the floor (~$115-130k base), plus Rambus's stated bonus, equity, and ESPP adding roughly 10-18%. Rambus is a mid-cap semiconductor IP firm — competitive for the semi sector but below big-tech software new-grad bands. Estimate, not fact; actual new-grad offers would likely be posted under a lower-level req than this one.</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -15209,7 +15213,7 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15218,38 +15222,38 @@
         <v>219</v>
       </c>
       <c r="B220" s="5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>$72k–$92k</t>
+          <t>$105k–$135k</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Integration Innovation (i3)</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Associate Software Developer - COMPASS</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Huntsville, AL</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Requires an active/obtainable DoD Secret clearance and on-site residency near Redstone Arsenal with a C#/HTML/CSS stack, all of which conflict with the candidate's stated constraints and backend/distributed-systems strengths, despite some Azure/AWS microservices and event-queue overlap.</t>
+          <t>Requires an active TS/SCI with Polygraph on day 1 and a Master's by start date, and the req is reserved for a converting RTX intern — all disqualifying for this candidate despite a reasonable C++/Linux/Kubernetes technical overlap.</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Mid-size employee-owned defense/government services contractor (i3) in Huntsville, AL — low cost-of-living market with cost-plus contract rate structures. Typical 0-3 yr associate developer base ~$70-85k plus 401(k) match and ESOP; no equity grant or notable signing bonus. Band is a general-knowledge estimate for the defense-services tier, not verified company data, and falls well below the candidate's ~$130k anchor.</t>
+          <t>Posting lists $75.8k-$144.2k across all experience levels. RTX is defense-tier (below big tech, minimal equity), but San Jose geo plus a cleared TS/SCI-poly role lifts entry-level offers into the upper half: roughly $100-128k base, ~5% bonus, 401k match. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -15275,7 +15279,7 @@
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -15293,29 +15297,29 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>ManTech</t>
+          <t>Integration Innovation (i3)</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Associate BI Analytics Engineer</t>
+          <t>Associate Software Developer - COMPASS</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Herndon, VA</t>
+          <t>Huntsville, AL</t>
         </is>
       </c>
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
-          <t>This is a Power BI dashboard/DAX/semantic-modeling BI analyst role, not backend or systems engineering — it uses almost none of the candidate's Rust/distributed-systems/AI-infra strengths, is hybrid-onsite in Herndon VA, and pays well below the ~130k anchor.</t>
+          <t>Requires an active/obtainable DoD Secret clearance and on-site residency near Redstone Arsenal with a C#/HTML/CSS stack, all of which conflict with the candidate's stated constraints and backend/distributed-systems strengths, despite some Azure/AWS microservices and event-queue overlap.</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Posting states a $69.9k–$116.4k range spanning HS+3yrs to degreed hires; an entry-level (0-2 yrs) BI analyst at a defense contractor lands near the bottom of that band. ManTech is a government services/cost-plus contractor with labor-category-capped pay and minimal equity, so TC ≈ base + small bonus/401k match.</t>
+          <t>Mid-size employee-owned defense/government services contractor (i3) in Huntsville, AL — low cost-of-living market with cost-plus contract rate structures. Typical 0-3 yr associate developer base ~$70-85k plus 401(k) match and ESOP; no equity grant or notable signing bonus. Band is a general-knowledge estimate for the defense-services tier, not verified company data, and falls well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -15341,7 +15345,7 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -15354,34 +15358,34 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>$70k–$92k</t>
+          <t>$72k–$92k</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>ManTech</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Associate BI Analytics Engineer</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA</t>
+          <t>Herndon, VA</t>
         </is>
       </c>
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Requires an active/obtainable DoD Secret clearance (an explicit candidate exclusion) for onsite embedded defense software in Cedar Rapids, IA, with a pay band well under the candidate's ~$130k anchor; only Rust/Linux/container overlap gives it any credit.</t>
+          <t>This is a Power BI dashboard/DAX/semantic-modeling BI analyst role, not backend or systems engineering — it uses almost none of the candidate's Rust/distributed-systems/AI-infra strengths, is hybrid-onsite in Herndon VA, and pays well below the ~130k anchor.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Posting lists $57.2k-$108.8k spanning all experience levels; RTX/Collins Aerospace is a defense prime paying below tech-industry new-grad rates, so an entry-level SWE I in low-COL Cedar Rapids realistically lands ~$70-85k base plus a small (~3-5%) annual incentive and 401k match, with the upper end unlikely for a fresh grad.</t>
+          <t>Posting states a $69.9k–$116.4k range spanning HS+3yrs to degreed hires; an entry-level (0-2 yrs) BI analyst at a defense contractor lands near the bottom of that band. ManTech is a government services/cost-plus contractor with labor-category-capped pay and minimal equity, so TC ≈ base + small bonus/401k match.</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -15420,34 +15424,34 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>$65k–$90k</t>
+          <t>$70k–$92k</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Apollo Mission Critical Engineering</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Software Engineering Associate - Software Development Associate</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Cedar Rapids, IA</t>
         </is>
       </c>
       <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Roughly half business-analyst/requirements-and-ticket-writing work with the engineering half limited to manual QA and Playwright test automation — essentially no backend, distributed systems, cloud, or AI-infra content, and the "crawl → walk → run" framing signals well below this candidate's demonstrated level.</t>
+          <t>Requires an active/obtainable DoD Secret clearance (an explicit candidate exclusion) for onsite embedded defense software in Cedar Rapids, IA, with a pay band well under the candidate's ~$130k anchor; only Rust/Linux/container overlap gives it any credit.</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Apollo Mission Critical Engineering is a small non-tech (mission-critical facilities/MEP services) company, not a software firm; an entry-level "associate" hybrid BA/QA role in Atlanta at a company like this typically pays base ~$65-85k with minimal equity and a 401k match. Wide band due to low company visibility — this is a rough estimate, well below the candidate's ~$130k anchor.</t>
+          <t>Posting lists $57.2k-$108.8k spanning all experience levels; RTX/Collins Aerospace is a defense prime paying below tech-industry new-grad rates, so an entry-level SWE I in low-COL Cedar Rapids realistically lands ~$70-85k base plus a small (~3-5%) annual incentive and 401k match, with the upper end unlikely for a fresh grad.</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -15482,38 +15486,38 @@
         <v>223</v>
       </c>
       <c r="B224" s="5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>$45k–$62k</t>
+          <t>$65k–$90k</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Trustpilot</t>
+          <t>Apollo Mission Critical Engineering</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Software Engineer 1 - Trust Tech</t>
+          <t>Software Engineering Associate - Software Development Associate</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Edinburgh, UK</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Backend-adjacent work the candidate could handle, but it is a UK/EU-located role (Edinburgh/London/Copenhagen) he lacks work authorization for, and the Node/TypeScript/React full-stack stack is off his Rust/Java distributed-systems and AI-infra profile.</t>
+          <t>Roughly half business-analyst/requirements-and-ticket-writing work with the engineering half limited to manual QA and Playwright test automation — essentially no backend, distributed systems, cloud, or AI-infra content, and the "crawl → walk → run" framing signals well below this candidate's demonstrated level.</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Trustpilot is a profitable FTSE-250 tech company, not a top-tier payer. Edinburgh/UK graduate-to-SWE I base bands typically run ~£35-48k with a modest bonus, converting to roughly $45-62k USD — well below the candidate's ~$130k anchor. Wide-ish band; UK pay data for this specific level is inferred from general UK market rates rather than verified comp reports.</t>
+          <t>Apollo Mission Critical Engineering is a small non-tech (mission-critical facilities/MEP services) company, not a software firm; an entry-level "associate" hybrid BA/QA role in Atlanta at a company like this typically pays base ~$65-85k with minimal equity and a 401k match. Wide band due to low company visibility — this is a rough estimate, well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -15539,7 +15543,7 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15548,38 +15552,38 @@
         <v>224</v>
       </c>
       <c r="B225" s="5" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>$125k–$155k</t>
+          <t>$45k–$62k</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Johns Hopkins Applied Physics Laboratory</t>
+          <t>Trustpilot</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Data Scientist / Computer Scientist PhD Graduate - Decision Systems</t>
+          <t>Software Engineer 1 - Trust Tech</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Laurel, MD</t>
+          <t>Edinburgh, UK</t>
         </is>
       </c>
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Requires a PhD, an Interim/final Secret clearance, and a 2026 start — all disqualifying for a May-2027 BS/MS grad with no clearance — and the decision-science/analytics focus is off his backend/distributed-systems profile.</t>
+          <t>Backend-adjacent work the candidate could handle, but it is a UK/EU-located role (Edinburgh/London/Copenhagen) he lacks work authorization for, and the Node/TypeScript/React full-stack stack is off his Rust/Java distributed-systems and AI-infra profile.</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>JHU APL is a non-profit university-affiliated research lab: no equity, modest bonuses, but strong retirement contributions. Posted $105k-$245k range covers all levels; PhD-entry Laurel, MD hires typically start around $125-150k base. Estimate, not fact.</t>
+          <t>Trustpilot is a profitable FTSE-250 tech company, not a top-tier payer. Edinburgh/UK graduate-to-SWE I base bands typically run ~£35-48k with a modest bonus, converting to roughly $45-62k USD — well below the candidate's ~$130k anchor. Wide-ish band; UK pay data for this specific level is inferred from general UK market rates rather than verified comp reports.</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -15605,7 +15609,7 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -15614,38 +15618,38 @@
         <v>225</v>
       </c>
       <c r="B226" s="5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>$79k–$105k</t>
+          <t>$125k–$155k</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Capital Health</t>
+          <t>Johns Hopkins Applied Physics Laboratory</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Product Engineer 1</t>
+          <t>Data Scientist / Computer Scientist PhD Graduate - Decision Systems</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Pennington, NJ</t>
+          <t>Laurel, MD</t>
         </is>
       </c>
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
-          <t>A healthcare-IT product/business-analyst role focused on IAM workflow discovery, user stories, and vendor platform configuration (Entra/ServiceNow/Jira) rather than backend, distributed-systems, or AI-infra engineering, with a posted ceiling ~$103K well under the candidate's ~$130K anchor.</t>
+          <t>Requires a PhD, an Interim/final Secret clearance, and a 2026 start — all disqualifying for a May-2027 BS/MS grad with no clearance — and the decision-science/analytics focus is off his backend/distributed-systems profile.</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Posting explicitly states a full-time base range of $78,769.60-$102,960.00. Capital Health is a regional non-profit hospital system, so there is no equity component and at most a small bonus; TC is effectively equal to base, with the low end of the band being the realistic new-grad landing point.</t>
+          <t>JHU APL is a non-profit university-affiliated research lab: no equity, modest bonuses, but strong retirement contributions. Posted $105k-$245k range covers all levels; PhD-entry Laurel, MD hires typically start around $125-150k base. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -15671,7 +15675,7 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -15680,38 +15684,38 @@
         <v>226</v>
       </c>
       <c r="B227" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>$60k–$80k</t>
+          <t>$79k–$105k</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Capital Health</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Entry Level Java Developer Associate</t>
+          <t>Product Engineer 1</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>San Antonio, TX</t>
+          <t>Pennington, NJ</t>
         </is>
       </c>
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Legacy J2EE/Struts/JSP federal consulting role in San Antonio with no distributed-systems, cloud, or AI-infra content, and comp roughly half the candidate's ~130k anchor.</t>
+          <t>A healthcare-IT product/business-analyst role focused on IAM workflow discovery, user stories, and vendor platform configuration (Entra/ServiceNow/Jira) rather than backend, distributed-systems, or AI-infra engineering, with a posted ceiling ~$103K well under the candidate's ~$130K anchor.</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Accenture Federal Services entry-level associate is consulting-tier, not product-tier: base ~$58-75k in a low-COL market (San Antonio), ~5% bonus, no equity. Estimate based on general knowledge of Accenture/AFS new-grad bands; not a verified figure.</t>
+          <t>Posting explicitly states a full-time base range of $78,769.60-$102,960.00. Capital Health is a regional non-profit hospital system, so there is no equity component and at most a small bonus; TC is effectively equal to base, with the low end of the band being the realistic new-grad landing point.</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -15737,7 +15741,7 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -15746,42 +15750,38 @@
         <v>227</v>
       </c>
       <c r="B228" s="5" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>$115k–$150k</t>
+          <t>$60k–$80k</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Johns Hopkins Applied Physics Laboratory</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Machine Learning PhD New Grad - Artificial Intelligence</t>
+          <t>Entry Level Java Developer Associate</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Laurel, MD</t>
+          <t>San Antonio, TX</t>
         </is>
       </c>
       <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>start date and can ultimately obtain top</t>
-        </is>
-      </c>
+      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Requires a PhD, an Interim Secret/Top Secret clearance by start date, and a 2026 start — the candidate is a May 2027 BS/MS-track grad with no clearance — and the ML-research/statistics scope is off his backend/distributed-systems/AI-infra profile.</t>
+          <t>Legacy J2EE/Struts/JSP federal consulting role in San Antonio with no distributed-systems, cloud, or AI-infra content, and comp roughly half the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>JHU/APL is an FFRDC (non-profit, government-funded), paying below big-tech but solid for the DoD/national-lab market; PhD-entry technical staff typically start in the low-to-mid $100s base with a small bonus and strong retirement contributions. APL does not publish level bands, so this is a wide estimate, not fact.</t>
+          <t>Accenture Federal Services entry-level associate is consulting-tier, not product-tier: base ~$58-75k in a low-COL market (San Antonio), ~5% bonus, no equity. Estimate based on general knowledge of Accenture/AFS new-grad bands; not a verified figure.</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15816,38 +15816,42 @@
         <v>228</v>
       </c>
       <c r="B229" s="5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>$80k–$100k</t>
+          <t>$115k–$150k</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>ITA International</t>
+          <t>Johns Hopkins Applied Physics Laboratory</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Junior Power Platform Developer</t>
+          <t>Machine Learning PhD New Grad - Artificial Intelligence</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Remote in USA</t>
+          <t>Laurel, MD</t>
         </is>
       </c>
       <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr"/>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>start date and can ultimately obtain top</t>
+        </is>
+      </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Low-code Power Platform/SharePoint/Power BI development is the opposite of this candidate's backend, distributed-systems, and AI-infra strengths, and the role is a proposal-contingent govcon position preferring an active Secret clearance with an immediate start rather than a May 2027 new grad.</t>
+          <t>Requires a PhD, an Interim Secret/Top Secret clearance by start date, and a 2026 start — the candidate is a May 2027 BS/MS-track grad with no clearance — and the ML-research/statistics scope is off his backend/distributed-systems/AI-infra profile.</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Posting states $75k-$125k, but explicitly notes the wide band covers contract pricing and all experience levels; a 0-3 yr "Junior" hire realistically sits near the floor. Small (~200-person) government-contracting services firm in Newport News, VA with no equity component, so TC is essentially base plus 401k match. Estimate, not fact — well below the candidate's ~130k anchor.</t>
+          <t>JHU/APL is an FFRDC (non-profit, government-funded), paying below big-tech but solid for the DoD/national-lab market; PhD-entry technical staff typically start in the low-to-mid $100s base with a small bonus and strong retirement contributions. APL does not publish level bands, so this is a wide estimate, not fact.</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -15882,38 +15886,38 @@
         <v>229</v>
       </c>
       <c r="B230" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>$90k–$120k</t>
+          <t>$80k–$100k</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>ITA International</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Junior Power Platform Developer</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>West Valley City, UT</t>
+          <t>Remote in USA</t>
         </is>
       </c>
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Requires an active TS/SCI with polygraph on day 1 — an absolute blocker for this uncleared candidate — and the role is onsite C++/embedded/signal-processing work in Utah rather than backend, distributed systems, or AI infra.</t>
+          <t>Low-code Power Platform/SharePoint/Power BI development is the opposite of this candidate's backend, distributed-systems, and AI-infra strengths, and the role is a proposal-contingent govcon position preferring an active Secret clearance with an immediate start rather than a May 2027 new grad.</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>RTX is a defense prime that pays below big-tech scales for new grads: typical SWE I base ~$80-100k plus a small bonus and 401k match. Cleared SIGINT/AST roles skew to the upper end of that band. Estimate from general defense-industry compensation knowledge, not a posted range; the posting listed no salary.</t>
+          <t>Posting states $75k-$125k, but explicitly notes the wide band covers contract pricing and all experience levels; a 0-3 yr "Junior" hire realistically sits near the floor. Small (~200-person) government-contracting services firm in Newport News, VA with no equity component, so TC is essentially base plus 401k match. Estimate, not fact — well below the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -15939,7 +15943,7 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -15948,38 +15952,38 @@
         <v>230</v>
       </c>
       <c r="B231" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>$105k–$145k</t>
+          <t>$90k–$120k</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Johns Hopkins Applied Physics Laboratory</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer - Intelligent Autonomous Systems</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Laurel, MD</t>
+          <t>West Valley City, UT</t>
         </is>
       </c>
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Requires a PhD, an interim Secret clearance escalating to Top Secret, and 2026 graduation — all disqualifying for a clearance-free May 2027 BS/MS new grad — and the robotics/UAS autonomy and flight-simulation focus is far from his backend, distributed-systems, and AI-infra strengths.</t>
+          <t>Requires an active TS/SCI with polygraph on day 1 — an absolute blocker for this uncleared candidate — and the role is onsite C++/embedded/signal-processing work in Utah rather than backend, distributed systems, or AI infra.</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Johns Hopkins APL is a nonprofit UARC that pays below big-tech tier with no equity, offsetting with strong benefits and a pension. This band reflects the posting's PhD entry level in the Laurel, MD / DC market; a BS-level new grad at APL would be roughly $85k-$110k, below the candidate's ~$120k floor. APL publishes little comp data, so confidence is moderate and the band is intentionally wide.</t>
+          <t>RTX is a defense prime that pays below big-tech scales for new grads: typical SWE I base ~$80-100k plus a small bonus and 401k match. Cleared SIGINT/AST roles skew to the upper end of that band. Estimate from general defense-industry compensation knowledge, not a posted range; the posting listed no salary.</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -16005,7 +16009,7 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16018,7 +16022,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>$115k–$145k</t>
+          <t>$105k–$145k</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -16028,7 +16032,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Systems Engineer/Analyst New Grad - Multi-Mission Planning Development</t>
+          <t>Artificial Intelligence Engineer - Intelligent Autonomous Systems</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -16037,19 +16041,15 @@
         </is>
       </c>
       <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>start date and can ultimately obtain a se</t>
-        </is>
-      </c>
+      <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Requires a 2026 PhD and an Interim Secret clearance by start date (candidate is a May 2027 non-PhD grad with no clearance), and the work is Matlab/Python military mission-planning modeling and systems analysis rather than backend, distributed-systems, or AI-infra software engineering.</t>
+          <t>Requires a PhD, an interim Secret clearance escalating to Top Secret, and 2026 graduation — all disqualifying for a clearance-free May 2027 BS/MS new grad — and the robotics/UAS autonomy and flight-simulation focus is far from his backend, distributed-systems, and AI-infra strengths.</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>JHU/APL is a non-profit FFRDC: solid base salary, no equity, generous retirement (~11%+ employer contribution) and education benefits. This posting is PhD-entry, which sits above APL's bachelor's/master's new-grad software bands (~$85-110k), so the band reflects doctoral-level entry pay in the Baltimore-DC market. Estimate from general knowledge of APL's public salary scale, not from the posting; treat as approximate. Note this figure is not what the candidate would be offered, since they do not meet the PhD requirement.</t>
+          <t>Johns Hopkins APL is a nonprofit UARC that pays below big-tech tier with no equity, offsetting with strong benefits and a pension. This band reflects the posting's PhD entry level in the Laurel, MD / DC market; a BS-level new grad at APL would be roughly $85k-$110k, below the candidate's ~$120k floor. APL publishes little comp data, so confidence is moderate and the band is intentionally wide.</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -16098,28 +16098,28 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Applied Algorithms Engineer New Grad</t>
+          <t>Systems Engineer/Analyst New Grad - Multi-Mission Planning Development</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Huntsville, AL</t>
+          <t>Laurel, MD</t>
         </is>
       </c>
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr">
         <is>
-          <t>start date and can ultimately obtain top</t>
+          <t>start date and can ultimately obtain a se</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Requires a PhD, US citizenship with Interim Top Secret clearance by start, and a 2026 start in Huntsville AL for missile-defense modeling/simulation and tracking algorithms in MATLAB/C++ — off-profile on nearly every axis for a 2027 BS-level backend/distributed-systems/AI-infra candidate with no clearance.</t>
+          <t>Requires a 2026 PhD and an Interim Secret clearance by start date (candidate is a May 2027 non-PhD grad with no clearance), and the work is Matlab/Python military mission-planning modeling and systems analysis rather than backend, distributed-systems, or AI-infra software engineering.</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>JHU APL is a non-profit university-affiliated research center; pay trails big-tech but PhD-level defense-research new grads land at the upper end of the government-adjacent band, plus unusually strong retirement contributions not counted in base. Band is wide because APL does not publish ranges and the posting's pay language is boilerplate. Estimate, not fact; low end falls below the candidate's ~120k floor.</t>
+          <t>JHU/APL is a non-profit FFRDC: solid base salary, no equity, generous retirement (~11%+ employer contribution) and education benefits. This posting is PhD-entry, which sits above APL's bachelor's/master's new-grad software bands (~$85-110k), so the band reflects doctoral-level entry pay in the Baltimore-DC market. Estimate from general knowledge of APL's public salary scale, not from the posting; treat as approximate. Note this figure is not what the candidate would be offered, since they do not meet the PhD requirement.</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -16168,28 +16168,28 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>PhD Graduate - Distributed Tactical Awareness</t>
+          <t>Applied Algorithms Engineer New Grad</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Laurel, MD</t>
+          <t>Huntsville, AL</t>
         </is>
       </c>
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr">
         <is>
-          <t>start date and can ultimately obtain a se</t>
+          <t>start date and can ultimately obtain top</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Requires a PhD and an obtainable Interim Secret clearance (candidate is a May 2027 BS/MS new grad with no clearance), and the role is sensor-fusion/Kalman-filtering/RF-physics algorithm analysis rather than backend, distributed systems, or AI-infra software engineering.</t>
+          <t>Requires a PhD, US citizenship with Interim Top Secret clearance by start, and a 2026 start in Huntsville AL for missile-defense modeling/simulation and tracking algorithms in MATLAB/C++ — off-profile on nearly every axis for a 2027 BS-level backend/distributed-systems/AI-infra candidate with no clearance.</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>JHU APL is a non-profit FFRDC: cash comp is below big-tech bands but retirement contributions (~10%+ non-elective) are unusually generous. Band reflects the PhD-level entry hire this posting targets in the Baltimore-DC market; a BS/MS new grad would land materially lower. Estimate from general knowledge of the employer tier, not posted data.</t>
+          <t>JHU APL is a non-profit university-affiliated research center; pay trails big-tech but PhD-level defense-research new grads land at the upper end of the government-adjacent band, plus unusually strong retirement contributions not counted in base. Band is wide because APL does not publish ranges and the posting's pay language is boilerplate. Estimate, not fact; low end falls below the candidate's ~120k floor.</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -16224,43 +16224,47 @@
         <v>234</v>
       </c>
       <c r="B235" s="5" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>$55k–$75k</t>
+          <t>$115k–$145k</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Arkansas Children's</t>
+          <t>Johns Hopkins Applied Physics Laboratory</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Systems Analyst 1</t>
+          <t>PhD Graduate - Distributed Tactical Awareness</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Little Rock, AR</t>
+          <t>Laurel, MD</t>
         </is>
       </c>
       <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>start date and can ultimately obtain a se</t>
+        </is>
+      </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>A junior "Systems Analyst" role at a pediatric hospital is healthcare-IT application support/configuration (Epic-style EHR, vendor systems, ticket triage) rather than backend/distributed-systems software engineering, so it uses almost none of the candidate's Rust/Java/cloud-infra strengths and sits far below his TC anchor.</t>
+          <t>Requires a PhD and an obtainable Interim Secret clearance (candidate is a May 2027 BS/MS new grad with no clearance), and the role is sensor-fusion/Kalman-filtering/RF-physics algorithm analysis rather than backend, distributed systems, or AI-infra software engineering.</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Non-profit regional children's hospital in Little Rock, AR — hospital IT pay bands with essentially no equity and a modest bonus; Analyst I titles in low-cost-of-living markets typically land in the mid-$50k to mid-$70k range. Estimate from general healthcare-IT market knowledge, not a posted range, so treat the band as approximate — well below the candidate's ~$130k target.</t>
+          <t>JHU APL is a non-profit FFRDC: cash comp is below big-tech bands but retirement contributions (~10%+ non-elective) are unusually generous. Band reflects the PhD-level entry hire this posting targets in the Baltimore-DC market; a BS/MS new grad would land materially lower. Estimate from general knowledge of the employer tier, not posted data.</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -16281,7 +16285,7 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -16290,43 +16294,43 @@
         <v>235</v>
       </c>
       <c r="B236" s="5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>$72k–$95k</t>
+          <t>$55k–$75k</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Northrop Grumman</t>
+          <t>Arkansas Children's</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Embedded Software Engineer</t>
+          <t>Systems Analyst 1</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Warner Robins, GA</t>
+          <t>Little Rock, AR</t>
         </is>
       </c>
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Embedded C/C++/Ada operational flight software with a mandatory DoD Secret clearance and on-site Warner Robins, GA presence directly matches three of the candidate's stated low-fit categories (embedded-only, clearance-required, off-target location) and shares almost nothing with his backend/distributed-systems/AI-infra strengths.</t>
+          <t>A junior "Systems Analyst" role at a pediatric hospital is healthcare-IT application support/configuration (Epic-style EHR, vendor systems, ticket triage) rather than backend/distributed-systems software engineering, so it uses almost none of the candidate's Rust/Java/cloud-infra strengths and sits far below his TC anchor.</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Posting lists Primary (Level 1) base range $65,800-$98,800; a new grad typically lands ~$70-85k base, plus a modest discretionary bonus and no equity. Consistent with traditional defense-prime new-grad comp (Northrop/Lockheed/RTX), which runs roughly 30-45% below tech-industry new-grad TC and well under the candidate's ~$130k anchor.</t>
+          <t>Non-profit regional children's hospital in Little Rock, AR — hospital IT pay bands with essentially no equity and a modest bonus; Analyst I titles in low-cost-of-living markets typically land in the mid-$50k to mid-$70k range. Estimate from general healthcare-IT market knowledge, not a posted range, so treat the band as approximate — well below the candidate's ~$130k target.</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -16347,7 +16351,7 @@
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -16360,34 +16364,34 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>$72k–$92k</t>
+          <t>$72k–$95k</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Northrop Grumman</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Software Engineering Associate</t>
+          <t>Embedded Software Engineer</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Arlington County, Arlington, VA</t>
+          <t>Warner Robins, GA</t>
         </is>
       </c>
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Federal consulting associate role centered on configuration changes, testing, and project-management support with Excel/Visio proficiency called out — far from the candidate's backend/distributed-systems/AI-infra profile — plus it is a stale posting (graduation "no later than December 2014"), requires US citizenship for a clearance-driven client, and is location-locked to Arlington, VA.</t>
+          <t>Embedded C/C++/Ada operational flight software with a mandatory DoD Secret clearance and on-site Warner Robins, GA presence directly matches three of the candidate's stated low-fit categories (embedded-only, clearance-required, off-target location) and shares almost nothing with his backend/distributed-systems/AI-infra strengths.</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Accenture Federal Services entry-level engineering is consulting-tier compensation: roughly $70-85k base with a modest performance bonus and no equity. The federal/public-sector practice pays below Accenture's commercial technology arm and well below product-company new-grad bands, so the total lands far under the candidate's ~130k anchor. Estimate based on general knowledge of Accenture Federal's DC-area entry-level analyst/associate pay, not on posted salary data.</t>
+          <t>Posting lists Primary (Level 1) base range $65,800-$98,800; a new grad typically lands ~$70-85k base, plus a modest discretionary bonus and no equity. Consistent with traditional defense-prime new-grad comp (Northrop/Lockheed/RTX), which runs roughly 30-45% below tech-industry new-grad TC and well under the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -16422,38 +16426,38 @@
         <v>237</v>
       </c>
       <c r="B238" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>$75k–$112k</t>
+          <t>$72k–$92k</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Illumina</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Systems Integration Engineer 1</t>
+          <t>Software Engineering Associate</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Arlington County, Arlington, VA</t>
         </is>
       </c>
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Wet-lab biochemical assay and DNA-sequencing instrumentation integration role requiring a bio/chem/bioengineering background, with only incidental Python scripting — almost no overlap with the candidate's backend, distributed-systems, and AI-infra profile.</t>
+          <t>Federal consulting associate role centered on configuration changes, testing, and project-management support with Excel/Visio proficiency called out — far from the candidate's backend/distributed-systems/AI-infra profile — plus it is a stale posting (graduation "no later than December 2014"), requires US citizenship for a clearance-driven client, and is location-locked to Arlington, VA.</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Posting states base range $68,400-$102,600 plus a variable cash bonus (~5-8%) and possible small equity; posting notes most hires land between minimum and midpoint, so realistic TC is likely ~$78-90K — below the candidate's $120K low-match floor and well under the $130K anchor.</t>
+          <t>Accenture Federal Services entry-level engineering is consulting-tier compensation: roughly $70-85k base with a modest performance bonus and no equity. The federal/public-sector practice pays below Accenture's commercial technology arm and well below product-company new-grad bands, so the total lands far under the candidate's ~130k anchor. Estimate based on general knowledge of Accenture Federal's DC-area entry-level analyst/associate pay, not on posted salary data.</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -16492,34 +16496,34 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>$85k–$110k</t>
+          <t>$75k–$112k</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Renesas Electronics</t>
+          <t>Illumina</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Systems Integration Engineer 1</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr">
         <is>
-          <t>EE-centric semiconductor product engineering (silicon characterization, yield/test analysis, BOM release, 100% onsite Austin) matches none of the candidate's backend/distributed-systems/AI-infra strengths and falls directly in his hardware/embedded-only exclusion, plus it reads as an immediate-start req rather than a 2027 new-grad pipeline.</t>
+          <t>Wet-lab biochemical assay and DNA-sequencing instrumentation integration role requiring a bio/chem/bioengineering background, with only incidental Python scripting — almost no overlap with the candidate's backend, distributed-systems, and AI-infra profile.</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Renesas is a mid-tier global semiconductor firm; entry-level product engineering in Austin typically pays ~$80-100k base with a modest bonus and little/no equity — below the candidate's ~130k anchor. Estimate, not fact.</t>
+          <t>Posting states base range $68,400-$102,600 plus a variable cash bonus (~5-8%) and possible small equity; posting notes most hires land between minimum and midpoint, so realistic TC is likely ~$78-90K — below the candidate's $120K low-match floor and well under the $130K anchor.</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -16545,7 +16549,7 @@
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16554,38 +16558,38 @@
         <v>239</v>
       </c>
       <c r="B240" s="5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>$48k–$65k</t>
+          <t>$85k–$110k</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Trustpilot</t>
+          <t>Renesas Electronics</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Software Engineer 1 - Trust Tech</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
-          <t>UK/Denmark-only role (no US location or stated sponsorship) with a Node.js/TypeScript full-stack + React internal-tooling focus, which misses the candidate's Java/Rust/Go backend and distributed-systems profile despite some AWS/Postgres and applied-AI overlap.</t>
+          <t>EE-centric semiconductor product engineering (silicon characterization, yield/test analysis, BOM release, 100% onsite Austin) matches none of the candidate's backend/distributed-systems/AI-infra strengths and falls directly in his hardware/embedded-only exclusion, plus it reads as an immediate-start req rather than a 2027 new-grad pipeline.</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Estimate, not fact: Trustpilot is a profitable FTSE-250 mid-tier tech company; London/Edinburgh graduate SWE I base typically ~£38-50k plus a modest bonus, converting to roughly $48-65k USD. UK/EU pay scales sit far below the candidate's ~$130-165k US anchor, so the shortfall is structural rather than negotiable.</t>
+          <t>Renesas is a mid-tier global semiconductor firm; entry-level product engineering in Austin typically pays ~$80-100k base with a modest bonus and little/no equity — below the candidate's ~130k anchor. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -16611,7 +16615,7 @@
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -16620,38 +16624,38 @@
         <v>240</v>
       </c>
       <c r="B241" s="5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>$42k–$50k</t>
+          <t>$48k–$65k</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>United Smart Tech</t>
+          <t>Trustpilot</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>AI Engineer - Agents &amp; Experimentation</t>
+          <t>Software Engineer 1 - Trust Tech</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Carrollton, TX</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Topically adjacent (LLM agents, Python, API/backend integration) but disqualifying on comp — the posting states $20-23/hour (~$42-48k), roughly a third of the ~$130k anchor — and it is an under-leveled hourly role inside an Operations department at a device-repair org rather than a product/infra engineering team, with no 2027 new-grad start signal.</t>
+          <t>UK/Denmark-only role (no US location or stated sponsorship) with a Node.js/TypeScript full-stack + React internal-tooling focus, which misses the candidate's Java/Rust/Go backend and distributed-systems profile despite some AWS/Postgres and applied-AI overlap.</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Compensation is explicitly stated in the posting as $20-$23/hour; annualized at 2080 hours that is $41.6k-$47.8k, with a small allowance on the high end for any unstated bonus. Company is Asurion/uBreakiFix (posting via BambooHR under "United Smart Tech") — a non-tech-tier employer for this Operations-department req, so no equity component assumed.</t>
+          <t>Estimate, not fact: Trustpilot is a profitable FTSE-250 mid-tier tech company; London/Edinburgh graduate SWE I base typically ~£38-50k plus a modest bonus, converting to roughly $48-65k USD. UK/EU pay scales sit far below the candidate's ~$130-165k US anchor, so the shortfall is structural rather than negotiable.</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -16677,7 +16681,7 @@
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -16686,38 +16690,38 @@
         <v>241</v>
       </c>
       <c r="B242" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>$58k–$85k</t>
+          <t>$42k–$50k</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>United Smart Tech</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Analyst AI Opportunity &amp; Value Creation</t>
+          <t>AI Engineer - Agents &amp; Experimentation</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Remote in USA</t>
+          <t>Carrollton, TX</t>
         </is>
       </c>
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Business/data-analyst role focused on healthcare RCM opportunity assessment and stakeholder communication rather than software engineering, so it barely touches the candidate's backend/distributed-systems/AI-infra profile.</t>
+          <t>Topically adjacent (LLM agents, Python, API/backend integration) but disqualifying on comp — the posting states $20-23/hour (~$42-48k), roughly a third of the ~$130k anchor — and it is an under-leveled hourly role inside an Operations department at a device-repair org rather than a product/infra engineering team, with no 2027 new-grad start signal.</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Posting states base range $50,461-$114,114 with a 10% target bonus; a new grad realistically sits near the low end (~$55-75k base + bonus). R1 RCM is a healthcare services/BPO company, not a tech-tier payer, so the top of the band is reserved for experienced healthcare-analytics hires. Well under the candidate's ~$130k anchor.</t>
+          <t>Compensation is explicitly stated in the posting as $20-$23/hour; annualized at 2080 hours that is $41.6k-$47.8k, with a small allowance on the high end for any unstated bonus. Company is Asurion/uBreakiFix (posting via BambooHR under "United Smart Tech") — a non-tech-tier employer for this Operations-department req, so no equity component assumed.</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -16743,7 +16747,7 @@
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16752,38 +16756,38 @@
         <v>242</v>
       </c>
       <c r="B243" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>$48k–$62k</t>
+          <t>$58k–$85k</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Sun Life</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Analyst AI Opportunity &amp; Value Creation</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>North York, ON, Canada, Waterloo, ON, Canada</t>
+          <t>Remote in USA</t>
         </is>
       </c>
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Both locations are in Ontario, Canada (outside the candidate's US target and requiring Canadian work authorization), the posting reads as an immediate-start Corporate IT role rather than a mid-2027 new-grad pipeline, and the work is Informatica/AWS Glue ETL plus AML application support — largely disconnected from the candidate's distributed-systems, backend-microservices, and AI-infra strengths.</t>
+          <t>Business/data-analyst role focused on healthcare RCM opportunity assessment and stakeholder communication rather than software engineering, so it barely touches the candidate's backend/distributed-systems/AI-infra profile.</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Sun Life is a non-tech insurance/financial-services employer; Canadian associate-engineer new-grad comp typically runs ~CAD 65-85k base with small bonus, converting to roughly USD 48-62k — far below the candidate's ~130k anchor. Estimate is approximate, based on general knowledge of Canadian insurance-sector IT pay bands.</t>
+          <t>Posting states base range $50,461-$114,114 with a 10% target bonus; a new grad realistically sits near the low end (~$55-75k base + bonus). R1 RCM is a healthcare services/BPO company, not a tech-tier payer, so the top of the band is reserved for experienced healthcare-analytics hires. Well under the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -16818,38 +16822,38 @@
         <v>243</v>
       </c>
       <c r="B244" s="5" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>$120k–$160k</t>
+          <t>$48k–$62k</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>GlobalFoundries</t>
+          <t>Sun Life</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Principal Engineer Technology Development</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Essex Junction, VT</t>
+          <t>North York, ON, Canada, Waterloo, ON, Canada</t>
         </is>
       </c>
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
-          <t>PhD-required semiconductor process/device development role in a VT fab cleanroom — EE/solid-state physics work with no backend, distributed-systems, or AI-infra overlap, matching the candidate's explicit hardware/EE-centric exclusion.</t>
+          <t>Both locations are in Ontario, Canada (outside the candidate's US target and requiring Canadian work authorization), the posting reads as an immediate-start Corporate IT role rather than a mid-2027 new-grad pipeline, and the work is Informatica/AWS Glue ETL plus AML application support — largely disconnected from the candidate's distributed-systems, backend-microservices, and AI-infra strengths.</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Posting states $85k-$146k base; as a PhD-level new-grad req, realistic base lands upper-half (~$125-145k) plus modest bonus/RSU typical of GlobalFoundries (semiconductor tier, below big-tech SWE comp). Estimate, not fact.</t>
+          <t>Sun Life is a non-tech insurance/financial-services employer; Canadian associate-engineer new-grad comp typically runs ~CAD 65-85k base with small bonus, converting to roughly USD 48-62k — far below the candidate's ~130k anchor. Estimate is approximate, based on general knowledge of Canadian insurance-sector IT pay bands.</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -16884,38 +16888,38 @@
         <v>244</v>
       </c>
       <c r="B245" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>$80k–$100k</t>
+          <t>$120k–$160k</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>GlobalFoundries</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Principal Engineer Technology Development</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN</t>
+          <t>Essex Junction, VT</t>
         </is>
       </c>
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Requires an active DoD Secret clearance on day 1 (candidate has none and is not clearance-eligible on this timeline), targets a 2026 start rather than May 2027, and is onsite defense C/C++/Ada development in Fort Wayne, IN — off-profile for a backend/distributed-systems/AI-infra new grad.</t>
+          <t>PhD-required semiconductor process/device development role in a VT fab cleanroom — EE/solid-state physics work with no backend, distributed-systems, or AI-infra overlap, matching the candidate's explicit hardware/EE-centric exclusion.</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Posting lists $57,200–$108,800 spanning all experience levels; RTX/Raytheon SWE I new grads typically land ~$78–95k base plus a modest (~5%) annual bonus and 401(k) match, with no equity. Low-cost-of-living Fort Wayne placement pulls toward the lower half of the band. Well below the candidate's ~$130k anchor.</t>
+          <t>Posting states $85k-$146k base; as a PhD-level new-grad req, realistic base lands upper-half (~$125-145k) plus modest bonus/RSU typical of GlobalFoundries (semiconductor tier, below big-tech SWE comp). Estimate, not fact.</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -16941,7 +16945,7 @@
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -16954,38 +16958,34 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>$68k–$100k</t>
+          <t>$80k–$100k</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada, Remote in Canada</t>
+          <t>Fort Wayne, IN</t>
         </is>
       </c>
       <c r="G246" t="inlineStr"/>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>expected graduation date in 2025 strong cs fundame</t>
-        </is>
-      </c>
+      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Canada-only role (candidate is US-authorized with no Canadian work rights), requires a 2025 graduation date vs. the candidate's May 2027, and the Digital Experience Platform work is customer-facing web/app development rather than backend, distributed systems, or AI infra — plus disclosed pay converts to well under the candidate's ~120k floor.</t>
+          <t>Requires an active DoD Secret clearance on day 1 (candidate has none and is not clearance-eligible on this timeline), targets a 2026 start rather than May 2027, and is onsite defense C/C++/Ada development in Fort Wayne, IN — off-profile for a backend/distributed-systems/AI-infra new grad.</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Posting discloses CAD $88,000–$128,700 base for Canada, which is roughly USD $64k–$94k at current rates. Autodesk is a solid mid-tier tech employer offering an annual cash bonus plus a modest RSU grant on top of base, so total comp lands a bit above the converted base range. Canadian new-grad comp runs materially below US equivalents for the same company, so this band is lower than an Autodesk US req would be. Estimate anchored on the disclosed range rather than general tier knowledge, so confidence is relatively high.</t>
+          <t>Posting lists $57,200–$108,800 spanning all experience levels; RTX/Raytheon SWE I new grads typically land ~$78–95k base plus a modest (~5%) annual bonus and 401(k) match, with no equity. Low-cost-of-living Fort Wayne placement pulls toward the lower half of the band. Well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -17024,38 +17024,38 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>$80k–$100k</t>
+          <t>$68k–$100k</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Tucson, AZ</t>
+          <t>Toronto, ON, Canada, Remote in Canada</t>
         </is>
       </c>
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr">
         <is>
-          <t>start date this requisition is for an rtx</t>
+          <t>expected graduation date in 2025 strong cs fundame</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Requires an active/interim DoD Secret clearance before start (candidate has none) and is explicitly earmarked for an RTX intern converting to FT, plus onsite-only embedded real-time C/C++ missile software in Tucson — off-profile for a backend/distributed-systems/AI-infra new grad, at a pay band below his ~$130k anchor.</t>
+          <t>Canada-only role (candidate is US-authorized with no Canadian work rights), requires a 2025 graduation date vs. the candidate's May 2027, and the Digital Experience Platform work is customer-facing web/app development rather than backend, distributed systems, or AI infra — plus disclosed pay converts to well under the candidate's ~120k floor.</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Posted range $57.2k–$108.8k covers all experience levels; defense primes (RTX/Raytheon) typically pay new-grad SWE ~$75–95k base with a small ~4–8% bonus and negligible equity, putting realistic entry TC in the high-$80s to low-$90s. Estimate, not fact.</t>
+          <t>Posting discloses CAD $88,000–$128,700 base for Canada, which is roughly USD $64k–$94k at current rates. Autodesk is a solid mid-tier tech employer offering an annual cash bonus plus a modest RSU grant on top of base, so total comp lands a bit above the converted base range. Canadian new-grad comp runs materially below US equivalents for the same company, so this band is lower than an Autodesk US req would be. Estimate anchored on the disclosed range rather than general tier knowledge, so confidence is relatively high.</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -17081,7 +17081,7 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17090,38 +17090,42 @@
         <v>247</v>
       </c>
       <c r="B248" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>$65k–$85k</t>
+          <t>$80k–$100k</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>M.C. Dean</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Systems Specialist - Associate</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Richmond, VA</t>
+          <t>Tucson, AZ</t>
         </is>
       </c>
       <c r="G248" t="inlineStr"/>
-      <c r="H248" t="inlineStr"/>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>start date this requisition is for an rtx</t>
+        </is>
+      </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Construction-project data/process support role (WBS maintenance, InfraLink/P6/Maximo configuration, earned-value reporting) with no software engineering, backend, or systems work — essentially none of the candidate's distributed-systems, cloud, or AI-infra strengths apply.</t>
+          <t>Requires an active/interim DoD Secret clearance before start (candidate has none) and is explicitly earmarked for an RTX intern converting to FT, plus onsite-only embedded real-time C/C++ missile software in Tucson — off-profile for a backend/distributed-systems/AI-infra new grad, at a pay band below his ~$130k anchor.</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Estimate, not fact: M.C. Dean is an engineering/construction contractor (non-tech pay tier), and this is an "Associate" 0+ years req in Richmond, VA — a low-cost market. Comparable contractor/AEC associate analyst roles run roughly $65-80k base with a small bonus, so ~$65-85k TC. Well below the candidate's ~130k anchor.</t>
+          <t>Posted range $57.2k–$108.8k covers all experience levels; defense primes (RTX/Raytheon) typically pay new-grad SWE ~$75–95k base with a small ~4–8% bonus and negligible equity, putting realistic entry TC in the high-$80s to low-$90s. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -17147,7 +17151,7 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -17156,42 +17160,38 @@
         <v>248</v>
       </c>
       <c r="B249" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>$80k–$98k</t>
+          <t>$65k–$85k</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>M.C. Dean</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Software Engineer 1 - Test Solutions</t>
+          <t>Systems Specialist - Associate</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Tucson, AZ</t>
+          <t>Richmond, VA</t>
         </is>
       </c>
       <c r="G249" t="inlineStr"/>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>start date at raytheon, the foundation of</t>
-        </is>
-      </c>
+      <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Requires an active/interim DoD Secret clearance before start (candidate has none), is C#/C++ Windows test-tooling rather than backend/distributed/AI-infra, is 100% onsite in Tucson, and pays below the candidate's ~120k floor with a start date ~9 months before his May 2027 graduation.</t>
+          <t>Construction-project data/process support role (WBS maintenance, InfraLink/P6/Maximo configuration, earned-value reporting) with no software engineering, backend, or systems work — essentially none of the candidate's distributed-systems, cloud, or AI-infra strengths apply.</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Posting states $57,200-$108,800 across all experience levels; a fresh-BS SWE I in low-COL Tucson typically lands ~$78-92k base plus a modest non-guaranteed annual incentive and 401(k) match. Defense primes (RTX/Raytheon) sit well below FAANG/Wayfair-tier new-grad comp.</t>
+          <t>Estimate, not fact: M.C. Dean is an engineering/construction contractor (non-tech pay tier), and this is an "Associate" 0+ years req in Richmond, VA — a low-cost market. Comparable contractor/AEC associate analyst roles run roughly $65-80k base with a small bonus, so ~$65-85k TC. Well below the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -17217,7 +17217,7 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>$78k–$98k</t>
+          <t>$80k–$98k</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Software Engineer 1 - Test Solutions</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -17251,17 +17251,17 @@
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr">
         <is>
-          <t>start date are you ready to explore the w</t>
+          <t>start date at raytheon, the foundation of</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Requires an active/interim DoD Secret clearance before start (candidate has none — an explicit disqualifier), and the work is C#/C++ test-equipment software in Tucson rather than backend/distributed-systems/AI-infra, with pay below the candidate's ~130k anchor.</t>
+          <t>Requires an active/interim DoD Secret clearance before start (candidate has none), is C#/C++ Windows test-tooling rather than backend/distributed/AI-infra, is 100% onsite in Tucson, and pays below the candidate's ~120k floor with a start date ~9 months before his May 2027 graduation.</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Posting lists 57.2k-108.8k across all experience levels; as a defense prime, RTX typically places a new-grad SWE I in the lower-middle of that band (~75-90k base) plus modest bonus and 401k match, with Tucson cost-of-labor adjustment. Estimate, not fact.</t>
+          <t>Posting states $57,200-$108,800 across all experience levels; a fresh-BS SWE I in low-COL Tucson typically lands ~$78-92k base plus a modest non-guaranteed annual incentive and 401(k) match. Defense primes (RTX/Raytheon) sit well below FAANG/Wayfair-tier new-grad comp.</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -17296,38 +17296,42 @@
         <v>250</v>
       </c>
       <c r="B251" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>$105k–$140k</t>
+          <t>$78k–$98k</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Johns Hopkins Applied Physics Laboratory</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Senior Engineer-Analyst - ISR Scientific Applications</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Laurel, MD</t>
+          <t>Tucson, AZ</t>
         </is>
       </c>
       <c r="G251" t="inlineStr"/>
-      <c r="H251" t="inlineStr"/>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>start date are you ready to explore the w</t>
+        </is>
+      </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Requires a Doctorate (2026 PhD-grad pipeline) and TS/SCI clearance eligibility, and centers on signal/image processing and sensor fusion rather than backend/distributed systems or AI infra — the candidate is a May 2027 BS/MS grad with no clearance.</t>
+          <t>Requires an active/interim DoD Secret clearance before start (candidate has none — an explicit disqualifier), and the work is C#/C++ test-equipment software in Tucson rather than backend/distributed-systems/AI-infra, with pay below the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>JHU APL is a nonprofit UARC: below-market cash comp offset by a strong pension, high retirement contributions, and education benefits; no equity and minimal bonus. Band reflects the PhD-entry "Senior Engineer-Analyst" level in the Laurel/Baltimore-DC market. A bachelor's-level APL new grad would be closer to $85-105k. Rough estimate from general knowledge of the employer tier, not sourced comp data.</t>
+          <t>Posting lists 57.2k-108.8k across all experience levels; as a defense prime, RTX typically places a new-grad SWE I in the lower-middle of that band (~75-90k base) plus modest bonus and 401k match, with Tucson cost-of-labor adjustment. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -17353,7 +17357,7 @@
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17362,38 +17366,38 @@
         <v>251</v>
       </c>
       <c r="B252" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>$70k–$95k</t>
+          <t>$105k–$140k</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Vanasse Hangen Brustlin</t>
+          <t>Johns Hopkins Applied Physics Laboratory</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Software Evaluation &amp; Enablement Analyst</t>
+          <t>Senior Engineer-Analyst - ISR Scientific Applications</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Augusta, ME, Watertown, MA, NYC</t>
+          <t>Laurel, MD</t>
         </is>
       </c>
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Non-engineering IT/business-analyst role (software procurement evaluation, documentation, vendor liaison) at a civil-engineering consultancy — no coding, no distributed systems or AI infra, and flagged as an "Experienced" career stage, so it's off-profile for a backend/systems new grad.</t>
+          <t>Requires a Doctorate (2026 PhD-grad pipeline) and TS/SCI clearance eligibility, and centers on signal/image processing and sensor fusion rather than backend/distributed systems or AI infra — the candidate is a May 2027 BS/MS grad with no clearance.</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>VHB is an AEC (architecture/engineering/construction) consulting firm, not a tech employer; internal IT analyst compensation at such firms in Boston/NYC typically runs well below software-engineering market rates. Estimate is a wide band given limited public comp data for this specific role.</t>
+          <t>JHU APL is a nonprofit UARC: below-market cash comp offset by a strong pension, high retirement contributions, and education benefits; no equity and minimal bonus. Band reflects the PhD-entry "Senior Engineer-Analyst" level in the Laurel/Baltimore-DC market. A bachelor's-level APL new grad would be closer to $85-105k. Rough estimate from general knowledge of the employer tier, not sourced comp data.</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -17419,7 +17423,7 @@
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -17432,34 +17436,34 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>$65k–$90k</t>
+          <t>$70k–$95k</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>Vanasse Hangen Brustlin</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Entry Level .NET Developer</t>
+          <t>Software Evaluation &amp; Enablement Analyst</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Louisville, CO</t>
+          <t>Augusta, ME, Watertown, MA, NYC</t>
         </is>
       </c>
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Hard-blocked by the SECRET clearance and Security+ certification requirements, and the work is legacy Java/.NET web-app consulting with no backend-distributed-systems, infra, or AI-platform overlap.</t>
+          <t>Non-engineering IT/business-analyst role (software procurement evaluation, documentation, vendor liaison) at a civil-engineering consultancy — no coding, no distributed systems or AI infra, and flagged as an "Experienced" career stage, so it's off-profile for a backend/systems new grad.</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Small IT staffing/consulting firm (Connecticut-based body shop) with no public comp data; estimate based on typical entry-level government-contract staffing pay in a mid-cost Colorado market. Wide band due to unknown company; likely far below the candidate's ~130k anchor.</t>
+          <t>VHB is an AEC (architecture/engineering/construction) consulting firm, not a tech employer; internal IT analyst compensation at such firms in Boston/NYC typically runs well below software-engineering market rates. Estimate is a wide band given limited public comp data for this specific role.</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -17485,7 +17489,7 @@
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -17508,24 +17512,24 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Entry Level .NET Developer</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Louisville, CO</t>
         </is>
       </c>
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Hard disqualifier: the posting requires an interim SECRET clearance to begin work plus existing CompTIA Security+ certification, which the candidate explicitly lacks — and the role itself is legacy full-stack JSP/Hibernate/WebLogic consulting work with graphic-designer/site-design duties, far from backend distributed systems or AI infra, at a comp tier well under the 120k floor.</t>
+          <t>Hard-blocked by the SECRET clearance and Security+ certification requirements, and the work is legacy Java/.NET web-app consulting with no backend-distributed-systems, infra, or AI-platform overlap.</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions is a small Connecticut-based IT services/staffing consultancy, not a product company — entry-level Java/consulting roles at this tier typically pay near-flat base with minimal bonus or equity. Wide band due to low visibility into this specific firm's pay; Portland, OR cost-of-living offers slight upward pressure but government-contract billing rates cap entry-level comp. Well below the candidate's ~130-165k anchor.</t>
+          <t>Small IT staffing/consulting firm (Connecticut-based body shop) with no public comp data; estimate based on typical entry-level government-contract staffing pay in a mid-cost Colorado market. Wide band due to unknown company; likely far below the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -17564,34 +17568,34 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>$60k–$90k</t>
+          <t>$65k–$90k</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Android Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Dallas, TX</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Android mobile app development at a staffing consultancy — off-profile versus the candidate's backend/distributed-systems/AI-infra focus, requires 2 years Java plus a published Play Store app, wants an immediate start (candidate grads May 2027), and pays $60-90k, well under the ~130k anchor.</t>
+          <t>Hard disqualifier: the posting requires an interim SECRET clearance to begin work plus existing CompTIA Security+ certification, which the candidate explicitly lacks — and the role itself is legacy full-stack JSP/Hibernate/WebLogic consulting work with graphic-designer/site-design duties, far from backend distributed systems or AI infra, at a comp tier well under the 120k floor.</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Salary band is stated explicitly in the posting ($60k-$90k, or $30-45/hr on contract). Small IT consulting/staffing firm, so assume no equity and negligible bonus — posted salary is effectively total comp. A new grad with no Android production experience would land near the floor (~$60-70k).</t>
+          <t>9to9 Software Solutions is a small Connecticut-based IT services/staffing consultancy, not a product company — entry-level Java/consulting roles at this tier typically pay near-flat base with minimal bonus or equity. Wide band due to low visibility into this specific firm's pay; Portland, OR cost-of-living offers slight upward pressure but government-contract billing rates cap entry-level comp. Well below the candidate's ~130-165k anchor.</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -17617,7 +17621,7 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -17630,34 +17634,34 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>$70k–$90k</t>
+          <t>$60k–$90k</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Dutch Bros</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Associate Endpoint Engineer</t>
+          <t>Android Developer</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Tempe, AZ</t>
+          <t>Dallas, TX</t>
         </is>
       </c>
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Title says "Endpoint Engineer" but the body is an entry-level BI/data-analyst role (Excel, Power Query, Tableau/Power BI, stakeholder dashboards) with zero backend/distributed-systems/infra content, plus it's an immediate-start onsite Tempe position rather than a mid-2027 new-grad req.</t>
+          <t>Android mobile app development at a staffing consultancy — off-profile versus the candidate's backend/distributed-systems/AI-infra focus, requires 2 years Java plus a published Play Store app, wants an immediate start (candidate grads May 2027), and pays $60-90k, well under the ~130k anchor.</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Non-tech QSR/retail corporate HQ employer (Dutch Bros, Tempe AZ) posting "Compensation: DOE" for a 0-1 yr analyst role; no public leveling data, so this is a wide low-confidence estimate based on typical entry-level BI analyst pay in the Phoenix market — far below the candidate's ~$130k anchor.</t>
+          <t>Salary band is stated explicitly in the posting ($60k-$90k, or $30-45/hr on contract). Small IT consulting/staffing firm, so assume no equity and negligible bonus — posted salary is effectively total comp. A new grad with no Android production experience would land near the floor (~$60-70k).</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -17683,7 +17687,7 @@
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17692,42 +17696,38 @@
         <v>256</v>
       </c>
       <c r="B257" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>$115k–$145k</t>
+          <t>$70k–$90k</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Johns Hopkins Applied Physics Laboratory</t>
+          <t>Dutch Bros</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Autonomous Systems Seeker and Sensor Engineer</t>
+          <t>Associate Endpoint Engineer</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Laurel, MD</t>
+          <t>Tempe, AZ</t>
         </is>
       </c>
       <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>start date and can ultimately obtain a se</t>
-        </is>
-      </c>
+      <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Requires a PhD in EE/Physics/Math, a 2026 graduation, and an obtainable Interim Secret clearance, and the work is RF/EO-IR seeker and sensor hardware/signal processing — all direct mismatches for a clearance-free May 2027 backend/distributed-systems/AI-infra new grad.</t>
+          <t>Title says "Endpoint Engineer" but the body is an entry-level BI/data-analyst role (Excel, Power Query, Tableau/Power BI, stakeholder dashboards) with zero backend/distributed-systems/infra content, plus it's an immediate-start onsite Tempe position rather than a mid-2027 new-grad req.</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>JHU APL is a non-profit UARC: no equity, modest bonus, but strong (~10%+) retirement contributions and tuition assistance. Band reflects the posting's PhD-level new-grad target (base ~$105-130k); a BS/MS new grad there would be closer to $85-110k, below the candidate's ~$120k floor. Moderate confidence — APL compensation bands are not widely reported.</t>
+          <t>Non-tech QSR/retail corporate HQ employer (Dutch Bros, Tempe AZ) posting "Compensation: DOE" for a 0-1 yr analyst role; no public leveling data, so this is a wide low-confidence estimate based on typical entry-level BI analyst pay in the Phoenix market — far below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -17753,7 +17753,7 @@
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -17762,38 +17762,42 @@
         <v>257</v>
       </c>
       <c r="B258" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>$70k–$88k</t>
+          <t>$115k–$145k</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>M.C. Dean</t>
+          <t>Johns Hopkins Applied Physics Laboratory</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Systems Specialist - Associate</t>
+          <t>Autonomous Systems Seeker and Sensor Engineer</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Laurel, MD</t>
         </is>
       </c>
       <c r="G258" t="inlineStr"/>
-      <c r="H258" t="inlineStr"/>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>start date and can ultimately obtain a se</t>
+        </is>
+      </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Construction-project data/process coordination role (WBS setup, P6 schedule sync, Earned Value tracking in an internal platform) rather than a software engineering role — it exercises none of the candidate's backend, distributed-systems, cloud, or AI-infra strengths.</t>
+          <t>Requires a PhD in EE/Physics/Math, a 2026 graduation, and an obtainable Interim Secret clearance, and the work is RF/EO-IR seeker and sensor hardware/signal processing — all direct mismatches for a clearance-free May 2027 backend/distributed-systems/AI-infra new grad.</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>M.C. Dean is a large engineering/construction integrator, not a tech-comp payer: associate/entry roles are base salary plus a modest bonus with no equity. Atlanta market and the "0+ years, BS" framing put this in the high-60s to high-80s range. Estimate from general knowledge of E&amp;C contractor new-grad pay, not a posted range; well below the candidate's ~130k anchor.</t>
+          <t>JHU APL is a non-profit UARC: no equity, modest bonus, but strong (~10%+) retirement contributions and tuition assistance. Band reflects the posting's PhD-level new-grad target (base ~$105-130k); a BS/MS new grad there would be closer to $85-110k, below the candidate's ~$120k floor. Moderate confidence — APL compensation bands are not widely reported.</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -17832,34 +17836,34 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>$60k–$85k</t>
+          <t>$70k–$88k</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>M.C. Dean</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Entry Level Java Developer</t>
+          <t>Systems Specialist - Associate</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Silver Creek, NY</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr">
         <is>
-          <t>IT staffing/consulting shop posting a legacy Java web-app contract role that hard-requires an interim SECRET clearance plus Security+ certification — an explicit disqualifier for this candidate — and the work (JSP/WebLogic/Subversion, "site-design instincts") is far below his distributed-systems/AI-infra profile and TC anchor.</t>
+          <t>Construction-project data/process coordination role (WBS setup, P6 schedule sync, Earned Value tracking in an internal platform) rather than a software engineering role — it exercises none of the candidate's backend, distributed-systems, cloud, or AI-infra strengths.</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions is a small Connecticut-based IT services/staffing firm with no public compensation data, so this is a wide, low-confidence band inferred from typical entry-level government-contract Java staffing rates (largely base salary, minimal equity or bonus). Well below the candidate's ~130-165k anchor.</t>
+          <t>M.C. Dean is a large engineering/construction integrator, not a tech-comp payer: associate/entry roles are base salary plus a modest bonus with no equity. Atlanta market and the "0+ years, BS" framing put this in the high-60s to high-80s range. Estimate from general knowledge of E&amp;C contractor new-grad pay, not a posted range; well below the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -17885,7 +17889,7 @@
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -17913,19 +17917,19 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Elk Grove, CA</t>
+          <t>Silver Creek, NY</t>
         </is>
       </c>
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Contract staffing role that hard-requires an interim/full SECRET clearance and Security+ certification (both explicit candidate disqualifiers), on legacy JSP/Hibernate/WebLogic web-app work with design responsibilities — off-profile for a backend/distributed-systems new grad and almost certainly below the ~120k TC floor.</t>
+          <t>IT staffing/consulting shop posting a legacy Java web-app contract role that hard-requires an interim SECRET clearance plus Security+ certification — an explicit disqualifier for this candidate — and the work (JSP/WebLogic/Subversion, "site-design instincts") is far below his distributed-systems/AI-infra profile and TC anchor.</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>No public comp data for 9to9 Software Solutions — a small CT-based IT staffing/consulting firm. Band inferred from typical entry-level contract Java roles at government-contract body shops (roughly $30–40/hr, little to no bonus or equity). Wide band reflects low confidence and the contract (non-FTE) structure.</t>
+          <t>9to9 Software Solutions is a small Connecticut-based IT services/staffing firm with no public compensation data, so this is a wide, low-confidence band inferred from typical entry-level government-contract Java staffing rates (largely base salary, minimal equity or bonus). Well below the candidate's ~130-165k anchor.</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -17964,34 +17968,34 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>$70k–$85k</t>
+          <t>$60k–$85k</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>PHIHONG USA</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Firmware Engineer</t>
+          <t>Entry Level Java Developer</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Bohemia, NY</t>
+          <t>Elk Grove, CA</t>
         </is>
       </c>
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Embedded/firmware role for power-supply hardware (microcontroller drivers, control algorithms, assembly, EE-leaning, strictly onsite Bohemia NY) is explicitly in the candidate's low-fit category and uses none of his backend, distributed-systems, cloud, or AI-infra strengths.</t>
+          <t>Contract staffing role that hard-requires an interim/full SECRET clearance and Security+ certification (both explicit candidate disqualifiers), on legacy JSP/Hibernate/WebLogic web-app work with design responsibilities — off-profile for a backend/distributed-systems new grad and almost certainly below the ~120k TC floor.</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Posting states $70-95K DOE with "Minimum Experience: Entry-level"; a new grad realistically lands at the bottom of that band. PHIHONG USA is a small hardware/power-supply subsidiary — no equity, minimal bonus — so base ≈ total comp. Well below the candidate's ~$130-165K anchor.</t>
+          <t>No public comp data for 9to9 Software Solutions — a small CT-based IT staffing/consulting firm. Band inferred from typical entry-level contract Java roles at government-contract body shops (roughly $30–40/hr, little to no bonus or equity). Wide band reflects low confidence and the contract (non-FTE) structure.</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -18017,7 +18021,7 @@
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -18026,38 +18030,38 @@
         <v>261</v>
       </c>
       <c r="B262" s="5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>$85k–$120k</t>
+          <t>$70k–$85k</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>PHIHONG USA</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Upgrade Install and Relocation Engineer - Duv</t>
+          <t>Firmware Engineer</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Austin, TX, Dallas, TX</t>
+          <t>Bohemia, NY</t>
         </is>
       </c>
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr">
         <is>
-          <t>This is a hands-on electromechanical field-service role (cleanroom equipment install, ME/EE degree preferred, 75% travel, rotating/on-call shifts) with essentially no software engineering content, putting it squarely in the candidate's role_fit_low bucket of hardware/EE-centric work, and the likely comp also lands under his ~120k floor.</t>
+          <t>Embedded/firmware role for power-supply hardware (microcontroller drivers, control algorithms, assembly, EE-leaning, strictly onsite Bohemia NY) is explicitly in the candidate's low-fit category and uses none of his backend, distributed-systems, cloud, or AI-infra strengths.</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>ASML US field service/install engineer at the 0-2 yr level typically pays roughly $75-95k base with shift differential, on-call/overtime pay, and a modest bonus, pushing realistic first-year TC into the ~$85-120k range; semiconductor field service pays below software tier, and the band is widened for uncertainty since ASML doesn't publish new-grad software-comparable numbers.</t>
+          <t>Posting states $70-95K DOE with "Minimum Experience: Entry-level"; a new grad realistically lands at the bottom of that band. PHIHONG USA is a small hardware/power-supply subsidiary — no equity, minimal bonus — so base ≈ total comp. Well below the candidate's ~$130-165K anchor.</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -18092,38 +18096,38 @@
         <v>262</v>
       </c>
       <c r="B263" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>$85k–$110k</t>
+          <t>$85k–$120k</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Failure Analysis Engineer</t>
+          <t>Upgrade Install and Relocation Engineer - Duv</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Acton, MA</t>
+          <t>Austin, TX, Dallas, TX</t>
         </is>
       </c>
       <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr">
         <is>
-          <t>EE/photonics lab failure-analysis role (coherent optical transceivers, oscilloscopes, RF/optical spectrum analyzers) with zero software content, requiring prior hands-on FA experience — squarely in the candidate's hardware/embedded-only low-fit bucket, and the immediate onsite start conflicts with a mid-2027 new-grad timeline.</t>
+          <t>This is a hands-on electromechanical field-service role (cleanroom equipment install, ME/EE degree preferred, 75% travel, rotating/on-call shifts) with essentially no software engineering content, putting it squarely in the candidate's role_fit_low bucket of hardware/EE-centric work, and the likely comp also lands under his ~120k floor.</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Posting explicitly states a new-hire base range of $79,200-$100,400; adding a ~5-8% Cisco bonus and a small RSU grant yields roughly $85-110k TC. Cisco's Supply Chain and Manufacturing Ops org pays materially below its SWE ladder, and a new grad would land in the lower half of the posted band, so the realistic center is ~$90k — below the candidate's ~120k low-match floor.</t>
+          <t>ASML US field service/install engineer at the 0-2 yr level typically pays roughly $75-95k base with shift differential, on-call/overtime pay, and a modest bonus, pushing realistic first-year TC into the ~$85-120k range; semiconductor field service pays below software tier, and the band is widened for uncertainty since ASML doesn't publish new-grad software-comparable numbers.</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -18149,7 +18153,7 @@
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18162,34 +18166,34 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>$90k–$110k</t>
+          <t>$85k–$110k</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Reliability Engineer 2</t>
+          <t>Failure Analysis Engineer</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Chandler, AZ</t>
+          <t>Acton, MA</t>
         </is>
       </c>
       <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr">
         <is>
-          <t>This is an EE-centric hardware reliability role (device physics, transistor-level ICs, HTOL burn-in, lab bench equipment, JMP/LabVIEW) with essentially no backend, distributed-systems, or AI-infra content — squarely in the candidate's stated low-fit bucket, and it's an immediate-start req rather than a May 2027 new-grad pipeline.</t>
+          <t>EE/photonics lab failure-analysis role (coherent optical transceivers, oscilloscopes, RF/optical spectrum analyzers) with zero software content, requiring prior hands-on FA experience — squarely in the candidate's hardware/embedded-only low-fit bucket, and the immediate onsite start conflicts with a mid-2027 new-grad timeline.</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Microchip is a mid-tier semiconductor employer in a low-cost metro (Chandler, AZ); new-grad/Engineer II reliability roles there typically pay ~$80-95k base plus modest bonus/ESPP/small RSU, landing around $90-110k TC. Estimate based on general semiconductor-industry knowledge, not a verified data point.</t>
+          <t>Posting explicitly states a new-hire base range of $79,200-$100,400; adding a ~5-8% Cisco bonus and a small RSU grant yields roughly $85-110k TC. Cisco's Supply Chain and Manufacturing Ops org pays materially below its SWE ladder, and a new grad would land in the lower half of the posted band, so the realistic center is ~$90k — below the candidate's ~120k low-match floor.</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -18228,34 +18232,34 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>$85k–$110k</t>
+          <t>$90k–$110k</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Data Analytics and Methods Engineer - Mission Applied Science &amp; Technology</t>
+          <t>Reliability Engineer 2</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Richardson, TX</t>
+          <t>Chandler, AZ</t>
         </is>
       </c>
       <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Hard-blocked: the posting requires an active TS/SCI clearance on day 1 and is explicitly reserved for a converting RTX intern, plus it's a data-analytics/AI-ML applications role onsite in Richardson TX rather than backend/distributed-systems, and the pay band tops out well below the candidate's ~130k anchor.</t>
+          <t>This is an EE-centric hardware reliability role (device physics, transistor-level ICs, HTOL burn-in, lab bench equipment, JMP/LabVIEW) with essentially no backend, distributed-systems, or AI-infra content — squarely in the candidate's stated low-fit bucket, and it's an immediate-start req rather than a May 2027 new-grad pipeline.</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Posting states a 57.2k–108.8k salary range; RTX/Raytheon new-grad engineers typically land ~80–95k base in a Texas market, plus a small annual incentive (~5%) and 401k match, so realistic new-grad TC is roughly 85–110k — defense-primes pay a tier below big tech, and even a cleared premium wouldn't reach the candidate's 130k target.</t>
+          <t>Microchip is a mid-tier semiconductor employer in a low-cost metro (Chandler, AZ); new-grad/Engineer II reliability roles there typically pay ~$80-95k base plus modest bonus/ESPP/small RSU, landing around $90-110k TC. Estimate based on general semiconductor-industry knowledge, not a verified data point.</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -18281,7 +18285,7 @@
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -18304,24 +18308,24 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Data Analytics and Methods Engineer - Mission Applied Science &amp; Technology</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>West Valley City, UT</t>
+          <t>Richardson, TX</t>
         </is>
       </c>
       <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Requires an active TS/SCI with polygraph on day one and is an internal RTX intern-to-FT conversion req, both of which the candidate cannot satisfy; the C++/SIGINT/embedded/Qt focus is also off his backend and distributed-systems profile.</t>
+          <t>Hard-blocked: the posting requires an active TS/SCI clearance on day 1 and is explicitly reserved for a converting RTX intern, plus it's a data-analytics/AI-ML applications role onsite in Richardson TX rather than backend/distributed-systems, and the pay band tops out well below the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Defense-prime (RTX/Applied Signal Technology) new-grad SWE band in Salt Lake City; defense contractors pay well below big-tech/Wayfair-tier new-grad comp, with a small premium for cleared work. Wide band since no range was posted — estimate from general knowledge of the company tier and market.</t>
+          <t>Posting states a 57.2k–108.8k salary range; RTX/Raytheon new-grad engineers typically land ~80–95k base in a Texas market, plus a small annual incentive (~5%) and 401k match, so realistic new-grad TC is roughly 85–110k — defense-primes pay a tier below big tech, and even a cleared premium wouldn't reach the candidate's 130k target.</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -18360,34 +18364,34 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>$70k–$110k</t>
+          <t>$85k–$110k</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Mapjects</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>MicroStrategy Developer</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Fairfax, VA</t>
+          <t>West Valley City, UT</t>
         </is>
       </c>
       <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Off-profile on nearly every axis: it's a contract (C2C/1099) MicroStrategy BI/reporting-dashboard role at a small logistics-portal shop, not a full-time new-grad SWE position, and it touches none of the candidate's backend/distributed-systems/AI-infra strengths while implying an immediate start rather than mid-2027.</t>
+          <t>Requires an active TS/SCI with polygraph on day one and is an internal RTX intern-to-FT conversion req, both of which the candidate cannot satisfy; the C++/SIGINT/embedded/Qt focus is also off his backend and distributed-systems profile.</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Unknown small logistics/staffing-style firm; contract C2C/1099/W2 with "commensurate with experience" pay and no equity — BI developer contract rates in the DC/VA area typically annualize to roughly $70-110k for a junior, well below the ~130k anchor. Wide band because compensation is undisclosed and structured as contract, not salaried new-grad TC.</t>
+          <t>Defense-prime (RTX/Applied Signal Technology) new-grad SWE band in Salt Lake City; defense contractors pay well below big-tech/Wayfair-tier new-grad comp, with a small premium for cleared work. Wide band since no range was posted — estimate from general knowledge of the company tier and market.</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -18426,39 +18430,39 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>$75k–$110k</t>
+          <t>$70k–$110k</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Andrew Morgan</t>
+          <t>Mapjects</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>OneStream Developer</t>
+          <t>MicroStrategy Developer</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Remote in USA</t>
+          <t>Fairfax, VA</t>
         </is>
       </c>
       <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr">
         <is>
-          <t>OneStream Developer is an enterprise EPM/financial-consolidation configuration role at a staffing agency, requiring OneStream platform and accounting-domain experience — essentially no overlap with the candidate's backend, distributed-systems, or AI-infra profile.</t>
+          <t>Off-profile on nearly every axis: it's a contract (C2C/1099) MicroStrategy BI/reporting-dashboard role at a small logistics-portal shop, not a full-time new-grad SWE position, and it touches none of the candidate's backend/distributed-systems/AI-infra strengths while implying an immediate start rather than mid-2027.</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Company unknown / appears to be a recruiting-staffing firm rather than a product company, so this is a wide low-confidence band based on typical entry-level EPM-consultant pay; OneStream roles are usually experienced-hire, not new-grad, and this sits well below the candidate's ~130k anchor.</t>
+          <t>Unknown small logistics/staffing-style firm; contract C2C/1099/W2 with "commensurate with experience" pay and no equity — BI developer contract rates in the DC/VA area typically annualize to roughly $70-110k for a junior, well below the ~130k anchor. Wide band because compensation is undisclosed and structured as contract, not salaried new-grad TC.</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -18488,43 +18492,43 @@
         <v>268</v>
       </c>
       <c r="B269" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>$62k–$82k</t>
+          <t>$75k–$110k</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Shearers Foods</t>
+          <t>Andrew Morgan</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>EDI Business Systems Analyst</t>
+          <t>OneStream Developer</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Massillon, OH</t>
+          <t>Remote in USA</t>
         </is>
       </c>
       <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr">
         <is>
-          <t>This is an internal IT/EDI integration and business-analysis role (X12/EDIFACT mappings, SQL Server queries, requirements gathering, end-user training) at a snack-food manufacturer, which uses almost none of the candidate's distributed-systems, backend-microservice, or AI-infra depth and sits far below their comp anchor.</t>
+          <t>OneStream Developer is an enterprise EPM/financial-consolidation configuration role at a staffing agency, requiring OneStream platform and accounting-domain experience — essentially no overlap with the candidate's backend, distributed-systems, or AI-infra profile.</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Private food-manufacturing company (non-tech industry) in Massillon, OH; EDI/BSA roles at this tier typically pay $60-80k base with a small bonus, well below the candidate's ~$130k anchor. Estimate from general knowledge of CPG/manufacturing IT pay in low-cost Midwest markets, not from posted data.</t>
+          <t>Company unknown / appears to be a recruiting-staffing firm rather than a product company, so this is a wide low-confidence band based on typical entry-level EPM-consultant pay; OneStream roles are usually experienced-hire, not new-grad, and this sits well below the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -18545,7 +18549,7 @@
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18554,43 +18558,43 @@
         <v>269</v>
       </c>
       <c r="B270" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>$85k–$110k</t>
+          <t>$62k–$82k</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>GlobalFoundries</t>
+          <t>Shearers Foods</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Advanced Manufacturing Equipment Engineer New Grad</t>
+          <t>EDI Business Systems Analyst</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Malta, NY</t>
+          <t>Massillon, OH</t>
         </is>
       </c>
       <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Semiconductor fab equipment engineering is a hardware/process role (EE/ChemE/MatSci-centric) with no meaningful overlap with the candidate's backend, distributed-systems, or AI-infra skill set, and matches his explicitly low-fit "hardware/embedded-only" category.</t>
+          <t>This is an internal IT/EDI integration and business-analysis role (X12/EDIFACT mappings, SQL Server queries, requirements gathering, end-user training) at a snack-food manufacturer, which uses almost none of the candidate's distributed-systems, backend-microservice, or AI-infra depth and sits far below their comp anchor.</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>GlobalFoundries is a semiconductor manufacturer rather than a tech-tier payer; new-grad equipment/process engineers at its Malta, NY fab typically see ~$80-95k base plus a modest bonus and small equity/sign-on. Wide-ish band given no specific datapoint; well below the candidate's ~$130k anchor.</t>
+          <t>Private food-manufacturing company (non-tech industry) in Massillon, OH; EDI/BSA roles at this tier typically pay $60-80k base with a small bonus, well below the candidate's ~$130k anchor. Estimate from general knowledge of CPG/manufacturing IT pay in low-cost Midwest markets, not from posted data.</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -18611,7 +18615,7 @@
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18628,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>$80k–$110k</t>
+          <t>$85k–$110k</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -18634,7 +18638,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Advanced Manufacturing Equipment Engineer</t>
+          <t>Advanced Manufacturing Equipment Engineer New Grad</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -18646,17 +18650,17 @@
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Hardware/fab equipment engineering role requiring an ME/EE/Materials Science/Physics degree with duties centered on tool installation, maintenance SOPs, and schematics — no overlap with the candidate's backend/distributed-systems/AI-infra software profile.</t>
+          <t>Semiconductor fab equipment engineering is a hardware/process role (EE/ChemE/MatSci-centric) with no meaningful overlap with the candidate's backend, distributed-systems, or AI-infra skill set, and matches his explicitly low-fit "hardware/embedded-only" category.</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Posting states a $58,400-$100,800 base range; GlobalFoundries new-grad equipment engineers typically land mid-range (~$75-95k base) plus a small annual bonus and possible relocation, putting TC well under the candidate's ~$130k anchor.</t>
+          <t>GlobalFoundries is a semiconductor manufacturer rather than a tech-tier payer; new-grad equipment/process engineers at its Malta, NY fab typically see ~$80-95k base plus a modest bonus and small equity/sign-on. Wide-ish band given no specific datapoint; well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -18686,38 +18690,38 @@
         <v>271</v>
       </c>
       <c r="B272" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>$75k–$95k</t>
+          <t>$80k–$110k</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>GlobalFoundries</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Advanced Manufacturing Equipment Engineer</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN</t>
+          <t>Malta, NY</t>
         </is>
       </c>
       <c r="G272" t="inlineStr"/>
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Hard-blocked: the req demands an active DoD Secret clearance from day 1 and is explicitly reserved for an RTX intern converting to full-time, and the Ada/Java C2 work in onsite Fort Wayne at 57–109k misses the candidate's distributed-systems/AI-infra profile and ~130k TC anchor.</t>
+          <t>Hardware/fab equipment engineering role requiring an ME/EE/Materials Science/Physics degree with duties centered on tool installation, maintenance SOPs, and schematics — no overlap with the candidate's backend/distributed-systems/AI-infra software profile.</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>Posted range 57.2k–108.8k; RTX defense new-grad SWE typically lands ~75–90k base with small (0–5%) bonus and no equity, and Fort Wayne IN is a low cost-of-living site so offers skew to the lower-middle of the band. Well below the candidate's ~130k anchor.</t>
+          <t>Posting states a $58,400-$100,800 base range; GlobalFoundries new-grad equipment engineers typically land mid-range (~$75-95k base) plus a small annual bonus and possible relocation, putting TC well under the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -18743,7 +18747,7 @@
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -18771,23 +18775,19 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Tucson, AZ</t>
+          <t>Fort Wayne, IN</t>
         </is>
       </c>
       <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>start date job description are you ready</t>
-        </is>
-      </c>
+      <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Requires an active/interim DoD Secret clearance before start (an explicit candidate disqualifier), and the work is C#/C++ test-equipment engineering onsite in Tucson rather than backend, distributed systems, or AI infra.</t>
+          <t>Hard-blocked: the req demands an active DoD Secret clearance from day 1 and is explicitly reserved for an RTX intern converting to full-time, and the Ada/Java C2 work in onsite Fort Wayne at 57–109k misses the candidate's distributed-systems/AI-infra profile and ~130k TC anchor.</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Posting lists $57.2k-$108.8k across all experience levels; a new-grad SWE I at a defense prime typically lands near the lower third (~$72-85k base) plus a modest annual incentive and 401k match. Well below the candidate's ~$130k anchor.</t>
+          <t>Posted range 57.2k–108.8k; RTX defense new-grad SWE typically lands ~75–90k base with small (0–5%) bonus and no equity, and Fort Wayne IN is a low cost-of-living site so offers skew to the lower-middle of the band. Well below the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -18813,7 +18813,7 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -18822,38 +18822,42 @@
         <v>273</v>
       </c>
       <c r="B274" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>$95k–$130k</t>
+          <t>$75k–$95k</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Lawrence Livermore National Laboratory (LLNL)</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Explainable AI Postdoctoral Researcher</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Livermore, CA</t>
+          <t>Tucson, AZ</t>
         </is>
       </c>
       <c r="G274" t="inlineStr"/>
-      <c r="H274" t="inlineStr"/>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>start date job description are you ready</t>
+        </is>
+      </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Postdoc role with a hard "recent Ph.D." + XAI publication-record requirement, which a May 2027 bachelor's-level backend/distributed-systems new grad cannot meet.</t>
+          <t>Requires an active/interim DoD Secret clearance before start (an explicit candidate disqualifier), and the work is C#/C++ test-equipment engineering onsite in Tucson rather than backend, distributed systems, or AI infra.</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>LLNL PDS.1 postdoc scale is roughly $95-125k base with no equity or meaningful bonus, offset somewhat by federal-lab benefits/pension; this is a postdoc pay band rather than an industry new-grad SWE band, so it lands at or below the candidate's ~$130-165k anchor. Estimate, not fact.</t>
+          <t>Posting lists $57.2k-$108.8k across all experience levels; a new-grad SWE I at a defense prime typically lands near the lower third (~$72-85k base) plus a modest annual incentive and 401k match. Well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -18888,38 +18892,38 @@
         <v>274</v>
       </c>
       <c r="B275" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>$68k–$80k</t>
+          <t>$95k–$130k</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>Lawrence Livermore National Laboratory (LLNL)</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Explainable AI Postdoctoral Researcher</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Livermore, CA</t>
         </is>
       </c>
       <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr">
         <is>
-          <t>SQL Server/SSIS/Salesforce-Apex BI rotational program at ~$75k TC — off-profile for a backend/distributed-systems candidate and far below the ~$130k anchor.</t>
+          <t>Postdoc role with a hard "recent Ph.D." + XAI publication-record requirement, which a May 2027 bachelor's-level backend/distributed-systems new grad cannot meet.</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Posting states an explicit flat rate of $30.00/hr (~$62.4k base at 2,080 hrs) plus a 10% discretionary cash bonus target and a 10% discretionary RSU target; band spans low-to-full attainment of both. Consistent with Axos as a mid-size digital bank running a below-market entry-level rotational pipeline rather than a comp-competitive tech employer.</t>
+          <t>LLNL PDS.1 postdoc scale is roughly $95-125k base with no equity or meaningful bonus, offset somewhat by federal-lab benefits/pension; this is a postdoc pay band rather than an industry new-grad SWE band, so it lands at or below the candidate's ~$130-165k anchor. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -18945,7 +18949,7 @@
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18954,38 +18958,38 @@
         <v>275</v>
       </c>
       <c r="B276" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>$88k–$108k</t>
+          <t>$68k–$80k</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Goleta, CA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Requires an active, transferable DoD Secret clearance on day 1 — which the candidate does not have and cannot obtain pre-offer — and the work is real-time embedded C/C++ for radar/EW systems rather than backend, distributed systems, or AI infra.</t>
+          <t>SQL Server/SSIS/Salesforce-Apex BI rotational program at ~$75k TC — off-profile for a backend/distributed-systems candidate and far below the ~$130k anchor.</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Posted range of $62,900–$119,700 covers all experience levels; a Software Engineer I new grad in Goleta, CA typically lands in the lower-middle at roughly $85–100k base plus a modest short-term incentive. RTX is a traditional defense prime, so equity is negligible and TC tracks close to base — well under the candidate's ~130k anchor.</t>
+          <t>Posting states an explicit flat rate of $30.00/hr (~$62.4k base at 2,080 hrs) plus a 10% discretionary cash bonus target and a 10% discretionary RSU target; band spans low-to-full attainment of both. Consistent with Axos as a mid-size digital bank running a below-market entry-level rotational pipeline rather than a comp-competitive tech employer.</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -19011,7 +19015,7 @@
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -19020,43 +19024,43 @@
         <v>276</v>
       </c>
       <c r="B277" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>$55k–$80k</t>
+          <t>$88k–$108k</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Senior Applied AI &amp; ML Engineer</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Goleta, CA</t>
         </is>
       </c>
       <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Applied AI/ML domain aligns with the candidate's AI-infra strengths, but the posting is a Senior-level role in London, UK — disqualifying on both seniority (2027 new grad) and location/work authorization (US-authorized, no UK right to work).</t>
+          <t>Requires an active, transferable DoD Secret clearance on day 1 — which the candidate does not have and cannot obtain pre-offer — and the work is real-time embedded C/C++ for radar/EW systems rather than backend, distributed systems, or AI infra.</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Estimate, low confidence. AstraZeneca is large pharma rather than a tech-tier payer, and this is a UK-based posting; UK early-career SWE/ML comp there is typically ~GBP 40-60k base plus modest bonus, converting to roughly $55-80k USD. Wide band given no public new-grad data for this specific req, and the posting is Senior-level so no true new-grad rate exists.</t>
+          <t>Posted range of $62,900–$119,700 covers all experience levels; a Software Engineer I new grad in Goleta, CA typically lands in the lower-middle at roughly $85–100k base plus a modest short-term incentive. RTX is a traditional defense prime, so equity is negligible and TC tracks close to base — well under the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -19077,7 +19081,7 @@
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19086,43 +19090,43 @@
         <v>277</v>
       </c>
       <c r="B278" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>$85k–$105k</t>
+          <t>$55k–$80k</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Validation Engineer 1</t>
+          <t>Senior Applied AI &amp; ML Engineer</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Chandler, AZ</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr">
         <is>
-          <t>EE-centric silicon/analog validation role requiring PCB layout, circuit design, and semiconductor device physics — explicitly in the candidate's low-fit "hardware/embedded-only" category with no backend, distributed-systems, or AI-infra overlap.</t>
+          <t>Applied AI/ML domain aligns with the candidate's AI-infra strengths, but the posting is a Senior-level role in London, UK — disqualifying on both seniority (2027 new grad) and location/work authorization (US-authorized, no UK right to work).</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Microchip is a mid-tier semiconductor company in a low-COL metro (Chandler, AZ); entry-level Engineer I roles there typically pay ~$78-95k base plus modest bonus and small equity/ESPP. Estimate, not fact — well below the candidate's ~$130k anchor.</t>
+          <t>Estimate, low confidence. AstraZeneca is large pharma rather than a tech-tier payer, and this is a UK-based posting; UK early-career SWE/ML comp there is typically ~GBP 40-60k base plus modest bonus, converting to roughly $55-80k USD. Wide band given no public new-grad data for this specific req, and the posting is Senior-level so no true new-grad rate exists.</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -19143,7 +19147,7 @@
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -19161,29 +19165,29 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Validation Engineer 1</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD</t>
+          <t>Chandler, AZ</t>
         </is>
       </c>
       <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Requires an active TS/SCI clearance on day 1 (candidate has none) and is an intern-conversion req for onsite C++/DSP SIGINT work in Annapolis Junction — off-profile on clearance, role type, and location.</t>
+          <t>EE-centric silicon/analog validation role requiring PCB layout, circuit design, and semiconductor device physics — explicitly in the candidate's low-fit "hardware/embedded-only" category with no backend, distributed-systems, or AI-infra overlap.</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Posting states a $62,900–$119,700 base range; defense primes (RTX/Applied Signal Technology) typically place new grads in the lower-middle of the posted band with a ~3-5% bonus and negligible equity, so realistic new-grad TC lands well under the candidate's ~$120k floor.</t>
+          <t>Microchip is a mid-tier semiconductor company in a low-COL metro (Chandler, AZ); entry-level Engineer I roles there typically pay ~$78-95k base plus modest bonus and small equity/ESPP. Estimate, not fact — well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -19222,34 +19226,34 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>$80k–$105k</t>
+          <t>$85k–$105k</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>GlobalFoundries</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Advanced Manufacturing Equipment Engineer New Grad</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Malta, NY</t>
+          <t>Annapolis Junction, MD</t>
         </is>
       </c>
       <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Semiconductor fab equipment engineering role explicitly requiring ME/EE/Materials Science/Solid-State Physics degree, focused on tool installation, maintenance SOPs, and schematics — no backend, distributed systems, or AI-infra software work, matching the candidate's stated hardware/EE-centric role_fit_low.</t>
+          <t>Requires an active TS/SCI clearance on day 1 (candidate has none) and is an intern-conversion req for onsite C++/DSP SIGINT work in Annapolis Junction — off-profile on clearance, role type, and location.</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Posting states base range $58,400-$100,800; new-grad offers typically land mid-low in that band (~$75-90k base) plus modest bonus/relocation. GlobalFoundries is a semiconductor manufacturer, not a top-tier software payer, and Malta, NY is a low-COL market — well under the candidate's ~$130k anchor.</t>
+          <t>Posting states a $62,900–$119,700 base range; defense primes (RTX/Applied Signal Technology) typically place new grads in the lower-middle of the posted band with a ~3-5% bonus and negligible equity, so realistic new-grad TC lands well under the candidate's ~$120k floor.</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -19275,7 +19279,7 @@
       </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19288,7 +19292,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>$75k–$105k</t>
+          <t>$80k–$105k</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -19310,12 +19314,12 @@
       <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Semiconductor fab equipment engineering role explicitly requiring an ME/EE/Materials Science/Solid State Physics degree and centered on tool installation, schematics, and maintenance KPIs — squarely in the candidate's hardware/EE-centric low-fit category with no backend, distributed systems, or AI-infra content.</t>
+          <t>Semiconductor fab equipment engineering role explicitly requiring ME/EE/Materials Science/Solid-State Physics degree, focused on tool installation, maintenance SOPs, and schematics — no backend, distributed systems, or AI-infra software work, matching the candidate's stated hardware/EE-centric role_fit_low.</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Posting states a $58,400–$100,800 salary range; new-grad hires in Malta, NY typically land in the $75–90k base band, plus a modest annual bonus and possible relocation, putting realistic TC around $75–105k — below the candidate's ~$130k anchor.</t>
+          <t>Posting states base range $58,400-$100,800; new-grad offers typically land mid-low in that band (~$75-90k base) plus modest bonus/relocation. GlobalFoundries is a semiconductor manufacturer, not a top-tier software payer, and Malta, NY is a low-COL market — well under the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -19350,38 +19354,38 @@
         <v>281</v>
       </c>
       <c r="B282" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>$85k–$115k</t>
+          <t>$75k–$105k</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>GlobalFoundries</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Upgrade Install and Relocation Engineer - Duv</t>
+          <t>Advanced Manufacturing Equipment Engineer New Grad</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Malta, NY</t>
         </is>
       </c>
       <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Hardware field-service role for ME/EE/mechatronics grads — cleanroom equipment install, electromechanical troubleshooting, 75% travel and rotating on-call shifts — with no software/backend/distributed-systems content, matching the candidate's explicit "hardware/embedded-only (EE-centric)" low-fit category.</t>
+          <t>Semiconductor fab equipment engineering role explicitly requiring an ME/EE/Materials Science/Solid State Physics degree and centered on tool installation, schematics, and maintenance KPIs — squarely in the candidate's hardware/EE-centric low-fit category with no backend, distributed systems, or AI-infra content.</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>ASML is a top-tier semiconductor equipment maker but pays field/install engineers on a hardware-engineering scale, not a software scale: new-grad base typically ~$75-95k in Austin, with overtime, shift differential, travel pay, and a modest bonus lifting realized TC into the ~$85-115k range. Estimate only; sits below the candidate's ~$130k anchor.</t>
+          <t>Posting states a $58,400–$100,800 salary range; new-grad hires in Malta, NY typically land in the $75–90k base band, plus a modest annual bonus and possible relocation, putting realistic TC around $75–105k — below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -19407,7 +19411,7 @@
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -19416,38 +19420,38 @@
         <v>282</v>
       </c>
       <c r="B283" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>$80k–$100k</t>
+          <t>$85k–$115k</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Upgrade Install and Relocation Engineer - Duv</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Requires an active DoD Secret clearance on day 1 (candidate has none) and is an intern-to-FT conversion req for embedded Linux/BSP/kernel work in Cedar Rapids, IA — a hard mismatch with a backend/distributed-systems/AI-infra new grad targeting $130k+.</t>
+          <t>Hardware field-service role for ME/EE/mechatronics grads — cleanroom equipment install, electromechanical troubleshooting, 75% travel and rotating on-call shifts — with no software/backend/distributed-systems content, matching the candidate's explicit "hardware/embedded-only (EE-centric)" low-fit category.</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Posting lists $57,200–$108,800 across all experience levels; RTX/Collins Aerospace new-grad SWE in low-COL Cedar Rapids typically lands ~$78–95k base plus a modest annual incentive (~5%) and 401(k) match. Defense primes pay well under the candidate's $130–165k anchor. Estimate, not fact.</t>
+          <t>ASML is a top-tier semiconductor equipment maker but pays field/install engineers on a hardware-engineering scale, not a software scale: new-grad base typically ~$75-95k in Austin, with overtime, shift differential, travel pay, and a modest bonus lifting realized TC into the ~$85-115k range. Estimate only; sits below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -19482,38 +19486,38 @@
         <v>283</v>
       </c>
       <c r="B284" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>$62k–$72k</t>
+          <t>$80k–$100k</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>State of Nebraska</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>IT Applications Developer - Public Health</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Lincoln, NE</t>
+          <t>Cedar Rapids, IA</t>
         </is>
       </c>
       <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Legacy state-government Java/JSF/jQuery maintenance role in Lincoln, NE at a stated $30/hr (~$62k), onsite-only, hiring immediately rather than for a 2027 new-grad start — it misses the candidate's distributed-systems/AI-infra profile, location preference, timeline, and pays roughly half his ~$130k anchor.</t>
+          <t>Requires an active DoD Secret clearance on day 1 (candidate has none) and is an intern-to-FT conversion req for embedded Linux/BSP/kernel work in Cedar Rapids, IA — a hard mismatch with a backend/distributed-systems/AI-infra new grad targeting $130k+.</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Hiring rate is stated explicitly in the posting at $30.008/hr, which is ~$62.4k/yr at 2,080 hours. No equity or bonus; public-sector pay bands are rigid, so the upside is limited to modest step increases. Upper end of the band accounts for Nebraska state benefits (pension match, health coverage) as imputed value, not cash. Confidence is high since the rate is published rather than inferred from company tier.</t>
+          <t>Posting lists $57,200–$108,800 across all experience levels; RTX/Collins Aerospace new-grad SWE in low-COL Cedar Rapids typically lands ~$78–95k base plus a modest annual incentive (~5%) and 401(k) match. Defense primes pay well under the candidate's $130–165k anchor. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -19548,42 +19552,38 @@
         <v>284</v>
       </c>
       <c r="B285" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>$80k–$100k</t>
+          <t>$62k–$72k</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>State of Nebraska</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>IT Applications Developer - Public Health</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>Lincoln, NE</t>
         </is>
       </c>
       <c r="G285" t="inlineStr"/>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>start date this requisition is for an rtx</t>
-        </is>
-      </c>
+      <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Hard-blocked: requires an active transferable Secret clearance before start date (candidate has none), the req is reserved for an RTX intern converting to FT, and the work is real-time embedded/device-driver engineering rather than backend, distributed systems, or AI infra.</t>
+          <t>Legacy state-government Java/JSF/jQuery maintenance role in Lincoln, NE at a stated $30/hr (~$62k), onsite-only, hiring immediately rather than for a 2027 new-grad start — it misses the candidate's distributed-systems/AI-infra profile, location preference, timeline, and pays roughly half his ~$130k anchor.</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>RTX is a defense prime with below-market cash comp, no meaningful equity, and a small (~3-5%) annual incentive. The posted $62.9k-$119.7k range covers all experience levels; a Software Engineer 1 in El Segundo realistically lands ~$85-95k base plus 401k match and bonus. Well below the candidate's $130k anchor.</t>
+          <t>Hiring rate is stated explicitly in the posting at $30.008/hr, which is ~$62.4k/yr at 2,080 hours. No equity or bonus; public-sector pay bands are rigid, so the upside is limited to modest step increases. Upper end of the band accounts for Nebraska state benefits (pension match, health coverage) as imputed value, not cash. Confidence is high since the rate is published rather than inferred from company tier.</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -19609,7 +19609,7 @@
       </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>$78k–$100k</t>
+          <t>$80k–$100k</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -19637,19 +19637,23 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>East Hartford, CT</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="G286" t="inlineStr"/>
-      <c r="H286" t="inlineStr"/>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>start date this requisition is for an rtx</t>
+        </is>
+      </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Requires an active DoD Secret clearance on day 1 and is explicitly a conversion req for existing RTX interns, and the work is PLC/LabVIEW facility controls engineering rather than backend/distributed/AI-infra software.</t>
+          <t>Hard-blocked: requires an active transferable Secret clearance before start date (candidate has none), the req is reserved for an RTX intern converting to FT, and the work is real-time embedded/device-driver engineering rather than backend, distributed systems, or AI infra.</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Posting lists $57,200-$108,800 across all experience levels; defense-primes pay new grads mid-range base (~$75-90k) plus small bonus and 401k match, so realistic new-grad TC lands ~$78-100k — well under the candidate's ~$130k anchor.</t>
+          <t>RTX is a defense prime with below-market cash comp, no meaningful equity, and a small (~3-5%) annual incentive. The posted $62.9k-$119.7k range covers all experience levels; a Software Engineer 1 in El Segundo realistically lands ~$85-95k base plus 401k match and bonus. Well below the candidate's $130k anchor.</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -19684,38 +19688,38 @@
         <v>286</v>
       </c>
       <c r="B287" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>$60k–$85k</t>
+          <t>$78k–$100k</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Entry Level Software Developer</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Randolph AFB, TX</t>
+          <t>East Hartford, CT</t>
         </is>
       </c>
       <c r="G287" t="inlineStr"/>
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr">
         <is>
-          <t>Requires an interim SECRET clearance to start plus Security+ certification (candidate has no clearance — an explicit disqualifier), and the work is legacy Java/JSP/WebLogic/Subversion web development at an IT staffing firm on an Air Force base, with no overlap with the candidate's distributed-systems, cloud-infra, or AI-platform strengths.</t>
+          <t>Requires an active DoD Secret clearance on day 1 and is explicitly a conversion req for existing RTX interns, and the work is PLC/LabVIEW facility controls engineering rather than backend/distributed/AI-infra software.</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions is a small Connecticut-based IT services/staffing firm placing contractors on government contracts. This tier typically pays far below product-company new-grad bands, and clearance-gated entry-level contract roles rarely carry equity or meaningful bonus. No public comp data for this company, so the band is wide and low-confidence; it falls well under the candidate's ~$120k floor.</t>
+          <t>Posting lists $57,200-$108,800 across all experience levels; defense-primes pay new grads mid-range base (~$75-90k) plus small bonus and 401k match, so realistic new-grad TC lands ~$78-100k — well under the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -19741,7 +19745,7 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -19750,38 +19754,38 @@
         <v>287</v>
       </c>
       <c r="B288" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>$90k–$120k</t>
+          <t>$60k–$85k</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Renesas Electronics</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Application Engineer - Performance Computing Power Application Engineering</t>
+          <t>Entry Level Software Developer</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Randolph AFB, TX</t>
         </is>
       </c>
       <c r="G288" t="inlineStr"/>
       <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr">
         <is>
-          <t>EE-centric power-electronics applications role (DC/DC converters, control-loop theory, SIMPLIS/MATLAB, lab bench work) with no backend/distributed-systems/AI-infra overlap, plus 100% onsite Austin and an immediate entry-level start rather than a May 2027 new-grad slot.</t>
+          <t>Requires an interim SECRET clearance to start plus Security+ certification (candidate has no clearance — an explicit disqualifier), and the work is legacy Java/JSP/WebLogic/Subversion web development at an IT staffing firm on an Air Force base, with no overlap with the candidate's distributed-systems, cloud-infra, or AI-platform strengths.</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Renesas is a mid-tier semiconductor company; entry-level applications engineers in Austin typically see ~$85-105k base with a ~5-10% bonus and minimal equity. Band is somewhat wide since hardware AE comp is less publicly reported than SWE; midpoint sits below the candidate's ~$130k anchor.</t>
+          <t>9to9 Software Solutions is a small Connecticut-based IT services/staffing firm placing contractors on government contracts. This tier typically pays far below product-company new-grad bands, and clearance-gated entry-level contract roles rarely carry equity or meaningful bonus. No public comp data for this company, so the band is wide and low-confidence; it falls well under the candidate's ~$120k floor.</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -19807,7 +19811,7 @@
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -19825,33 +19829,29 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Johns Hopkins Applied Physics Laboratory</t>
+          <t>Renesas Electronics</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Artificial Intelligence and Complex Systems Postdoc Researcher</t>
+          <t>Application Engineer - Performance Computing Power Application Engineering</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Laurel, MD</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="G289" t="inlineStr"/>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>start date and can ultimately obtain a to</t>
-        </is>
-      </c>
+      <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
         <is>
-          <t>This is a PhD-required postdoc research position (2026 PhD graduates) that also mandates an Interim Secret clearance by start date and eventual Top Secret — the candidate is a May 2027 BS/MS new grad with no clearance, so he is ineligible on two hard filters, and the AI-for-Science research focus (surrogate models, neural operators, diffusion, materials/chemistry/omics) is a poor match for his backend/distributed-systems/AI-infra engineering profile.</t>
+          <t>EE-centric power-electronics applications role (DC/DC converters, control-loop theory, SIMPLIS/MATLAB, lab bench work) with no backend/distributed-systems/AI-infra overlap, plus 100% onsite Austin and an immediate entry-level start rather than a May 2027 new-grad slot.</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>JHU/APL is a federally funded lab (non-profit UARC) paying below industry tech scale; postdoc researcher salaries there typically run ~$90-120k base with modest bonus but strong retirement contributions. Band reflects a PhD postdoc, not a BS/MS new-grad SWE role. Moderate confidence from general knowledge of national-lab/UARC postdoc pay.</t>
+          <t>Renesas is a mid-tier semiconductor company; entry-level applications engineers in Austin typically see ~$85-105k base with a ~5-10% bonus and minimal equity. Band is somewhat wide since hardware AE comp is less publicly reported than SWE; midpoint sits below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -19877,7 +19877,7 @@
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19886,38 +19886,42 @@
         <v>289</v>
       </c>
       <c r="B290" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>$70k–$105k</t>
+          <t>$90k–$120k</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>Johns Hopkins Applied Physics Laboratory</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Applied Early Career Program - Field Service Engineer</t>
+          <t>Artificial Intelligence and Complex Systems Postdoc Researcher</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Austin, TX, Hillsboro, OR, Boise, ID, Phoenix, AZ, Chandler, AZ, Richardson, TX</t>
+          <t>Laurel, MD</t>
         </is>
       </c>
       <c r="G290" t="inlineStr"/>
-      <c r="H290" t="inlineStr"/>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>start date and can ultimately obtain a to</t>
+        </is>
+      </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>This is a hands-on hardware/equipment maintenance role (electrical, vacuum, plasma, hydraulic, gas systems) with an associate-degree/trade-cert minimum and hourly pay — it uses none of the candidate's backend, distributed-systems, or AI-infra skills and pays roughly half the target TC.</t>
+          <t>This is a PhD-required postdoc research position (2026 PhD graduates) that also mandates an Interim Secret clearance by start date and eventual Top Secret — the candidate is a May 2027 BS/MS new grad with no clearance, so he is ineligible on two hard filters, and the AI-for-Science research focus (surrogate models, neural operators, diffusion, materials/chemistry/omics) is a poor match for his backend/distributed-systems/AI-infra engineering profile.</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Posted hourly range $27.00–$37.40 → ~$56k–$78k base at 40 hrs/wk. Field Service Engineer roles at Applied Materials carry heavy overtime (frequently 10–25%+ of pay) plus a modest bonus/ESPP, which typically pushes realistic first-year earnings into the ~$70k–$105k range. Well below the candidate's ~$130k anchor and not a software-engineering pay band.</t>
+          <t>JHU/APL is a federally funded lab (non-profit UARC) paying below industry tech scale; postdoc researcher salaries there typically run ~$90-120k base with modest bonus but strong retirement contributions. Band reflects a PhD postdoc, not a BS/MS new-grad SWE role. Moderate confidence from general knowledge of national-lab/UARC postdoc pay.</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -19943,7 +19947,7 @@
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -19952,38 +19956,38 @@
         <v>290</v>
       </c>
       <c r="B291" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>$80k–$110k</t>
+          <t>$70k–$105k</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>GlobalFoundries</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Advanced Manufacturing Equipment Engineer New Grad</t>
+          <t>Applied Early Career Program - Field Service Engineer</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Malta, NY</t>
+          <t>Austin, TX, Hillsboro, OR, Boise, ID, Phoenix, AZ, Chandler, AZ, Richardson, TX</t>
         </is>
       </c>
       <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr">
         <is>
-          <t>Semiconductor fab equipment engineering role requiring an ME/EE/Materials Science/Solid State Physics degree and hands-on tool troubleshooting — no software/backend/distributed-systems content, directly matching the candidate's hardware-only low-fit exclusion.</t>
+          <t>This is a hands-on hardware/equipment maintenance role (electrical, vacuum, plasma, hydraulic, gas systems) with an associate-degree/trade-cert minimum and hourly pay — it uses none of the candidate's backend, distributed-systems, or AI-infra skills and pays roughly half the target TC.</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Posting lists a $69k-$120k base range; new grads typically land lower-middle of a posted band, plus ~5-10% bonus and a modest sign-on. Malta, NY semiconductor manufacturing pays well below software-tier comp, so this sits under the candidate's ~$130k anchor.</t>
+          <t>Posted hourly range $27.00–$37.40 → ~$56k–$78k base at 40 hrs/wk. Field Service Engineer roles at Applied Materials carry heavy overtime (frequently 10–25%+ of pay) plus a modest bonus/ESPP, which typically pushes realistic first-year earnings into the ~$70k–$105k range. Well below the candidate's ~$130k anchor and not a software-engineering pay band.</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -20018,38 +20022,38 @@
         <v>291</v>
       </c>
       <c r="B292" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>$123k–$130k</t>
+          <t>$80k–$110k</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Lawrence Livermore National Laboratory (LLNL)</t>
+          <t>GlobalFoundries</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Heavy-Ion Physics and Scientific Machine Learning Postdoctoral Researcher</t>
+          <t>Advanced Manufacturing Equipment Engineer New Grad</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Livermore, CA</t>
+          <t>Malta, NY</t>
         </is>
       </c>
       <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
-          <t>Hard-gated postdoc requiring a PhD in Physics/Nuclear/HEP plus experimental collider research experience — the candidate is a 2027 new grad with no doctorate, so the C++/Python/HPC/ML overlap is irrelevant to eligibility.</t>
+          <t>Semiconductor fab equipment engineering role requiring an ME/EE/Materials Science/Solid State Physics degree and hands-on tool troubleshooting — no software/backend/distributed-systems content, directly matching the candidate's hardware-only low-fit exclusion.</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>Posting states an explicit flat rate of $123,048/yr. National-lab postdoc comp has no equity and negligible bonus; the upper end reflects benefits/401k/relocation value only. Not a new-grad SWE band.</t>
+          <t>Posting lists a $69k-$120k base range; new grads typically land lower-middle of a posted band, plus ~5-10% bonus and a modest sign-on. Malta, NY semiconductor manufacturing pays well below software-tier comp, so this sits under the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -20075,7 +20079,7 @@
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -20084,38 +20088,38 @@
         <v>292</v>
       </c>
       <c r="B293" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>$65k–$95k</t>
+          <t>$123k–$130k</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Lawrence Livermore National Laboratory (LLNL)</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>iOS Developer</t>
+          <t>Heavy-Ion Physics and Scientific Machine Learning Postdoctoral Researcher</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Livermore, CA</t>
         </is>
       </c>
       <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
-          <t>iOS/Swift mobile development at a consulting staffing firm requiring 1-3 years experience and a shipped App Store app, with an immediate start — off-profile against the candidate's backend/distributed-systems/AI-infra focus and May 2027 grad date.</t>
+          <t>Hard-gated postdoc requiring a PhD in Physics/Nuclear/HEP plus experimental collider research experience — the candidate is a 2027 new grad with no doctorate, so the C++/Python/HPC/ML overlap is irrelevant to eligibility.</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Adidev Technologies is a small, low-visibility IT consulting/staffing firm with no public comp data; band is a wide low-confidence estimate based on typical consultancy iOS developer pay in the Charlotte, NC market, well below the candidate's ~$130k anchor.</t>
+          <t>Posting states an explicit flat rate of $123,048/yr. National-lab postdoc comp has no equity and negligible bonus; the upper end reflects benefits/401k/relocation value only. Not a new-grad SWE band.</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -20159,29 +20163,29 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Engineering Technician - Intermediate</t>
+          <t>iOS Developer</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Charlotte, NC</t>
         </is>
       </c>
       <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr">
         <is>
-          <t>This is a hands-on lab/hardware technician position (bench test, equipment support, typically AA/vocational plus lab experience), not a software engineering role — it lands squarely in the candidate's low-fit buckets (hardware/EE-centric, non-SWE) and uses none of his backend, distributed-systems, or AI-infra strengths.</t>
+          <t>iOS/Swift mobile development at a consulting staffing firm requiring 1-3 years experience and a shipped App Store app, with an immediate start — off-profile against the candidate's backend/distributed-systems/AI-infra focus and May 2027 grad date.</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Qualcomm is a top-tier semiconductor employer, but Engineering Technician roles are non-exempt/hourly (~$28-40/hr in San Diego) with modest bonus and little to no equity — a separate, much lower ladder than Qualcomm's SWE new-grad band (~$150-190k TC). Band kept wide because technician "Intermediate" leveling and San Diego hourly rates are not publicly well-documented; this is an estimate, not fact.</t>
+          <t>Adidev Technologies is a small, low-visibility IT consulting/staffing firm with no public comp data; band is a wide low-confidence estimate based on typical consultancy iOS developer pay in the Charlotte, NC market, well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -20207,7 +20211,7 @@
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20220,34 +20224,34 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>$70k–$95k</t>
+          <t>$65k–$95k</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Design Verification Engineer</t>
+          <t>Engineering Technician - Intermediate</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Markham, ON, Canada</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
-          <t>Pure ASIC design-verification role (SystemVerilog/UVM/tapeout) in Markham, Ontario — hardware/EE-centric work that matches none of the candidate's backend, distributed-systems, or AI-infra strengths, sits in his explicit role_fit_low list, is outside his US location preference, and pays below his ~120k TC floor.</t>
+          <t>This is a hands-on lab/hardware technician position (bench test, equipment support, typically AA/vocational plus lab experience), not a software engineering role — it lands squarely in the candidate's low-fit buckets (hardware/EE-centric, non-SWE) and uses none of his backend, distributed-systems, or AI-infra strengths.</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>Posting states CAD 91,200-136,800 base; a new grad would anchor near the bottom (~CAD 90-105k), converted at ~0.72 USD/CAD and grossed up ~10-15% for AMD bonus + RSUs. AMD is a strong semiconductor employer, but Canadian bands run well under US big-tech software comp and DV trails SWE at the same company. Estimate, not fact.</t>
+          <t>Qualcomm is a top-tier semiconductor employer, but Engineering Technician roles are non-exempt/hourly (~$28-40/hr in San Diego) with modest bonus and little to no equity — a separate, much lower ladder than Qualcomm's SWE new-grad band (~$150-190k TC). Band kept wide because technician "Intermediate" leveling and San Diego hourly rates are not publicly well-documented; this is an estimate, not fact.</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -20282,38 +20286,38 @@
         <v>295</v>
       </c>
       <c r="B296" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>$85k–$115k</t>
+          <t>$70k–$95k</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Failure Analysis Engineer - TEM/AutoTEM</t>
+          <t>Design Verification Engineer</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Phoenix, AZ</t>
+          <t>Markham, ON, Canada</t>
         </is>
       </c>
       <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr">
         <is>
-          <t>Hardware failure-analysis lab role centered on TEM/SEM/FIB microscopy, materials characterization, and semiconductor device physics — no backend/distributed-systems/AI-infra overlap, and it requires US citizenship plus ability to obtain a security clearance, which conflicts with the candidate's stated constraints.</t>
+          <t>Pure ASIC design-verification role (SystemVerilog/UVM/tapeout) in Markham, Ontario — hardware/EE-centric work that matches none of the candidate's backend, distributed-systems, or AI-infra strengths, sits in his explicit role_fit_low list, is outside his US location preference, and pays below his ~120k TC floor.</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>Intel is a large-cap tech company but its manufacturing/fab engineering track (non-SWE) pays notably below its software bands, and Phoenix/Chandler is a lower-cost market. Typical new-grad FA/process engineer base ~$80-100k with a small bonus and modest RSU grant. Estimate, not fact — below the candidate's ~$130k anchor.</t>
+          <t>Posting states CAD 91,200-136,800 base; a new grad would anchor near the bottom (~CAD 90-105k), converted at ~0.72 USD/CAD and grossed up ~10-15% for AMD bonus + RSUs. AMD is a strong semiconductor employer, but Canadian bands run well under US big-tech software comp and DV trails SWE at the same company. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -20339,7 +20343,7 @@
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -20348,38 +20352,38 @@
         <v>296</v>
       </c>
       <c r="B297" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>$60k–$90k</t>
+          <t>$85k–$115k</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Failure Analysis Engineer - TEM/AutoTEM</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Phoenix, AZ</t>
         </is>
       </c>
       <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
-          <t>Hard-blocked by an explicit interim SECRET clearance + Security+ certification requirement (both listed as minimum quals) that the candidate cannot meet, and the work itself is legacy contract JSP/Hibernate/WebLogic web development at a staffing firm — no overlap with distributed systems, infra, or AI platform work, at contractor-tier pay far below the $130k anchor.</t>
+          <t>Hardware failure-analysis lab role centered on TEM/SEM/FIB microscopy, materials characterization, and semiconductor device physics — no backend/distributed-systems/AI-infra overlap, and it requires US citizenship plus ability to obtain a security clearance, which conflicts with the candidate's stated constraints.</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions is a small IT staffing/consulting body shop, and this is an explicitly Contract (not FTE) government-adjacent role — no equity, likely hourly with little or no bonus. Comparable entry-level contract Java dev rates through such firms run roughly $30-45/hr, i.e. ~$60-90k annualized. Low confidence, wide band; well below the candidate's ~$130k anchor.</t>
+          <t>Intel is a large-cap tech company but its manufacturing/fab engineering track (non-SWE) pays notably below its software bands, and Phoenix/Chandler is a lower-cost market. Typical new-grad FA/process engineer base ~$80-100k with a small bonus and modest RSU grant. Estimate, not fact — below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -20405,7 +20409,7 @@
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -20418,34 +20422,34 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>$70k–$90k</t>
+          <t>$60k–$90k</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Avnet</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Associate Field Application Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Hopkins, MN</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr">
         <is>
-          <t>EE-centric technical-sales/field-application role (design wins, pre/post-sales support, account strategy) with no software engineering content — matches the candidate's explicit role_fit_low categories and none of their backend/distributed-systems/AI-infra strengths.</t>
+          <t>Hard-blocked by an explicit interim SECRET clearance + Security+ certification requirement (both listed as minimum quals) that the candidate cannot meet, and the work itself is legacy contract JSP/Hibernate/WebLogic web development at a staffing firm — no overlap with distributed systems, infra, or AI platform work, at contractor-tier pay far below the $130k anchor.</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>Avnet is a Fortune 500 electronics distributor rather than a product-tech employer; entry-level FAE roles typically pay a modest base (~$65-80k) plus small sales incentive in the Minneapolis market. Distributor FAE comp is not well documented publicly, so this is a wide, moderate-confidence estimate — well below the candidate's ~$130k anchor.</t>
+          <t>9to9 Software Solutions is a small IT staffing/consulting body shop, and this is an explicitly Contract (not FTE) government-adjacent role — no equity, likely hourly with little or no bonus. Comparable entry-level contract Java dev rates through such firms run roughly $30-45/hr, i.e. ~$60-90k annualized. Low confidence, wide band; well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -20471,7 +20475,7 @@
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -20480,38 +20484,38 @@
         <v>298</v>
       </c>
       <c r="B299" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>$40k–$58k</t>
+          <t>$70k–$90k</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Avnet</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Graduate Data Engineer</t>
+          <t>Associate Field Application Engineer</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Hopkins, MN</t>
         </is>
       </c>
       <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr">
         <is>
-          <t>London-only role requiring UK work authorization, at a small affiliate-marketing firm doing entry-level ETL/data-pipeline work rather than backend, distributed systems, or AI-infra engineering — both location and role type are off-profile.</t>
+          <t>EE-centric technical-sales/field-application role (design wins, pre/post-sales support, account strategy) with no software engineering content — matches the candidate's explicit role_fit_low categories and none of their backend/distributed-systems/AI-infra strengths.</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>No published comp data for Quantum (small private UK affiliate-marketing company), so this is a wide, low-confidence band anchored to typical UK graduate data-engineer salaries (~£30-45k base plus a modest company bonus), converted to USD. Well below the candidate's ~$130k target.</t>
+          <t>Avnet is a Fortune 500 electronics distributor rather than a product-tech employer; entry-level FAE roles typically pay a modest base (~$65-80k) plus small sales incentive in the Minneapolis market. Distributor FAE comp is not well documented publicly, so this is a wide, moderate-confidence estimate — well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -20537,7 +20541,7 @@
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -20546,38 +20550,38 @@
         <v>299</v>
       </c>
       <c r="B300" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>$60k–$85k</t>
+          <t>$40k–$58k</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>9to9 Software Solutions</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Entry Level Software Developer</t>
+          <t>Graduate Data Engineer</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Copperhill, TN</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Requires an existing interim SECRET clearance and Security+ certification to start (candidate has neither and lists clearance roles as a hard mismatch), and it is a contract legacy Java/JSP/WebLogic web-dev role at a staffing consultancy in rural Copperhill, TN with no distributed-systems, infra, or AI-platform content.</t>
+          <t>London-only role requiring UK work authorization, at a small affiliate-marketing firm doing entry-level ETL/data-pipeline work rather than backend, distributed systems, or AI-infra engineering — both location and role type are off-profile.</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Company is not well known publicly — wide, low-confidence band. 9to9 Software Solutions is a small Connecticut-based IT staffing/services consultancy rather than a product company, and this is explicitly a Contract position, implying an hourly rate with minimal-to-no equity or bonus. Cleared entry-level government-contract Java work in a low-cost rural TN market typically pays in the $60-85k equivalent range, well below the candidate's ~$130-165k anchor and under the ~$120k low-match floor.</t>
+          <t>No published comp data for Quantum (small private UK affiliate-marketing company), so this is a wide, low-confidence band anchored to typical UK graduate data-engineer salaries (~£30-45k base plus a modest company bonus), converted to USD. Well below the candidate's ~$130k target.</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -20603,7 +20607,7 @@
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20612,38 +20616,38 @@
         <v>300</v>
       </c>
       <c r="B301" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>$95k–$120k</t>
+          <t>$60k–$85k</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Northrop Grumman</t>
+          <t>9to9 Software Solutions</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Structural Analysis Engineer</t>
+          <t>Entry Level Software Developer</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Palmdale, CA</t>
+          <t>Copperhill, TN</t>
         </is>
       </c>
       <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Aerospace structural/stress analysis role (FEMAP, Nastran, composites, finite element models) requiring an active in-scope DoD Secret clearance and 2+ years of experience on a 2nd-shift schedule — disqualifying on clearance, discipline, and seniority for a backend/distributed-systems new grad.</t>
+          <t>Requires an existing interim SECRET clearance and Security+ certification to start (candidate has neither and lists clearance roles as a hard mismatch), and it is a contract legacy Java/JSP/WebLogic web-dev role at a staffing consultancy in rural Copperhill, TN with no distributed-systems, infra, or AI-platform content.</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Posting lists a primary-level base range of $91.8k–$137.6k; an entry-level hire would land in the bottom third, plus a small discretionary bonus and shift differential. Defense primes like Northrop Grumman pay well below software-industry tiers, and this is not a new-grad requisition.</t>
+          <t>Company is not well known publicly — wide, low-confidence band. 9to9 Software Solutions is a small Connecticut-based IT staffing/services consultancy rather than a product company, and this is explicitly a Contract position, implying an hourly rate with minimal-to-no equity or bonus. Cleared entry-level government-contract Java work in a low-cost rural TN market typically pays in the $60-85k equivalent range, well below the candidate's ~$130-165k anchor and under the ~$120k low-match floor.</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -20669,7 +20673,7 @@
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -20678,38 +20682,38 @@
         <v>301</v>
       </c>
       <c r="B302" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>$78k–$105k</t>
+          <t>$95k–$120k</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Northrop Grumman</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Structural Analysis Engineer</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Goleta, CA</t>
+          <t>Palmdale, CA</t>
         </is>
       </c>
       <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr">
         <is>
-          <t>Hard-blocked: requires an active DoD Secret clearance on day 1 (candidate has none and can't get one before a 2027 start), and the work is onsite real-time embedded C/C++ radar/EW software — squarely in the candidate's low-fit bucket, with a posted range topping out below the ~130k anchor.</t>
+          <t>Aerospace structural/stress analysis role (FEMAP, Nastran, composites, finite element models) requiring an active in-scope DoD Secret clearance and 2+ years of experience on a 2nd-shift schedule — disqualifying on clearance, discipline, and seniority for a backend/distributed-systems new grad.</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>Posted range is 62.9k–119.7k across all experience levels; a new grad lands near the bottom third, so ~72–90k base in Goleta plus a small (~5–8%) annual incentive and 401k match, giving roughly 78–105k TC. Defense primes like RTX pay well below tech-industry new-grad levels and grant no meaningful equity.</t>
+          <t>Posting lists a primary-level base range of $91.8k–$137.6k; an entry-level hire would land in the bottom third, plus a small discretionary bonus and shift differential. Defense primes like Northrop Grumman pay well below software-industry tiers, and this is not a new-grad requisition.</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -20735,7 +20739,7 @@
       </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -20744,43 +20748,43 @@
         <v>302</v>
       </c>
       <c r="B303" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>$38k–$55k</t>
+          <t>$78k–$105k</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Options Technology</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>PHP/SQL Web Developer - Options Market Data Team</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Cambridge, UK</t>
+          <t>Goleta, CA</t>
         </is>
       </c>
       <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr">
         <is>
-          <t>PHP/SQL web development is far off the candidate's backend/distributed-systems/AI-infra profile, and the Cambridge, UK location conflicts with a US-authorized new grad targeting US roles.</t>
+          <t>Hard-blocked: requires an active DoD Secret clearance on day 1 (candidate has none and can't get one before a 2027 start), and the work is onsite real-time embedded C/C++ radar/EW software — squarely in the candidate's low-fit bucket, with a posted range topping out below the ~130k anchor.</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>Options Technology is a mid-tier managed IT/infrastructure provider for financial services (not a prop trading firm), and UK graduate web-developer bands outside London typically run ~GBP 30-43k. Converted to USD gives a wide, low-confidence band well under the candidate's ~130k anchor.</t>
+          <t>Posted range is 62.9k–119.7k across all experience levels; a new grad lands near the bottom third, so ~72–90k base in Goleta plus a small (~5–8%) annual incentive and 401k match, giving roughly 78–105k TC. Defense primes like RTX pay well below tech-industry new-grad levels and grant no meaningful equity.</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -20814,39 +20818,39 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>$38k–$52k</t>
+          <t>$38k–$55k</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Dawn Meats</t>
+          <t>Options Technology</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Graduate Business Intelligence Developer</t>
+          <t>PHP/SQL Web Developer - Options Market Data Team</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Waterford, Ireland, Dungannon, UK, Preston, UK</t>
+          <t>Cambridge, UK</t>
         </is>
       </c>
       <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr">
         <is>
-          <t>A BI/reporting developer role (SQL, Qlik/Power BI, ETL, internal IT support) based in Ireland/UK uses none of the candidate's backend, distributed-systems, or AI-infra strengths, would require visa sponsorship for a US-authorized candidate, and starts ~a year before his May 2027 graduation.</t>
+          <t>PHP/SQL web development is far off the candidate's backend/distributed-systems/AI-infra profile, and the Cambridge, UK location conflicts with a US-authorized new grad targeting US roles.</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>No public comp data for Dawn Meats, so this is a tier inference: a €4.5bn-turnover non-tech food processor running a standard graduate program in Waterford/Dungannon/Preston. Irish/UK graduate IT salaries at non-tech corporates in these low-cost regional markets typically run €30-42k base with minimal bonus and no equity (~$38-50k USD); band widened slightly upward for the UK/Preston option. Roughly a third of the candidate's ~130k anchor, so a low comp match.</t>
+          <t>Options Technology is a mid-tier managed IT/infrastructure provider for financial services (not a prop trading firm), and UK graduate web-developer bands outside London typically run ~GBP 30-43k. Converted to USD gives a wide, low-confidence band well under the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -20867,7 +20871,7 @@
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20876,38 +20880,38 @@
         <v>304</v>
       </c>
       <c r="B305" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>$75k–$100k</t>
+          <t>$38k–$52k</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Pacific Northwest National Laboratory</t>
+          <t>Dawn Meats</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Postdoctoral Research Associate - Integrated Energy &amp; Earth Systems</t>
+          <t>Graduate Business Intelligence Developer</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Richland, WA</t>
+          <t>Waterford, Ireland, Dungannon, UK, Preston, UK</t>
         </is>
       </c>
       <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr">
         <is>
-          <t>Postdoc position that hard-requires a PhD (received within 5 years or within 8 months), which the candidate will not have as a May 2027 new grad; the work is Earth-systems/sensor-telemetry research in MATLAB/Python with physics-informed ML, not backend, distributed systems, or AI-infra engineering.</t>
+          <t>A BI/reporting developer role (SQL, Qlik/Power BI, ETL, internal IT support) based in Ireland/UK uses none of the candidate's backend, distributed-systems, or AI-infra strengths, would require visa sponsorship for a US-authorized candidate, and starts ~a year before his May 2027 graduation.</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>Posting explicitly states USD $69,000–$119,100/yr. PNNL is a DOE national lab: no equity, minimal bonus, so TC ≈ base. Postdoc appointments typically land in the lower-middle of a posted band, hence a ~$75k–$100k realistic band. Well below the candidate's ~$130k anchor.</t>
+          <t>No public comp data for Dawn Meats, so this is a tier inference: a €4.5bn-turnover non-tech food processor running a standard graduate program in Waterford/Dungannon/Preston. Irish/UK graduate IT salaries at non-tech corporates in these low-cost regional markets typically run €30-42k base with minimal bonus and no equity (~$38-50k USD); band widened slightly upward for the UK/Preston option. Roughly a third of the candidate's ~130k anchor, so a low comp match.</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -20933,7 +20937,7 @@
       </c>
       <c r="P305" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -20946,38 +20950,34 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>$80k–$100k</t>
+          <t>$75k–$100k</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Pacific Northwest National Laboratory</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Postdoctoral Research Associate - Integrated Energy &amp; Earth Systems</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Richland, WA</t>
         </is>
       </c>
       <c r="G306" t="inlineStr"/>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>start date prior rtx internship experienc</t>
-        </is>
-      </c>
+      <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr">
         <is>
-          <t>Hard-blocked: requires an active TS/SCI clearance on day 1 plus prior RTX internship experience (candidate has neither and cannot obtain either), and the role is C++/DSP/SIGINT signal processing rather than backend, distributed systems, or AI infra.</t>
+          <t>Postdoc position that hard-requires a PhD (received within 5 years or within 8 months), which the candidate will not have as a May 2027 new grad; the work is Earth-systems/sensor-telemetry research in MATLAB/Python with physics-informed ML, not backend, distributed systems, or AI-infra engineering.</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>Posting lists a $62,900-$119,700 range for the level; new-grad SWE I at a defense prime in San Jose typically lands ~$85-95k base plus a small (~5%) bonus and no meaningful equity. Well below the candidate's ~$130k anchor.</t>
+          <t>Posting explicitly states USD $69,000–$119,100/yr. PNNL is a DOE national lab: no equity, minimal bonus, so TC ≈ base. Postdoc appointments typically land in the lower-middle of a posted band, hence a ~$75k–$100k realistic band. Well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -21012,38 +21012,42 @@
         <v>306</v>
       </c>
       <c r="B307" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>$65k–$85k</t>
+          <t>$80k–$100k</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>SOSi</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>PeopleSoft Software Developer</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Charleston, SC</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="G307" t="inlineStr"/>
-      <c r="H307" t="inlineStr"/>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>start date prior rtx internship experienc</t>
+        </is>
+      </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>Hard-blocked by the Secret clearance requirement (an explicit candidate constraint) and the work is PeopleSoft/PeopleCode ERP maintenance — no overlap with backend distributed systems, Rust/systems, or AI infra — plus onsite 5 days in Charleston at roughly half the target TC.</t>
+          <t>Hard-blocked: requires an active TS/SCI clearance on day 1 plus prior RTX internship experience (candidate has neither and cannot obtain either), and the role is C++/DSP/SIGINT signal processing rather than backend, distributed systems, or AI infra.</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>Defense/government services integrator (SOSi) entry-level ERP developer in Charleston, SC — cleared-work government contracting pay bands are well below product-tech; base likely $65-80k with minimal bonus/equity. Wide band due to no public comp data for SOSi.</t>
+          <t>Posting lists a $62,900-$119,700 range for the level; new-grad SWE I at a defense prime in San Jose typically lands ~$85-95k base plus a small (~5%) bonus and no meaningful equity. Well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -21069,7 +21073,7 @@
       </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -21078,38 +21082,38 @@
         <v>307</v>
       </c>
       <c r="B308" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>$60k–$75k</t>
+          <t>$65k–$85k</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>SOSi</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Mobile Developer - iOS/Android</t>
+          <t>PeopleSoft Software Developer</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Charleston, SC</t>
         </is>
       </c>
       <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr">
         <is>
-          <t>Mobile app development (Swift/Kotlin, Play Store publishing) at an IT staffing/consulting firm is essentially orthogonal to the candidate's backend/distributed-systems/AI-infra profile, and the role also demands 1-2 years of prior mobile experience, mandatory onsite relocation on 6-18 month client assignments, and pays $60-85k — far below the ~130k anchor.</t>
+          <t>Hard-blocked by the Secret clearance requirement (an explicit candidate constraint) and the work is PeopleSoft/PeopleCode ERP maintenance — no overlap with backend distributed systems, Rust/systems, or AI infra — plus onsite 5 days in Charleston at roughly half the target TC.</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>Posting explicitly states $60k–$85k salary ($30–$40/hr); IT staffing/consulting firms of this type offer little to no bonus or equity, so TC ≈ base. Entry-level placement would land at the bottom of that range.</t>
+          <t>Defense/government services integrator (SOSi) entry-level ERP developer in Charleston, SC — cleared-work government contracting pay bands are well below product-tech; base likely $65-80k with minimal bonus/equity. Wide band due to no public comp data for SOSi.</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -21135,7 +21139,7 @@
       </c>
       <c r="P308" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -21148,39 +21152,39 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>$50k–$75k</t>
+          <t>$60k–$75k</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Teledyne</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Engineering Technician</t>
+          <t>Mobile Developer - iOS/Android</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Huntsville, AL</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr">
         <is>
-          <t>Engineering Technician is a hands-on hardware/lab technician role rather than a software engineering position, at a defense contractor site where clearance is commonly expected — directly matching the candidate's low-fit categories (hardware/embedded-only, non-SWE) with no backend, distributed-systems, or AI-infra component.</t>
+          <t>Mobile app development (Swift/Kotlin, Play Store publishing) at an IT staffing/consulting firm is essentially orthogonal to the candidate's backend/distributed-systems/AI-infra profile, and the role also demands 1-2 years of prior mobile experience, mandatory onsite relocation on 6-18 month client assignments, and pays $60-85k — far below the ~130k anchor.</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>Teledyne is a mid-tier defense/industrial technology company, and Engineering Technician titles are paid on a technician/associate scale (often hourly) rather than a software-engineer scale. Huntsville, AL cost of living further lowers the band. Estimate is inferred from general defense-contractor technician pay norms, not posted data; the entire band falls below the candidate's ~$120k floor.</t>
+          <t>Posting explicitly states $60k–$85k salary ($30–$40/hr); IT staffing/consulting firms of this type offer little to no bonus or equity, so TC ≈ base. Entry-level placement would land at the bottom of that range.</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -21201,7 +21205,7 @@
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -21210,43 +21214,43 @@
         <v>309</v>
       </c>
       <c r="B310" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>$80k–$95k</t>
+          <t>$50k–$75k</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Teledyne</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Engineering Technician</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA</t>
+          <t>Huntsville, AL</t>
         </is>
       </c>
       <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr">
         <is>
-          <t>Requires an active DoD Secret clearance from day 1 (candidate has none) and is an intern-to-FT conversion req, plus the work is embedded Linux BSP/kernel/driver development onsite in Cedar Rapids, IA — squarely in the candidate's low-fit hardware/embedded bucket rather than backend/distributed systems.</t>
+          <t>Engineering Technician is a hands-on hardware/lab technician role rather than a software engineering position, at a defense contractor site where clearance is commonly expected — directly matching the candidate's low-fit categories (hardware/embedded-only, non-SWE) with no backend, distributed-systems, or AI-infra component.</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>Posting states a $57.2k-$108.8k range across all experience levels; new grads at defense primes (RTX/Collins) in low-COL Cedar Rapids typically land ~$78-90k base plus a small, non-guaranteed annual incentive. Defense-prime tier pays well below the candidate's $130-165k anchor and under the $120k low-match floor.</t>
+          <t>Teledyne is a mid-tier defense/industrial technology company, and Engineering Technician titles are paid on a technician/associate scale (often hourly) rather than a software-engineer scale. Huntsville, AL cost of living further lowers the band. Estimate is inferred from general defense-contractor technician pay norms, not posted data; the entire band falls below the candidate's ~$120k floor.</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -21267,7 +21271,7 @@
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -21276,38 +21280,38 @@
         <v>310</v>
       </c>
       <c r="B311" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>$45k–$70k</t>
+          <t>$80k–$95k</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>ERPA</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Franklin County, OH</t>
+          <t>Cedar Rapids, IA</t>
         </is>
       </c>
       <c r="G311" t="inlineStr"/>
       <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr">
         <is>
-          <t>Contract "training and placement" body-shop posting at an Oracle/PeopleSoft consulting partner targeting candidates with "basic technical skills" — no backend, distributed-systems, or AI-infra content, and the contract/staffing model is far off-profile for this candidate.</t>
+          <t>Requires an active DoD Secret clearance from day 1 (candidate has none) and is an intern-to-FT conversion req, plus the work is embedded Linux BSP/kernel/driver development onsite in Cedar Rapids, IA — squarely in the candidate's low-fit hardware/embedded bucket rather than backend/distributed systems.</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>ERP Analysts is a small Oracle Platinum Partner consulting/staffing firm; "training and placement" contract roles are typically hourly W2/C2C with no equity and minimal bonus. Band is wide because comp is unpublished and contract terms vary — estimate based on general IT-staffing/consulting entry-level market rates, not company data. Well below the candidate's ~$130k anchor.</t>
+          <t>Posting states a $57.2k-$108.8k range across all experience levels; new grads at defense primes (RTX/Collins) in low-COL Cedar Rapids typically land ~$78-90k base plus a small, non-guaranteed annual incentive. Defense-prime tier pays well below the candidate's $130-165k anchor and under the $120k low-match floor.</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -21333,7 +21337,7 @@
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -21342,43 +21346,43 @@
         <v>311</v>
       </c>
       <c r="B312" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>$65k–$90k</t>
+          <t>$45k–$70k</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Intertek</t>
+          <t>ERPA</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>EMC Engineer - 2nd Shift</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Boxborough, MA</t>
+          <t>Franklin County, OH</t>
         </is>
       </c>
       <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr">
         <is>
-          <t>EMC (electromagnetic compatibility) engineering is an EE/hardware lab compliance-testing role — explicitly in the candidate's low-fit bucket and unrelated to his backend, distributed-systems, and AI-infra software profile.</t>
+          <t>Contract "training and placement" body-shop posting at an Oracle/PeopleSoft consulting partner targeting candidates with "basic technical skills" — no backend, distributed-systems, or AI-infra content, and the contract/staffing model is far off-profile for this candidate.</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>Intertek is a testing/inspection/certification (TIC) services firm, not a tech-tier employer; new-grad EMC/test engineer base pay in the Boston area typically runs ~$65-80k, with a 2nd-shift differential pushing the top end toward ~$90k. Comp for this segment is not well benchmarked publicly, so the band is intentionally wide — and it falls well below the candidate's ~$130k anchor.</t>
+          <t>ERP Analysts is a small Oracle Platinum Partner consulting/staffing firm; "training and placement" contract roles are typically hourly W2/C2C with no equity and minimal bonus. Band is wide because comp is unpublished and contract terms vary — estimate based on general IT-staffing/consulting entry-level market rates, not company data. Well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -21399,7 +21403,7 @@
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -21417,29 +21421,29 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>GE Healthcare</t>
+          <t>Intertek</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Field Engineer 1 - Imaging</t>
+          <t>EMC Engineer - 2nd Shift</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Remote in USA</t>
+          <t>Boxborough, MA</t>
         </is>
       </c>
       <c r="G313" t="inlineStr"/>
       <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr">
         <is>
-          <t>Hands-on medical imaging hardware field-service role (on-site install/repair, heavy travel despite the "Remote in USA" label) with no backend, distributed systems, or software work — directly matches the candidate's hardware/EE-centric role_fit_low exclusion.</t>
+          <t>EMC (electromagnetic compatibility) engineering is an EE/hardware lab compliance-testing role — explicitly in the candidate's low-fit bucket and unrelated to his backend, distributed-systems, and AI-infra software profile.</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>GE Healthcare Field Engineer 1 sits on a field-service technician pay scale, not the software engineering scale: base roughly $60-75k plus overtime/on-call pay and a modest bonus, with a small or no equity component. Band widened slightly for geographic variation and OT variability. Well below the candidate's ~$130-165k anchor and below the ~$120k low-match floor. Estimate only.</t>
+          <t>Intertek is a testing/inspection/certification (TIC) services firm, not a tech-tier employer; new-grad EMC/test engineer base pay in the Boston area typically runs ~$65-80k, with a 2nd-shift differential pushing the top end toward ~$90k. Comp for this segment is not well benchmarked publicly, so the band is intentionally wide — and it falls well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -21474,38 +21478,38 @@
         <v>313</v>
       </c>
       <c r="B314" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>$75k–$98k</t>
+          <t>$65k–$90k</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>The Boeing Company</t>
+          <t>GE Healthcare</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>MP&amp;P Engineer - Nondestructive Evaluation</t>
+          <t>Field Engineer 1 - Imaging</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Mesa, AZ</t>
+          <t>Remote in USA</t>
         </is>
       </c>
       <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr">
         <is>
-          <t>This is a materials/aerospace engineering role (Materials, Process &amp;amp; Physics — nondestructive evaluation of structures via ultrasound/radiography), not a software role, and Boeing's Mesa site is defense work that will likely require a clearance the candidate doesn't hold — essentially no overlap with backend/distributed-systems/AI-infra, and TC is well below the ~120k floor.</t>
+          <t>Hands-on medical imaging hardware field-service role (on-site install/repair, heavy travel despite the "Remote in USA" label) with no backend, distributed systems, or software work — directly matches the candidate's hardware/EE-centric role_fit_low exclusion.</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>Boeing new-grad engineering (Level 1) pay is base-heavy with a small bonus and no meaningful equity; Mesa, AZ is a low-cost-of-living site, so entry-level base typically lands ~$72–92k with a ~4–6% incentive target. Estimate from general knowledge of Boeing's compensation tier, not verified data for this req.</t>
+          <t>GE Healthcare Field Engineer 1 sits on a field-service technician pay scale, not the software engineering scale: base roughly $60-75k plus overtime/on-call pay and a modest bonus, with a small or no equity component. Band widened slightly for geographic variation and OT variability. Well below the candidate's ~$130-165k anchor and below the ~$120k low-match floor. Estimate only.</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -21540,43 +21544,43 @@
         <v>314</v>
       </c>
       <c r="B315" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>$68k–$78k</t>
+          <t>$75k–$98k</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Ameren</t>
+          <t>The Boeing Company</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Engineering Representative</t>
+          <t>MP&amp;P Engineer - Nondestructive Evaluation</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Collinsville, IL</t>
+          <t>Mesa, AZ</t>
         </is>
       </c>
       <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Utility GIS/ArcFM mapping technician role requiring only a HS diploma and A.C./D.C. electricity coursework — no software engineering, backend, or distributed-systems content, and it's an hourly craft classification rather than a new-grad SWE track.</t>
+          <t>This is a materials/aerospace engineering role (Materials, Process &amp;amp; Physics — nondestructive evaluation of structures via ultrasound/radiography), not a software role, and Boeing's Mesa site is defense work that will likely require a clearance the candidate doesn't hold — essentially no overlap with backend/distributed-systems/AI-infra, and TC is well below the ~120k floor.</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>Rate is stated in the posting: $32.20-$33.24/hr (2-step scale) = ~$67k-$69k base at 2080 hours, plus a discretionary annual incentive and standard regulated-utility benefits. Not a new-grad SWE band; far below the candidate's ~$120k floor.</t>
+          <t>Boeing new-grad engineering (Level 1) pay is base-heavy with a small bonus and no meaningful equity; Mesa, AZ is a low-cost-of-living site, so entry-level base typically lands ~$72–92k with a ~4–6% incentive target. Estimate from general knowledge of Boeing's compensation tier, not verified data for this req.</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -21606,38 +21610,38 @@
         <v>315</v>
       </c>
       <c r="B316" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>$55k–$90k</t>
+          <t>$68k–$78k</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>ConeTec Group</t>
+          <t>Ameren</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Field Geologist/Engineer</t>
+          <t>Engineering Representative</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Richmond, CA</t>
+          <t>Collinsville, IL</t>
         </is>
       </c>
       <c r="G316" t="inlineStr"/>
       <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr">
         <is>
-          <t>Physical field geotechnical/geology role requiring an Engineering/Geology degree, heavy equipment operation, and outdoor travel — no overlap with the candidate's backend, distributed-systems, or AI-infra software profile.</t>
+          <t>Utility GIS/ArcFM mapping technician role requiring only a HS diploma and A.C./D.C. electricity coursework — no software engineering, backend, or distributed-systems content, and it's an hourly craft classification rather than a new-grad SWE track.</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>Posting lists $20-$60/hour; entry-level field engineers typically start near the bottom of that range (~$45-55k base), with the upper end driven by field overtime and per diem common at site-characterization contractors. ConeTec is a private geotechnical services firm, not a tech-tier compensator, so this falls well below the candidate's $130-165k anchor. Estimate, not fact.</t>
+          <t>Rate is stated in the posting: $32.20-$33.24/hr (2-step scale) = ~$67k-$69k base at 2080 hours, plus a discretionary annual incentive and standard regulated-utility benefits. Not a new-grad SWE band; far below the candidate's ~$120k floor.</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -21676,34 +21680,34 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>$70k–$88k</t>
+          <t>$55k–$90k</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Newell Brands</t>
+          <t>ConeTec Group</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Associate Product Engineer - Home Fragrance</t>
+          <t>Field Geologist/Engineer</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Amherst, MA</t>
+          <t>Richmond, CA</t>
         </is>
       </c>
       <c r="G317" t="inlineStr"/>
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr">
         <is>
-          <t>Mechanical/product-design engineering role for physical home-fragrance goods (CAD/Creo, DFMEA, prototyping, material selection) requiring an ME/ChemE/MatSci degree — zero overlap with the candidate's backend, distributed-systems, and AI-infra software profile.</t>
+          <t>Physical field geotechnical/geology role requiring an Engineering/Geology degree, heavy equipment operation, and outdoor travel — no overlap with the candidate's backend, distributed-systems, or AI-infra software profile.</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>Newell Brands is a mid-tier consumer-packaged-goods manufacturer, not a tech-tier payer; entry-level ("Associate", 0-2 yrs) engineering roles in Western MA typically pay ~$68-80k base plus a modest annual bonus. Estimate from general CPG/manufacturing new-grad engineering benchmarks, not a posted range — well below the candidate's ~$130k anchor.</t>
+          <t>Posting lists $20-$60/hour; entry-level field engineers typically start near the bottom of that range (~$45-55k base), with the upper end driven by field overtime and per diem common at site-characterization contractors. ConeTec is a private geotechnical services firm, not a tech-tier compensator, so this falls well below the candidate's $130-165k anchor. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -21738,38 +21742,38 @@
         <v>317</v>
       </c>
       <c r="B318" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>$55k–$80k</t>
+          <t>$70k–$88k</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Presidency Solutions</t>
+          <t>Newell Brands</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Associate Product Engineer - Home Fragrance</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI</t>
+          <t>Amherst, MA</t>
         </is>
       </c>
       <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr"/>
       <c r="I318" t="inlineStr">
         <is>
-          <t>Posting explicitly requires Mexican citizenship for TN/H1B sponsorship and targets mid/senior mobile (iOS/Android/Windows Mobile), Pega, Oracle DBA, and Hadoop consultants — disqualifying and off-profile for a US-authorized backend/distributed-systems new grad.</t>
+          <t>Mechanical/product-design engineering role for physical home-fragrance goods (CAD/Creo, DFMEA, prototyping, material selection) requiring an ME/ChemE/MatSci degree — zero overlap with the candidate's backend, distributed-systems, and AI-infra software profile.</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>No public comp data for Presidency Solutions; small Farmington Hills, MI IT consulting/staffing firm placing visa-sponsored developers at government and bank clients. Band inferred from typical Midwest body-shop consultant salaries (low confidence, wide band), well below the candidate's ~130k anchor.</t>
+          <t>Newell Brands is a mid-tier consumer-packaged-goods manufacturer, not a tech-tier payer; entry-level ("Associate", 0-2 yrs) engineering roles in Western MA typically pay ~$68-80k base plus a modest annual bonus. Estimate from general CPG/manufacturing new-grad engineering benchmarks, not a posted range — well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -21804,38 +21808,38 @@
         <v>318</v>
       </c>
       <c r="B319" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>$55k–$72k</t>
+          <t>$55k–$80k</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Loblaw Companies</t>
+          <t>Presidency Solutions</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Front-End Developer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Farmington Hills, MI</t>
         </is>
       </c>
       <c r="G319" t="inlineStr"/>
       <c r="H319" t="inlineStr"/>
       <c r="I319" t="inlineStr">
         <is>
-          <t>Pure front-end React/CSS contract role (explicit low-fit category) that is an 18-month Toronto-based parental-leave backfill starting immediately — wrong discipline, wrong country, wrong employment type, and wrong timeline for a US new grad targeting mid-2027 backend/infra work.</t>
+          <t>Posting explicitly requires Mexican citizenship for TN/H1B sponsorship and targets mid/senior mobile (iOS/Android/Windows Mobile), Pega, Oracle DBA, and Hadoop consultants — disqualifying and off-profile for a US-authorized backend/distributed-systems new grad.</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>Loblaw Digital is a mid-tier Canadian retail-tech org; early-career front-end roles in Toronto typically land around CAD 75-100k base with limited equity, converting to roughly USD 55-72k. Fixed-term contract status further caps upside. Band is a rough estimate — Canadian retail-tech contract comp is not well documented publicly.</t>
+          <t>No public comp data for Presidency Solutions; small Farmington Hills, MI IT consulting/staffing firm placing visa-sponsored developers at government and bank clients. Band inferred from typical Midwest body-shop consultant salaries (low confidence, wide band), well below the candidate's ~130k anchor.</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -21870,38 +21874,38 @@
         <v>319</v>
       </c>
       <c r="B320" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>$65k–$85k</t>
+          <t>$55k–$72k</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>ConeTec Group</t>
+          <t>Loblaw Companies</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Field Engineer/Field Geologist</t>
+          <t>Front-End Developer</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="G320" t="inlineStr"/>
       <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr">
         <is>
-          <t>This is a physically-demanding geotechnical/geophysical field operations job (operating CPT rigs, lifting 50 lbs, 30% travel to remote sites) requiring a geology/civil background — it has essentially zero overlap with the candidate's backend, distributed-systems, and AI-infra software profile, and involves no software engineering work.</t>
+          <t>Pure front-end React/CSS contract role (explicit low-fit category) that is an 18-month Toronto-based parental-leave backfill starting immediately — wrong discipline, wrong country, wrong employment type, and wrong timeline for a US new grad targeting mid-2027 backend/infra work.</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>ConeTec is a private geo-environmental site-characterization contractor, not a tech employer. Entry-level field engineer/geologist pay in this industry typically runs ~$65-80k base in a higher-cost market like Seattle, with meaningful overtime and per-diem on 10-12+ hour field days potentially pushing realized earnings higher; equity is limited to a nominal corporate stock incentive. Wide band given no public comp data — well below the candidate's ~$130k anchor.</t>
+          <t>Loblaw Digital is a mid-tier Canadian retail-tech org; early-career front-end roles in Toronto typically land around CAD 75-100k base with limited equity, converting to roughly USD 55-72k. Fixed-term contract status further caps upside. Band is a rough estimate — Canadian retail-tech contract comp is not well documented publicly.</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -21940,34 +21944,34 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>$58k–$85k</t>
+          <t>$65k–$85k</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>TRIMEDX</t>
+          <t>ConeTec Group</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Imaging Engineer 1</t>
+          <t>Field Engineer/Field Geologist</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Norfolk, VA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="G321" t="inlineStr"/>
       <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr">
         <is>
-          <t>This is a hands-on medical imaging field service technician role (X-ray/ultrasound diagnosis, repair, calibration, site travel) requiring an associate's degree in electronics — it contains zero software engineering work and directly matches the candidate's "hardware/embedded-only" low-fit exclusion.</t>
+          <t>This is a physically-demanding geotechnical/geophysical field operations job (operating CPT rigs, lifting 50 lbs, 30% travel to remote sites) requiring a geology/civil background — it has essentially zero overlap with the candidate's backend, distributed-systems, and AI-infra software profile, and involves no software engineering work.</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>Posting states an explicit hourly range of $27.00-40.00, which annualizes to roughly $56k-83k at 2080 hours; adding the listed benefits/401k match and annual merit increases gives a ~$58k-85k total comp band, with an entry-level hire realistically near the low end (~$56-65k). TRIMEDX is a healthcare technology management services firm, not a tech-tier payer, so there is no equity component. Well below the candidate's ~$120k floor.</t>
+          <t>ConeTec is a private geo-environmental site-characterization contractor, not a tech employer. Entry-level field engineer/geologist pay in this industry typically runs ~$65-80k base in a higher-cost market like Seattle, with meaningful overtime and per-diem on 10-12+ hour field days potentially pushing realized earnings higher; equity is limited to a nominal corporate stock incentive. Wide band given no public comp data — well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -22006,34 +22010,34 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>$70k–$85k</t>
+          <t>$58k–$85k</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>AIR Control Concepts</t>
+          <t>TRIMEDX</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Application Engineer</t>
+          <t>Imaging Engineer 1</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Elkridge, MD</t>
+          <t>Norfolk, VA</t>
         </is>
       </c>
       <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr">
         <is>
-          <t>HVAC applications/sales-support engineering role requiring a Mechanical or Architectural Engineering degree plus AutoCAD/Revit and commercial HVAC systems knowledge — no software, backend, or infra content, and entirely outside the candidate's profile and target roles.</t>
+          <t>This is a hands-on medical imaging field service technician role (X-ray/ultrasound diagnosis, repair, calibration, site travel) requiring an associate's degree in electronics — it contains zero software engineering work and directly matches the candidate's "hardware/embedded-only" low-fit exclusion.</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>Posting explicitly lists a $70-120k base range covering 0-5 years of experience; a true entry-level hire would land near the floor. Small private HVAC rep firm (Advanced Thermal Solutions / AIR Control Concepts family) — no equity, standard 401(k) match, so TC ~= base. Even the top of the posted band is well below the ~$130k anchor.</t>
+          <t>Posting states an explicit hourly range of $27.00-40.00, which annualizes to roughly $56k-83k at 2080 hours; adding the listed benefits/401k match and annual merit increases gives a ~$58k-85k total comp band, with an entry-level hire realistically near the low end (~$56-65k). TRIMEDX is a healthcare technology management services firm, not a tech-tier payer, so there is no equity component. Well below the candidate's ~$120k floor.</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -22068,38 +22072,38 @@
         <v>322</v>
       </c>
       <c r="B323" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>$35k–$50k</t>
+          <t>$70k–$85k</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Valeo Foods</t>
+          <t>AIR Control Concepts</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Enterprise Applications Developer - Enterprise Applications</t>
+          <t>Application Engineer</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Leeds, UK</t>
+          <t>Elkridge, MD</t>
         </is>
       </c>
       <c r="G323" t="inlineStr"/>
       <c r="H323" t="inlineStr"/>
       <c r="I323" t="inlineStr">
         <is>
-          <t>UK-based (Leeds) ERP/Power Apps/SSRS enterprise-applications role in a Microsoft low-code stack at a food manufacturer — no backend/distributed-systems or AI-infra content, wrong geography for a US-authorized candidate, immediate start rather than mid-2027, and comp far below the ~$130k anchor.</t>
+          <t>HVAC applications/sales-support engineering role requiring a Mechanical or Architectural Engineering degree plus AutoCAD/Revit and commercial HVAC systems knowledge — no software, backend, or infra content, and entirely outside the candidate's profile and target roles.</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>UK non-tech-sector (food manufacturing) enterprise applications developer in a regional, non-London market; junior/grad-level Microsoft ERP dev bands in Leeds run roughly £28-38k base, converting to ~$35-50k USD. Benefits listed are largely non-cash (25 days + bank holidays, matched pension, cycle-to-work, staff discount), so total cash comp is close to base. Wide-ish band because no salary was posted and the company is not a known tech-comp benchmark; this is an estimate, not fact.</t>
+          <t>Posting explicitly lists a $70-120k base range covering 0-5 years of experience; a true entry-level hire would land near the floor. Small private HVAC rep firm (Advanced Thermal Solutions / AIR Control Concepts family) — no equity, standard 401(k) match, so TC ~= base. Even the top of the posted band is well below the ~$130k anchor.</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
@@ -22125,7 +22129,7 @@
       </c>
       <c r="P323" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -22138,7 +22142,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>$34k–$48k</t>
+          <t>$35k–$50k</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -22153,19 +22157,19 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Norwich, UK</t>
+          <t>Leeds, UK</t>
         </is>
       </c>
       <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr">
         <is>
-          <t>UK-only (Norwich) internal-IT ERP/low-code role built on C#, SSRS/Power BI, Logic Apps and Power Apps — no overlap with the candidate's backend/distributed-systems/AI-infra profile, and the location is impractical for a US-authorized new grad.</t>
+          <t>UK-based (Leeds) ERP/Power Apps/SSRS enterprise-applications role in a Microsoft low-code stack at a food manufacturer — no backend/distributed-systems or AI-infra content, wrong geography for a US-authorized candidate, immediate start rather than mid-2027, and comp far below the ~$130k anchor.</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>Valeo Foods is a UK food manufacturer, not a tech company; this is an internal enterprise-applications/IT position in Norwich, a low-cost regional UK market. No salary posted, so the band is inferred from typical UK junior enterprise/ERP developer pay outside London (~£27-38k) converted to USD. Wide band, low confidence; well below the candidate's ~$130k anchor.</t>
+          <t>UK non-tech-sector (food manufacturing) enterprise applications developer in a regional, non-London market; junior/grad-level Microsoft ERP dev bands in Leeds run roughly £28-38k base, converting to ~$35-50k USD. Benefits listed are largely non-cash (25 days + bank holidays, matched pension, cycle-to-work, staff discount), so total cash comp is close to base. Wide-ish band because no salary was posted and the company is not a known tech-comp benchmark; this is an estimate, not fact.</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -22204,34 +22208,34 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>$33k–$45k</t>
+          <t>$34k–$48k</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Radius Limited</t>
+          <t>Valeo Foods</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Graduate Mobile Developer - Vehicle Telematics</t>
+          <t>Enterprise Applications Developer - Enterprise Applications</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Crewe, UK</t>
+          <t>Norwich, UK</t>
         </is>
       </c>
       <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr"/>
       <c r="I325" t="inlineStr">
         <is>
-          <t>UK-only role in Crewe with explicit no-visa-sponsorship and UK right-to-work requirement, focused on cross-platform mobile app development (Flutter/React Native/Kotlin/Swift) — off-profile on both geography/authorization and technical domain for a US-based backend/distributed-systems candidate.</t>
+          <t>UK-only (Norwich) internal-IT ERP/low-code role built on C#, SSRS/Power BI, Logic Apps and Power Apps — no overlap with the candidate's backend/distributed-systems/AI-infra profile, and the location is impractical for a US-authorized new grad.</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>Estimate, not fact. Radius Limited is a mid-market UK fleet services/telematics company (fuel cards, leasing, telecoms), not a tech-tier compensator. Regional graduate developer salaries in Cheshire/North West England typically run roughly £26–35k GBP base with a benefits package (pension, life assurance, fuel card, EV scheme) and little to no equity; converted at ~1.27 USD/GBP that is ~$33–45k USD. Band is wide because the posting states only "competitive salary" with no figure. Note this is GBP-denominated UK comp and not directly comparable to US new-grad TC benchmarks — it sits far below the candidate's ~$130k anchor.</t>
+          <t>Valeo Foods is a UK food manufacturer, not a tech company; this is an internal enterprise-applications/IT position in Norwich, a low-cost regional UK market. No salary posted, so the band is inferred from typical UK junior enterprise/ERP developer pay outside London (~£27-38k) converted to USD. Wide band, low confidence; well below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -22270,34 +22274,34 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>$35k–$45k</t>
+          <t>$33k–$45k</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Epos Now Group</t>
+          <t>Radius Limited</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Graduate Mobile Developer - Vehicle Telematics</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Norwich, UK</t>
+          <t>Crewe, UK</t>
         </is>
       </c>
       <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr"/>
       <c r="I326" t="inlineStr">
         <is>
-          <t>On-site Norwich, UK role requiring UK work authorization with a £28–35k (~$35–44k USD) salary — the backend/data-pipeline work is mildly on-profile, but the location and comp are both disqualifying for a US-authorized new grad anchoring at ~$130k.</t>
+          <t>UK-only role in Crewe with explicit no-visa-sponsorship and UK right-to-work requirement, focused on cross-platform mobile app development (Flutter/React Native/Kotlin/Swift) — off-profile on both geography/authorization and technical domain for a US-based backend/distributed-systems candidate.</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>Salary stated directly in the posting: £28,000–£35,000/yr. Epos Now is a mid-size UK POS/SaaS company; no meaningful equity expected at IC3, so TC ≈ base converted at ~1.27 USD/GBP. Estimate, not fact.</t>
+          <t>Estimate, not fact. Radius Limited is a mid-market UK fleet services/telematics company (fuel cards, leasing, telecoms), not a tech-tier compensator. Regional graduate developer salaries in Cheshire/North West England typically run roughly £26–35k GBP base with a benefits package (pension, life assurance, fuel card, EV scheme) and little to no equity; converted at ~1.27 USD/GBP that is ~$33–45k USD. Band is wide because the posting states only "competitive salary" with no figure. Note this is GBP-denominated UK comp and not directly comparable to US new-grad TC benchmarks — it sits far below the candidate's ~$130k anchor.</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -22323,7 +22327,7 @@
       </c>
       <c r="P326" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -22332,38 +22336,38 @@
         <v>326</v>
       </c>
       <c r="B327" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>$45k–$65k</t>
+          <t>$35k–$45k</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>M.C. Dean</t>
+          <t>Epos Now Group</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Systems Engineering Technician 1</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Norfolk, VA</t>
+          <t>Norwich, UK</t>
         </is>
       </c>
       <c r="G327" t="inlineStr"/>
       <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr">
         <is>
-          <t>Entry-level shipboard cable/equipment installation trade technician requiring a Secret clearance, HS diploma, and heavy physical labor — no software engineering content and a hard clearance blocker for this candidate.</t>
+          <t>On-site Norwich, UK role requiring UK work authorization with a £28–35k (~$35–44k USD) salary — the backend/data-pipeline work is mildly on-profile, but the location and comp are both disqualifying for a US-authorized new grad anchoring at ~$130k.</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>M.C. Dean is a defense/critical-infrastructure integrator; "Technician 1" is an hourly entry trade role (est. ~$20-28/hr) with significant shipyard overtime and benefits. Estimate is approximate and based on general knowledge of defense-contractor technician pay bands, not posted data.</t>
+          <t>Salary stated directly in the posting: £28,000–£35,000/yr. Epos Now is a mid-size UK POS/SaaS company; no meaningful equity expected at IC3, so TC ≈ base converted at ~1.27 USD/GBP. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -22389,7 +22393,7 @@
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -22398,38 +22402,38 @@
         <v>327</v>
       </c>
       <c r="B328" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>$35k–$48k</t>
+          <t>$45k–$65k</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>CPI Card Group</t>
+          <t>M.C. Dean</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Software Developer 1</t>
+          <t>Systems Engineering Technician 1</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Norwich, UK</t>
+          <t>Norfolk, VA</t>
         </is>
       </c>
       <c r="G328" t="inlineStr"/>
       <c r="H328" t="inlineStr"/>
       <c r="I328" t="inlineStr">
         <is>
-          <t>UK-only role in Norwich that explicitly cannot sponsor visas (candidate is US-authorized only), with an immediate junior Python/AWS web-app scope rather than a mid-2027 new-grad req.</t>
+          <t>Entry-level shipboard cable/equipment installation trade technician requiring a Secret clearance, HS diploma, and heavy physical labor — no software engineering content and a hard clearance blocker for this candidate.</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>Estimate: junior backend dev in Norwich (low-cost UK regional market) at a mid-tier payments company typically pays ~£28-38k, converting to roughly $35-48k USD. Well below the candidate's ~$130k anchor due to UK market rates rather than company tier.</t>
+          <t>M.C. Dean is a defense/critical-infrastructure integrator; "Technician 1" is an hourly entry trade role (est. ~$20-28/hr) with significant shipyard overtime and benefits. Estimate is approximate and based on general knowledge of defense-contractor technician pay bands, not posted data.</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -22464,38 +22468,38 @@
         <v>328</v>
       </c>
       <c r="B329" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>$42k–$52k</t>
+          <t>$35k–$48k</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>EagleView</t>
+          <t>CPI Card Group</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Flight Systems Technician - Capture Systems R&amp;D</t>
+          <t>Software Developer 1</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Rochester, NY</t>
+          <t>Norwich, UK</t>
         </is>
       </c>
       <c r="G329" t="inlineStr"/>
       <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr">
         <is>
-          <t>Hands-on hardware/mechanical technician role (camera assembly, calibration, image-quality testing, lifting 40 lbs) with no software engineering ownership and no degree requirement — entirely off-profile for a backend/distributed-systems/AI-infra new grad, and the stated $20-24/hr pay is far below the ~130k anchor.</t>
+          <t>UK-only role in Norwich that explicitly cannot sponsor visas (candidate is US-authorized only), with an immediate junior Python/AWS web-app scope rather than a mid-2027 new-grad req.</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>Pay rate is stated explicitly in the posting: $20.00-$24.00/hour, on-site Rochester NY, which annualizes to ~$41.6k-$49.9k at 40 hrs/week; upper bound nudged to ~$52k to account for possible overtime. No equity or meaningful bonus expected at this technician level; EagleView is a mid-tier private geospatial/insurtech company, not a top-of-market payer.</t>
+          <t>Estimate: junior backend dev in Norwich (low-cost UK regional market) at a mid-tier payments company typically pays ~£28-38k, converting to roughly $35-48k USD. Well below the candidate's ~$130k anchor due to UK market rates rather than company tier.</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -22530,38 +22534,38 @@
         <v>329</v>
       </c>
       <c r="B330" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>$44k–$56k</t>
+          <t>$42k–$52k</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>TOMRA</t>
+          <t>EagleView</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Field Service Engineer - London/South East</t>
+          <t>Flight Systems Technician - Capture Systems R&amp;D</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Rochester, NY</t>
         </is>
       </c>
       <c r="G330" t="inlineStr"/>
       <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr">
         <is>
-          <t>Hands-on electro-mechanical field service role repairing reverse vending machines across London/South East, requiring a full UK driving licence and on-site/rota shift work — zero software engineering overlap with the candidate's backend/distributed-systems/AI-infra profile, and wrong country.</t>
+          <t>Hands-on hardware/mechanical technician role (camera assembly, calibration, image-quality testing, lifting 40 lbs) with no software engineering ownership and no degree requirement — entirely off-profile for a backend/distributed-systems/AI-infra new grad, and the stated $20-24/hr pay is far below the ~130k anchor.</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>Posting explicitly lists GBP 35,000-41,000/year base; adding 10% non-contributory pension, company bonus, and paid overtime and converting at ~1.27 USD/GBP gives roughly $44k-$56k USD equivalent. UK field-service comp bands are not comparable to US new-grad SWE, and this sits far below the candidate's ~$130k target.</t>
+          <t>Pay rate is stated explicitly in the posting: $20.00-$24.00/hour, on-site Rochester NY, which annualizes to ~$41.6k-$49.9k at 40 hrs/week; upper bound nudged to ~$52k to account for possible overtime. No equity or meaningful bonus expected at this technician level; EagleView is a mid-tier private geospatial/insurtech company, not a top-of-market payer.</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -22587,7 +22591,7 @@
       </c>
       <c r="P330" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -22596,38 +22600,38 @@
         <v>330</v>
       </c>
       <c r="B331" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>$36k–$40k</t>
+          <t>$44k–$56k</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>PaperCut</t>
+          <t>TOMRA</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Associate Support Engineer</t>
+          <t>Field Service Engineer - London/South East</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Bracknell, UK</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="G331" t="inlineStr"/>
       <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr">
         <is>
-          <t>Frontline customer-support role in Bracknell, UK — not a backend/distributed-systems SWE position, outside the candidate's US work authorization, and capped at ~$38k TC versus a ~$130k anchor.</t>
+          <t>Hands-on electro-mechanical field service role repairing reverse vending machines across London/South East, requiring a full UK driving licence and on-site/rota shift work — zero software engineering overlap with the candidate's backend/distributed-systems/AI-infra profile, and wrong country.</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>Posting states "up to GBP 30,000 - yearly"; converted at ~1.27 USD/GBP. PaperCut is a mid-size private print-management vendor, and associate support roles in the UK typically have no meaningful equity component, so base is effectively total comp. Estimate, not fact.</t>
+          <t>Posting explicitly lists GBP 35,000-41,000/year base; adding 10% non-contributory pension, company bonus, and paid overtime and converting at ~1.27 USD/GBP gives roughly $44k-$56k USD equivalent. UK field-service comp bands are not comparable to US new-grad SWE, and this sits far below the candidate's ~$130k target.</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -22662,42 +22666,38 @@
         <v>331</v>
       </c>
       <c r="B332" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>$20k–$45k</t>
+          <t>$36k–$40k</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Hawk-Eye Innovations</t>
+          <t>PaperCut</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Football Tracking Systems Operator - Remote Operations Centre</t>
+          <t>Associate Support Engineer</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Basingstoke, UK, Southampton, UK, Reading, UK</t>
+          <t>Bracknell, UK</t>
         </is>
       </c>
       <c r="G332" t="inlineStr"/>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>start date: july</t>
-        </is>
-      </c>
+      <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr">
         <is>
-          <t>A UK-based, in-office casual hourly shift role operating live Goal Line Technology broadcast systems — not a software engineering position, wrong country, wrong start date (July/August 2026 vs. May 2027 graduation), and pay far below the candidate's floor.</t>
+          <t>Frontline customer-support role in Bracknell, UK — not a backend/distributed-systems SWE position, outside the candidate's US work authorization, and capped at ~$38k TC versus a ~$130k anchor.</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>Posting states £13.00–£18.20/hr on a casual contract with 10–12 hour match-day shifts. At ~$1.27/£, full-time-equivalent hours (~2,080) would be roughly $34k–48k; because hours are casual and clustered around the football calendar, realized annual earnings are likely lower, hence the wide $20k–45k band. This is not a salaried new-grad SWE offer and Hawk-Eye (Sony-owned sports tech) does not run this as a graduate engineering pipeline, so no standard new-grad TC benchmark applies. Estimate only, low confidence on total realized comp.</t>
+          <t>Posting states "up to GBP 30,000 - yearly"; converted at ~1.27 USD/GBP. PaperCut is a mid-size private print-management vendor, and associate support roles in the UK typically have no meaningful equity component, so base is effectively total comp. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -22732,38 +22732,42 @@
         <v>332</v>
       </c>
       <c r="B333" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>$42k–$52k</t>
+          <t>$20k–$45k</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>M.C. Dean</t>
+          <t>Hawk-Eye Innovations</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Electronics Associate - Security and Electronic Systems</t>
+          <t>Football Tracking Systems Operator - Remote Operations Centre</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Dallas, TX</t>
+          <t>Basingstoke, UK, Southampton, UK, Reading, UK</t>
         </is>
       </c>
       <c r="G333" t="inlineStr"/>
-      <c r="H333" t="inlineStr"/>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>start date: july</t>
+        </is>
+      </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>Hands-on electronics/security-systems technician apprenticeship (HS diploma, $20/hr, cabling and raceway installation on construction sites, clearance-track) with no software engineering scope — a near-total mismatch for a backend/distributed-systems/AI-infra new grad.</t>
+          <t>A UK-based, in-office casual hourly shift role operating live Goal Line Technology broadcast systems — not a software engineering position, wrong country, wrong start date (July/August 2026 vs. May 2027 graduation), and pay far below the candidate's floor.</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>Posting explicitly states starting pay of $20/hr (~$41.6k at 2,080 hrs); upper end accounts for overtime, travel/per-diem, and the mentioned clearance hourly incentive. Well below the candidate's ~$120k low-match floor.</t>
+          <t>Posting states £13.00–£18.20/hr on a casual contract with 10–12 hour match-day shifts. At ~$1.27/£, full-time-equivalent hours (~2,080) would be roughly $34k–48k; because hours are casual and clustered around the football calendar, realized annual earnings are likely lower, hence the wide $20k–45k band. This is not a salaried new-grad SWE offer and Hawk-Eye (Sony-owned sports tech) does not run this as a graduate engineering pipeline, so no standard new-grad TC benchmark applies. Estimate only, low confidence on total realized comp.</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -22789,7 +22793,7 @@
       </c>
       <c r="P333" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -22802,34 +22806,34 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>$15k–$45k</t>
+          <t>$42k–$52k</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Lilt</t>
+          <t>M.C. Dean</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>AI Training Contributor - French</t>
+          <t>Electronics Associate - Security and Electronic Systems</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Remote in Canada, Québec City, QC, Canada</t>
+          <t>Dallas, TX</t>
         </is>
       </c>
       <c r="G334" t="inlineStr"/>
       <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr">
         <is>
-          <t>This is a part-time 1099 data-annotation/linguist gig in Canada requiring native French fluency — no software engineering content, no US full-time new-grad path, and nothing touching the candidate's backend/distributed-systems/AI-infra profile.</t>
+          <t>Hands-on electronics/security-systems technician apprenticeship (HS diploma, $20/hr, cabling and raceway installation on construction sites, clearance-track) with no software engineering scope — a near-total mismatch for a backend/distributed-systems/AI-infra new grad.</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>Not a salaried role — Lilt pays AI-training contractors hourly/per-task (typically ~$15-30/hr USD equivalent) with no benefits and no guaranteed hours; the posting explicitly says it is unsuitable as primary income. Band shown is a rough annualized figure assuming the stated 10+ hrs/week minimum up to near-full-time utilization, and is highly uncertain. Far below the ~$130k anchor.</t>
+          <t>Posting explicitly states starting pay of $20/hr (~$41.6k at 2,080 hrs); upper end accounts for overtime, travel/per-diem, and the mentioned clearance hourly incentive. Well below the candidate's ~$120k low-match floor.</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -22855,7 +22859,7 @@
       </c>
       <c r="P334" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -22868,38 +22872,34 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>$5k–$12k</t>
+          <t>$15k–$45k</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Hawk-Eye Innovations</t>
+          <t>Lilt</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Rugby Systems Operator</t>
+          <t>AI Training Contributor - French</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Manchester, UK</t>
+          <t>Remote in Canada, Québec City, QC, Canada</t>
         </is>
       </c>
       <c r="G335" t="inlineStr"/>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>start date: asap the role hawk</t>
-        </is>
-      </c>
+      <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr">
         <is>
-          <t>A freelance, weekend-only match-day AV/hardware operator role in Manchester, UK at £14/hour is off-profile in role type, location/work authorization, employment type, start timing, and comp for a US-based backend/distributed-systems new grad targeting May 2027 full-time at ~$130k.</t>
+          <t>This is a part-time 1099 data-annotation/linguist gig in Canada requiring native French fluency — no software engineering content, no US full-time new-grad path, and nothing touching the candidate's backend/distributed-systems/AI-infra profile.</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>Computed from the posting's own stated pay rather than company tier: £14/hr (holiday-inclusive) x ~8 hrs per match-day x ~15-25 Sale Sharks home fixtures across a Sept-June season, converted at roughly 1.27 USD/GBP. Casual/freelance hourly engagement with no base salary, bonus, or equity, so this is not a true new-grad TC comparable; band is wide to cover uncertainty in fixture count and any additional event work.</t>
+          <t>Not a salaried role — Lilt pays AI-training contractors hourly/per-task (typically ~$15-30/hr USD equivalent) with no benefits and no guaranteed hours; the posting explicitly says it is unsuitable as primary income. Band shown is a rough annualized figure assuming the stated 10+ hrs/week minimum up to near-full-time utilization, and is highly uncertain. Far below the ~$130k anchor.</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -22924,6 +22924,76 @@
         </is>
       </c>
       <c r="P335" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>$5k–$12k</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Hawk-Eye Innovations</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Rugby Systems Operator</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Manchester, UK</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr"/>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>start date: asap the role hawk</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>A freelance, weekend-only match-day AV/hardware operator role in Manchester, UK at £14/hour is off-profile in role type, location/work authorization, employment type, start timing, and comp for a US-based backend/distributed-systems new grad targeting May 2027 full-time at ~$130k.</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>Computed from the posting's own stated pay rather than company tier: £14/hr (holiday-inclusive) x ~8 hrs per match-day x ~15-25 Sale Sharks home fixtures across a Sept-June season, converted at roughly 1.27 USD/GBP. Casual/freelance hourly engagement with no base salary, bonus, or equity, so this is not a true new-grad TC comparable; band is wide to cover uncertainty in fixture count and any additional event work.</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>scored</t>
+        </is>
+      </c>
+      <c r="M336" s="3" t="inlineStr">
+        <is>
+          <t>Apply ↗</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr"/>
+      <c r="O336" s="3" t="inlineStr">
+        <is>
+          <t>levels.fyi ↗</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
@@ -23278,355 +23348,358 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M160" r:id="rId345"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O160" r:id="rId346"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M161" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M162" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M163" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M164" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O164" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M165" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O165" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M166" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O166" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M167" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M168" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M169" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O169" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O170" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M173" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M174" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M175" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M176" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M177" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O177" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M178" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M184" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O184" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M185" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M186" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O186" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M187" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O187" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M189" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O189" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O190" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M191" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M192" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M193" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O193" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M194" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O194" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M195" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O199" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O200" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O201" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O202" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M205" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O205" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M206" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M207" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O207" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M208" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M209" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M210" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M211" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O211" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M212" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M213" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M214" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M215" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O215" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M216" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M217" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M218" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M219" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M220" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M221" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M222" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M223" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O223" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M224" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M225" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M226" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M227" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M228" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M229" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M230" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M231" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M232" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O232" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M233" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O233" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M234" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O234" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M235" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M236" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M237" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O237" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M238" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O238" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M239" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O239" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M240" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M241" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O241" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M242" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O242" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M243" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O243" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M244" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M245" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O245" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M246" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O246" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M247" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M248" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O248" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M249" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M250" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M251" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M252" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M253" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M254" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M255" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O255" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M256" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O256" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M257" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O257" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M258" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M259" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O259" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M260" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M261" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O261" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M262" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M263" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M264" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M265" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O265" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M266" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O266" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M267" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O267" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M268" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O268" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M269" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O269" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M270" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O270" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M271" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O271" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M272" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O272" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M273" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O273" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M274" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O274" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M275" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O275" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M276" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O276" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M277" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O277" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M278" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O278" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M279" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O279" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M280" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O280" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M281" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O281" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M282" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O282" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M283" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O283" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M284" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O284" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M285" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O285" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M286" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O286" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M287" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O287" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M288" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O288" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M289" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O289" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M290" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O290" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M291" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O291" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M292" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O292" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M293" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O293" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M294" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O294" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M295" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O295" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M296" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O296" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M297" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O297" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M298" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O298" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M299" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O299" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M300" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O300" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M301" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O301" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M302" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O302" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M303" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O303" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M304" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O304" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M305" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O305" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M306" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O306" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M307" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O307" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M308" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O308" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M309" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O309" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M310" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O310" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M311" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O311" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M312" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O312" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M313" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O313" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M314" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O314" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M315" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O315" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M316" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O316" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M317" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O317" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M318" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O318" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M319" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O319" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M320" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O320" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M321" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O321" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M322" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O322" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M323" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O323" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M324" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O324" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M325" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O325" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M326" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O326" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M327" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O327" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M328" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O328" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M329" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O329" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M330" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O330" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M331" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O331" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M332" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O332" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M333" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O333" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M334" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O334" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M335" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O335" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N161" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M162" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M163" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M164" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O164" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M165" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O165" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M166" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O166" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M167" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M168" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M169" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O169" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O170" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M173" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M174" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M175" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M176" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M177" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O177" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M178" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M184" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O184" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M185" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M186" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O186" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M187" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O187" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M189" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O189" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O190" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M191" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M192" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M193" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O193" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M194" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O194" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M195" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O199" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O200" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O201" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O202" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M205" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O205" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M206" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M207" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O207" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M208" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M209" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M210" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M211" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O211" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M212" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M213" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M214" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M215" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O215" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M216" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M217" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M218" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M219" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M220" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M221" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M222" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M223" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O223" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M224" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M225" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M226" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M227" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M228" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M229" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M230" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M231" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M232" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O232" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M233" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O233" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M234" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O234" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M235" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M236" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M237" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O237" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M238" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O238" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M239" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O239" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M240" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M241" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O241" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M242" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O242" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M243" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O243" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M244" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M245" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O245" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M246" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O246" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M247" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M248" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O248" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M249" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M250" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M251" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M252" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M253" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M254" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M255" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O255" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M256" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O256" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M257" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O257" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M258" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M259" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O259" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M260" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M261" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O261" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M262" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M263" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M264" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M265" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O265" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M266" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O266" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M267" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O267" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M268" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O268" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M269" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O269" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M270" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O270" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M271" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O271" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M272" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O272" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M273" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O273" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M274" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O274" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M275" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O275" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M276" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O276" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M277" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O277" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M278" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O278" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M279" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O279" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M280" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O280" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M281" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O281" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M282" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O282" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M283" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O283" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M284" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O284" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M285" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O285" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M286" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O286" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M287" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O287" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M288" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O288" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M289" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O289" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M290" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O290" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M291" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O291" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M292" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O292" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M293" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O293" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M294" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O294" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M295" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O295" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M296" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O296" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M297" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O297" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M298" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O298" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M299" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O299" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M300" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O300" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M301" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O301" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M302" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O302" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M303" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O303" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M304" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O304" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M305" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O305" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M306" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O306" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M307" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O307" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M308" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O308" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M309" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O309" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M310" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O310" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M311" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O311" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M312" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O312" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M313" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O313" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M314" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O314" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M315" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O315" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M316" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O316" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M317" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O317" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M318" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O318" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M319" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O319" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M320" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O320" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M321" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O321" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M322" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O322" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M323" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O323" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M324" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O324" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M325" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O325" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M326" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O326" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M327" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O327" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M328" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O328" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M329" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O329" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M330" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O330" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M331" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O331" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M332" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O332" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M333" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O333" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M334" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O334" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M335" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O335" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M336" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O336" r:id="rId699"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/tailored_resumes.xlsx
+++ b/output/tailored_resumes.xlsx
@@ -2721,7 +2721,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2729,7 +2729,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Composio_Forward_Deployed_Engineer_New_Grad_55c35f.pdf</t>
+        </is>
+      </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -4497,7 +4501,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -4505,7 +4509,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>LiteLLM_Forward_Deployed_Engineer_New_Grad_609cc8.pdf</t>
+        </is>
+      </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -5573,7 +5581,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
@@ -5581,7 +5589,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
+          <t>Applied_Intuition_Software_Integration_Engineer_Ne_72fe15.pdf</t>
+        </is>
+      </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -23075,631 +23087,634 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N79" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N83" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O98" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N100" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N106" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M108" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M109" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N109" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M110" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N110" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M113" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M114" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M115" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M116" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M117" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M118" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M119" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M123" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M124" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M125" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M126" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M127" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M128" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M129" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M137" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M138" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M139" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M140" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M143" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M144" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M145" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M147" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M148" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M149" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O149" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M150" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M151" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M152" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M153" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M154" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M155" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M156" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M157" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M158" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M159" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M160" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O160" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M161" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N161" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M162" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M163" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M164" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O164" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M165" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O165" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M166" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O166" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M167" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M168" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M169" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O169" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O170" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M173" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M174" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M175" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M176" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M177" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O177" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M178" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M184" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O184" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M185" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M186" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O186" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M187" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O187" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M189" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O189" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O190" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M191" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M192" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M193" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O193" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M194" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O194" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M195" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O199" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O200" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O201" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O202" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M205" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O205" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M206" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M207" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O207" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M208" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M209" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M210" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M211" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O211" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M212" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M213" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M214" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M215" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O215" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M216" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M217" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M218" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M219" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M220" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M221" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M222" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M223" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O223" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M224" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M225" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M226" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M227" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M228" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M229" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M230" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M231" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M232" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O232" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M233" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O233" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M234" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O234" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M235" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M236" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M237" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O237" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M238" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O238" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M239" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O239" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M240" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M241" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O241" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M242" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O242" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M243" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O243" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M244" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M245" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O245" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M246" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O246" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M247" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M248" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O248" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M249" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M250" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M251" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M252" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M253" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M254" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M255" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O255" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M256" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O256" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M257" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O257" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M258" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M259" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O259" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M260" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M261" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O261" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M262" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M263" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M264" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M265" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O265" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M266" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O266" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M267" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O267" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M268" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O268" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M269" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O269" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M270" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O270" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M271" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O271" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M272" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O272" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M273" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O273" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M274" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O274" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M275" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O275" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M276" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O276" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M277" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O277" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M278" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O278" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M279" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O279" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M280" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O280" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M281" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O281" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M282" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O282" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M283" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O283" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M284" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O284" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M285" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O285" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M286" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O286" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M287" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O287" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M288" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O288" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M289" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O289" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M290" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O290" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M291" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O291" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M292" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O292" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M293" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O293" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M294" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O294" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M295" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O295" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M296" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O296" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M297" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O297" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M298" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O298" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M299" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O299" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M300" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O300" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M301" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O301" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M302" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O302" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M303" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O303" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M304" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O304" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M305" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O305" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M306" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O306" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M307" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O307" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M308" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O308" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M309" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O309" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M310" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O310" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M311" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O311" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M312" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O312" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M313" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O313" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M314" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O314" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M315" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O315" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M316" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O316" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M317" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O317" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M318" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O318" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M319" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O319" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M320" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O320" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M321" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O321" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M322" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O322" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M323" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O323" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M324" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O324" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M325" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O325" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M326" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O326" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M327" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O327" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M328" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O328" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M329" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O329" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M330" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O330" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M331" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O331" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M332" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O332" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M333" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O333" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M334" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O334" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M335" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O335" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M336" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O336" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N75" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N79" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N83" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O98" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N100" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N106" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M108" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M109" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N109" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M110" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N110" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M113" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M114" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M115" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M116" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M117" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M118" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M119" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M123" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M124" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M125" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M126" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M127" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M128" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M129" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M137" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M138" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M139" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M140" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M143" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M144" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M145" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M147" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M148" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M149" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O149" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M150" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M151" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M152" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M153" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M154" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M155" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M156" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M157" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M158" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M159" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M160" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O160" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M161" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N161" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M162" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M163" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M164" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O164" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M165" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O165" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M166" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O166" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M167" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M168" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M169" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O169" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O170" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M173" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M174" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M175" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M176" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M177" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O177" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M178" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M184" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O184" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M185" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M186" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O186" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M187" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O187" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M189" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O189" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O190" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M191" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M192" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M193" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O193" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M194" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O194" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M195" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O199" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O200" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O201" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O202" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M205" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O205" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M206" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M207" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O207" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M208" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M209" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M210" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M211" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O211" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M212" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M213" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M214" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M215" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O215" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M216" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M217" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M218" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M219" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M220" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M221" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M222" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M223" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O223" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M224" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M225" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M226" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M227" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M228" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M229" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M230" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M231" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M232" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O232" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M233" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O233" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M234" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O234" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M235" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M236" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M237" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O237" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M238" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O238" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M239" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O239" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M240" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M241" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O241" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M242" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O242" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M243" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O243" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M244" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M245" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O245" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M246" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O246" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M247" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M248" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O248" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M249" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M250" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M251" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M252" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M253" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M254" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M255" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O255" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M256" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O256" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M257" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O257" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M258" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M259" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O259" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M260" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M261" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O261" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M262" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M263" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M264" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M265" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O265" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M266" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O266" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M267" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O267" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M268" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O268" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M269" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O269" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M270" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O270" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M271" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O271" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M272" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O272" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M273" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O273" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M274" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O274" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M275" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O275" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M276" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O276" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M277" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O277" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M278" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O278" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M279" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O279" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M280" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O280" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M281" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O281" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M282" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O282" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M283" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O283" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M284" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O284" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M285" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O285" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M286" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O286" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M287" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O287" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M288" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O288" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M289" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O289" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M290" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O290" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M291" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O291" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M292" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O292" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M293" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O293" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M294" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O294" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M295" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O295" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M296" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O296" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M297" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O297" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M298" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O298" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M299" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O299" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M300" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O300" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M301" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O301" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M302" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O302" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M303" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O303" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M304" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O304" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M305" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O305" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M306" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O306" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M307" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O307" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M308" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O308" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M309" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O309" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M310" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O310" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M311" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O311" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M312" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O312" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M313" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O313" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M314" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O314" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M315" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O315" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M316" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O316" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M317" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O317" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M318" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O318" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M319" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O319" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M320" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O320" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M321" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O321" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M322" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O322" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M323" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O323" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M324" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O324" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M325" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O325" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M326" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O326" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M327" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O327" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M328" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O328" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M329" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O329" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M330" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O330" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M331" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O331" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M332" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O332" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M333" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O333" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M334" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O334" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M335" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O335" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M336" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O336" r:id="rId702"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/tailored_resumes.xlsx
+++ b/output/tailored_resumes.xlsx
@@ -8192,39 +8192,43 @@
         <v>114</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>$150k–$210k</t>
+          <t>$250k–$420k</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2027 Internships - Software Engineering</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
+          <t>Data Knowledge System Research Scientist Graduate - Data Platform-Global Live</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Excellent technical and company-tier alignment (systems, CUDA/GPU, AI infrastructure), but this is a 2027 internship requisition rather than a full-time new-grad role, and a Summer 2027 internship falls after the candidate's May 2027 graduation and target full-time start.</t>
+          <t>Technical content is an excellent match (RAG, agentic systems, vector DBs, knowledge/data platform, distributed systems, Python/Java), but the minimum qualification is a completed or near-complete PhD, which hard-gates a May 2027 bachelor's-level new grad.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Band reflects NVIDIA full-time new-grad SWE TC (roughly $130-150k base + ~$25-50k/yr RSU + 10-15% bonus), which has run high given stock appreciation; the actual posting is an internship (~$45-60/hr plus housing/relocation, i.e. ~$25-35k for a summer), so the full-time figure is the comparable-role estimate rather than what this req pays. Estimate only.</t>
+          <t>Posting states base $218,400-$480,000 for San Jose, which reflects PhD research-scientist banding rather than a BS/MS new-grad band; adding typical TikTok bonus/RSU on a mid-range base yields roughly $250k-$420k TC. This is an estimate, and it is not the band this candidate would be hired into — TikTok's comparable BS/MS new-grad SWE roles are closer to $145k-$200k TC.</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8239,7 +8243,7 @@
       </c>
       <c r="N115" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA_2027_Internships_Software_Engineering_4d8ba5.pdf</t>
+          <t>TikTok_Data_Knowledge_System_Research_Scientist_Gr_e0c0d2.pdf</t>
         </is>
       </c>
       <c r="O115" s="3" t="inlineStr">
@@ -8249,7 +8253,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -8262,17 +8266,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>$250k–$420k</t>
+          <t>$300k–$550k</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>ByteDance</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Data Knowledge System Research Scientist Graduate - Data Platform-Global Live</t>
+          <t>Research Scientist Graduate - Seed AI Foundation Model Infrastructure - PhD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -8284,12 +8288,12 @@
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Technical content is an excellent match (RAG, agentic systems, vector DBs, knowledge/data platform, distributed systems, Python/Java), but the minimum qualification is a completed or near-complete PhD, which hard-gates a May 2027 bachelor's-level new grad.</t>
+          <t>Domain is an excellent match (distributed training infra, ML systems, C++/Python, large-scale reliability), but the posting hard-requires a completed/near-complete PhD for a Research Scientist track, which disqualifies a May 2027 non-PhD new grad — the parallel ByteDance SWE Graduate (Infrastructure/AML) 2027 req is the correct target.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Posting states base $218,400-$480,000 for San Jose, which reflects PhD research-scientist banding rather than a BS/MS new-grad band; adding typical TikTok bonus/RSU on a mid-range base yields roughly $250k-$420k TC. This is an estimate, and it is not the band this candidate would be hired into — TikTok's comparable BS/MS new-grad SWE roles are closer to $145k-$200k TC.</t>
+          <t>Posted base range for this PhD Research Scientist role is $254,400-$480,000 plus RSUs and discretionary bonus, implying roughly $300k-$550k TC at that level. This is not the band Nate would see: ByteDance BS/MS new-grad SWE TC is approximately $180k-$240k (base ~$145-175k plus RSUs and sign-on), which still clears the ~$130k anchor.</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -8299,7 +8303,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>tailored</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M116" s="3" t="inlineStr">
@@ -8307,11 +8311,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N116" s="3" t="inlineStr">
-        <is>
-          <t>TikTok_Data_Knowledge_System_Research_Scientist_Gr_e0c0d2.pdf</t>
-        </is>
-      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="O116" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8328,38 +8328,38 @@
         <v>116</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>$300k–$550k</t>
+          <t>$110k–$170k</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>Normal Computing</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Research Scientist Graduate - Seed AI Foundation Model Infrastructure - PhD</t>
+          <t>AI Research Resident</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Palo Alto, CA, London, UK, NYC</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Domain is an excellent match (distributed training infra, ML systems, C++/Python, large-scale reliability), but the posting hard-requires a completed/near-complete PhD for a Research Scientist track, which disqualifies a May 2027 non-PhD new grad — the parallel ByteDance SWE Graduate (Infrastructure/AML) 2027 req is the correct target.</t>
+          <t>Genuine overlap on agentic LLMs, tool-use, and turning research into working code, but this is a fixed-term research residency aimed at MS/PhD candidates with a research/publication track record and deep PyTorch/RL depth — it neither matches his full-time new-grad backend/distributed-systems target nor leverages his Rust/systems/cloud-infra core.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Posted base range for this PhD Research Scientist role is $254,400-$480,000 plus RSUs and discretionary bonus, implying roughly $300k-$550k TC at that level. This is not the band Nate would see: ByteDance BS/MS new-grad SWE TC is approximately $180k-$240k (base ~$145-175k plus RSUs and sign-on), which still clears the ~$130k anchor.</t>
+          <t>Normal Computing is a well-funded applied-AI/semiconductor startup with NYC/SF/London/Palo Alto presence, so base pay tracks the frontier-AI-startup band; however, research residencies are typically fixed-term, stipend-style roles paying at or below full-time L3 research comp, with equity that may not meaningfully vest over a short program. No public levels data exists for this specific residency, so the band is deliberately wide and low-confidence: Palo Alto/NYC would sit near the top, London materially lower. Posting does not state residency duration, which adds further uncertainty to annualized TC.</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -8385,7 +8385,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -8394,38 +8394,38 @@
         <v>117</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>$110k–$170k</t>
+          <t>$88k–$125k</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Normal Computing</t>
+          <t>Chamberlain Group</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AI Research Resident</t>
+          <t>Software Engineer 1 - AI</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, London, UK, NYC</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Genuine overlap on agentic LLMs, tool-use, and turning research into working code, but this is a fixed-term research residency aimed at MS/PhD candidates with a research/publication track record and deep PyTorch/RL depth — it neither matches his full-time new-grad backend/distributed-systems target nor leverages his Rust/systems/cloud-infra core.</t>
+          <t>Genuinely relevant AI/LLM/RAG application work that matches the candidate's agentic-AI strengths, but it's integration/prototyping rather than backend or distributed-systems depth, the posted base range caps at $118.6k (below the ~130k anchor), and it appears to be an immediate-start req rather than a May-2027 new-grad pipeline role.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Normal Computing is a well-funded applied-AI/semiconductor startup with NYC/SF/London/Palo Alto presence, so base pay tracks the frontier-AI-startup band; however, research residencies are typically fixed-term, stipend-style roles paying at or below full-time L3 research comp, with equity that may not meaningfully vest over a short program. No public levels data exists for this specific residency, so the band is deliberately wide and low-confidence: Palo Alto/NYC would sit near the top, London materially lower. Posting does not state residency duration, which adds further uncertainty to annualized TC.</t>
+          <t>Posting states base pay $69,495-$118,619.50 plus a short-term incentive plan; a strong CS new grad would likely land $85k-$115k base with a ~5-10% STI. Chamberlain Group is a Blackstone-owned IoT/access-hardware company, not a tech-tier compensator, and no equity component is mentioned, so realistic TC lands modestly above base and below the candidate's $130k target.</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8459,44 +8459,44 @@
       <c r="A119" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="5" t="n">
-        <v>48</v>
+      <c r="B119" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>$88k–$125k</t>
+          <t>$85k–$110k</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Chamberlain Group</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Software Engineer 1 - AI</t>
+          <t>Software Engineering</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Plantation, FL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Genuinely relevant AI/LLM/RAG application work that matches the candidate's agentic-AI strengths, but it's integration/prototyping rather than backend or distributed-systems depth, the posted base range caps at $118.6k (below the ~130k anchor), and it appears to be an immediate-start req rather than a May-2027 new-grad pipeline role.</t>
+          <t>Generic "Software Engineering" posting with no description to match against — Motorola Solutions does real backend/cloud work for public-safety systems so the skills likely transfer, but the Plantation, FL location and a comp tier that sits below the candidate's ~130k anchor pull this to a middling fit.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Posting states base pay $69,495-$118,619.50 plus a short-term incentive plan; a strong CS new grad would likely land $85k-$115k base with a ~5-10% STI. Chamberlain Group is a Blackstone-owned IoT/access-hardware company, not a tech-tier compensator, and no equity component is mentioned, so realistic TC lands modestly above base and below the candidate's $130k target.</t>
+          <t>Estimate, not fact — and a wide-ish band because the posting has no level, team, or description. Based on general knowledge of Motorola Solutions as a mid-tier non-FAANG hardware/公共-safety company: new-grad base typically ~$78-95k with a small bonus, and South Florida (Plantation) carries no HCOL adjustment. Likely lands below the candidate's ~120k floor.</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>metadata-only</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -8525,49 +8525,49 @@
       <c r="A120" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="4" t="n">
-        <v>50</v>
+      <c r="B120" s="5" t="n">
+        <v>32</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>$85k–$110k</t>
+          <t>$160k–$230k</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Software Engineering</t>
+          <t>Software Engineer - Early Career</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Plantation, FL</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Generic "Software Engineering" posting with no description to match against — Motorola Solutions does real backend/cloud work for public-safety systems so the skills likely transfer, but the Plantation, FL location and a comp tier that sits below the candidate's ~130k anchor pull this to a middling fit.</t>
+          <t>Comp, tier, and NYC location are excellent fits, but the posting hard-gates on a degree completed between December 2024 and September 2026 while the candidate graduates May 2027, making him ineligible for this cohort; the role is also full-stack/web-leaning rather than backend/distributed-systems focused.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Estimate, not fact — and a wide-ish band because the posting has no level, team, or description. Based on general knowledge of Motorola Solutions as a mid-tier non-FAANG hardware/公共-safety company: new-grad base typically ~$78-95k with a small bonus, and South Florida (Plantation) carries no HCOL adjustment. Likely lands below the candidate's ~120k floor.</t>
+          <t>Posted NYC base range is $138,400-$198,000; a new grad would land near the low end (~$138-155k base). Uniswap Labs is a well-funded crypto/DeFi employer paying at or above top-tier tech, and the posting explicitly lists token compensation plus benefits on top of base. The band is intentionally wide on the upper end because token grant sizing and valuation are undisclosed and volatile. Estimate, not fact.</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>metadata-only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M120" s="3" t="inlineStr">
@@ -8575,7 +8575,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr"/>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
+          <t>Uniswap_Software_Engineer_Early_Career_5a340c.pdf</t>
+        </is>
+      </c>
       <c r="O120" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -8583,7 +8587,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -8592,38 +8596,38 @@
         <v>120</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>$160k–$230k</t>
+          <t>$300k–$550k</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>ByteDance</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Software Engineer - Early Career</t>
+          <t>Research Engineer Graduate - Seed Infra</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Comp, tier, and NYC location are excellent fits, but the posting hard-gates on a degree completed between December 2024 and September 2026 while the candidate graduates May 2027, making him ineligible for this cohort; the role is also full-stack/web-leaning rather than backend/distributed-systems focused.</t>
+          <t>The work itself (agent runtimes, sandboxed code execution, K8s/distributed orchestration, LLM infra) maps closely to his strengths, but the role hard-requires a completed PhD and a 2026 onboarding date, both of which he cannot meet as a May 2027 BS/MS grad.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Posted NYC base range is $138,400-$198,000; a new grad would land near the low end (~$138-155k base). Uniswap Labs is a well-funded crypto/DeFi employer paying at or above top-tier tech, and the posting explicitly lists token compensation plus benefits on top of base. The band is intentionally wide on the upper end because token grant sizing and valuation are undisclosed and volatile. Estimate, not fact.</t>
+          <t>The posting lists base $241,680–$456,000 plus RSUs and bonus, so total package lands roughly $300k–$550k+. Note this is PhD-level research-engineer comp, not a normal new-grad band — ByteDance standard US new-grad SWE TC is more like $180k–$230k, which is the number relevant to this candidate's actual eligibility.</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -8633,7 +8637,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>tailored</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="M121" s="3" t="inlineStr">
@@ -8641,11 +8645,7 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N121" s="3" t="inlineStr">
-        <is>
-          <t>Uniswap_Software_Engineer_Early_Career_5a340c.pdf</t>
-        </is>
-      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="O121" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>$300k–$550k</t>
+          <t>$230k–$340k</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Research Engineer Graduate - Seed Infra</t>
+          <t>Machine Learning Engineer Graduate - E-Commerce Risk Control</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -8688,12 +8688,12 @@
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
-          <t>The work itself (agent runtimes, sandboxed code execution, K8s/distributed orchestration, LLM infra) maps closely to his strengths, but the role hard-requires a completed PhD and a 2026 onboarding date, both of which he cannot meet as a May 2027 BS/MS grad.</t>
+          <t>Explicit PhD-only minimum qualification disqualifies a May 2027 BS new grad, and the role's core is research-grade ML (ensemble trees, RL, graph theory, transfer learning, Hive/Hadoop) rather than his backend/distributed-systems/AI-infra strengths — only the multi-agent/ReAct/tool-use architecture overlaps with his agentic-AI experience.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>The posting lists base $241,680–$456,000 plus RSUs and bonus, so total package lands roughly $300k–$550k+. Note this is PhD-level research-engineer comp, not a normal new-grad band — ByteDance standard US new-grad SWE TC is more like $180k–$230k, which is the number relevant to this candidate's actual eligibility.</t>
+          <t>Posting discloses Seattle base of $153,900–$300,960; adding ByteDance's typical RSU grant and discretionary bonus puts PhD-level new-grad ML TC roughly $230k–$340k. Note this is PhD-track compensation, not the BS new-grad band the candidate would actually be hired into (~$150–200k for a comparable non-PhD ByteDance SWE new grad).</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -8728,38 +8728,42 @@
         <v>122</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>$230k–$340k</t>
+          <t>$140k–$180k</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>General Motors</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate - E-Commerce Risk Control</t>
+          <t>Machine Learning Engineer - AI Inference Solutions</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Sunnyvale, CA</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>spring 2026</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Explicit PhD-only minimum qualification disqualifies a May 2027 BS new grad, and the role's core is research-grade ML (ensemble trees, RL, graph theory, transfer learning, Hive/Hadoop) rather than his backend/distributed-systems/AI-infra strengths — only the multi-agent/ReAct/tool-use architecture overlaps with his agentic-AI experience.</t>
+          <t>ML-inference/platform work is adjacent to his AI-infra and systems strengths, but the posting requires a degree completed by Spring/June 2026 (a year before his May 2027 grad) and leans on CUDA/ML-compiler/quantization depth he doesn't have.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Posting discloses Seattle base of $153,900–$300,960; adding ByteDance's typical RSU grant and discretionary bonus puts PhD-level new-grad ML TC roughly $230k–$340k. Note this is PhD-track compensation, not the BS new-grad band the candidate would actually be hired into (~$150–200k for a comparable non-PhD ByteDance SWE new grad).</t>
+          <t>GM's AV group in Sunnyvale pays Bay Area market (largely ex-Cruise footprint) rather than legacy-automotive rates; new-grad base ~$125-150k plus bonus and RSUs. Estimate, not fact — GM AV new-grad data points are thinner than FAANG.</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8785,7 +8789,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8794,42 +8798,34 @@
         <v>123</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>$140k–$180k</t>
+          <t>$170k–$235k</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>General Motors</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - AI Inference Solutions</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA</t>
-        </is>
-      </c>
+          <t>2027 Internships - Software Engineering</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>spring 2026</t>
-        </is>
-      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>ML-inference/platform work is adjacent to his AI-infra and systems strengths, but the posting requires a degree completed by Spring/June 2026 (a year before his May 2027 grad) and leans on CUDA/ML-compiler/quantization depth he doesn't have.</t>
+          <t>Technical content is an excellent match (cloud storage infra, distributed systems, Kubernetes/microservices, MLOps/GPU infra), but it is a Summer 2027 12-week internship requiring active enrollment for the full duration — incompatible with a May 2027 graduation and a full-time new-grad target start.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>GM's AV group in Sunnyvale pays Bay Area market (largely ex-Cruise footprint) rather than legacy-automotive rates; new-grad base ~$125-150k plus bonus and RSUs. Estimate, not fact — GM AV new-grad data points are thinner than FAANG.</t>
+          <t>Estimate for NVIDIA full-time new-grad SWE (not this internship): base ~$130-155k + RSUs ~$40-80k/yr amortized (elevated by recent stock appreciation) + annual bonus; NVIDIA sits in the top compensation tier for entry-level SWE. The internship itself would pay hourly (~$45-65/hr, ~$25-35k over 12 weeks). Estimate only, not fact.</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8839,7 +8835,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M124" s="3" t="inlineStr">
@@ -8847,7 +8843,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr"/>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
+          <t>NVIDIA_2027_Internships_Software_Engineering_4d8ba5.pdf</t>
+        </is>
+      </c>
       <c r="O124" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -8855,7 +8855,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -33790,24 +33790,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N115" r:id="rId253"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M116" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N116" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M117" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M118" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M119" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M117" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M118" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M119" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N120" r:id="rId264"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId265"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N121" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M123" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M124" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M123" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M124" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N124" r:id="rId273"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId274"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M125" r:id="rId275"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId276"/>

--- a/output/tailored_resumes.xlsx
+++ b/output/tailored_resumes.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -805,7 +805,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Point72_Software_Developer_Developers_a00cd4.pdf</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -33543,1019 +33547,1020 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N80" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N82" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N87" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O98" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N100" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M108" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M109" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M110" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N111" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M113" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M114" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M115" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N115" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M116" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M117" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M118" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M119" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N120" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M123" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M124" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N124" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M125" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M126" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M127" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M128" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M129" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M137" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M138" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M139" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M140" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M143" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M144" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N144" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M145" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M147" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M148" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M149" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O149" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M150" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M151" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N151" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M152" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M153" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M154" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N154" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M155" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M156" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N156" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M157" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M158" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M159" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M160" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O160" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M161" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M162" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M163" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M164" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O164" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M165" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O165" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M166" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O166" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M167" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M168" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M169" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O169" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O170" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M173" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M174" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M175" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M176" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M177" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O177" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M178" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M184" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O184" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M185" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M186" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O186" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M187" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O187" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M189" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O189" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O190" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M191" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M192" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M193" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O193" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M194" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O194" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M195" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O199" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O200" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O201" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O202" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M205" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O205" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M206" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M207" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O207" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M208" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M209" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M210" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M211" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O211" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M212" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M213" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M214" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M215" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O215" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M216" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M217" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M218" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M219" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M220" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M221" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M222" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M223" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O223" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M224" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M225" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M226" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M227" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M228" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M229" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M230" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M231" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M232" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O232" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M233" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N233" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O233" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M234" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O234" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M235" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M236" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M237" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O237" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M238" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O238" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M239" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O239" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M240" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M241" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O241" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M242" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O242" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M243" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O243" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M244" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M245" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O245" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M246" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O246" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M247" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M248" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O248" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M249" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M250" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M251" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M252" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M253" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M254" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M255" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O255" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M256" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O256" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M257" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O257" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M258" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M259" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O259" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M260" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M261" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O261" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M262" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M263" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M264" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M265" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O265" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M266" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O266" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M267" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O267" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M268" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O268" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M269" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O269" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M270" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O270" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M271" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O271" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M272" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O272" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M273" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O273" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M274" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O274" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M275" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O275" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M276" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O276" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M277" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O277" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M278" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O278" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M279" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O279" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M280" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O280" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M281" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O281" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M282" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O282" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M283" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O283" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M284" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O284" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M285" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O285" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M286" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O286" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M287" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O287" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M288" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O288" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M289" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O289" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M290" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O290" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M291" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O291" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M292" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O292" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M293" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O293" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M294" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O294" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M295" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O295" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M296" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O296" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M297" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O297" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M298" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O298" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M299" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O299" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M300" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O300" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M301" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O301" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M302" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O302" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M303" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O303" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M304" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O304" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M305" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O305" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M306" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O306" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M307" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O307" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M308" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O308" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M309" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O309" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M310" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O310" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M311" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O311" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M312" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O312" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M313" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O313" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M314" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O314" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M315" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O315" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M316" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O316" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M317" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O317" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M318" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O318" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M319" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O319" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M320" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O320" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M321" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O321" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M322" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O322" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M323" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O323" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M324" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O324" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M325" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O325" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M326" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O326" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M327" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O327" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M328" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O328" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M329" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O329" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M330" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O330" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M331" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O331" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M332" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O332" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M333" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O333" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M334" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O334" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M335" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O335" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M336" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O336" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M337" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O337" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M338" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O338" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M339" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O339" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M340" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O340" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M341" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O341" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M342" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O342" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M343" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O343" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M344" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O344" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M345" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O345" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M346" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O346" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M347" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O347" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M348" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O348" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M349" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O349" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M350" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O350" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M351" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O351" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M352" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O352" r:id="rId735"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M353" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O353" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M354" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O354" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M355" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O355" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M356" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O356" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M357" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O357" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M358" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O358" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M359" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O359" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M360" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O360" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M361" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O361" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M362" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O362" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M363" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O363" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M364" r:id="rId758"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O364" r:id="rId759"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M365" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O365" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M366" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O366" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M367" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O367" r:id="rId765"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M368" r:id="rId766"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O368" r:id="rId767"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M369" r:id="rId768"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O369" r:id="rId769"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M370" r:id="rId770"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O370" r:id="rId771"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M371" r:id="rId772"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O371" r:id="rId773"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M372" r:id="rId774"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O372" r:id="rId775"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M373" r:id="rId776"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O373" r:id="rId777"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M374" r:id="rId778"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O374" r:id="rId779"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M375" r:id="rId780"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O375" r:id="rId781"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M376" r:id="rId782"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O376" r:id="rId783"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M377" r:id="rId784"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O377" r:id="rId785"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M378" r:id="rId786"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O378" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M379" r:id="rId788"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O379" r:id="rId789"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M380" r:id="rId790"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O380" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M381" r:id="rId792"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O381" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M382" r:id="rId794"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O382" r:id="rId795"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M383" r:id="rId796"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O383" r:id="rId797"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M384" r:id="rId798"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O384" r:id="rId799"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M385" r:id="rId800"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O385" r:id="rId801"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M386" r:id="rId802"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O386" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M387" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O387" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M388" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O388" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M389" r:id="rId808"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O389" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M390" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O390" r:id="rId811"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M391" r:id="rId812"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O391" r:id="rId813"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M392" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O392" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M393" r:id="rId816"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O393" r:id="rId817"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M394" r:id="rId818"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O394" r:id="rId819"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M395" r:id="rId820"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O395" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M396" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O396" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M397" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O397" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M398" r:id="rId826"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O398" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M399" r:id="rId828"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O399" r:id="rId829"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M400" r:id="rId830"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O400" r:id="rId831"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M401" r:id="rId832"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O401" r:id="rId833"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M402" r:id="rId834"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O402" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M403" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O403" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M404" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O404" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M405" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O405" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M406" r:id="rId842"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O406" r:id="rId843"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M407" r:id="rId844"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O407" r:id="rId845"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M408" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O408" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M409" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O409" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M410" r:id="rId850"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O410" r:id="rId851"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M411" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O411" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M412" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O412" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M413" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O413" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M414" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O414" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M415" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O415" r:id="rId861"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M416" r:id="rId862"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O416" r:id="rId863"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M417" r:id="rId864"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O417" r:id="rId865"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M418" r:id="rId866"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O418" r:id="rId867"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M419" r:id="rId868"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O419" r:id="rId869"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M420" r:id="rId870"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O420" r:id="rId871"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M421" r:id="rId872"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O421" r:id="rId873"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M422" r:id="rId874"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O422" r:id="rId875"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M423" r:id="rId876"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O423" r:id="rId877"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M424" r:id="rId878"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O424" r:id="rId879"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M425" r:id="rId880"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O425" r:id="rId881"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M426" r:id="rId882"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O426" r:id="rId883"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M427" r:id="rId884"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O427" r:id="rId885"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M428" r:id="rId886"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O428" r:id="rId887"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M429" r:id="rId888"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O429" r:id="rId889"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M430" r:id="rId890"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O430" r:id="rId891"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M431" r:id="rId892"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O431" r:id="rId893"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M432" r:id="rId894"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O432" r:id="rId895"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M433" r:id="rId896"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O433" r:id="rId897"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M434" r:id="rId898"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O434" r:id="rId899"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M435" r:id="rId900"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O435" r:id="rId901"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M436" r:id="rId902"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O436" r:id="rId903"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M437" r:id="rId904"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O437" r:id="rId905"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M438" r:id="rId906"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O438" r:id="rId907"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M439" r:id="rId908"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O439" r:id="rId909"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M440" r:id="rId910"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O440" r:id="rId911"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M441" r:id="rId912"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O441" r:id="rId913"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M442" r:id="rId914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O442" r:id="rId915"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M443" r:id="rId916"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O443" r:id="rId917"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M444" r:id="rId918"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O444" r:id="rId919"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M445" r:id="rId920"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O445" r:id="rId921"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M446" r:id="rId922"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O446" r:id="rId923"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M447" r:id="rId924"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O447" r:id="rId925"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M448" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O448" r:id="rId927"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M449" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O449" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M450" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O450" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M451" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O451" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M452" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O452" r:id="rId935"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M453" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O453" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M454" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O454" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M455" r:id="rId940"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O455" r:id="rId941"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M456" r:id="rId942"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O456" r:id="rId943"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M457" r:id="rId944"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O457" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M458" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O458" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M459" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O459" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M460" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O460" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M461" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O461" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M462" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O462" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M463" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O463" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M464" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O464" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M465" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O465" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M466" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O466" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M467" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O467" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M468" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O468" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M469" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O469" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M470" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O470" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M471" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O471" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M472" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O472" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M473" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O473" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M474" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O474" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M475" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O475" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M476" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O476" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M477" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O477" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M478" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O478" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M479" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O479" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M480" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O480" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M481" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O481" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M482" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O482" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M483" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O483" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M484" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O484" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M485" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O485" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M486" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O486" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M487" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O487" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M488" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O488" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M489" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O489" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M490" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O490" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M491" r:id="rId1012"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O491" r:id="rId1013"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M492" r:id="rId1014"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O492" r:id="rId1015"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M493" r:id="rId1016"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O493" r:id="rId1017"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M494" r:id="rId1018"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O494" r:id="rId1019"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M495" r:id="rId1020"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O495" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N80" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N82" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N87" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O98" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N100" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M108" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M109" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M110" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N111" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M113" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M114" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M115" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N115" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M116" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M117" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M118" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M119" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N120" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M123" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M124" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N124" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M125" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M126" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M127" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M128" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M129" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M137" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M138" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M139" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M140" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M143" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M144" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N144" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M145" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M147" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M148" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M149" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O149" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M150" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M151" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N151" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M152" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M153" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M154" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N154" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M155" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M156" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N156" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M157" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M158" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M159" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M160" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O160" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M161" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M162" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M163" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M164" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O164" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M165" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O165" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M166" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O166" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M167" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M168" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M169" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O169" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O170" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M173" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M174" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M175" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M176" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M177" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O177" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M178" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M184" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O184" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M185" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M186" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O186" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M187" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O187" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M189" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O189" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O190" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M191" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M192" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M193" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O193" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M194" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O194" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M195" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O199" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O200" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O201" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O202" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M205" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O205" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M206" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M207" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O207" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M208" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M209" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M210" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M211" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O211" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M212" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M213" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M214" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M215" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O215" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M216" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M217" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M218" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M219" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M220" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M221" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M222" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M223" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O223" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M224" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M225" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M226" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M227" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M228" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M229" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M230" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M231" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M232" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O232" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M233" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N233" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O233" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M234" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O234" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M235" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M236" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M237" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O237" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M238" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O238" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M239" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O239" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M240" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M241" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O241" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M242" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O242" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M243" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O243" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M244" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M245" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O245" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M246" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O246" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M247" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M248" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O248" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M249" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M250" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M251" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M252" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M253" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M254" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M255" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O255" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M256" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O256" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M257" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O257" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M258" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M259" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O259" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M260" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M261" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O261" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M262" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M263" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M264" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M265" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O265" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M266" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O266" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M267" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O267" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M268" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O268" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M269" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O269" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M270" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O270" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M271" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O271" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M272" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O272" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M273" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O273" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M274" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O274" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M275" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O275" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M276" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O276" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M277" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O277" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M278" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O278" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M279" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O279" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M280" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O280" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M281" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O281" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M282" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O282" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M283" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O283" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M284" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O284" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M285" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O285" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M286" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O286" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M287" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O287" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M288" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O288" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M289" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O289" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M290" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O290" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M291" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O291" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M292" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O292" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M293" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O293" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M294" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O294" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M295" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O295" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M296" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O296" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M297" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O297" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M298" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O298" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M299" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O299" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M300" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O300" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M301" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O301" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M302" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O302" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M303" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O303" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M304" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O304" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M305" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O305" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M306" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O306" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M307" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O307" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M308" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O308" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M309" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O309" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M310" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O310" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M311" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O311" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M312" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O312" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M313" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O313" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M314" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O314" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M315" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O315" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M316" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O316" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M317" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O317" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M318" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O318" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M319" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O319" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M320" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O320" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M321" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O321" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M322" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O322" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M323" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O323" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M324" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O324" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M325" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O325" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M326" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O326" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M327" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O327" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M328" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O328" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M329" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O329" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M330" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O330" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M331" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O331" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M332" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O332" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M333" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O333" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M334" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O334" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M335" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O335" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M336" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O336" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M337" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O337" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M338" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O338" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M339" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O339" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M340" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O340" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M341" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O341" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M342" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O342" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M343" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O343" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M344" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O344" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M345" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O345" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M346" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O346" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M347" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O347" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M348" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O348" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M349" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O349" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M350" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O350" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M351" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O351" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M352" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O352" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M353" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O353" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M354" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O354" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M355" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O355" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M356" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O356" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M357" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O357" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M358" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O358" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M359" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O359" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M360" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O360" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M361" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O361" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M362" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O362" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M363" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O363" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M364" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O364" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M365" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O365" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M366" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O366" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M367" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O367" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M368" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O368" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M369" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O369" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M370" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O370" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M371" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O371" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M372" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O372" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M373" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O373" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M374" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O374" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M375" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O375" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M376" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O376" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M377" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O377" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M378" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O378" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M379" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O379" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M380" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O380" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M381" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O381" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M382" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O382" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M383" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O383" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M384" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O384" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M385" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O385" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M386" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O386" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M387" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O387" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M388" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O388" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M389" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O389" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M390" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O390" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M391" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O391" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M392" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O392" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M393" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O393" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M394" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O394" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M395" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O395" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M396" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O396" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M397" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O397" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M398" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O398" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M399" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O399" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M400" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O400" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M401" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O401" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M402" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O402" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M403" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O403" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M404" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O404" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M405" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O405" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M406" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O406" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M407" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O407" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M408" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O408" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M409" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O409" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M410" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O410" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M411" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O411" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M412" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O412" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M413" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O413" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M414" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O414" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M415" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O415" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M416" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O416" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M417" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O417" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M418" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O418" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M419" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O419" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M420" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O420" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M421" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O421" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M422" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O422" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M423" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O423" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M424" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O424" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M425" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O425" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M426" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O426" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M427" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O427" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M428" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O428" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M429" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O429" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M430" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O430" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M431" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O431" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M432" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O432" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M433" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O433" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M434" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O434" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M435" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O435" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M436" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O436" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M437" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O437" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M438" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O438" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M439" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O439" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M440" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O440" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M441" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O441" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M442" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O442" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M443" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O443" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M444" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O444" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M445" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O445" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M446" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O446" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M447" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O447" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M448" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O448" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M449" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O449" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M450" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O450" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M451" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O451" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M452" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O452" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M453" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O453" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M454" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O454" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M455" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O455" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M456" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O456" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M457" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O457" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M458" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O458" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M459" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O459" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M460" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O460" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M461" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O461" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M462" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O462" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M463" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O463" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M464" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O464" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M465" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O465" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M466" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O466" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M467" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O467" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M468" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O468" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M469" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O469" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M470" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O470" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M471" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O471" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M472" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O472" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M473" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O473" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M474" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O474" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M475" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O475" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M476" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O476" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M477" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O477" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M478" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O478" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M479" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O479" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M480" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O480" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M481" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O481" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M482" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O482" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M483" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O483" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M484" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O484" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M485" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O485" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M486" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O486" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M487" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O487" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M488" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O488" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M489" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O489" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M490" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O490" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M491" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O491" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M492" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O492" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M493" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O493" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M494" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O494" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M495" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O495" r:id="rId1022"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/tailored_resumes.xlsx
+++ b/output/tailored_resumes.xlsx
@@ -2713,7 +2713,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2721,7 +2721,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Relativity_Space_AI_Software_Engineer_Terrestrial__95cec1.pdf</t>
+        </is>
+      </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -33612,955 +33616,956 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N80" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N82" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N87" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O98" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N100" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M108" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M109" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M110" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N111" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M113" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M114" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M115" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N115" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M116" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M117" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M118" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M119" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N120" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M123" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M124" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N124" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M125" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M126" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M127" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M128" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M129" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M137" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M138" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M139" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M140" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M143" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M144" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N144" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M145" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M147" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M148" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M149" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O149" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M150" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M151" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N151" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M152" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M153" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M154" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N154" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M155" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M156" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N156" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M157" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M158" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M159" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M160" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O160" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M161" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M162" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M163" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M164" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O164" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M165" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O165" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M166" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O166" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M167" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M168" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M169" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O169" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O170" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M173" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M174" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M175" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M176" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M177" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O177" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M178" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M184" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O184" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M185" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M186" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O186" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M187" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O187" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M189" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O189" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O190" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M191" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M192" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M193" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O193" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M194" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O194" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M195" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O199" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O200" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O201" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O202" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M205" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O205" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M206" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M207" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O207" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M208" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M209" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M210" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M211" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O211" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M212" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M213" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M214" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M215" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O215" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M216" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M217" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M218" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M219" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M220" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M221" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M222" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M223" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O223" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M224" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M225" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M226" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M227" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M228" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M229" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M230" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M231" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M232" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O232" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M233" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N233" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O233" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M234" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O234" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M235" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M236" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M237" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O237" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M238" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O238" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M239" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O239" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M240" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M241" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O241" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M242" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O242" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M243" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O243" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M244" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M245" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O245" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M246" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O246" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M247" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M248" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O248" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M249" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M250" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M251" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M252" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M253" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M254" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M255" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O255" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M256" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O256" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M257" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O257" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M258" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M259" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O259" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M260" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M261" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O261" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M262" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M263" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M264" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M265" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O265" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M266" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O266" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M267" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O267" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M268" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O268" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M269" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O269" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M270" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O270" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M271" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O271" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M272" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O272" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M273" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O273" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M274" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O274" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M275" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O275" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M276" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O276" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M277" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O277" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M278" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O278" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M279" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O279" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M280" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O280" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M281" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O281" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M282" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O282" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M283" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O283" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M284" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O284" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M285" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O285" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M286" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O286" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M287" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O287" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M288" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O288" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M289" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O289" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M290" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O290" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M291" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O291" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M292" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O292" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M293" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O293" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M294" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O294" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M295" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O295" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M296" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O296" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M297" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O297" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M298" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O298" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M299" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O299" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M300" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O300" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M301" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O301" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M302" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O302" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M303" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O303" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M304" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O304" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M305" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O305" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M306" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O306" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M307" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O307" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M308" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O308" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M309" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O309" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M310" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O310" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M311" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O311" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M312" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O312" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M313" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O313" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M314" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O314" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M315" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O315" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M316" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O316" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M317" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O317" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M318" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O318" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M319" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O319" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M320" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O320" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M321" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O321" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M322" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O322" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M323" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O323" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M324" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O324" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M325" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O325" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M326" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O326" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M327" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O327" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M328" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O328" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M329" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O329" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M330" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O330" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M331" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O331" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M332" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O332" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M333" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O333" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M334" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O334" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M335" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O335" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M336" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O336" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M337" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O337" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M338" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O338" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M339" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O339" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M340" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O340" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M341" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O341" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M342" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O342" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M343" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O343" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M344" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O344" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M345" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O345" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M346" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O346" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M347" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O347" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M348" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O348" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M349" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O349" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M350" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O350" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M351" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O351" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M352" r:id="rId735"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O352" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M353" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O353" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M354" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O354" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M355" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O355" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M356" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O356" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M357" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O357" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M358" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O358" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M359" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O359" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M360" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O360" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M361" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O361" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M362" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O362" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M363" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O363" r:id="rId758"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M364" r:id="rId759"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O364" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M365" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O365" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M366" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O366" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M367" r:id="rId765"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O367" r:id="rId766"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M368" r:id="rId767"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O368" r:id="rId768"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M369" r:id="rId769"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O369" r:id="rId770"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M370" r:id="rId771"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O370" r:id="rId772"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M371" r:id="rId773"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O371" r:id="rId774"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M372" r:id="rId775"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O372" r:id="rId776"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M373" r:id="rId777"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O373" r:id="rId778"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M374" r:id="rId779"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O374" r:id="rId780"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M375" r:id="rId781"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O375" r:id="rId782"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M376" r:id="rId783"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O376" r:id="rId784"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M377" r:id="rId785"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O377" r:id="rId786"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M378" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O378" r:id="rId788"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M379" r:id="rId789"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O379" r:id="rId790"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M380" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O380" r:id="rId792"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M381" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O381" r:id="rId794"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M382" r:id="rId795"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O382" r:id="rId796"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M383" r:id="rId797"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O383" r:id="rId798"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M384" r:id="rId799"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O384" r:id="rId800"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M385" r:id="rId801"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O385" r:id="rId802"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M386" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O386" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M387" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O387" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M388" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O388" r:id="rId808"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M389" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O389" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M390" r:id="rId811"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O390" r:id="rId812"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M391" r:id="rId813"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O391" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M392" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O392" r:id="rId816"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M393" r:id="rId817"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O393" r:id="rId818"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M394" r:id="rId819"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O394" r:id="rId820"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M395" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O395" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M396" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O396" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M397" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O397" r:id="rId826"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M398" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O398" r:id="rId828"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M399" r:id="rId829"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O399" r:id="rId830"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M400" r:id="rId831"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O400" r:id="rId832"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M401" r:id="rId833"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O401" r:id="rId834"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M402" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O402" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M403" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O403" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M404" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O404" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M405" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O405" r:id="rId842"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M406" r:id="rId843"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O406" r:id="rId844"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M407" r:id="rId845"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O407" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M408" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O408" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M409" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O409" r:id="rId850"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M410" r:id="rId851"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O410" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M411" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O411" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M412" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O412" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M413" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O413" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M414" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O414" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M415" r:id="rId861"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O415" r:id="rId862"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M416" r:id="rId863"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O416" r:id="rId864"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M417" r:id="rId865"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O417" r:id="rId866"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M418" r:id="rId867"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O418" r:id="rId868"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M419" r:id="rId869"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O419" r:id="rId870"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M420" r:id="rId871"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O420" r:id="rId872"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M421" r:id="rId873"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O421" r:id="rId874"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M422" r:id="rId875"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O422" r:id="rId876"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M423" r:id="rId877"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O423" r:id="rId878"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M424" r:id="rId879"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O424" r:id="rId880"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M425" r:id="rId881"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O425" r:id="rId882"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M426" r:id="rId883"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O426" r:id="rId884"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M427" r:id="rId885"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O427" r:id="rId886"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M428" r:id="rId887"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O428" r:id="rId888"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M429" r:id="rId889"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O429" r:id="rId890"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M430" r:id="rId891"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O430" r:id="rId892"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M431" r:id="rId893"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O431" r:id="rId894"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M432" r:id="rId895"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O432" r:id="rId896"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M433" r:id="rId897"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O433" r:id="rId898"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M434" r:id="rId899"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O434" r:id="rId900"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M435" r:id="rId901"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O435" r:id="rId902"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M436" r:id="rId903"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O436" r:id="rId904"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M437" r:id="rId905"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O437" r:id="rId906"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M438" r:id="rId907"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O438" r:id="rId908"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M439" r:id="rId909"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O439" r:id="rId910"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M440" r:id="rId911"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O440" r:id="rId912"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M441" r:id="rId913"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O441" r:id="rId914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M442" r:id="rId915"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O442" r:id="rId916"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M443" r:id="rId917"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O443" r:id="rId918"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M444" r:id="rId919"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O444" r:id="rId920"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M445" r:id="rId921"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O445" r:id="rId922"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M446" r:id="rId923"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O446" r:id="rId924"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M447" r:id="rId925"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O447" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M448" r:id="rId927"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O448" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M449" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O449" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M450" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O450" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M451" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O451" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M452" r:id="rId935"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O452" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M453" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O453" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M454" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O454" r:id="rId940"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M455" r:id="rId941"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O455" r:id="rId942"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M456" r:id="rId943"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O456" r:id="rId944"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M457" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O457" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M458" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O458" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M459" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O459" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M460" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O460" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M461" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O461" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M462" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O462" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M463" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O463" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M464" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O464" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M465" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O465" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M466" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O466" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M467" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O467" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M468" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O468" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M469" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O469" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M470" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O470" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M471" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O471" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M472" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O472" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M473" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O473" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M474" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O474" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M475" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O475" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M476" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O476" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M477" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O477" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M478" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O478" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M479" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O479" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M480" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O480" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M481" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O481" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M482" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O482" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M483" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O483" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M484" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O484" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M485" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O485" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M486" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O486" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M487" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O487" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M488" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O488" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M489" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O489" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M490" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O490" r:id="rId1012"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M491" r:id="rId1013"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O491" r:id="rId1014"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M492" r:id="rId1015"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O492" r:id="rId1016"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M493" r:id="rId1017"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O493" r:id="rId1018"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M494" r:id="rId1019"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O494" r:id="rId1020"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M495" r:id="rId1021"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O495" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N80" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N82" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N87" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O98" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N100" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M108" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M109" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M110" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N111" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M113" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M114" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M115" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N115" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M116" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M117" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M118" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M119" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N120" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M123" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M124" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N124" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M125" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M126" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M127" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M128" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M129" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M137" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M138" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M139" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M140" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M143" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M144" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N144" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M145" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M147" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M148" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M149" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O149" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M150" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M151" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N151" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M152" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M153" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M154" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N154" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M155" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M156" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N156" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M157" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M158" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M159" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M160" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O160" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M161" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M162" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M163" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M164" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O164" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M165" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O165" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M166" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O166" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M167" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M168" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M169" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O169" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O170" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M173" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M174" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M175" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M176" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M177" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O177" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M178" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M184" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O184" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M185" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M186" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O186" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M187" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O187" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M189" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O189" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O190" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M191" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M192" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M193" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O193" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M194" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O194" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M195" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O199" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O200" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O201" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O202" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M205" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O205" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M206" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M207" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O207" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M208" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M209" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M210" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M211" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O211" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M212" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M213" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M214" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M215" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O215" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M216" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M217" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M218" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M219" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M220" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M221" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M222" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M223" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O223" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M224" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M225" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M226" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M227" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M228" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M229" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M230" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M231" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M232" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O232" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M233" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N233" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O233" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M234" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O234" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M235" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M236" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M237" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O237" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M238" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O238" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M239" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O239" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M240" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M241" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O241" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M242" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O242" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M243" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O243" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M244" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M245" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O245" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M246" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O246" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M247" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M248" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O248" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M249" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M250" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M251" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M252" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M253" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M254" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M255" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O255" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M256" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O256" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M257" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O257" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M258" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M259" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O259" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M260" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M261" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O261" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M262" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M263" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M264" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M265" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O265" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M266" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O266" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M267" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O267" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M268" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O268" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M269" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O269" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M270" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O270" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M271" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O271" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M272" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O272" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M273" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O273" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M274" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O274" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M275" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O275" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M276" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O276" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M277" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O277" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M278" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O278" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M279" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O279" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M280" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O280" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M281" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O281" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M282" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O282" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M283" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O283" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M284" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O284" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M285" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O285" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M286" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O286" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M287" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O287" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M288" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O288" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M289" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O289" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M290" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O290" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M291" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O291" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M292" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O292" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M293" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O293" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M294" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O294" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M295" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O295" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M296" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O296" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M297" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O297" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M298" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O298" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M299" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O299" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M300" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O300" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M301" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O301" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M302" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O302" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M303" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O303" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M304" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O304" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M305" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O305" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M306" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O306" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M307" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O307" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M308" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O308" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M309" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O309" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M310" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O310" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M311" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O311" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M312" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O312" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M313" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O313" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M314" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O314" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M315" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O315" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M316" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O316" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M317" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O317" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M318" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O318" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M319" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O319" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M320" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O320" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M321" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O321" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M322" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O322" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M323" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O323" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M324" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O324" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M325" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O325" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M326" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O326" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M327" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O327" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M328" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O328" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M329" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O329" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M330" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O330" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M331" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O331" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M332" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O332" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M333" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O333" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M334" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O334" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M335" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O335" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M336" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O336" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M337" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O337" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M338" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O338" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M339" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O339" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M340" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O340" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M341" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O341" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M342" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O342" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M343" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O343" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M344" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O344" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M345" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O345" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M346" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O346" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M347" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O347" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M348" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O348" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M349" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O349" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M350" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O350" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M351" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O351" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M352" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O352" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M353" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O353" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M354" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O354" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M355" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O355" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M356" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O356" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M357" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O357" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M358" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O358" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M359" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O359" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M360" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O360" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M361" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O361" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M362" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O362" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M363" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O363" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M364" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O364" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M365" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O365" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M366" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O366" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M367" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O367" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M368" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O368" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M369" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O369" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M370" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O370" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M371" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O371" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M372" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O372" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M373" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O373" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M374" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O374" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M375" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O375" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M376" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O376" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M377" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O377" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M378" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O378" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M379" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O379" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M380" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O380" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M381" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O381" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M382" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O382" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M383" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O383" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M384" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O384" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M385" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O385" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M386" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O386" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M387" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O387" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M388" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O388" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M389" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O389" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M390" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O390" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M391" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O391" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M392" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O392" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M393" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O393" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M394" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O394" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M395" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O395" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M396" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O396" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M397" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O397" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M398" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O398" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M399" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O399" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M400" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O400" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M401" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O401" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M402" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O402" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M403" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O403" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M404" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O404" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M405" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O405" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M406" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O406" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M407" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O407" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M408" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O408" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M409" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O409" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M410" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O410" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M411" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O411" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M412" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O412" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M413" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O413" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M414" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O414" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M415" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O415" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M416" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O416" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M417" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O417" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M418" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O418" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M419" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O419" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M420" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O420" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M421" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O421" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M422" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O422" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M423" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O423" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M424" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O424" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M425" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O425" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M426" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O426" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M427" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O427" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M428" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O428" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M429" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O429" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M430" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O430" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M431" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O431" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M432" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O432" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M433" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O433" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M434" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O434" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M435" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O435" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M436" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O436" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M437" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O437" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M438" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O438" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M439" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O439" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M440" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O440" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M441" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O441" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M442" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O442" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M443" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O443" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M444" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O444" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M445" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O445" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M446" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O446" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M447" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O447" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M448" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O448" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M449" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O449" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M450" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O450" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M451" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O451" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M452" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O452" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M453" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O453" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M454" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O454" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M455" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O455" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M456" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O456" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M457" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O457" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M458" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O458" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M459" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O459" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M460" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O460" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M461" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O461" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M462" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O462" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M463" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O463" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M464" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O464" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M465" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O465" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M466" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O466" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M467" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O467" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M468" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O468" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M469" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O469" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M470" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O470" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M471" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O471" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M472" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O472" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M473" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O473" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M474" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O474" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M475" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O475" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M476" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O476" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M477" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O477" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M478" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O478" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M479" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O479" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M480" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O480" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M481" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O481" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M482" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O482" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M483" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O483" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M484" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O484" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M485" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O485" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M486" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O486" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M487" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O487" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M488" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O488" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M489" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O489" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M490" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O490" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M491" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O491" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M492" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O492" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M493" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O493" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M494" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O494" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M495" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O495" r:id="rId1023"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/tailored_resumes.xlsx
+++ b/output/tailored_resumes.xlsx
@@ -3261,7 +3261,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>scored</t>
+          <t>tailored</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -3269,7 +3269,11 @@
           <t>Apply ↗</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Selector_Software_Software_Engineer_10bcf5.pdf</t>
+        </is>
+      </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
           <t>levels.fyi ↗</t>
@@ -33635,937 +33639,938 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N80" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N82" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N87" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O98" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N100" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M108" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M109" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M110" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N111" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M113" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M114" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M115" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N115" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M116" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M117" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M118" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M119" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N120" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M123" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M124" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N124" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M125" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M126" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M127" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M128" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M129" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M137" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M138" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M139" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M140" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M143" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M144" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N144" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M145" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M147" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M148" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M149" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O149" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M150" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M151" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N151" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M152" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M153" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M154" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N154" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M155" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M156" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N156" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M157" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M158" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M159" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M160" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O160" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M161" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M162" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M163" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M164" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O164" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M165" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O165" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M166" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O166" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M167" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M168" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M169" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O169" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O170" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M173" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M174" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M175" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M176" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M177" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O177" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M178" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M184" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O184" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M185" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M186" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O186" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M187" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O187" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M189" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O189" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O190" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M191" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M192" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M193" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O193" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M194" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O194" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M195" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O199" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O200" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O201" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O202" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M205" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O205" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M206" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M207" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O207" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M208" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M209" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M210" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M211" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O211" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M212" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M213" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M214" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M215" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O215" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M216" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M217" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M218" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M219" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M220" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M221" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M222" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M223" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O223" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M224" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M225" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M226" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M227" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M228" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M229" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M230" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M231" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M232" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O232" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M233" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N233" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O233" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M234" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O234" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M235" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M236" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M237" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O237" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M238" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O238" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M239" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O239" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M240" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M241" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O241" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M242" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O242" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M243" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O243" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M244" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M245" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O245" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M246" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O246" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M247" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M248" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O248" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M249" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M250" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M251" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M252" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M253" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M254" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M255" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O255" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M256" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O256" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M257" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O257" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M258" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M259" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O259" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M260" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M261" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O261" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M262" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M263" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M264" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M265" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O265" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M266" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O266" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M267" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O267" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M268" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O268" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M269" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O269" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M270" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O270" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M271" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O271" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M272" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O272" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M273" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O273" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M274" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O274" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M275" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O275" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M276" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O276" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M277" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O277" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M278" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O278" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M279" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O279" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M280" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O280" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M281" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O281" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M282" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O282" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M283" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O283" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M284" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O284" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M285" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O285" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M286" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O286" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M287" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O287" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M288" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O288" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M289" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O289" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M290" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O290" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M291" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O291" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M292" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O292" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M293" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O293" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M294" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O294" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M295" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O295" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M296" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O296" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M297" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O297" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M298" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O298" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M299" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O299" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M300" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O300" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M301" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O301" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M302" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O302" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M303" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O303" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M304" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O304" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M305" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O305" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M306" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O306" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M307" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O307" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M308" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O308" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M309" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O309" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M310" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O310" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M311" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O311" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M312" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O312" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M313" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O313" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M314" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O314" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M315" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O315" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M316" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O316" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M317" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O317" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M318" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O318" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M319" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O319" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M320" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O320" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M321" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O321" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M322" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O322" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M323" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O323" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M324" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O324" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M325" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O325" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M326" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O326" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M327" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O327" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M328" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O328" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M329" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O329" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M330" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O330" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M331" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O331" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M332" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O332" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M333" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O333" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M334" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O334" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M335" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O335" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M336" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O336" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M337" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O337" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M338" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O338" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M339" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O339" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M340" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O340" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M341" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O341" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M342" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O342" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M343" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O343" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M344" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O344" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M345" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O345" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M346" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O346" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M347" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O347" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M348" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O348" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M349" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O349" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M350" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O350" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M351" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O351" r:id="rId735"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M352" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O352" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M353" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O353" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M354" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O354" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M355" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O355" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M356" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O356" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M357" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O357" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M358" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O358" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M359" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O359" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M360" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O360" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M361" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O361" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M362" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O362" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M363" r:id="rId758"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O363" r:id="rId759"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M364" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O364" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M365" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O365" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M366" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O366" r:id="rId765"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M367" r:id="rId766"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O367" r:id="rId767"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M368" r:id="rId768"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O368" r:id="rId769"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M369" r:id="rId770"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O369" r:id="rId771"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M370" r:id="rId772"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O370" r:id="rId773"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M371" r:id="rId774"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O371" r:id="rId775"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M372" r:id="rId776"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O372" r:id="rId777"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M373" r:id="rId778"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O373" r:id="rId779"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M374" r:id="rId780"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O374" r:id="rId781"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M375" r:id="rId782"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O375" r:id="rId783"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M376" r:id="rId784"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O376" r:id="rId785"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M377" r:id="rId786"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O377" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M378" r:id="rId788"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O378" r:id="rId789"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M379" r:id="rId790"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O379" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M380" r:id="rId792"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O380" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M381" r:id="rId794"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O381" r:id="rId795"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M382" r:id="rId796"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O382" r:id="rId797"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M383" r:id="rId798"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O383" r:id="rId799"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M384" r:id="rId800"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O384" r:id="rId801"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M385" r:id="rId802"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O385" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M386" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O386" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M387" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O387" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M388" r:id="rId808"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O388" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M389" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O389" r:id="rId811"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M390" r:id="rId812"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O390" r:id="rId813"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M391" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O391" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M392" r:id="rId816"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O392" r:id="rId817"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M393" r:id="rId818"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O393" r:id="rId819"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M394" r:id="rId820"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O394" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M395" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O395" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M396" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O396" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M397" r:id="rId826"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O397" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M398" r:id="rId828"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O398" r:id="rId829"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M399" r:id="rId830"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O399" r:id="rId831"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M400" r:id="rId832"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O400" r:id="rId833"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M401" r:id="rId834"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O401" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M402" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O402" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M403" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O403" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M404" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O404" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M405" r:id="rId842"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O405" r:id="rId843"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M406" r:id="rId844"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O406" r:id="rId845"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M407" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O407" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M408" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O408" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M409" r:id="rId850"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O409" r:id="rId851"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M410" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O410" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M411" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O411" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M412" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O412" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M413" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O413" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M414" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O414" r:id="rId861"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M415" r:id="rId862"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O415" r:id="rId863"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M416" r:id="rId864"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O416" r:id="rId865"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M417" r:id="rId866"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O417" r:id="rId867"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M418" r:id="rId868"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O418" r:id="rId869"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M419" r:id="rId870"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O419" r:id="rId871"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M420" r:id="rId872"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O420" r:id="rId873"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M421" r:id="rId874"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O421" r:id="rId875"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M422" r:id="rId876"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O422" r:id="rId877"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M423" r:id="rId878"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O423" r:id="rId879"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M424" r:id="rId880"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O424" r:id="rId881"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M425" r:id="rId882"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O425" r:id="rId883"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M426" r:id="rId884"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O426" r:id="rId885"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M427" r:id="rId886"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O427" r:id="rId887"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M428" r:id="rId888"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O428" r:id="rId889"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M429" r:id="rId890"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O429" r:id="rId891"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M430" r:id="rId892"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O430" r:id="rId893"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M431" r:id="rId894"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O431" r:id="rId895"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M432" r:id="rId896"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O432" r:id="rId897"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M433" r:id="rId898"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O433" r:id="rId899"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M434" r:id="rId900"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O434" r:id="rId901"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M435" r:id="rId902"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O435" r:id="rId903"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M436" r:id="rId904"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O436" r:id="rId905"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M437" r:id="rId906"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O437" r:id="rId907"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M438" r:id="rId908"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O438" r:id="rId909"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M439" r:id="rId910"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O439" r:id="rId911"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M440" r:id="rId912"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O440" r:id="rId913"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M441" r:id="rId914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O441" r:id="rId915"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M442" r:id="rId916"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O442" r:id="rId917"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M443" r:id="rId918"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O443" r:id="rId919"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M444" r:id="rId920"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O444" r:id="rId921"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M445" r:id="rId922"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O445" r:id="rId923"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M446" r:id="rId924"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O446" r:id="rId925"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M447" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O447" r:id="rId927"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M448" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O448" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M449" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O449" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M450" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O450" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M451" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O451" r:id="rId935"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M452" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O452" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M453" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O453" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M454" r:id="rId940"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O454" r:id="rId941"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M455" r:id="rId942"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O455" r:id="rId943"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M456" r:id="rId944"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O456" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M457" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O457" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M458" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O458" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M459" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O459" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M460" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O460" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M461" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O461" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M462" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O462" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M463" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O463" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M464" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O464" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M465" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O465" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M466" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O466" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M467" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O467" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M468" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O468" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M469" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O469" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M470" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O470" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M471" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O471" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M472" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O472" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M473" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O473" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M474" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O474" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M475" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O475" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M476" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O476" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M477" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O477" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M478" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O478" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M479" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O479" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M480" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O480" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M481" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O481" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M482" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O482" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M483" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O483" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M484" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O484" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M485" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O485" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M486" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O486" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M487" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O487" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M488" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O488" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M489" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O489" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M490" r:id="rId1012"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O490" r:id="rId1013"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M491" r:id="rId1014"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O491" r:id="rId1015"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M492" r:id="rId1016"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O492" r:id="rId1017"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M493" r:id="rId1018"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O493" r:id="rId1019"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M494" r:id="rId1020"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O494" r:id="rId1021"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M495" r:id="rId1022"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O495" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N80" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N82" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N87" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O98" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N100" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M108" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M109" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M110" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N111" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M113" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M114" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M115" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N115" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M116" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M117" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M118" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M119" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N120" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M123" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M124" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N124" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M125" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M126" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M127" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M128" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M129" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M137" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M138" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M139" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M140" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M143" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M144" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N144" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M145" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M147" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M148" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M149" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O149" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M150" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M151" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N151" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M152" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M153" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M154" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N154" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M155" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M156" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N156" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M157" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M158" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M159" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M160" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O160" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M161" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M162" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M163" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M164" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O164" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M165" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O165" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M166" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O166" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M167" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M168" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M169" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O169" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O170" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M173" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M174" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M175" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M176" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M177" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O177" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M178" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M184" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O184" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M185" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M186" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O186" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M187" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O187" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M188" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M189" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O189" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M190" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O190" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M191" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M192" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M193" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O193" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M194" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O194" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M195" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O199" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O200" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O201" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O202" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M205" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O205" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M206" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M207" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O207" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M208" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M209" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M210" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M211" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O211" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M212" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M213" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M214" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M215" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O215" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M216" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M217" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M218" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M219" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M220" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M221" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M222" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M223" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O223" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M224" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M225" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M226" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M227" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M228" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M229" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M230" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M231" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M232" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O232" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M233" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N233" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O233" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M234" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O234" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M235" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M236" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M237" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O237" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M238" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O238" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M239" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O239" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M240" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M241" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O241" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M242" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O242" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M243" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O243" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M244" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M245" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O245" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M246" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O246" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M247" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M248" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O248" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M249" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M250" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M251" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M252" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M253" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M254" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M255" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O255" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M256" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O256" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M257" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O257" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M258" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M259" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O259" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M260" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M261" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O261" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M262" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M263" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M264" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlfo